--- a/cd3_automation_toolkit/example/CD3-GCP-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-GCP-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802FF5F5-BB15-144B-A941-3E90E115C658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA691CF-24C4-3144-81D9-7018B5E49C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="30240" windowHeight="17440" tabRatio="1000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -126,35 +126,56 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Suruchi</author>
+    <author>suruchi</author>
   </authors>
   <commentList>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{316BBA31-E99D-8B4D-9151-F6A2026A5120}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{948BE757-713B-774B-95CF-59F458D82EC8}">
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>This is size for VM cluster and not just the node.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{F1F8A714-CF0E-AF4B-9B33-1BC1C4F21F95}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>This is size for VM cluster and not just the node.</t>
+          <t>The cluster name must begin with an alphabetic character and may contain hyphens(-) but can not contain underscores(_). It should be not more than 11 characters and is not case sensitive.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{542EDA5D-A989-6949-8F78-A937D507BC27}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>The hostname must be a unique resolvable hostname for the Oracle Exadata VM Cluster and will be used to connect externally to the system. The hostname must begin with an alphabetic character, can contain only alphanumeric characters and hyphens, and not exceed 12 characters in length</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
@@ -185,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="541">
   <si>
     <t>Region</t>
   </si>
@@ -1714,8 +1735,150 @@
     <t>Resource Group Name</t>
   </si>
   <si>
+    <t>Exadata Infra Display Name</t>
+  </si>
+  <si>
+    <t>Database Servers</t>
+  </si>
+  <si>
+    <t>Storage Servers</t>
+  </si>
+  <si>
+    <t>Database Server Type</t>
+  </si>
+  <si>
+    <t>Storage Server type</t>
+  </si>
+  <si>
+    <t>Maintenance Method</t>
+  </si>
+  <si>
+    <t>Preference</t>
+  </si>
+  <si>
+    <t>Weeks of Month</t>
+  </si>
+  <si>
+    <t>Hours of Day</t>
+  </si>
+  <si>
+    <t>Days of Week</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>Lead Time in Weeks</t>
+  </si>
+  <si>
+    <t>Exadata.X11M</t>
+  </si>
+  <si>
+    <t>X11M</t>
+  </si>
+  <si>
+    <t>X11M-HC</t>
+  </si>
+  <si>
+    <t>VM Cluster Display Name</t>
+  </si>
+  <si>
+    <t>CPU Core Count</t>
+  </si>
+  <si>
+    <t>GI Version</t>
+  </si>
+  <si>
+    <t>SSH Public Keys</t>
+  </si>
+  <si>
+    <t>Time Zone</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>GCP Oracle Zone</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Labels</t>
+  </si>
+  <si>
+    <t>'</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>NO_PREFERENCE</t>
+  </si>
+  <si>
+    <t>ROLLING</t>
+  </si>
+  <si>
+    <t>License Type</t>
+  </si>
+  <si>
+    <t>Hostname Prefix</t>
+  </si>
+  <si>
+    <t>Memory Size GB</t>
+  </si>
+  <si>
+    <t>DB Node Storage Size GB</t>
+  </si>
+  <si>
+    <t>Data Storage Size TB</t>
+  </si>
+  <si>
+    <t>Sparse Diskgroup Enabled</t>
+  </si>
+  <si>
+    <t>Local Backup Enabled</t>
+  </si>
+  <si>
+    <t>ODB Network Details</t>
+  </si>
+  <si>
+    <t>us-east4</t>
+  </si>
+  <si>
+    <t>us-east4-b-r1</t>
+  </si>
+  <si>
+    <t>23.0.0.0</t>
+  </si>
+  <si>
+    <t>Cluster Name</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Project : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Specify project ID</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 "Defined Tags" - </t>
     </r>
     <r>
@@ -1764,67 +1927,64 @@
     </r>
   </si>
   <si>
-    <t>Exadata Infra Display Name</t>
-  </si>
-  <si>
-    <t>Database Servers</t>
-  </si>
-  <si>
-    <t>Storage Servers</t>
-  </si>
-  <si>
-    <t>Database Server Type</t>
-  </si>
-  <si>
-    <t>Storage Server type</t>
-  </si>
-  <si>
-    <t>Maintenance Method</t>
-  </si>
-  <si>
-    <t>Preference</t>
-  </si>
-  <si>
-    <t>Weeks of Month</t>
-  </si>
-  <si>
-    <t>Hours of Day</t>
-  </si>
-  <si>
-    <t>Days of Week</t>
-  </si>
-  <si>
-    <t>Months</t>
-  </si>
-  <si>
-    <t>Lead Time in Weeks</t>
-  </si>
-  <si>
-    <t>test</t>
+    <t>ODB Network Subnets Details</t>
   </si>
   <si>
     <t>Exa-1</t>
   </si>
   <si>
-    <t>Exadata.X11M</t>
-  </si>
-  <si>
-    <t>X11M</t>
-  </si>
-  <si>
-    <t>X11M-HC</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>Monday, Saturday</t>
-  </si>
-  <si>
-    <t>March, June</t>
+    <t>abc@oracle.com</t>
+  </si>
+  <si>
+    <t>environment=prod</t>
+  </si>
+  <si>
+    <t>vm-cluster-1</t>
+  </si>
+  <si>
+    <t>cluster1</t>
+  </si>
+  <si>
+    <t>ssh-rsa AAAAB3NzaC1yc2EAAAADAQABAAABAQCcQ1JVp//N4A7tsB/eLkBc/tE0WKo3cXSJVemCI/2iUb6svkXuTvMPjj1d73QfV/U21OihobXJWyVzw+1vECTlGTneYnhanX4SIeEKa7W9sreB38gKp7PXkrL6QdKxrvq1iQe6D789mcmmLW9vFFDqr8Z1E9SD4guP1mGM6UZeSl9n+WdNpse9V AL_ADT_GCP_EXA</t>
+  </si>
+  <si>
+    <t>ß</t>
+  </si>
+  <si>
+    <t>vm-cluster-2</t>
+  </si>
+  <si>
+    <t>cluster2</t>
+  </si>
+  <si>
+    <t>CREATE::dbclient-1::10.110.252.0/24::dbbkp-1::10.110.253.0/24</t>
+  </si>
+  <si>
+    <t>CREATE::dbclient-2::10.110.254.0/24::dbbkp-2::10.110.255.0/24</t>
+  </si>
+  <si>
+    <t>hostname1</t>
+  </si>
+  <si>
+    <t>hostname2</t>
+  </si>
+  <si>
+    <t>CREATE::oradb_gcp_project_id::vpc-gcp::gcp_odbnetwork::us-east4-b-r1</t>
+  </si>
+  <si>
+    <t>oradb_gcp_project_id::vpc-gcp::gcp_odbnetwork</t>
+  </si>
+  <si>
+    <t>oradb_gcp_project_2</t>
+  </si>
+  <si>
+    <t>oradb_gcp_project_1</t>
   </si>
   <si>
     <t>Exa-2</t>
+  </si>
+  <si>
+    <t>oradb_gcp_project_2@Exa-2</t>
   </si>
   <si>
     <r>
@@ -1839,8 +1999,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Change CPU core as per shape selected.
-Software edition is ENTERPRISE_EDITION_EXTREME_PERFORMANCE by default.
 </t>
     </r>
     <r>
@@ -1852,7 +2010,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>"CPU core"</t>
+      <t>Project</t>
     </r>
     <r>
       <rPr>
@@ -1862,31 +2020,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> - if the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Shape</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is Exadata.Base.48 - Specify a multiple of 2, from 0 to 48 | Exadata.Quarter1.84 - Specify a multiple of 2, from 22 to 84  | Exadata.Half1.168 - Specify a multiple of 4, from 44 to 168
-                        | Exadata.Full1.336 - Specify a multiple of 8, from 88 to 336 | Exadata.Quarter2.92 - Specify a multiple of 2, from 0 to 92
-                        | Exadata.Half2.184 - Specify a multiple of 4, from 0 to 184 | Exadata.Full2.368 - Specify a multiple of 8, from 0 to 368 | Exadata.Half3.200 - Specify a multiple of 4, from 8 through 200
-                        | Exadata.Quater3.100 - Specify a multiple of 2, from 4 through 100 | Exadata.Full3.400 - Specify a multiple of 8, from 16 through 400</t>
+      <t xml:space="preserve"> : Specify project ID</t>
     </r>
     <r>
       <rPr>
@@ -1898,7 +2032,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Enter Network Details as : </t>
+Exadata Infra Display Name : </t>
     </r>
     <r>
       <rPr>
@@ -1908,7 +2042,51 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>&lt;Network-Compartment-Name&gt;@&lt;vcn-name&gt;::&lt;subnet-name&gt;</t>
+      <t>If Exa Infra is in different project than VM cluster then specify as &lt;exa_infra_project&gt;@&lt;exa_infra_display_name&gt;. See sample data in row 4.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ODB Network Details :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If you want to create new network, use CREATE::&lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;::&lt;GCP_ORACLE_ZONE&gt; else &lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;. See sample data.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ODB Network Subnets Details : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If you want to create new subnets, use CREATE::&lt;Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt;::&lt;Backup_Subnet_ID&gt;::&lt;Backup_Subnet_CIDR&gt; else Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt;::&lt;Backup_Subnet_ID&gt;::&lt;Backup_Subnet_CIDR&gt; See sample data.</t>
     </r>
     <r>
       <rPr>
@@ -1988,114 +2166,12 @@
       <t>Example: Asia/Calcutta | UTC | US/Pacific-New</t>
     </r>
   </si>
-  <si>
-    <t>VM Cluster Display Name</t>
-  </si>
-  <si>
-    <t>Backup Subnet CIDR</t>
-  </si>
-  <si>
-    <t>CPU Core Count</t>
-  </si>
-  <si>
-    <t>Hostname</t>
-  </si>
-  <si>
-    <t>GI Version</t>
-  </si>
-  <si>
-    <t>DB Node Storage Size in GBS</t>
-  </si>
-  <si>
-    <t>Memory Size in GBS</t>
-  </si>
-  <si>
-    <t>Data Storage Size in TBS</t>
-  </si>
-  <si>
-    <t>sparse_diskgroup_enabled</t>
-  </si>
-  <si>
-    <t>local_backup_enabled</t>
-  </si>
-  <si>
-    <t>SSH Public Keys</t>
-  </si>
-  <si>
-    <t>Time Zone</t>
-  </si>
-  <si>
-    <t>EXA-1</t>
-  </si>
-  <si>
-    <t>VMCluster-1</t>
-  </si>
-  <si>
-    <t>10.1.0.0/16</t>
-  </si>
-  <si>
-    <t>vmname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9.0.0 </t>
-  </si>
-  <si>
-    <t>hellooonsmdn</t>
-  </si>
-  <si>
-    <t>Asia/Calcutta</t>
-  </si>
-  <si>
-    <t>tag1=value1;tag2=value2</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>GCP Oracle Zone</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Labels</t>
-  </si>
-  <si>
-    <t>'</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>abc.com</t>
-  </si>
-  <si>
-    <t>us-central1-a-r1</t>
-  </si>
-  <si>
-    <t>us-central1</t>
-  </si>
-  <si>
-    <t>odb_gcp_project</t>
-  </si>
-  <si>
-    <t>NO_PREFERENCE</t>
-  </si>
-  <si>
-    <t>CUSTOM_PREFERENCE</t>
-  </si>
-  <si>
-    <t>NONROLLING</t>
-  </si>
-  <si>
-    <t>ROLLING</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2215,7 +2291,12 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <sz val="9.8000000000000007"/>
+      <color theme="1"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -2572,7 +2653,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -2602,10 +2682,13 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4561,27 +4644,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="79" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="61" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
     </row>
     <row r="2" spans="1:19" ht="80">
       <c r="A2" s="7" t="s">
@@ -4763,13 +4846,13 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:R924"/>
+  <dimension ref="A1:R923"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" customWidth="1"/>
     <col min="8" max="9" width="0" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="11.5" customWidth="1"/>
@@ -4778,2972 +4861,2966 @@
     <col min="13" max="13" width="11.5" customWidth="1"/>
     <col min="14" max="14" width="14.6640625" customWidth="1"/>
     <col min="15" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="15.6640625" customWidth="1"/>
+    <col min="17" max="17" width="19.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="119.25" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>479</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
     </row>
     <row r="2" spans="1:18" ht="48">
       <c r="A2" s="47" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="D2" s="48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="47" t="s">
+        <v>480</v>
+      </c>
+      <c r="G2" s="47" t="s">
         <v>481</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="H2" s="47" t="s">
         <v>482</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="I2" s="47" t="s">
         <v>483</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="J2" s="47" t="s">
         <v>484</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="K2" s="47" t="s">
         <v>485</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="L2" s="47" t="s">
         <v>486</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="M2" s="47" t="s">
         <v>487</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="N2" s="47" t="s">
         <v>488</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="O2" s="47" t="s">
         <v>489</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="P2" s="47" t="s">
         <v>490</v>
       </c>
-      <c r="P2" s="47" t="s">
+      <c r="Q2" s="47" t="s">
+        <v>504</v>
+      </c>
+      <c r="R2" s="49" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>491</v>
       </c>
-      <c r="Q2" s="47" t="s">
-        <v>527</v>
-      </c>
-      <c r="R2" s="49" t="s">
-        <v>525</v>
+      <c r="F3" s="24">
+        <v>2</v>
+      </c>
+      <c r="G3" s="24">
+        <v>3</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>506</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="R3" s="24" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="24" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>531</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>494</v>
-      </c>
-      <c r="F4" s="25">
+        <v>536</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>538</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="F4" s="24">
         <v>2</v>
       </c>
       <c r="G4" s="24">
         <v>3</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>532</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>497</v>
-      </c>
-      <c r="M4" s="24">
-        <v>4</v>
-      </c>
-      <c r="N4" s="24" t="s">
-        <v>498</v>
-      </c>
-      <c r="O4" s="24" t="s">
-        <v>499</v>
-      </c>
-      <c r="P4" s="24">
-        <v>1</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
       <c r="Q4" s="24" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="R4" s="24" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="24" t="s">
-        <v>530</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>529</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>531</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>500</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>494</v>
-      </c>
-      <c r="F5" s="25">
-        <v>2</v>
-      </c>
-      <c r="G5" s="24">
-        <v>3</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>495</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>496</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>533</v>
-      </c>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="25"/>
-    </row>
-    <row r="6" spans="1:18" ht="16">
-      <c r="A6" s="60" t="s">
+    <row r="5" spans="1:18" ht="16">
+      <c r="A5" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="59"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="58"/>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="E6" s="50"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="E7" s="51"/>
+      <c r="E7" s="50"/>
     </row>
     <row r="8" spans="1:18">
-      <c r="E8" s="51"/>
+      <c r="E8" s="50"/>
     </row>
     <row r="9" spans="1:18">
-      <c r="E9" s="51"/>
+      <c r="E9" s="50"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="E10" s="51"/>
+      <c r="E10" s="50"/>
+      <c r="P10" s="55" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="E11" s="51"/>
-      <c r="P11" s="56" t="s">
-        <v>526</v>
-      </c>
+      <c r="E11" s="50"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="E12" s="51"/>
+      <c r="E12" s="50"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="E13" s="51"/>
+      <c r="E13" s="50"/>
     </row>
     <row r="14" spans="1:18">
-      <c r="E14" s="51"/>
+      <c r="E14" s="50"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="E15" s="51"/>
+      <c r="E15" s="50"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="E16" s="51"/>
+      <c r="E16" s="50"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="51"/>
+      <c r="E17" s="50"/>
     </row>
     <row r="18" spans="5:5">
-      <c r="E18" s="51"/>
+      <c r="E18" s="50"/>
     </row>
     <row r="19" spans="5:5">
-      <c r="E19" s="51"/>
+      <c r="E19" s="50"/>
     </row>
     <row r="20" spans="5:5">
-      <c r="E20" s="51"/>
+      <c r="E20" s="50"/>
     </row>
     <row r="21" spans="5:5">
-      <c r="E21" s="51"/>
+      <c r="E21" s="50"/>
     </row>
     <row r="22" spans="5:5">
-      <c r="E22" s="51"/>
+      <c r="E22" s="50"/>
     </row>
     <row r="23" spans="5:5">
-      <c r="E23" s="51"/>
+      <c r="E23" s="50"/>
     </row>
     <row r="24" spans="5:5">
-      <c r="E24" s="51"/>
+      <c r="E24" s="50"/>
     </row>
     <row r="25" spans="5:5">
-      <c r="E25" s="51"/>
+      <c r="E25" s="50"/>
     </row>
     <row r="26" spans="5:5">
-      <c r="E26" s="51"/>
+      <c r="E26" s="50"/>
     </row>
     <row r="27" spans="5:5">
-      <c r="E27" s="51"/>
+      <c r="E27" s="50"/>
     </row>
     <row r="28" spans="5:5">
-      <c r="E28" s="51"/>
+      <c r="E28" s="50"/>
     </row>
     <row r="29" spans="5:5">
-      <c r="E29" s="51"/>
+      <c r="E29" s="50"/>
     </row>
     <row r="30" spans="5:5">
-      <c r="E30" s="51"/>
+      <c r="E30" s="50"/>
     </row>
     <row r="31" spans="5:5">
-      <c r="E31" s="51"/>
+      <c r="E31" s="50"/>
     </row>
     <row r="32" spans="5:5">
-      <c r="E32" s="51"/>
+      <c r="E32" s="50"/>
     </row>
     <row r="33" spans="5:5">
-      <c r="E33" s="51"/>
+      <c r="E33" s="50"/>
     </row>
     <row r="34" spans="5:5">
-      <c r="E34" s="51"/>
+      <c r="E34" s="50"/>
     </row>
     <row r="35" spans="5:5">
-      <c r="E35" s="51"/>
+      <c r="E35" s="50"/>
     </row>
     <row r="36" spans="5:5">
-      <c r="E36" s="51"/>
+      <c r="E36" s="50"/>
     </row>
     <row r="37" spans="5:5">
-      <c r="E37" s="51"/>
+      <c r="E37" s="50"/>
     </row>
     <row r="38" spans="5:5">
-      <c r="E38" s="51"/>
+      <c r="E38" s="50"/>
     </row>
     <row r="39" spans="5:5">
-      <c r="E39" s="51"/>
+      <c r="E39" s="50"/>
     </row>
     <row r="40" spans="5:5">
-      <c r="E40" s="51"/>
+      <c r="E40" s="50"/>
     </row>
     <row r="41" spans="5:5">
-      <c r="E41" s="51"/>
+      <c r="E41" s="50"/>
     </row>
     <row r="42" spans="5:5">
-      <c r="E42" s="51"/>
+      <c r="E42" s="50"/>
     </row>
     <row r="43" spans="5:5">
-      <c r="E43" s="51"/>
+      <c r="E43" s="50"/>
     </row>
     <row r="44" spans="5:5">
-      <c r="E44" s="51"/>
+      <c r="E44" s="50"/>
     </row>
     <row r="45" spans="5:5">
-      <c r="E45" s="51"/>
+      <c r="E45" s="50"/>
     </row>
     <row r="46" spans="5:5">
-      <c r="E46" s="51"/>
+      <c r="E46" s="50"/>
     </row>
     <row r="47" spans="5:5">
-      <c r="E47" s="51"/>
+      <c r="E47" s="50"/>
     </row>
     <row r="48" spans="5:5">
-      <c r="E48" s="51"/>
+      <c r="E48" s="50"/>
     </row>
     <row r="49" spans="5:5">
-      <c r="E49" s="51"/>
+      <c r="E49" s="50"/>
     </row>
     <row r="50" spans="5:5">
-      <c r="E50" s="51"/>
+      <c r="E50" s="50"/>
     </row>
     <row r="51" spans="5:5">
-      <c r="E51" s="51"/>
+      <c r="E51" s="50"/>
     </row>
     <row r="52" spans="5:5">
-      <c r="E52" s="51"/>
+      <c r="E52" s="50"/>
     </row>
     <row r="53" spans="5:5">
-      <c r="E53" s="51"/>
+      <c r="E53" s="50"/>
     </row>
     <row r="54" spans="5:5">
-      <c r="E54" s="51"/>
+      <c r="E54" s="50"/>
     </row>
     <row r="55" spans="5:5">
-      <c r="E55" s="51"/>
+      <c r="E55" s="50"/>
     </row>
     <row r="56" spans="5:5">
-      <c r="E56" s="51"/>
+      <c r="E56" s="50"/>
     </row>
     <row r="57" spans="5:5">
-      <c r="E57" s="51"/>
+      <c r="E57" s="50"/>
     </row>
     <row r="58" spans="5:5">
-      <c r="E58" s="51"/>
+      <c r="E58" s="50"/>
     </row>
     <row r="59" spans="5:5">
-      <c r="E59" s="51"/>
+      <c r="E59" s="50"/>
     </row>
     <row r="60" spans="5:5">
-      <c r="E60" s="51"/>
+      <c r="E60" s="50"/>
     </row>
     <row r="61" spans="5:5">
-      <c r="E61" s="51"/>
+      <c r="E61" s="50"/>
     </row>
     <row r="62" spans="5:5">
-      <c r="E62" s="51"/>
+      <c r="E62" s="50"/>
     </row>
     <row r="63" spans="5:5">
-      <c r="E63" s="51"/>
+      <c r="E63" s="50"/>
     </row>
     <row r="64" spans="5:5">
-      <c r="E64" s="51"/>
+      <c r="E64" s="50"/>
     </row>
     <row r="65" spans="5:5">
-      <c r="E65" s="51"/>
+      <c r="E65" s="50"/>
     </row>
     <row r="66" spans="5:5">
-      <c r="E66" s="51"/>
+      <c r="E66" s="50"/>
     </row>
     <row r="67" spans="5:5">
-      <c r="E67" s="51"/>
+      <c r="E67" s="50"/>
     </row>
     <row r="68" spans="5:5">
-      <c r="E68" s="51"/>
+      <c r="E68" s="50"/>
     </row>
     <row r="69" spans="5:5">
-      <c r="E69" s="51"/>
+      <c r="E69" s="50"/>
     </row>
     <row r="70" spans="5:5">
-      <c r="E70" s="51"/>
+      <c r="E70" s="50"/>
     </row>
     <row r="71" spans="5:5">
-      <c r="E71" s="51"/>
+      <c r="E71" s="50"/>
     </row>
     <row r="72" spans="5:5">
-      <c r="E72" s="51"/>
+      <c r="E72" s="50"/>
     </row>
     <row r="73" spans="5:5">
-      <c r="E73" s="51"/>
+      <c r="E73" s="50"/>
     </row>
     <row r="74" spans="5:5">
-      <c r="E74" s="51"/>
+      <c r="E74" s="50"/>
     </row>
     <row r="75" spans="5:5">
-      <c r="E75" s="51"/>
+      <c r="E75" s="50"/>
     </row>
     <row r="76" spans="5:5">
-      <c r="E76" s="51"/>
+      <c r="E76" s="50"/>
     </row>
     <row r="77" spans="5:5">
-      <c r="E77" s="51"/>
+      <c r="E77" s="50"/>
     </row>
     <row r="78" spans="5:5">
-      <c r="E78" s="51"/>
+      <c r="E78" s="50"/>
     </row>
     <row r="79" spans="5:5">
-      <c r="E79" s="51"/>
+      <c r="E79" s="50"/>
     </row>
     <row r="80" spans="5:5">
-      <c r="E80" s="51"/>
+      <c r="E80" s="50"/>
     </row>
     <row r="81" spans="5:5">
-      <c r="E81" s="51"/>
+      <c r="E81" s="50"/>
     </row>
     <row r="82" spans="5:5">
-      <c r="E82" s="51"/>
+      <c r="E82" s="50"/>
     </row>
     <row r="83" spans="5:5">
-      <c r="E83" s="51"/>
+      <c r="E83" s="50"/>
     </row>
     <row r="84" spans="5:5">
-      <c r="E84" s="51"/>
+      <c r="E84" s="50"/>
     </row>
     <row r="85" spans="5:5">
-      <c r="E85" s="51"/>
+      <c r="E85" s="50"/>
     </row>
     <row r="86" spans="5:5">
-      <c r="E86" s="51"/>
+      <c r="E86" s="50"/>
     </row>
     <row r="87" spans="5:5">
-      <c r="E87" s="51"/>
+      <c r="E87" s="50"/>
     </row>
     <row r="88" spans="5:5">
-      <c r="E88" s="51"/>
+      <c r="E88" s="50"/>
     </row>
     <row r="89" spans="5:5">
-      <c r="E89" s="51"/>
+      <c r="E89" s="50"/>
     </row>
     <row r="90" spans="5:5">
-      <c r="E90" s="51"/>
+      <c r="E90" s="50"/>
     </row>
     <row r="91" spans="5:5">
-      <c r="E91" s="51"/>
+      <c r="E91" s="50"/>
     </row>
     <row r="92" spans="5:5">
-      <c r="E92" s="51"/>
+      <c r="E92" s="50"/>
     </row>
     <row r="93" spans="5:5">
-      <c r="E93" s="51"/>
+      <c r="E93" s="50"/>
     </row>
     <row r="94" spans="5:5">
-      <c r="E94" s="51"/>
+      <c r="E94" s="50"/>
     </row>
     <row r="95" spans="5:5">
-      <c r="E95" s="51"/>
+      <c r="E95" s="50"/>
     </row>
     <row r="96" spans="5:5">
-      <c r="E96" s="51"/>
+      <c r="E96" s="50"/>
     </row>
     <row r="97" spans="5:5">
-      <c r="E97" s="51"/>
+      <c r="E97" s="50"/>
     </row>
     <row r="98" spans="5:5">
-      <c r="E98" s="51"/>
+      <c r="E98" s="50"/>
     </row>
     <row r="99" spans="5:5">
-      <c r="E99" s="51"/>
+      <c r="E99" s="50"/>
     </row>
     <row r="100" spans="5:5">
-      <c r="E100" s="51"/>
+      <c r="E100" s="50"/>
     </row>
     <row r="101" spans="5:5">
-      <c r="E101" s="51"/>
+      <c r="E101" s="50"/>
     </row>
     <row r="102" spans="5:5">
-      <c r="E102" s="51"/>
+      <c r="E102" s="50"/>
     </row>
     <row r="103" spans="5:5">
-      <c r="E103" s="51"/>
+      <c r="E103" s="50"/>
     </row>
     <row r="104" spans="5:5">
-      <c r="E104" s="51"/>
+      <c r="E104" s="50"/>
     </row>
     <row r="105" spans="5:5">
-      <c r="E105" s="51"/>
+      <c r="E105" s="50"/>
     </row>
     <row r="106" spans="5:5">
-      <c r="E106" s="51"/>
+      <c r="E106" s="50"/>
     </row>
     <row r="107" spans="5:5">
-      <c r="E107" s="51"/>
+      <c r="E107" s="50"/>
     </row>
     <row r="108" spans="5:5">
-      <c r="E108" s="51"/>
+      <c r="E108" s="50"/>
     </row>
     <row r="109" spans="5:5">
-      <c r="E109" s="51"/>
+      <c r="E109" s="50"/>
     </row>
     <row r="110" spans="5:5">
-      <c r="E110" s="51"/>
+      <c r="E110" s="50"/>
     </row>
     <row r="111" spans="5:5">
-      <c r="E111" s="51"/>
+      <c r="E111" s="50"/>
     </row>
     <row r="112" spans="5:5">
-      <c r="E112" s="51"/>
+      <c r="E112" s="50"/>
     </row>
     <row r="113" spans="5:5">
-      <c r="E113" s="51"/>
+      <c r="E113" s="50"/>
     </row>
     <row r="114" spans="5:5">
-      <c r="E114" s="51"/>
+      <c r="E114" s="50"/>
     </row>
     <row r="115" spans="5:5">
-      <c r="E115" s="51"/>
+      <c r="E115" s="50"/>
     </row>
     <row r="116" spans="5:5">
-      <c r="E116" s="51"/>
+      <c r="E116" s="50"/>
     </row>
     <row r="117" spans="5:5">
-      <c r="E117" s="51"/>
+      <c r="E117" s="50"/>
     </row>
     <row r="118" spans="5:5">
-      <c r="E118" s="51"/>
+      <c r="E118" s="50"/>
     </row>
     <row r="119" spans="5:5">
-      <c r="E119" s="51"/>
+      <c r="E119" s="50"/>
     </row>
     <row r="120" spans="5:5">
-      <c r="E120" s="51"/>
+      <c r="E120" s="50"/>
     </row>
     <row r="121" spans="5:5">
-      <c r="E121" s="51"/>
+      <c r="E121" s="50"/>
     </row>
     <row r="122" spans="5:5">
-      <c r="E122" s="51"/>
+      <c r="E122" s="50"/>
     </row>
     <row r="123" spans="5:5">
-      <c r="E123" s="51"/>
+      <c r="E123" s="50"/>
     </row>
     <row r="124" spans="5:5">
-      <c r="E124" s="51"/>
+      <c r="E124" s="50"/>
     </row>
     <row r="125" spans="5:5">
-      <c r="E125" s="51"/>
+      <c r="E125" s="50"/>
     </row>
     <row r="126" spans="5:5">
-      <c r="E126" s="51"/>
+      <c r="E126" s="50"/>
     </row>
     <row r="127" spans="5:5">
-      <c r="E127" s="51"/>
+      <c r="E127" s="50"/>
     </row>
     <row r="128" spans="5:5">
-      <c r="E128" s="51"/>
+      <c r="E128" s="50"/>
     </row>
     <row r="129" spans="5:5">
-      <c r="E129" s="51"/>
+      <c r="E129" s="50"/>
     </row>
     <row r="130" spans="5:5">
-      <c r="E130" s="51"/>
+      <c r="E130" s="50"/>
     </row>
     <row r="131" spans="5:5">
-      <c r="E131" s="51"/>
+      <c r="E131" s="50"/>
     </row>
     <row r="132" spans="5:5">
-      <c r="E132" s="51"/>
+      <c r="E132" s="50"/>
     </row>
     <row r="133" spans="5:5">
-      <c r="E133" s="51"/>
+      <c r="E133" s="50"/>
     </row>
     <row r="134" spans="5:5">
-      <c r="E134" s="51"/>
+      <c r="E134" s="50"/>
     </row>
     <row r="135" spans="5:5">
-      <c r="E135" s="51"/>
+      <c r="E135" s="50"/>
     </row>
     <row r="136" spans="5:5">
-      <c r="E136" s="51"/>
+      <c r="E136" s="50"/>
     </row>
     <row r="137" spans="5:5">
-      <c r="E137" s="51"/>
+      <c r="E137" s="50"/>
     </row>
     <row r="138" spans="5:5">
-      <c r="E138" s="51"/>
+      <c r="E138" s="50"/>
     </row>
     <row r="139" spans="5:5">
-      <c r="E139" s="51"/>
+      <c r="E139" s="50"/>
     </row>
     <row r="140" spans="5:5">
-      <c r="E140" s="51"/>
+      <c r="E140" s="50"/>
     </row>
     <row r="141" spans="5:5">
-      <c r="E141" s="51"/>
+      <c r="E141" s="50"/>
     </row>
     <row r="142" spans="5:5">
-      <c r="E142" s="51"/>
+      <c r="E142" s="50"/>
     </row>
     <row r="143" spans="5:5">
-      <c r="E143" s="51"/>
+      <c r="E143" s="50"/>
     </row>
     <row r="144" spans="5:5">
-      <c r="E144" s="51"/>
+      <c r="E144" s="50"/>
     </row>
     <row r="145" spans="5:5">
-      <c r="E145" s="51"/>
+      <c r="E145" s="50"/>
     </row>
     <row r="146" spans="5:5">
-      <c r="E146" s="51"/>
+      <c r="E146" s="50"/>
     </row>
     <row r="147" spans="5:5">
-      <c r="E147" s="51"/>
+      <c r="E147" s="50"/>
     </row>
     <row r="148" spans="5:5">
-      <c r="E148" s="51"/>
+      <c r="E148" s="50"/>
     </row>
     <row r="149" spans="5:5">
-      <c r="E149" s="51"/>
+      <c r="E149" s="50"/>
     </row>
     <row r="150" spans="5:5">
-      <c r="E150" s="51"/>
+      <c r="E150" s="50"/>
     </row>
     <row r="151" spans="5:5">
-      <c r="E151" s="51"/>
+      <c r="E151" s="50"/>
     </row>
     <row r="152" spans="5:5">
-      <c r="E152" s="51"/>
+      <c r="E152" s="50"/>
     </row>
     <row r="153" spans="5:5">
-      <c r="E153" s="51"/>
+      <c r="E153" s="50"/>
     </row>
     <row r="154" spans="5:5">
-      <c r="E154" s="51"/>
+      <c r="E154" s="50"/>
     </row>
     <row r="155" spans="5:5">
-      <c r="E155" s="51"/>
+      <c r="E155" s="50"/>
     </row>
     <row r="156" spans="5:5">
-      <c r="E156" s="51"/>
+      <c r="E156" s="50"/>
     </row>
     <row r="157" spans="5:5">
-      <c r="E157" s="51"/>
+      <c r="E157" s="50"/>
     </row>
     <row r="158" spans="5:5">
-      <c r="E158" s="51"/>
+      <c r="E158" s="50"/>
     </row>
     <row r="159" spans="5:5">
-      <c r="E159" s="51"/>
+      <c r="E159" s="50"/>
     </row>
     <row r="160" spans="5:5">
-      <c r="E160" s="51"/>
+      <c r="E160" s="50"/>
     </row>
     <row r="161" spans="5:5">
-      <c r="E161" s="51"/>
+      <c r="E161" s="50"/>
     </row>
     <row r="162" spans="5:5">
-      <c r="E162" s="51"/>
+      <c r="E162" s="50"/>
     </row>
     <row r="163" spans="5:5">
-      <c r="E163" s="51"/>
+      <c r="E163" s="50"/>
     </row>
     <row r="164" spans="5:5">
-      <c r="E164" s="51"/>
+      <c r="E164" s="50"/>
     </row>
     <row r="165" spans="5:5">
-      <c r="E165" s="51"/>
+      <c r="E165" s="50"/>
     </row>
     <row r="166" spans="5:5">
-      <c r="E166" s="51"/>
+      <c r="E166" s="50"/>
     </row>
     <row r="167" spans="5:5">
-      <c r="E167" s="51"/>
+      <c r="E167" s="50"/>
     </row>
     <row r="168" spans="5:5">
-      <c r="E168" s="51"/>
+      <c r="E168" s="50"/>
     </row>
     <row r="169" spans="5:5">
-      <c r="E169" s="51"/>
+      <c r="E169" s="50"/>
     </row>
     <row r="170" spans="5:5">
-      <c r="E170" s="51"/>
+      <c r="E170" s="50"/>
     </row>
     <row r="171" spans="5:5">
-      <c r="E171" s="51"/>
+      <c r="E171" s="50"/>
     </row>
     <row r="172" spans="5:5">
-      <c r="E172" s="51"/>
+      <c r="E172" s="50"/>
     </row>
     <row r="173" spans="5:5">
-      <c r="E173" s="51"/>
+      <c r="E173" s="50"/>
     </row>
     <row r="174" spans="5:5">
-      <c r="E174" s="51"/>
+      <c r="E174" s="50"/>
     </row>
     <row r="175" spans="5:5">
-      <c r="E175" s="51"/>
+      <c r="E175" s="50"/>
     </row>
     <row r="176" spans="5:5">
-      <c r="E176" s="51"/>
+      <c r="E176" s="50"/>
     </row>
     <row r="177" spans="5:5">
-      <c r="E177" s="51"/>
+      <c r="E177" s="50"/>
     </row>
     <row r="178" spans="5:5">
-      <c r="E178" s="51"/>
+      <c r="E178" s="50"/>
     </row>
     <row r="179" spans="5:5">
-      <c r="E179" s="51"/>
+      <c r="E179" s="50"/>
     </row>
     <row r="180" spans="5:5">
-      <c r="E180" s="51"/>
+      <c r="E180" s="50"/>
     </row>
     <row r="181" spans="5:5">
-      <c r="E181" s="51"/>
+      <c r="E181" s="50"/>
     </row>
     <row r="182" spans="5:5">
-      <c r="E182" s="51"/>
+      <c r="E182" s="50"/>
     </row>
     <row r="183" spans="5:5">
-      <c r="E183" s="51"/>
+      <c r="E183" s="50"/>
     </row>
     <row r="184" spans="5:5">
-      <c r="E184" s="51"/>
+      <c r="E184" s="50"/>
     </row>
     <row r="185" spans="5:5">
-      <c r="E185" s="51"/>
+      <c r="E185" s="50"/>
     </row>
     <row r="186" spans="5:5">
-      <c r="E186" s="51"/>
+      <c r="E186" s="50"/>
     </row>
     <row r="187" spans="5:5">
-      <c r="E187" s="51"/>
+      <c r="E187" s="50"/>
     </row>
     <row r="188" spans="5:5">
-      <c r="E188" s="51"/>
+      <c r="E188" s="50"/>
     </row>
     <row r="189" spans="5:5">
-      <c r="E189" s="51"/>
+      <c r="E189" s="50"/>
     </row>
     <row r="190" spans="5:5">
-      <c r="E190" s="51"/>
+      <c r="E190" s="50"/>
     </row>
     <row r="191" spans="5:5">
-      <c r="E191" s="51"/>
+      <c r="E191" s="50"/>
     </row>
     <row r="192" spans="5:5">
-      <c r="E192" s="51"/>
+      <c r="E192" s="50"/>
     </row>
     <row r="193" spans="5:5">
-      <c r="E193" s="51"/>
+      <c r="E193" s="50"/>
     </row>
     <row r="194" spans="5:5">
-      <c r="E194" s="51"/>
+      <c r="E194" s="50"/>
     </row>
     <row r="195" spans="5:5">
-      <c r="E195" s="51"/>
+      <c r="E195" s="50"/>
     </row>
     <row r="196" spans="5:5">
-      <c r="E196" s="51"/>
+      <c r="E196" s="50"/>
     </row>
     <row r="197" spans="5:5">
-      <c r="E197" s="51"/>
+      <c r="E197" s="50"/>
     </row>
     <row r="198" spans="5:5">
-      <c r="E198" s="51"/>
+      <c r="E198" s="50"/>
     </row>
     <row r="199" spans="5:5">
-      <c r="E199" s="51"/>
+      <c r="E199" s="50"/>
     </row>
     <row r="200" spans="5:5">
-      <c r="E200" s="51"/>
+      <c r="E200" s="50"/>
     </row>
     <row r="201" spans="5:5">
-      <c r="E201" s="51"/>
+      <c r="E201" s="50"/>
     </row>
     <row r="202" spans="5:5">
-      <c r="E202" s="51"/>
+      <c r="E202" s="50"/>
     </row>
     <row r="203" spans="5:5">
-      <c r="E203" s="51"/>
+      <c r="E203" s="50"/>
     </row>
     <row r="204" spans="5:5">
-      <c r="E204" s="51"/>
+      <c r="E204" s="50"/>
     </row>
     <row r="205" spans="5:5">
-      <c r="E205" s="51"/>
+      <c r="E205" s="50"/>
     </row>
     <row r="206" spans="5:5">
-      <c r="E206" s="51"/>
+      <c r="E206" s="50"/>
     </row>
     <row r="207" spans="5:5">
-      <c r="E207" s="51"/>
+      <c r="E207" s="50"/>
     </row>
     <row r="208" spans="5:5">
-      <c r="E208" s="51"/>
+      <c r="E208" s="50"/>
     </row>
     <row r="209" spans="5:5">
-      <c r="E209" s="51"/>
+      <c r="E209" s="50"/>
     </row>
     <row r="210" spans="5:5">
-      <c r="E210" s="51"/>
+      <c r="E210" s="50"/>
     </row>
     <row r="211" spans="5:5">
-      <c r="E211" s="51"/>
+      <c r="E211" s="50"/>
     </row>
     <row r="212" spans="5:5">
-      <c r="E212" s="51"/>
+      <c r="E212" s="50"/>
     </row>
     <row r="213" spans="5:5">
-      <c r="E213" s="51"/>
+      <c r="E213" s="50"/>
     </row>
     <row r="214" spans="5:5">
-      <c r="E214" s="51"/>
+      <c r="E214" s="50"/>
     </row>
     <row r="215" spans="5:5">
-      <c r="E215" s="51"/>
+      <c r="E215" s="50"/>
     </row>
     <row r="216" spans="5:5">
-      <c r="E216" s="51"/>
+      <c r="E216" s="50"/>
     </row>
     <row r="217" spans="5:5">
-      <c r="E217" s="51"/>
+      <c r="E217" s="50"/>
     </row>
     <row r="218" spans="5:5">
-      <c r="E218" s="51"/>
+      <c r="E218" s="50"/>
     </row>
     <row r="219" spans="5:5">
-      <c r="E219" s="51"/>
+      <c r="E219" s="50"/>
     </row>
     <row r="220" spans="5:5">
-      <c r="E220" s="51"/>
+      <c r="E220" s="50"/>
     </row>
     <row r="221" spans="5:5">
-      <c r="E221" s="51"/>
+      <c r="E221" s="50"/>
     </row>
     <row r="222" spans="5:5">
-      <c r="E222" s="51"/>
+      <c r="E222" s="50"/>
     </row>
     <row r="223" spans="5:5">
-      <c r="E223" s="51"/>
+      <c r="E223" s="50"/>
     </row>
     <row r="224" spans="5:5">
-      <c r="E224" s="51"/>
+      <c r="E224" s="50"/>
     </row>
     <row r="225" spans="5:5">
-      <c r="E225" s="51"/>
+      <c r="E225" s="50"/>
     </row>
     <row r="226" spans="5:5">
-      <c r="E226" s="51"/>
+      <c r="E226" s="50"/>
     </row>
     <row r="227" spans="5:5">
-      <c r="E227" s="51"/>
+      <c r="E227" s="50"/>
     </row>
     <row r="228" spans="5:5">
-      <c r="E228" s="51"/>
+      <c r="E228" s="50"/>
     </row>
     <row r="229" spans="5:5">
-      <c r="E229" s="51"/>
+      <c r="E229" s="50"/>
     </row>
     <row r="230" spans="5:5">
-      <c r="E230" s="51"/>
+      <c r="E230" s="50"/>
     </row>
     <row r="231" spans="5:5">
-      <c r="E231" s="51"/>
+      <c r="E231" s="50"/>
     </row>
     <row r="232" spans="5:5">
-      <c r="E232" s="51"/>
+      <c r="E232" s="50"/>
     </row>
     <row r="233" spans="5:5">
-      <c r="E233" s="51"/>
+      <c r="E233" s="50"/>
     </row>
     <row r="234" spans="5:5">
-      <c r="E234" s="51"/>
+      <c r="E234" s="50"/>
     </row>
     <row r="235" spans="5:5">
-      <c r="E235" s="51"/>
+      <c r="E235" s="50"/>
     </row>
     <row r="236" spans="5:5">
-      <c r="E236" s="51"/>
+      <c r="E236" s="50"/>
     </row>
     <row r="237" spans="5:5">
-      <c r="E237" s="51"/>
+      <c r="E237" s="50"/>
     </row>
     <row r="238" spans="5:5">
-      <c r="E238" s="51"/>
+      <c r="E238" s="50"/>
     </row>
     <row r="239" spans="5:5">
-      <c r="E239" s="51"/>
+      <c r="E239" s="50"/>
     </row>
     <row r="240" spans="5:5">
-      <c r="E240" s="51"/>
+      <c r="E240" s="50"/>
     </row>
     <row r="241" spans="5:5">
-      <c r="E241" s="51"/>
+      <c r="E241" s="50"/>
     </row>
     <row r="242" spans="5:5">
-      <c r="E242" s="51"/>
+      <c r="E242" s="50"/>
     </row>
     <row r="243" spans="5:5">
-      <c r="E243" s="51"/>
+      <c r="E243" s="50"/>
     </row>
     <row r="244" spans="5:5">
-      <c r="E244" s="51"/>
+      <c r="E244" s="50"/>
     </row>
     <row r="245" spans="5:5">
-      <c r="E245" s="51"/>
+      <c r="E245" s="50"/>
     </row>
     <row r="246" spans="5:5">
-      <c r="E246" s="51"/>
+      <c r="E246" s="50"/>
     </row>
     <row r="247" spans="5:5">
-      <c r="E247" s="51"/>
+      <c r="E247" s="50"/>
     </row>
     <row r="248" spans="5:5">
-      <c r="E248" s="51"/>
+      <c r="E248" s="50"/>
     </row>
     <row r="249" spans="5:5">
-      <c r="E249" s="51"/>
+      <c r="E249" s="50"/>
     </row>
     <row r="250" spans="5:5">
-      <c r="E250" s="51"/>
+      <c r="E250" s="50"/>
     </row>
     <row r="251" spans="5:5">
-      <c r="E251" s="51"/>
+      <c r="E251" s="50"/>
     </row>
     <row r="252" spans="5:5">
-      <c r="E252" s="51"/>
+      <c r="E252" s="50"/>
     </row>
     <row r="253" spans="5:5">
-      <c r="E253" s="51"/>
+      <c r="E253" s="50"/>
     </row>
     <row r="254" spans="5:5">
-      <c r="E254" s="51"/>
+      <c r="E254" s="50"/>
     </row>
     <row r="255" spans="5:5">
-      <c r="E255" s="51"/>
+      <c r="E255" s="50"/>
     </row>
     <row r="256" spans="5:5">
-      <c r="E256" s="51"/>
+      <c r="E256" s="50"/>
     </row>
     <row r="257" spans="5:5">
-      <c r="E257" s="51"/>
+      <c r="E257" s="50"/>
     </row>
     <row r="258" spans="5:5">
-      <c r="E258" s="51"/>
+      <c r="E258" s="50"/>
     </row>
     <row r="259" spans="5:5">
-      <c r="E259" s="51"/>
+      <c r="E259" s="50"/>
     </row>
     <row r="260" spans="5:5">
-      <c r="E260" s="51"/>
+      <c r="E260" s="50"/>
     </row>
     <row r="261" spans="5:5">
-      <c r="E261" s="51"/>
+      <c r="E261" s="50"/>
     </row>
     <row r="262" spans="5:5">
-      <c r="E262" s="51"/>
+      <c r="E262" s="50"/>
     </row>
     <row r="263" spans="5:5">
-      <c r="E263" s="51"/>
+      <c r="E263" s="50"/>
     </row>
     <row r="264" spans="5:5">
-      <c r="E264" s="51"/>
+      <c r="E264" s="50"/>
     </row>
     <row r="265" spans="5:5">
-      <c r="E265" s="51"/>
+      <c r="E265" s="50"/>
     </row>
     <row r="266" spans="5:5">
-      <c r="E266" s="51"/>
+      <c r="E266" s="50"/>
     </row>
     <row r="267" spans="5:5">
-      <c r="E267" s="51"/>
+      <c r="E267" s="50"/>
     </row>
     <row r="268" spans="5:5">
-      <c r="E268" s="51"/>
+      <c r="E268" s="50"/>
     </row>
     <row r="269" spans="5:5">
-      <c r="E269" s="51"/>
+      <c r="E269" s="50"/>
     </row>
     <row r="270" spans="5:5">
-      <c r="E270" s="51"/>
+      <c r="E270" s="50"/>
     </row>
     <row r="271" spans="5:5">
-      <c r="E271" s="51"/>
+      <c r="E271" s="50"/>
     </row>
     <row r="272" spans="5:5">
-      <c r="E272" s="51"/>
+      <c r="E272" s="50"/>
     </row>
     <row r="273" spans="5:5">
-      <c r="E273" s="51"/>
+      <c r="E273" s="50"/>
     </row>
     <row r="274" spans="5:5">
-      <c r="E274" s="51"/>
+      <c r="E274" s="50"/>
     </row>
     <row r="275" spans="5:5">
-      <c r="E275" s="51"/>
+      <c r="E275" s="50"/>
     </row>
     <row r="276" spans="5:5">
-      <c r="E276" s="51"/>
+      <c r="E276" s="50"/>
     </row>
     <row r="277" spans="5:5">
-      <c r="E277" s="51"/>
+      <c r="E277" s="50"/>
     </row>
     <row r="278" spans="5:5">
-      <c r="E278" s="51"/>
+      <c r="E278" s="50"/>
     </row>
     <row r="279" spans="5:5">
-      <c r="E279" s="51"/>
+      <c r="E279" s="50"/>
     </row>
     <row r="280" spans="5:5">
-      <c r="E280" s="51"/>
+      <c r="E280" s="50"/>
     </row>
     <row r="281" spans="5:5">
-      <c r="E281" s="51"/>
+      <c r="E281" s="50"/>
     </row>
     <row r="282" spans="5:5">
-      <c r="E282" s="51"/>
+      <c r="E282" s="50"/>
     </row>
     <row r="283" spans="5:5">
-      <c r="E283" s="51"/>
+      <c r="E283" s="50"/>
     </row>
     <row r="284" spans="5:5">
-      <c r="E284" s="51"/>
+      <c r="E284" s="50"/>
     </row>
     <row r="285" spans="5:5">
-      <c r="E285" s="51"/>
+      <c r="E285" s="50"/>
     </row>
     <row r="286" spans="5:5">
-      <c r="E286" s="51"/>
+      <c r="E286" s="50"/>
     </row>
     <row r="287" spans="5:5">
-      <c r="E287" s="51"/>
+      <c r="E287" s="50"/>
     </row>
     <row r="288" spans="5:5">
-      <c r="E288" s="51"/>
+      <c r="E288" s="50"/>
     </row>
     <row r="289" spans="5:5">
-      <c r="E289" s="51"/>
+      <c r="E289" s="50"/>
     </row>
     <row r="290" spans="5:5">
-      <c r="E290" s="51"/>
+      <c r="E290" s="50"/>
     </row>
     <row r="291" spans="5:5">
-      <c r="E291" s="51"/>
+      <c r="E291" s="50"/>
     </row>
     <row r="292" spans="5:5">
-      <c r="E292" s="51"/>
+      <c r="E292" s="50"/>
     </row>
     <row r="293" spans="5:5">
-      <c r="E293" s="51"/>
+      <c r="E293" s="50"/>
     </row>
     <row r="294" spans="5:5">
-      <c r="E294" s="51"/>
+      <c r="E294" s="50"/>
     </row>
     <row r="295" spans="5:5">
-      <c r="E295" s="51"/>
+      <c r="E295" s="50"/>
     </row>
     <row r="296" spans="5:5">
-      <c r="E296" s="51"/>
+      <c r="E296" s="50"/>
     </row>
     <row r="297" spans="5:5">
-      <c r="E297" s="51"/>
+      <c r="E297" s="50"/>
     </row>
     <row r="298" spans="5:5">
-      <c r="E298" s="51"/>
+      <c r="E298" s="50"/>
     </row>
     <row r="299" spans="5:5">
-      <c r="E299" s="51"/>
+      <c r="E299" s="50"/>
     </row>
     <row r="300" spans="5:5">
-      <c r="E300" s="51"/>
+      <c r="E300" s="50"/>
     </row>
     <row r="301" spans="5:5">
-      <c r="E301" s="51"/>
+      <c r="E301" s="50"/>
     </row>
     <row r="302" spans="5:5">
-      <c r="E302" s="51"/>
+      <c r="E302" s="50"/>
     </row>
     <row r="303" spans="5:5">
-      <c r="E303" s="51"/>
+      <c r="E303" s="50"/>
     </row>
     <row r="304" spans="5:5">
-      <c r="E304" s="51"/>
+      <c r="E304" s="50"/>
     </row>
     <row r="305" spans="5:5">
-      <c r="E305" s="51"/>
+      <c r="E305" s="50"/>
     </row>
     <row r="306" spans="5:5">
-      <c r="E306" s="51"/>
+      <c r="E306" s="50"/>
     </row>
     <row r="307" spans="5:5">
-      <c r="E307" s="51"/>
+      <c r="E307" s="50"/>
     </row>
     <row r="308" spans="5:5">
-      <c r="E308" s="51"/>
+      <c r="E308" s="50"/>
     </row>
     <row r="309" spans="5:5">
-      <c r="E309" s="51"/>
+      <c r="E309" s="50"/>
     </row>
     <row r="310" spans="5:5">
-      <c r="E310" s="51"/>
+      <c r="E310" s="50"/>
     </row>
     <row r="311" spans="5:5">
-      <c r="E311" s="51"/>
+      <c r="E311" s="50"/>
     </row>
     <row r="312" spans="5:5">
-      <c r="E312" s="51"/>
+      <c r="E312" s="50"/>
     </row>
     <row r="313" spans="5:5">
-      <c r="E313" s="51"/>
+      <c r="E313" s="50"/>
     </row>
     <row r="314" spans="5:5">
-      <c r="E314" s="51"/>
+      <c r="E314" s="50"/>
     </row>
     <row r="315" spans="5:5">
-      <c r="E315" s="51"/>
+      <c r="E315" s="50"/>
     </row>
     <row r="316" spans="5:5">
-      <c r="E316" s="51"/>
+      <c r="E316" s="50"/>
     </row>
     <row r="317" spans="5:5">
-      <c r="E317" s="51"/>
+      <c r="E317" s="50"/>
     </row>
     <row r="318" spans="5:5">
-      <c r="E318" s="51"/>
+      <c r="E318" s="50"/>
     </row>
     <row r="319" spans="5:5">
-      <c r="E319" s="51"/>
+      <c r="E319" s="50"/>
     </row>
     <row r="320" spans="5:5">
-      <c r="E320" s="51"/>
+      <c r="E320" s="50"/>
     </row>
     <row r="321" spans="5:5">
-      <c r="E321" s="51"/>
+      <c r="E321" s="50"/>
     </row>
     <row r="322" spans="5:5">
-      <c r="E322" s="51"/>
+      <c r="E322" s="50"/>
     </row>
     <row r="323" spans="5:5">
-      <c r="E323" s="51"/>
+      <c r="E323" s="50"/>
     </row>
     <row r="324" spans="5:5">
-      <c r="E324" s="51"/>
+      <c r="E324" s="50"/>
     </row>
     <row r="325" spans="5:5">
-      <c r="E325" s="51"/>
+      <c r="E325" s="50"/>
     </row>
     <row r="326" spans="5:5">
-      <c r="E326" s="51"/>
+      <c r="E326" s="50"/>
     </row>
     <row r="327" spans="5:5">
-      <c r="E327" s="51"/>
+      <c r="E327" s="50"/>
     </row>
     <row r="328" spans="5:5">
-      <c r="E328" s="51"/>
+      <c r="E328" s="50"/>
     </row>
     <row r="329" spans="5:5">
-      <c r="E329" s="51"/>
+      <c r="E329" s="50"/>
     </row>
     <row r="330" spans="5:5">
-      <c r="E330" s="51"/>
+      <c r="E330" s="50"/>
     </row>
     <row r="331" spans="5:5">
-      <c r="E331" s="51"/>
+      <c r="E331" s="50"/>
     </row>
     <row r="332" spans="5:5">
-      <c r="E332" s="51"/>
+      <c r="E332" s="50"/>
     </row>
     <row r="333" spans="5:5">
-      <c r="E333" s="51"/>
+      <c r="E333" s="50"/>
     </row>
     <row r="334" spans="5:5">
-      <c r="E334" s="51"/>
+      <c r="E334" s="50"/>
     </row>
     <row r="335" spans="5:5">
-      <c r="E335" s="51"/>
+      <c r="E335" s="50"/>
     </row>
     <row r="336" spans="5:5">
-      <c r="E336" s="51"/>
+      <c r="E336" s="50"/>
     </row>
     <row r="337" spans="5:5">
-      <c r="E337" s="51"/>
+      <c r="E337" s="50"/>
     </row>
     <row r="338" spans="5:5">
-      <c r="E338" s="51"/>
+      <c r="E338" s="50"/>
     </row>
     <row r="339" spans="5:5">
-      <c r="E339" s="51"/>
+      <c r="E339" s="50"/>
     </row>
     <row r="340" spans="5:5">
-      <c r="E340" s="51"/>
+      <c r="E340" s="50"/>
     </row>
     <row r="341" spans="5:5">
-      <c r="E341" s="51"/>
+      <c r="E341" s="50"/>
     </row>
     <row r="342" spans="5:5">
-      <c r="E342" s="51"/>
+      <c r="E342" s="50"/>
     </row>
     <row r="343" spans="5:5">
-      <c r="E343" s="51"/>
+      <c r="E343" s="50"/>
     </row>
     <row r="344" spans="5:5">
-      <c r="E344" s="51"/>
+      <c r="E344" s="50"/>
     </row>
     <row r="345" spans="5:5">
-      <c r="E345" s="51"/>
+      <c r="E345" s="50"/>
     </row>
     <row r="346" spans="5:5">
-      <c r="E346" s="51"/>
+      <c r="E346" s="50"/>
     </row>
     <row r="347" spans="5:5">
-      <c r="E347" s="51"/>
+      <c r="E347" s="50"/>
     </row>
     <row r="348" spans="5:5">
-      <c r="E348" s="51"/>
+      <c r="E348" s="50"/>
     </row>
     <row r="349" spans="5:5">
-      <c r="E349" s="51"/>
+      <c r="E349" s="50"/>
     </row>
     <row r="350" spans="5:5">
-      <c r="E350" s="51"/>
+      <c r="E350" s="50"/>
     </row>
     <row r="351" spans="5:5">
-      <c r="E351" s="51"/>
+      <c r="E351" s="50"/>
     </row>
     <row r="352" spans="5:5">
-      <c r="E352" s="51"/>
+      <c r="E352" s="50"/>
     </row>
     <row r="353" spans="5:5">
-      <c r="E353" s="51"/>
+      <c r="E353" s="50"/>
     </row>
     <row r="354" spans="5:5">
-      <c r="E354" s="51"/>
+      <c r="E354" s="50"/>
     </row>
     <row r="355" spans="5:5">
-      <c r="E355" s="51"/>
+      <c r="E355" s="50"/>
     </row>
     <row r="356" spans="5:5">
-      <c r="E356" s="51"/>
+      <c r="E356" s="50"/>
     </row>
     <row r="357" spans="5:5">
-      <c r="E357" s="51"/>
+      <c r="E357" s="50"/>
     </row>
     <row r="358" spans="5:5">
-      <c r="E358" s="51"/>
+      <c r="E358" s="50"/>
     </row>
     <row r="359" spans="5:5">
-      <c r="E359" s="51"/>
+      <c r="E359" s="50"/>
     </row>
     <row r="360" spans="5:5">
-      <c r="E360" s="51"/>
+      <c r="E360" s="50"/>
     </row>
     <row r="361" spans="5:5">
-      <c r="E361" s="51"/>
+      <c r="E361" s="50"/>
     </row>
     <row r="362" spans="5:5">
-      <c r="E362" s="51"/>
+      <c r="E362" s="50"/>
     </row>
     <row r="363" spans="5:5">
-      <c r="E363" s="51"/>
+      <c r="E363" s="50"/>
     </row>
     <row r="364" spans="5:5">
-      <c r="E364" s="51"/>
+      <c r="E364" s="50"/>
     </row>
     <row r="365" spans="5:5">
-      <c r="E365" s="51"/>
+      <c r="E365" s="50"/>
     </row>
     <row r="366" spans="5:5">
-      <c r="E366" s="51"/>
+      <c r="E366" s="50"/>
     </row>
     <row r="367" spans="5:5">
-      <c r="E367" s="51"/>
+      <c r="E367" s="50"/>
     </row>
     <row r="368" spans="5:5">
-      <c r="E368" s="51"/>
+      <c r="E368" s="50"/>
     </row>
     <row r="369" spans="5:5">
-      <c r="E369" s="51"/>
+      <c r="E369" s="50"/>
     </row>
     <row r="370" spans="5:5">
-      <c r="E370" s="51"/>
+      <c r="E370" s="50"/>
     </row>
     <row r="371" spans="5:5">
-      <c r="E371" s="51"/>
+      <c r="E371" s="50"/>
     </row>
     <row r="372" spans="5:5">
-      <c r="E372" s="51"/>
+      <c r="E372" s="50"/>
     </row>
     <row r="373" spans="5:5">
-      <c r="E373" s="51"/>
+      <c r="E373" s="50"/>
     </row>
     <row r="374" spans="5:5">
-      <c r="E374" s="51"/>
+      <c r="E374" s="50"/>
     </row>
     <row r="375" spans="5:5">
-      <c r="E375" s="51"/>
+      <c r="E375" s="50"/>
     </row>
     <row r="376" spans="5:5">
-      <c r="E376" s="51"/>
+      <c r="E376" s="50"/>
     </row>
     <row r="377" spans="5:5">
-      <c r="E377" s="51"/>
+      <c r="E377" s="50"/>
     </row>
     <row r="378" spans="5:5">
-      <c r="E378" s="51"/>
+      <c r="E378" s="50"/>
     </row>
     <row r="379" spans="5:5">
-      <c r="E379" s="51"/>
+      <c r="E379" s="50"/>
     </row>
     <row r="380" spans="5:5">
-      <c r="E380" s="51"/>
+      <c r="E380" s="50"/>
     </row>
     <row r="381" spans="5:5">
-      <c r="E381" s="51"/>
+      <c r="E381" s="50"/>
     </row>
     <row r="382" spans="5:5">
-      <c r="E382" s="51"/>
+      <c r="E382" s="50"/>
     </row>
     <row r="383" spans="5:5">
-      <c r="E383" s="51"/>
+      <c r="E383" s="50"/>
     </row>
     <row r="384" spans="5:5">
-      <c r="E384" s="51"/>
+      <c r="E384" s="50"/>
     </row>
     <row r="385" spans="5:5">
-      <c r="E385" s="51"/>
+      <c r="E385" s="50"/>
     </row>
     <row r="386" spans="5:5">
-      <c r="E386" s="51"/>
+      <c r="E386" s="50"/>
     </row>
     <row r="387" spans="5:5">
-      <c r="E387" s="51"/>
+      <c r="E387" s="50"/>
     </row>
     <row r="388" spans="5:5">
-      <c r="E388" s="51"/>
+      <c r="E388" s="50"/>
     </row>
     <row r="389" spans="5:5">
-      <c r="E389" s="51"/>
+      <c r="E389" s="50"/>
     </row>
     <row r="390" spans="5:5">
-      <c r="E390" s="51"/>
+      <c r="E390" s="50"/>
     </row>
     <row r="391" spans="5:5">
-      <c r="E391" s="51"/>
+      <c r="E391" s="50"/>
     </row>
     <row r="392" spans="5:5">
-      <c r="E392" s="51"/>
+      <c r="E392" s="50"/>
     </row>
     <row r="393" spans="5:5">
-      <c r="E393" s="51"/>
+      <c r="E393" s="50"/>
     </row>
     <row r="394" spans="5:5">
-      <c r="E394" s="51"/>
+      <c r="E394" s="50"/>
     </row>
     <row r="395" spans="5:5">
-      <c r="E395" s="51"/>
+      <c r="E395" s="50"/>
     </row>
     <row r="396" spans="5:5">
-      <c r="E396" s="51"/>
+      <c r="E396" s="50"/>
     </row>
     <row r="397" spans="5:5">
-      <c r="E397" s="51"/>
+      <c r="E397" s="50"/>
     </row>
     <row r="398" spans="5:5">
-      <c r="E398" s="51"/>
+      <c r="E398" s="50"/>
     </row>
     <row r="399" spans="5:5">
-      <c r="E399" s="51"/>
+      <c r="E399" s="50"/>
     </row>
     <row r="400" spans="5:5">
-      <c r="E400" s="51"/>
+      <c r="E400" s="50"/>
     </row>
     <row r="401" spans="5:5">
-      <c r="E401" s="51"/>
+      <c r="E401" s="50"/>
     </row>
     <row r="402" spans="5:5">
-      <c r="E402" s="51"/>
+      <c r="E402" s="50"/>
     </row>
     <row r="403" spans="5:5">
-      <c r="E403" s="51"/>
+      <c r="E403" s="50"/>
     </row>
     <row r="404" spans="5:5">
-      <c r="E404" s="51"/>
+      <c r="E404" s="50"/>
     </row>
     <row r="405" spans="5:5">
-      <c r="E405" s="51"/>
+      <c r="E405" s="50"/>
     </row>
     <row r="406" spans="5:5">
-      <c r="E406" s="51"/>
+      <c r="E406" s="50"/>
     </row>
     <row r="407" spans="5:5">
-      <c r="E407" s="51"/>
+      <c r="E407" s="50"/>
     </row>
     <row r="408" spans="5:5">
-      <c r="E408" s="51"/>
+      <c r="E408" s="50"/>
     </row>
     <row r="409" spans="5:5">
-      <c r="E409" s="51"/>
+      <c r="E409" s="50"/>
     </row>
     <row r="410" spans="5:5">
-      <c r="E410" s="51"/>
+      <c r="E410" s="50"/>
     </row>
     <row r="411" spans="5:5">
-      <c r="E411" s="51"/>
+      <c r="E411" s="50"/>
     </row>
     <row r="412" spans="5:5">
-      <c r="E412" s="51"/>
+      <c r="E412" s="50"/>
     </row>
     <row r="413" spans="5:5">
-      <c r="E413" s="51"/>
+      <c r="E413" s="50"/>
     </row>
     <row r="414" spans="5:5">
-      <c r="E414" s="51"/>
+      <c r="E414" s="50"/>
     </row>
     <row r="415" spans="5:5">
-      <c r="E415" s="51"/>
+      <c r="E415" s="50"/>
     </row>
     <row r="416" spans="5:5">
-      <c r="E416" s="51"/>
+      <c r="E416" s="50"/>
     </row>
     <row r="417" spans="5:5">
-      <c r="E417" s="51"/>
+      <c r="E417" s="50"/>
     </row>
     <row r="418" spans="5:5">
-      <c r="E418" s="51"/>
+      <c r="E418" s="50"/>
     </row>
     <row r="419" spans="5:5">
-      <c r="E419" s="51"/>
+      <c r="E419" s="50"/>
     </row>
     <row r="420" spans="5:5">
-      <c r="E420" s="51"/>
+      <c r="E420" s="50"/>
     </row>
     <row r="421" spans="5:5">
-      <c r="E421" s="51"/>
+      <c r="E421" s="50"/>
     </row>
     <row r="422" spans="5:5">
-      <c r="E422" s="51"/>
+      <c r="E422" s="50"/>
     </row>
     <row r="423" spans="5:5">
-      <c r="E423" s="51"/>
+      <c r="E423" s="50"/>
     </row>
     <row r="424" spans="5:5">
-      <c r="E424" s="51"/>
+      <c r="E424" s="50"/>
     </row>
     <row r="425" spans="5:5">
-      <c r="E425" s="51"/>
+      <c r="E425" s="50"/>
     </row>
     <row r="426" spans="5:5">
-      <c r="E426" s="51"/>
+      <c r="E426" s="50"/>
     </row>
     <row r="427" spans="5:5">
-      <c r="E427" s="51"/>
+      <c r="E427" s="50"/>
     </row>
     <row r="428" spans="5:5">
-      <c r="E428" s="51"/>
+      <c r="E428" s="50"/>
     </row>
     <row r="429" spans="5:5">
-      <c r="E429" s="51"/>
+      <c r="E429" s="50"/>
     </row>
     <row r="430" spans="5:5">
-      <c r="E430" s="51"/>
+      <c r="E430" s="50"/>
     </row>
     <row r="431" spans="5:5">
-      <c r="E431" s="51"/>
+      <c r="E431" s="50"/>
     </row>
     <row r="432" spans="5:5">
-      <c r="E432" s="51"/>
+      <c r="E432" s="50"/>
     </row>
     <row r="433" spans="5:5">
-      <c r="E433" s="51"/>
+      <c r="E433" s="50"/>
     </row>
     <row r="434" spans="5:5">
-      <c r="E434" s="51"/>
+      <c r="E434" s="50"/>
     </row>
     <row r="435" spans="5:5">
-      <c r="E435" s="51"/>
+      <c r="E435" s="50"/>
     </row>
     <row r="436" spans="5:5">
-      <c r="E436" s="51"/>
+      <c r="E436" s="50"/>
     </row>
     <row r="437" spans="5:5">
-      <c r="E437" s="51"/>
+      <c r="E437" s="50"/>
     </row>
     <row r="438" spans="5:5">
-      <c r="E438" s="51"/>
+      <c r="E438" s="50"/>
     </row>
     <row r="439" spans="5:5">
-      <c r="E439" s="51"/>
+      <c r="E439" s="50"/>
     </row>
     <row r="440" spans="5:5">
-      <c r="E440" s="51"/>
+      <c r="E440" s="50"/>
     </row>
     <row r="441" spans="5:5">
-      <c r="E441" s="51"/>
+      <c r="E441" s="50"/>
     </row>
     <row r="442" spans="5:5">
-      <c r="E442" s="51"/>
+      <c r="E442" s="50"/>
     </row>
     <row r="443" spans="5:5">
-      <c r="E443" s="51"/>
+      <c r="E443" s="50"/>
     </row>
     <row r="444" spans="5:5">
-      <c r="E444" s="51"/>
+      <c r="E444" s="50"/>
     </row>
     <row r="445" spans="5:5">
-      <c r="E445" s="51"/>
+      <c r="E445" s="50"/>
     </row>
     <row r="446" spans="5:5">
-      <c r="E446" s="51"/>
+      <c r="E446" s="50"/>
     </row>
     <row r="447" spans="5:5">
-      <c r="E447" s="51"/>
+      <c r="E447" s="50"/>
     </row>
     <row r="448" spans="5:5">
-      <c r="E448" s="51"/>
+      <c r="E448" s="50"/>
     </row>
     <row r="449" spans="5:5">
-      <c r="E449" s="51"/>
+      <c r="E449" s="50"/>
     </row>
     <row r="450" spans="5:5">
-      <c r="E450" s="51"/>
+      <c r="E450" s="50"/>
     </row>
     <row r="451" spans="5:5">
-      <c r="E451" s="51"/>
+      <c r="E451" s="50"/>
     </row>
     <row r="452" spans="5:5">
-      <c r="E452" s="51"/>
+      <c r="E452" s="50"/>
     </row>
     <row r="453" spans="5:5">
-      <c r="E453" s="51"/>
+      <c r="E453" s="50"/>
     </row>
     <row r="454" spans="5:5">
-      <c r="E454" s="51"/>
+      <c r="E454" s="50"/>
     </row>
     <row r="455" spans="5:5">
-      <c r="E455" s="51"/>
+      <c r="E455" s="50"/>
     </row>
     <row r="456" spans="5:5">
-      <c r="E456" s="51"/>
+      <c r="E456" s="50"/>
     </row>
     <row r="457" spans="5:5">
-      <c r="E457" s="51"/>
+      <c r="E457" s="50"/>
     </row>
     <row r="458" spans="5:5">
-      <c r="E458" s="51"/>
+      <c r="E458" s="50"/>
     </row>
     <row r="459" spans="5:5">
-      <c r="E459" s="51"/>
+      <c r="E459" s="50"/>
     </row>
     <row r="460" spans="5:5">
-      <c r="E460" s="51"/>
+      <c r="E460" s="50"/>
     </row>
     <row r="461" spans="5:5">
-      <c r="E461" s="51"/>
+      <c r="E461" s="50"/>
     </row>
     <row r="462" spans="5:5">
-      <c r="E462" s="51"/>
+      <c r="E462" s="50"/>
     </row>
     <row r="463" spans="5:5">
-      <c r="E463" s="51"/>
+      <c r="E463" s="50"/>
     </row>
     <row r="464" spans="5:5">
-      <c r="E464" s="51"/>
+      <c r="E464" s="50"/>
     </row>
     <row r="465" spans="5:5">
-      <c r="E465" s="51"/>
+      <c r="E465" s="50"/>
     </row>
     <row r="466" spans="5:5">
-      <c r="E466" s="51"/>
+      <c r="E466" s="50"/>
     </row>
     <row r="467" spans="5:5">
-      <c r="E467" s="51"/>
+      <c r="E467" s="50"/>
     </row>
     <row r="468" spans="5:5">
-      <c r="E468" s="51"/>
+      <c r="E468" s="50"/>
     </row>
     <row r="469" spans="5:5">
-      <c r="E469" s="51"/>
+      <c r="E469" s="50"/>
     </row>
     <row r="470" spans="5:5">
-      <c r="E470" s="51"/>
+      <c r="E470" s="50"/>
     </row>
     <row r="471" spans="5:5">
-      <c r="E471" s="51"/>
+      <c r="E471" s="50"/>
     </row>
     <row r="472" spans="5:5">
-      <c r="E472" s="51"/>
+      <c r="E472" s="50"/>
     </row>
     <row r="473" spans="5:5">
-      <c r="E473" s="51"/>
+      <c r="E473" s="50"/>
     </row>
     <row r="474" spans="5:5">
-      <c r="E474" s="51"/>
+      <c r="E474" s="50"/>
     </row>
     <row r="475" spans="5:5">
-      <c r="E475" s="51"/>
+      <c r="E475" s="50"/>
     </row>
     <row r="476" spans="5:5">
-      <c r="E476" s="51"/>
+      <c r="E476" s="50"/>
     </row>
     <row r="477" spans="5:5">
-      <c r="E477" s="51"/>
+      <c r="E477" s="50"/>
     </row>
     <row r="478" spans="5:5">
-      <c r="E478" s="51"/>
+      <c r="E478" s="50"/>
     </row>
     <row r="479" spans="5:5">
-      <c r="E479" s="51"/>
+      <c r="E479" s="50"/>
     </row>
     <row r="480" spans="5:5">
-      <c r="E480" s="51"/>
+      <c r="E480" s="50"/>
     </row>
     <row r="481" spans="5:5">
-      <c r="E481" s="51"/>
+      <c r="E481" s="50"/>
     </row>
     <row r="482" spans="5:5">
-      <c r="E482" s="51"/>
+      <c r="E482" s="50"/>
     </row>
     <row r="483" spans="5:5">
-      <c r="E483" s="51"/>
+      <c r="E483" s="50"/>
     </row>
     <row r="484" spans="5:5">
-      <c r="E484" s="51"/>
+      <c r="E484" s="50"/>
     </row>
     <row r="485" spans="5:5">
-      <c r="E485" s="51"/>
+      <c r="E485" s="50"/>
     </row>
     <row r="486" spans="5:5">
-      <c r="E486" s="51"/>
+      <c r="E486" s="50"/>
     </row>
     <row r="487" spans="5:5">
-      <c r="E487" s="51"/>
+      <c r="E487" s="50"/>
     </row>
     <row r="488" spans="5:5">
-      <c r="E488" s="51"/>
+      <c r="E488" s="50"/>
     </row>
     <row r="489" spans="5:5">
-      <c r="E489" s="51"/>
+      <c r="E489" s="50"/>
     </row>
     <row r="490" spans="5:5">
-      <c r="E490" s="51"/>
+      <c r="E490" s="50"/>
     </row>
     <row r="491" spans="5:5">
-      <c r="E491" s="51"/>
+      <c r="E491" s="50"/>
     </row>
     <row r="492" spans="5:5">
-      <c r="E492" s="51"/>
+      <c r="E492" s="50"/>
     </row>
     <row r="493" spans="5:5">
-      <c r="E493" s="51"/>
+      <c r="E493" s="50"/>
     </row>
     <row r="494" spans="5:5">
-      <c r="E494" s="51"/>
+      <c r="E494" s="50"/>
     </row>
     <row r="495" spans="5:5">
-      <c r="E495" s="51"/>
+      <c r="E495" s="50"/>
     </row>
     <row r="496" spans="5:5">
-      <c r="E496" s="51"/>
+      <c r="E496" s="50"/>
     </row>
     <row r="497" spans="5:5">
-      <c r="E497" s="51"/>
+      <c r="E497" s="50"/>
     </row>
     <row r="498" spans="5:5">
-      <c r="E498" s="51"/>
+      <c r="E498" s="50"/>
     </row>
     <row r="499" spans="5:5">
-      <c r="E499" s="51"/>
+      <c r="E499" s="50"/>
     </row>
     <row r="500" spans="5:5">
-      <c r="E500" s="51"/>
+      <c r="E500" s="50"/>
     </row>
     <row r="501" spans="5:5">
-      <c r="E501" s="51"/>
+      <c r="E501" s="50"/>
     </row>
     <row r="502" spans="5:5">
-      <c r="E502" s="51"/>
+      <c r="E502" s="50"/>
     </row>
     <row r="503" spans="5:5">
-      <c r="E503" s="51"/>
+      <c r="E503" s="50"/>
     </row>
     <row r="504" spans="5:5">
-      <c r="E504" s="51"/>
+      <c r="E504" s="50"/>
     </row>
     <row r="505" spans="5:5">
-      <c r="E505" s="51"/>
+      <c r="E505" s="50"/>
     </row>
     <row r="506" spans="5:5">
-      <c r="E506" s="51"/>
+      <c r="E506" s="50"/>
     </row>
     <row r="507" spans="5:5">
-      <c r="E507" s="51"/>
+      <c r="E507" s="50"/>
     </row>
     <row r="508" spans="5:5">
-      <c r="E508" s="51"/>
+      <c r="E508" s="50"/>
     </row>
     <row r="509" spans="5:5">
-      <c r="E509" s="51"/>
+      <c r="E509" s="50"/>
     </row>
     <row r="510" spans="5:5">
-      <c r="E510" s="51"/>
+      <c r="E510" s="50"/>
     </row>
     <row r="511" spans="5:5">
-      <c r="E511" s="51"/>
+      <c r="E511" s="50"/>
     </row>
     <row r="512" spans="5:5">
-      <c r="E512" s="51"/>
+      <c r="E512" s="50"/>
     </row>
     <row r="513" spans="5:5">
-      <c r="E513" s="51"/>
+      <c r="E513" s="50"/>
     </row>
     <row r="514" spans="5:5">
-      <c r="E514" s="51"/>
+      <c r="E514" s="50"/>
     </row>
     <row r="515" spans="5:5">
-      <c r="E515" s="51"/>
+      <c r="E515" s="50"/>
     </row>
     <row r="516" spans="5:5">
-      <c r="E516" s="51"/>
+      <c r="E516" s="50"/>
     </row>
     <row r="517" spans="5:5">
-      <c r="E517" s="51"/>
+      <c r="E517" s="50"/>
     </row>
     <row r="518" spans="5:5">
-      <c r="E518" s="51"/>
+      <c r="E518" s="50"/>
     </row>
     <row r="519" spans="5:5">
-      <c r="E519" s="51"/>
+      <c r="E519" s="50"/>
     </row>
     <row r="520" spans="5:5">
-      <c r="E520" s="51"/>
+      <c r="E520" s="50"/>
     </row>
     <row r="521" spans="5:5">
-      <c r="E521" s="51"/>
+      <c r="E521" s="50"/>
     </row>
     <row r="522" spans="5:5">
-      <c r="E522" s="51"/>
+      <c r="E522" s="50"/>
     </row>
     <row r="523" spans="5:5">
-      <c r="E523" s="51"/>
+      <c r="E523" s="50"/>
     </row>
     <row r="524" spans="5:5">
-      <c r="E524" s="51"/>
+      <c r="E524" s="50"/>
     </row>
     <row r="525" spans="5:5">
-      <c r="E525" s="51"/>
+      <c r="E525" s="50"/>
     </row>
     <row r="526" spans="5:5">
-      <c r="E526" s="51"/>
+      <c r="E526" s="50"/>
     </row>
     <row r="527" spans="5:5">
-      <c r="E527" s="51"/>
+      <c r="E527" s="50"/>
     </row>
     <row r="528" spans="5:5">
-      <c r="E528" s="51"/>
+      <c r="E528" s="50"/>
     </row>
     <row r="529" spans="5:5">
-      <c r="E529" s="51"/>
+      <c r="E529" s="50"/>
     </row>
     <row r="530" spans="5:5">
-      <c r="E530" s="51"/>
+      <c r="E530" s="50"/>
     </row>
     <row r="531" spans="5:5">
-      <c r="E531" s="51"/>
+      <c r="E531" s="50"/>
     </row>
     <row r="532" spans="5:5">
-      <c r="E532" s="51"/>
+      <c r="E532" s="50"/>
     </row>
     <row r="533" spans="5:5">
-      <c r="E533" s="51"/>
+      <c r="E533" s="50"/>
     </row>
     <row r="534" spans="5:5">
-      <c r="E534" s="51"/>
+      <c r="E534" s="50"/>
     </row>
     <row r="535" spans="5:5">
-      <c r="E535" s="51"/>
+      <c r="E535" s="50"/>
     </row>
     <row r="536" spans="5:5">
-      <c r="E536" s="51"/>
+      <c r="E536" s="50"/>
     </row>
     <row r="537" spans="5:5">
-      <c r="E537" s="51"/>
+      <c r="E537" s="50"/>
     </row>
     <row r="538" spans="5:5">
-      <c r="E538" s="51"/>
+      <c r="E538" s="50"/>
     </row>
     <row r="539" spans="5:5">
-      <c r="E539" s="51"/>
+      <c r="E539" s="50"/>
     </row>
     <row r="540" spans="5:5">
-      <c r="E540" s="51"/>
+      <c r="E540" s="50"/>
     </row>
     <row r="541" spans="5:5">
-      <c r="E541" s="51"/>
+      <c r="E541" s="50"/>
     </row>
     <row r="542" spans="5:5">
-      <c r="E542" s="51"/>
+      <c r="E542" s="50"/>
     </row>
     <row r="543" spans="5:5">
-      <c r="E543" s="51"/>
+      <c r="E543" s="50"/>
     </row>
     <row r="544" spans="5:5">
-      <c r="E544" s="51"/>
+      <c r="E544" s="50"/>
     </row>
     <row r="545" spans="5:5">
-      <c r="E545" s="51"/>
+      <c r="E545" s="50"/>
     </row>
     <row r="546" spans="5:5">
-      <c r="E546" s="51"/>
+      <c r="E546" s="50"/>
     </row>
     <row r="547" spans="5:5">
-      <c r="E547" s="51"/>
+      <c r="E547" s="50"/>
     </row>
     <row r="548" spans="5:5">
-      <c r="E548" s="51"/>
+      <c r="E548" s="50"/>
     </row>
     <row r="549" spans="5:5">
-      <c r="E549" s="51"/>
+      <c r="E549" s="50"/>
     </row>
     <row r="550" spans="5:5">
-      <c r="E550" s="51"/>
+      <c r="E550" s="50"/>
     </row>
     <row r="551" spans="5:5">
-      <c r="E551" s="51"/>
+      <c r="E551" s="50"/>
     </row>
     <row r="552" spans="5:5">
-      <c r="E552" s="51"/>
+      <c r="E552" s="50"/>
     </row>
     <row r="553" spans="5:5">
-      <c r="E553" s="51"/>
+      <c r="E553" s="50"/>
     </row>
     <row r="554" spans="5:5">
-      <c r="E554" s="51"/>
+      <c r="E554" s="50"/>
     </row>
     <row r="555" spans="5:5">
-      <c r="E555" s="51"/>
+      <c r="E555" s="50"/>
     </row>
     <row r="556" spans="5:5">
-      <c r="E556" s="51"/>
+      <c r="E556" s="50"/>
     </row>
     <row r="557" spans="5:5">
-      <c r="E557" s="51"/>
+      <c r="E557" s="50"/>
     </row>
     <row r="558" spans="5:5">
-      <c r="E558" s="51"/>
+      <c r="E558" s="50"/>
     </row>
     <row r="559" spans="5:5">
-      <c r="E559" s="51"/>
+      <c r="E559" s="50"/>
     </row>
     <row r="560" spans="5:5">
-      <c r="E560" s="51"/>
+      <c r="E560" s="50"/>
     </row>
     <row r="561" spans="5:5">
-      <c r="E561" s="51"/>
+      <c r="E561" s="50"/>
     </row>
     <row r="562" spans="5:5">
-      <c r="E562" s="51"/>
+      <c r="E562" s="50"/>
     </row>
     <row r="563" spans="5:5">
-      <c r="E563" s="51"/>
+      <c r="E563" s="50"/>
     </row>
     <row r="564" spans="5:5">
-      <c r="E564" s="51"/>
+      <c r="E564" s="50"/>
     </row>
     <row r="565" spans="5:5">
-      <c r="E565" s="51"/>
+      <c r="E565" s="50"/>
     </row>
     <row r="566" spans="5:5">
-      <c r="E566" s="51"/>
+      <c r="E566" s="50"/>
     </row>
     <row r="567" spans="5:5">
-      <c r="E567" s="51"/>
+      <c r="E567" s="50"/>
     </row>
     <row r="568" spans="5:5">
-      <c r="E568" s="51"/>
+      <c r="E568" s="50"/>
     </row>
     <row r="569" spans="5:5">
-      <c r="E569" s="51"/>
+      <c r="E569" s="50"/>
     </row>
     <row r="570" spans="5:5">
-      <c r="E570" s="51"/>
+      <c r="E570" s="50"/>
     </row>
     <row r="571" spans="5:5">
-      <c r="E571" s="51"/>
+      <c r="E571" s="50"/>
     </row>
     <row r="572" spans="5:5">
-      <c r="E572" s="51"/>
+      <c r="E572" s="50"/>
     </row>
     <row r="573" spans="5:5">
-      <c r="E573" s="51"/>
+      <c r="E573" s="50"/>
     </row>
     <row r="574" spans="5:5">
-      <c r="E574" s="51"/>
+      <c r="E574" s="50"/>
     </row>
     <row r="575" spans="5:5">
-      <c r="E575" s="51"/>
+      <c r="E575" s="50"/>
     </row>
     <row r="576" spans="5:5">
-      <c r="E576" s="51"/>
+      <c r="E576" s="50"/>
     </row>
     <row r="577" spans="5:5">
-      <c r="E577" s="51"/>
+      <c r="E577" s="50"/>
     </row>
     <row r="578" spans="5:5">
-      <c r="E578" s="51"/>
+      <c r="E578" s="50"/>
     </row>
     <row r="579" spans="5:5">
-      <c r="E579" s="51"/>
+      <c r="E579" s="50"/>
     </row>
     <row r="580" spans="5:5">
-      <c r="E580" s="51"/>
+      <c r="E580" s="50"/>
     </row>
     <row r="581" spans="5:5">
-      <c r="E581" s="51"/>
+      <c r="E581" s="50"/>
     </row>
     <row r="582" spans="5:5">
-      <c r="E582" s="51"/>
+      <c r="E582" s="50"/>
     </row>
     <row r="583" spans="5:5">
-      <c r="E583" s="51"/>
+      <c r="E583" s="50"/>
     </row>
     <row r="584" spans="5:5">
-      <c r="E584" s="51"/>
+      <c r="E584" s="50"/>
     </row>
     <row r="585" spans="5:5">
-      <c r="E585" s="51"/>
+      <c r="E585" s="50"/>
     </row>
     <row r="586" spans="5:5">
-      <c r="E586" s="51"/>
+      <c r="E586" s="50"/>
     </row>
     <row r="587" spans="5:5">
-      <c r="E587" s="51"/>
+      <c r="E587" s="50"/>
     </row>
     <row r="588" spans="5:5">
-      <c r="E588" s="51"/>
+      <c r="E588" s="50"/>
     </row>
     <row r="589" spans="5:5">
-      <c r="E589" s="51"/>
+      <c r="E589" s="50"/>
     </row>
     <row r="590" spans="5:5">
-      <c r="E590" s="51"/>
+      <c r="E590" s="50"/>
     </row>
     <row r="591" spans="5:5">
-      <c r="E591" s="51"/>
+      <c r="E591" s="50"/>
     </row>
     <row r="592" spans="5:5">
-      <c r="E592" s="51"/>
+      <c r="E592" s="50"/>
     </row>
     <row r="593" spans="5:5">
-      <c r="E593" s="51"/>
+      <c r="E593" s="50"/>
     </row>
     <row r="594" spans="5:5">
-      <c r="E594" s="51"/>
+      <c r="E594" s="50"/>
     </row>
     <row r="595" spans="5:5">
-      <c r="E595" s="51"/>
+      <c r="E595" s="50"/>
     </row>
     <row r="596" spans="5:5">
-      <c r="E596" s="51"/>
+      <c r="E596" s="50"/>
     </row>
     <row r="597" spans="5:5">
-      <c r="E597" s="51"/>
+      <c r="E597" s="50"/>
     </row>
     <row r="598" spans="5:5">
-      <c r="E598" s="51"/>
+      <c r="E598" s="50"/>
     </row>
     <row r="599" spans="5:5">
-      <c r="E599" s="51"/>
+      <c r="E599" s="50"/>
     </row>
     <row r="600" spans="5:5">
-      <c r="E600" s="51"/>
+      <c r="E600" s="50"/>
     </row>
     <row r="601" spans="5:5">
-      <c r="E601" s="51"/>
+      <c r="E601" s="50"/>
     </row>
     <row r="602" spans="5:5">
-      <c r="E602" s="51"/>
+      <c r="E602" s="50"/>
     </row>
     <row r="603" spans="5:5">
-      <c r="E603" s="51"/>
+      <c r="E603" s="50"/>
     </row>
     <row r="604" spans="5:5">
-      <c r="E604" s="51"/>
+      <c r="E604" s="50"/>
     </row>
     <row r="605" spans="5:5">
-      <c r="E605" s="51"/>
+      <c r="E605" s="50"/>
     </row>
     <row r="606" spans="5:5">
-      <c r="E606" s="51"/>
+      <c r="E606" s="50"/>
     </row>
     <row r="607" spans="5:5">
-      <c r="E607" s="51"/>
+      <c r="E607" s="50"/>
     </row>
     <row r="608" spans="5:5">
-      <c r="E608" s="51"/>
+      <c r="E608" s="50"/>
     </row>
     <row r="609" spans="5:5">
-      <c r="E609" s="51"/>
+      <c r="E609" s="50"/>
     </row>
     <row r="610" spans="5:5">
-      <c r="E610" s="51"/>
+      <c r="E610" s="50"/>
     </row>
     <row r="611" spans="5:5">
-      <c r="E611" s="51"/>
+      <c r="E611" s="50"/>
     </row>
     <row r="612" spans="5:5">
-      <c r="E612" s="51"/>
+      <c r="E612" s="50"/>
     </row>
     <row r="613" spans="5:5">
-      <c r="E613" s="51"/>
+      <c r="E613" s="50"/>
     </row>
     <row r="614" spans="5:5">
-      <c r="E614" s="51"/>
+      <c r="E614" s="50"/>
     </row>
     <row r="615" spans="5:5">
-      <c r="E615" s="51"/>
+      <c r="E615" s="50"/>
     </row>
     <row r="616" spans="5:5">
-      <c r="E616" s="51"/>
+      <c r="E616" s="50"/>
     </row>
     <row r="617" spans="5:5">
-      <c r="E617" s="51"/>
+      <c r="E617" s="50"/>
     </row>
     <row r="618" spans="5:5">
-      <c r="E618" s="51"/>
+      <c r="E618" s="50"/>
     </row>
     <row r="619" spans="5:5">
-      <c r="E619" s="51"/>
+      <c r="E619" s="50"/>
     </row>
     <row r="620" spans="5:5">
-      <c r="E620" s="51"/>
+      <c r="E620" s="50"/>
     </row>
     <row r="621" spans="5:5">
-      <c r="E621" s="51"/>
+      <c r="E621" s="50"/>
     </row>
     <row r="622" spans="5:5">
-      <c r="E622" s="51"/>
+      <c r="E622" s="50"/>
     </row>
     <row r="623" spans="5:5">
-      <c r="E623" s="51"/>
+      <c r="E623" s="50"/>
     </row>
     <row r="624" spans="5:5">
-      <c r="E624" s="51"/>
+      <c r="E624" s="50"/>
     </row>
     <row r="625" spans="5:5">
-      <c r="E625" s="51"/>
+      <c r="E625" s="50"/>
     </row>
     <row r="626" spans="5:5">
-      <c r="E626" s="51"/>
+      <c r="E626" s="50"/>
     </row>
     <row r="627" spans="5:5">
-      <c r="E627" s="51"/>
+      <c r="E627" s="50"/>
     </row>
     <row r="628" spans="5:5">
-      <c r="E628" s="51"/>
+      <c r="E628" s="50"/>
     </row>
     <row r="629" spans="5:5">
-      <c r="E629" s="51"/>
+      <c r="E629" s="50"/>
     </row>
     <row r="630" spans="5:5">
-      <c r="E630" s="51"/>
+      <c r="E630" s="50"/>
     </row>
     <row r="631" spans="5:5">
-      <c r="E631" s="51"/>
+      <c r="E631" s="50"/>
     </row>
     <row r="632" spans="5:5">
-      <c r="E632" s="51"/>
+      <c r="E632" s="50"/>
     </row>
     <row r="633" spans="5:5">
-      <c r="E633" s="51"/>
+      <c r="E633" s="50"/>
     </row>
     <row r="634" spans="5:5">
-      <c r="E634" s="51"/>
+      <c r="E634" s="50"/>
     </row>
     <row r="635" spans="5:5">
-      <c r="E635" s="51"/>
+      <c r="E635" s="50"/>
     </row>
     <row r="636" spans="5:5">
-      <c r="E636" s="51"/>
+      <c r="E636" s="50"/>
     </row>
     <row r="637" spans="5:5">
-      <c r="E637" s="51"/>
+      <c r="E637" s="50"/>
     </row>
     <row r="638" spans="5:5">
-      <c r="E638" s="51"/>
+      <c r="E638" s="50"/>
     </row>
     <row r="639" spans="5:5">
-      <c r="E639" s="51"/>
+      <c r="E639" s="50"/>
     </row>
     <row r="640" spans="5:5">
-      <c r="E640" s="51"/>
+      <c r="E640" s="50"/>
     </row>
     <row r="641" spans="5:5">
-      <c r="E641" s="51"/>
+      <c r="E641" s="50"/>
     </row>
     <row r="642" spans="5:5">
-      <c r="E642" s="51"/>
+      <c r="E642" s="50"/>
     </row>
     <row r="643" spans="5:5">
-      <c r="E643" s="51"/>
+      <c r="E643" s="50"/>
     </row>
     <row r="644" spans="5:5">
-      <c r="E644" s="51"/>
+      <c r="E644" s="50"/>
     </row>
     <row r="645" spans="5:5">
-      <c r="E645" s="51"/>
+      <c r="E645" s="50"/>
     </row>
     <row r="646" spans="5:5">
-      <c r="E646" s="51"/>
+      <c r="E646" s="50"/>
     </row>
     <row r="647" spans="5:5">
-      <c r="E647" s="51"/>
+      <c r="E647" s="50"/>
     </row>
     <row r="648" spans="5:5">
-      <c r="E648" s="51"/>
+      <c r="E648" s="50"/>
     </row>
     <row r="649" spans="5:5">
-      <c r="E649" s="51"/>
+      <c r="E649" s="50"/>
     </row>
     <row r="650" spans="5:5">
-      <c r="E650" s="51"/>
+      <c r="E650" s="50"/>
     </row>
     <row r="651" spans="5:5">
-      <c r="E651" s="51"/>
+      <c r="E651" s="50"/>
     </row>
     <row r="652" spans="5:5">
-      <c r="E652" s="51"/>
+      <c r="E652" s="50"/>
     </row>
     <row r="653" spans="5:5">
-      <c r="E653" s="51"/>
+      <c r="E653" s="50"/>
     </row>
     <row r="654" spans="5:5">
-      <c r="E654" s="51"/>
+      <c r="E654" s="50"/>
     </row>
     <row r="655" spans="5:5">
-      <c r="E655" s="51"/>
+      <c r="E655" s="50"/>
     </row>
     <row r="656" spans="5:5">
-      <c r="E656" s="51"/>
+      <c r="E656" s="50"/>
     </row>
     <row r="657" spans="5:5">
-      <c r="E657" s="51"/>
+      <c r="E657" s="50"/>
     </row>
     <row r="658" spans="5:5">
-      <c r="E658" s="51"/>
+      <c r="E658" s="50"/>
     </row>
     <row r="659" spans="5:5">
-      <c r="E659" s="51"/>
+      <c r="E659" s="50"/>
     </row>
     <row r="660" spans="5:5">
-      <c r="E660" s="51"/>
+      <c r="E660" s="50"/>
     </row>
     <row r="661" spans="5:5">
-      <c r="E661" s="51"/>
+      <c r="E661" s="50"/>
     </row>
     <row r="662" spans="5:5">
-      <c r="E662" s="51"/>
+      <c r="E662" s="50"/>
     </row>
     <row r="663" spans="5:5">
-      <c r="E663" s="51"/>
+      <c r="E663" s="50"/>
     </row>
     <row r="664" spans="5:5">
-      <c r="E664" s="51"/>
+      <c r="E664" s="50"/>
     </row>
     <row r="665" spans="5:5">
-      <c r="E665" s="51"/>
+      <c r="E665" s="50"/>
     </row>
     <row r="666" spans="5:5">
-      <c r="E666" s="51"/>
+      <c r="E666" s="50"/>
     </row>
     <row r="667" spans="5:5">
-      <c r="E667" s="51"/>
+      <c r="E667" s="50"/>
     </row>
     <row r="668" spans="5:5">
-      <c r="E668" s="51"/>
+      <c r="E668" s="50"/>
     </row>
     <row r="669" spans="5:5">
-      <c r="E669" s="51"/>
+      <c r="E669" s="50"/>
     </row>
     <row r="670" spans="5:5">
-      <c r="E670" s="51"/>
+      <c r="E670" s="50"/>
     </row>
     <row r="671" spans="5:5">
-      <c r="E671" s="51"/>
+      <c r="E671" s="50"/>
     </row>
     <row r="672" spans="5:5">
-      <c r="E672" s="51"/>
+      <c r="E672" s="50"/>
     </row>
     <row r="673" spans="5:5">
-      <c r="E673" s="51"/>
+      <c r="E673" s="50"/>
     </row>
     <row r="674" spans="5:5">
-      <c r="E674" s="51"/>
+      <c r="E674" s="50"/>
     </row>
     <row r="675" spans="5:5">
-      <c r="E675" s="51"/>
+      <c r="E675" s="50"/>
     </row>
     <row r="676" spans="5:5">
-      <c r="E676" s="51"/>
+      <c r="E676" s="50"/>
     </row>
     <row r="677" spans="5:5">
-      <c r="E677" s="51"/>
+      <c r="E677" s="50"/>
     </row>
     <row r="678" spans="5:5">
-      <c r="E678" s="51"/>
+      <c r="E678" s="50"/>
     </row>
     <row r="679" spans="5:5">
-      <c r="E679" s="51"/>
+      <c r="E679" s="50"/>
     </row>
     <row r="680" spans="5:5">
-      <c r="E680" s="51"/>
+      <c r="E680" s="50"/>
     </row>
     <row r="681" spans="5:5">
-      <c r="E681" s="51"/>
+      <c r="E681" s="50"/>
     </row>
     <row r="682" spans="5:5">
-      <c r="E682" s="51"/>
+      <c r="E682" s="50"/>
     </row>
     <row r="683" spans="5:5">
-      <c r="E683" s="51"/>
+      <c r="E683" s="50"/>
     </row>
     <row r="684" spans="5:5">
-      <c r="E684" s="51"/>
+      <c r="E684" s="50"/>
     </row>
     <row r="685" spans="5:5">
-      <c r="E685" s="51"/>
+      <c r="E685" s="50"/>
     </row>
     <row r="686" spans="5:5">
-      <c r="E686" s="51"/>
+      <c r="E686" s="50"/>
     </row>
     <row r="687" spans="5:5">
-      <c r="E687" s="51"/>
+      <c r="E687" s="50"/>
     </row>
     <row r="688" spans="5:5">
-      <c r="E688" s="51"/>
+      <c r="E688" s="50"/>
     </row>
     <row r="689" spans="5:5">
-      <c r="E689" s="51"/>
+      <c r="E689" s="50"/>
     </row>
     <row r="690" spans="5:5">
-      <c r="E690" s="51"/>
+      <c r="E690" s="50"/>
     </row>
     <row r="691" spans="5:5">
-      <c r="E691" s="51"/>
+      <c r="E691" s="50"/>
     </row>
     <row r="692" spans="5:5">
-      <c r="E692" s="51"/>
+      <c r="E692" s="50"/>
     </row>
     <row r="693" spans="5:5">
-      <c r="E693" s="51"/>
+      <c r="E693" s="50"/>
     </row>
     <row r="694" spans="5:5">
-      <c r="E694" s="51"/>
+      <c r="E694" s="50"/>
     </row>
     <row r="695" spans="5:5">
-      <c r="E695" s="51"/>
+      <c r="E695" s="50"/>
     </row>
     <row r="696" spans="5:5">
-      <c r="E696" s="51"/>
+      <c r="E696" s="50"/>
     </row>
     <row r="697" spans="5:5">
-      <c r="E697" s="51"/>
+      <c r="E697" s="50"/>
     </row>
     <row r="698" spans="5:5">
-      <c r="E698" s="51"/>
+      <c r="E698" s="50"/>
     </row>
     <row r="699" spans="5:5">
-      <c r="E699" s="51"/>
+      <c r="E699" s="50"/>
     </row>
     <row r="700" spans="5:5">
-      <c r="E700" s="51"/>
+      <c r="E700" s="50"/>
     </row>
     <row r="701" spans="5:5">
-      <c r="E701" s="51"/>
+      <c r="E701" s="50"/>
     </row>
     <row r="702" spans="5:5">
-      <c r="E702" s="51"/>
+      <c r="E702" s="50"/>
     </row>
     <row r="703" spans="5:5">
-      <c r="E703" s="51"/>
+      <c r="E703" s="50"/>
     </row>
     <row r="704" spans="5:5">
-      <c r="E704" s="51"/>
+      <c r="E704" s="50"/>
     </row>
     <row r="705" spans="5:5">
-      <c r="E705" s="51"/>
+      <c r="E705" s="50"/>
     </row>
     <row r="706" spans="5:5">
-      <c r="E706" s="51"/>
+      <c r="E706" s="50"/>
     </row>
     <row r="707" spans="5:5">
-      <c r="E707" s="51"/>
+      <c r="E707" s="50"/>
     </row>
     <row r="708" spans="5:5">
-      <c r="E708" s="51"/>
+      <c r="E708" s="50"/>
     </row>
     <row r="709" spans="5:5">
-      <c r="E709" s="51"/>
+      <c r="E709" s="50"/>
     </row>
     <row r="710" spans="5:5">
-      <c r="E710" s="51"/>
+      <c r="E710" s="50"/>
     </row>
     <row r="711" spans="5:5">
-      <c r="E711" s="51"/>
+      <c r="E711" s="50"/>
     </row>
     <row r="712" spans="5:5">
-      <c r="E712" s="51"/>
+      <c r="E712" s="50"/>
     </row>
     <row r="713" spans="5:5">
-      <c r="E713" s="51"/>
+      <c r="E713" s="50"/>
     </row>
     <row r="714" spans="5:5">
-      <c r="E714" s="51"/>
+      <c r="E714" s="50"/>
     </row>
     <row r="715" spans="5:5">
-      <c r="E715" s="51"/>
+      <c r="E715" s="50"/>
     </row>
     <row r="716" spans="5:5">
-      <c r="E716" s="51"/>
+      <c r="E716" s="50"/>
     </row>
     <row r="717" spans="5:5">
-      <c r="E717" s="51"/>
+      <c r="E717" s="50"/>
     </row>
     <row r="718" spans="5:5">
-      <c r="E718" s="51"/>
+      <c r="E718" s="50"/>
     </row>
     <row r="719" spans="5:5">
-      <c r="E719" s="51"/>
+      <c r="E719" s="50"/>
     </row>
     <row r="720" spans="5:5">
-      <c r="E720" s="51"/>
+      <c r="E720" s="50"/>
     </row>
     <row r="721" spans="5:5">
-      <c r="E721" s="51"/>
+      <c r="E721" s="50"/>
     </row>
     <row r="722" spans="5:5">
-      <c r="E722" s="51"/>
+      <c r="E722" s="50"/>
     </row>
     <row r="723" spans="5:5">
-      <c r="E723" s="51"/>
+      <c r="E723" s="50"/>
     </row>
     <row r="724" spans="5:5">
-      <c r="E724" s="51"/>
+      <c r="E724" s="50"/>
     </row>
     <row r="725" spans="5:5">
-      <c r="E725" s="51"/>
+      <c r="E725" s="50"/>
     </row>
     <row r="726" spans="5:5">
-      <c r="E726" s="51"/>
+      <c r="E726" s="50"/>
     </row>
     <row r="727" spans="5:5">
-      <c r="E727" s="51"/>
+      <c r="E727" s="50"/>
     </row>
     <row r="728" spans="5:5">
-      <c r="E728" s="51"/>
+      <c r="E728" s="50"/>
     </row>
     <row r="729" spans="5:5">
-      <c r="E729" s="51"/>
+      <c r="E729" s="50"/>
     </row>
     <row r="730" spans="5:5">
-      <c r="E730" s="51"/>
+      <c r="E730" s="50"/>
     </row>
     <row r="731" spans="5:5">
-      <c r="E731" s="51"/>
+      <c r="E731" s="50"/>
     </row>
     <row r="732" spans="5:5">
-      <c r="E732" s="51"/>
+      <c r="E732" s="50"/>
     </row>
     <row r="733" spans="5:5">
-      <c r="E733" s="51"/>
+      <c r="E733" s="50"/>
     </row>
     <row r="734" spans="5:5">
-      <c r="E734" s="51"/>
+      <c r="E734" s="50"/>
     </row>
     <row r="735" spans="5:5">
-      <c r="E735" s="51"/>
+      <c r="E735" s="50"/>
     </row>
     <row r="736" spans="5:5">
-      <c r="E736" s="51"/>
+      <c r="E736" s="50"/>
     </row>
     <row r="737" spans="5:5">
-      <c r="E737" s="51"/>
+      <c r="E737" s="50"/>
     </row>
     <row r="738" spans="5:5">
-      <c r="E738" s="51"/>
+      <c r="E738" s="50"/>
     </row>
     <row r="739" spans="5:5">
-      <c r="E739" s="51"/>
+      <c r="E739" s="50"/>
     </row>
     <row r="740" spans="5:5">
-      <c r="E740" s="51"/>
+      <c r="E740" s="50"/>
     </row>
     <row r="741" spans="5:5">
-      <c r="E741" s="51"/>
+      <c r="E741" s="50"/>
     </row>
     <row r="742" spans="5:5">
-      <c r="E742" s="51"/>
+      <c r="E742" s="50"/>
     </row>
     <row r="743" spans="5:5">
-      <c r="E743" s="51"/>
+      <c r="E743" s="50"/>
     </row>
     <row r="744" spans="5:5">
-      <c r="E744" s="51"/>
+      <c r="E744" s="50"/>
     </row>
     <row r="745" spans="5:5">
-      <c r="E745" s="51"/>
+      <c r="E745" s="50"/>
     </row>
     <row r="746" spans="5:5">
-      <c r="E746" s="51"/>
+      <c r="E746" s="50"/>
     </row>
     <row r="747" spans="5:5">
-      <c r="E747" s="51"/>
+      <c r="E747" s="50"/>
     </row>
     <row r="748" spans="5:5">
-      <c r="E748" s="51"/>
+      <c r="E748" s="50"/>
     </row>
     <row r="749" spans="5:5">
-      <c r="E749" s="51"/>
+      <c r="E749" s="50"/>
     </row>
     <row r="750" spans="5:5">
-      <c r="E750" s="51"/>
+      <c r="E750" s="50"/>
     </row>
     <row r="751" spans="5:5">
-      <c r="E751" s="51"/>
+      <c r="E751" s="50"/>
     </row>
     <row r="752" spans="5:5">
-      <c r="E752" s="51"/>
+      <c r="E752" s="50"/>
     </row>
     <row r="753" spans="5:5">
-      <c r="E753" s="51"/>
+      <c r="E753" s="50"/>
     </row>
     <row r="754" spans="5:5">
-      <c r="E754" s="51"/>
+      <c r="E754" s="50"/>
     </row>
     <row r="755" spans="5:5">
-      <c r="E755" s="51"/>
+      <c r="E755" s="50"/>
     </row>
     <row r="756" spans="5:5">
-      <c r="E756" s="51"/>
+      <c r="E756" s="50"/>
     </row>
     <row r="757" spans="5:5">
-      <c r="E757" s="51"/>
+      <c r="E757" s="50"/>
     </row>
     <row r="758" spans="5:5">
-      <c r="E758" s="51"/>
+      <c r="E758" s="50"/>
     </row>
     <row r="759" spans="5:5">
-      <c r="E759" s="51"/>
+      <c r="E759" s="50"/>
     </row>
     <row r="760" spans="5:5">
-      <c r="E760" s="51"/>
+      <c r="E760" s="50"/>
     </row>
     <row r="761" spans="5:5">
-      <c r="E761" s="51"/>
+      <c r="E761" s="50"/>
     </row>
     <row r="762" spans="5:5">
-      <c r="E762" s="51"/>
+      <c r="E762" s="50"/>
     </row>
     <row r="763" spans="5:5">
-      <c r="E763" s="51"/>
+      <c r="E763" s="50"/>
     </row>
     <row r="764" spans="5:5">
-      <c r="E764" s="51"/>
+      <c r="E764" s="50"/>
     </row>
     <row r="765" spans="5:5">
-      <c r="E765" s="51"/>
+      <c r="E765" s="50"/>
     </row>
     <row r="766" spans="5:5">
-      <c r="E766" s="51"/>
+      <c r="E766" s="50"/>
     </row>
     <row r="767" spans="5:5">
-      <c r="E767" s="51"/>
+      <c r="E767" s="50"/>
     </row>
     <row r="768" spans="5:5">
-      <c r="E768" s="51"/>
+      <c r="E768" s="50"/>
     </row>
     <row r="769" spans="5:5">
-      <c r="E769" s="51"/>
+      <c r="E769" s="50"/>
     </row>
     <row r="770" spans="5:5">
-      <c r="E770" s="51"/>
+      <c r="E770" s="50"/>
     </row>
     <row r="771" spans="5:5">
-      <c r="E771" s="51"/>
+      <c r="E771" s="50"/>
     </row>
     <row r="772" spans="5:5">
-      <c r="E772" s="51"/>
+      <c r="E772" s="50"/>
     </row>
     <row r="773" spans="5:5">
-      <c r="E773" s="51"/>
+      <c r="E773" s="50"/>
     </row>
     <row r="774" spans="5:5">
-      <c r="E774" s="51"/>
+      <c r="E774" s="50"/>
     </row>
     <row r="775" spans="5:5">
-      <c r="E775" s="51"/>
+      <c r="E775" s="50"/>
     </row>
     <row r="776" spans="5:5">
-      <c r="E776" s="51"/>
+      <c r="E776" s="50"/>
     </row>
     <row r="777" spans="5:5">
-      <c r="E777" s="51"/>
+      <c r="E777" s="50"/>
     </row>
     <row r="778" spans="5:5">
-      <c r="E778" s="51"/>
+      <c r="E778" s="50"/>
     </row>
     <row r="779" spans="5:5">
-      <c r="E779" s="51"/>
+      <c r="E779" s="50"/>
     </row>
     <row r="780" spans="5:5">
-      <c r="E780" s="51"/>
+      <c r="E780" s="50"/>
     </row>
     <row r="781" spans="5:5">
-      <c r="E781" s="51"/>
+      <c r="E781" s="50"/>
     </row>
     <row r="782" spans="5:5">
-      <c r="E782" s="51"/>
+      <c r="E782" s="50"/>
     </row>
     <row r="783" spans="5:5">
-      <c r="E783" s="51"/>
+      <c r="E783" s="50"/>
     </row>
     <row r="784" spans="5:5">
-      <c r="E784" s="51"/>
+      <c r="E784" s="50"/>
     </row>
     <row r="785" spans="5:5">
-      <c r="E785" s="51"/>
+      <c r="E785" s="50"/>
     </row>
     <row r="786" spans="5:5">
-      <c r="E786" s="51"/>
+      <c r="E786" s="50"/>
     </row>
     <row r="787" spans="5:5">
-      <c r="E787" s="51"/>
+      <c r="E787" s="50"/>
     </row>
     <row r="788" spans="5:5">
-      <c r="E788" s="51"/>
+      <c r="E788" s="50"/>
     </row>
     <row r="789" spans="5:5">
-      <c r="E789" s="51"/>
+      <c r="E789" s="50"/>
     </row>
     <row r="790" spans="5:5">
-      <c r="E790" s="51"/>
+      <c r="E790" s="50"/>
     </row>
     <row r="791" spans="5:5">
-      <c r="E791" s="51"/>
+      <c r="E791" s="50"/>
     </row>
     <row r="792" spans="5:5">
-      <c r="E792" s="51"/>
+      <c r="E792" s="50"/>
     </row>
     <row r="793" spans="5:5">
-      <c r="E793" s="51"/>
+      <c r="E793" s="50"/>
     </row>
     <row r="794" spans="5:5">
-      <c r="E794" s="51"/>
+      <c r="E794" s="50"/>
     </row>
     <row r="795" spans="5:5">
-      <c r="E795" s="51"/>
+      <c r="E795" s="50"/>
     </row>
     <row r="796" spans="5:5">
-      <c r="E796" s="51"/>
+      <c r="E796" s="50"/>
     </row>
     <row r="797" spans="5:5">
-      <c r="E797" s="51"/>
+      <c r="E797" s="50"/>
     </row>
     <row r="798" spans="5:5">
-      <c r="E798" s="51"/>
+      <c r="E798" s="50"/>
     </row>
     <row r="799" spans="5:5">
-      <c r="E799" s="51"/>
+      <c r="E799" s="50"/>
     </row>
     <row r="800" spans="5:5">
-      <c r="E800" s="51"/>
+      <c r="E800" s="50"/>
     </row>
     <row r="801" spans="5:5">
-      <c r="E801" s="51"/>
+      <c r="E801" s="50"/>
     </row>
     <row r="802" spans="5:5">
-      <c r="E802" s="51"/>
+      <c r="E802" s="50"/>
     </row>
     <row r="803" spans="5:5">
-      <c r="E803" s="51"/>
+      <c r="E803" s="50"/>
     </row>
     <row r="804" spans="5:5">
-      <c r="E804" s="51"/>
+      <c r="E804" s="50"/>
     </row>
     <row r="805" spans="5:5">
-      <c r="E805" s="51"/>
+      <c r="E805" s="50"/>
     </row>
     <row r="806" spans="5:5">
-      <c r="E806" s="51"/>
+      <c r="E806" s="50"/>
     </row>
     <row r="807" spans="5:5">
-      <c r="E807" s="51"/>
+      <c r="E807" s="50"/>
     </row>
     <row r="808" spans="5:5">
-      <c r="E808" s="51"/>
+      <c r="E808" s="50"/>
     </row>
     <row r="809" spans="5:5">
-      <c r="E809" s="51"/>
+      <c r="E809" s="50"/>
     </row>
     <row r="810" spans="5:5">
-      <c r="E810" s="51"/>
+      <c r="E810" s="50"/>
     </row>
     <row r="811" spans="5:5">
-      <c r="E811" s="51"/>
+      <c r="E811" s="50"/>
     </row>
     <row r="812" spans="5:5">
-      <c r="E812" s="51"/>
+      <c r="E812" s="50"/>
     </row>
     <row r="813" spans="5:5">
-      <c r="E813" s="51"/>
+      <c r="E813" s="50"/>
     </row>
     <row r="814" spans="5:5">
-      <c r="E814" s="51"/>
+      <c r="E814" s="50"/>
     </row>
     <row r="815" spans="5:5">
-      <c r="E815" s="51"/>
+      <c r="E815" s="50"/>
     </row>
     <row r="816" spans="5:5">
-      <c r="E816" s="51"/>
+      <c r="E816" s="50"/>
     </row>
     <row r="817" spans="5:5">
-      <c r="E817" s="51"/>
+      <c r="E817" s="50"/>
     </row>
     <row r="818" spans="5:5">
-      <c r="E818" s="51"/>
+      <c r="E818" s="50"/>
     </row>
     <row r="819" spans="5:5">
-      <c r="E819" s="51"/>
+      <c r="E819" s="50"/>
     </row>
     <row r="820" spans="5:5">
-      <c r="E820" s="51"/>
+      <c r="E820" s="50"/>
     </row>
     <row r="821" spans="5:5">
-      <c r="E821" s="51"/>
+      <c r="E821" s="50"/>
     </row>
     <row r="822" spans="5:5">
-      <c r="E822" s="51"/>
+      <c r="E822" s="50"/>
     </row>
     <row r="823" spans="5:5">
-      <c r="E823" s="51"/>
+      <c r="E823" s="50"/>
     </row>
     <row r="824" spans="5:5">
-      <c r="E824" s="51"/>
+      <c r="E824" s="50"/>
     </row>
     <row r="825" spans="5:5">
-      <c r="E825" s="51"/>
+      <c r="E825" s="50"/>
     </row>
     <row r="826" spans="5:5">
-      <c r="E826" s="51"/>
+      <c r="E826" s="50"/>
     </row>
     <row r="827" spans="5:5">
-      <c r="E827" s="51"/>
+      <c r="E827" s="50"/>
     </row>
     <row r="828" spans="5:5">
-      <c r="E828" s="51"/>
+      <c r="E828" s="50"/>
     </row>
     <row r="829" spans="5:5">
-      <c r="E829" s="51"/>
+      <c r="E829" s="50"/>
     </row>
     <row r="830" spans="5:5">
-      <c r="E830" s="51"/>
+      <c r="E830" s="50"/>
     </row>
     <row r="831" spans="5:5">
-      <c r="E831" s="51"/>
+      <c r="E831" s="50"/>
     </row>
     <row r="832" spans="5:5">
-      <c r="E832" s="51"/>
+      <c r="E832" s="50"/>
     </row>
     <row r="833" spans="5:5">
-      <c r="E833" s="51"/>
+      <c r="E833" s="50"/>
     </row>
     <row r="834" spans="5:5">
-      <c r="E834" s="51"/>
+      <c r="E834" s="50"/>
     </row>
     <row r="835" spans="5:5">
-      <c r="E835" s="51"/>
+      <c r="E835" s="50"/>
     </row>
     <row r="836" spans="5:5">
-      <c r="E836" s="51"/>
+      <c r="E836" s="50"/>
     </row>
     <row r="837" spans="5:5">
-      <c r="E837" s="51"/>
+      <c r="E837" s="50"/>
     </row>
     <row r="838" spans="5:5">
-      <c r="E838" s="51"/>
+      <c r="E838" s="50"/>
     </row>
     <row r="839" spans="5:5">
-      <c r="E839" s="51"/>
+      <c r="E839" s="50"/>
     </row>
     <row r="840" spans="5:5">
-      <c r="E840" s="51"/>
+      <c r="E840" s="50"/>
     </row>
     <row r="841" spans="5:5">
-      <c r="E841" s="51"/>
+      <c r="E841" s="50"/>
     </row>
     <row r="842" spans="5:5">
-      <c r="E842" s="51"/>
+      <c r="E842" s="50"/>
     </row>
     <row r="843" spans="5:5">
-      <c r="E843" s="51"/>
+      <c r="E843" s="50"/>
     </row>
     <row r="844" spans="5:5">
-      <c r="E844" s="51"/>
+      <c r="E844" s="50"/>
     </row>
     <row r="845" spans="5:5">
-      <c r="E845" s="51"/>
+      <c r="E845" s="50"/>
     </row>
     <row r="846" spans="5:5">
-      <c r="E846" s="51"/>
+      <c r="E846" s="50"/>
     </row>
     <row r="847" spans="5:5">
-      <c r="E847" s="51"/>
+      <c r="E847" s="50"/>
     </row>
     <row r="848" spans="5:5">
-      <c r="E848" s="51"/>
+      <c r="E848" s="50"/>
     </row>
     <row r="849" spans="5:5">
-      <c r="E849" s="51"/>
+      <c r="E849" s="50"/>
     </row>
     <row r="850" spans="5:5">
-      <c r="E850" s="51"/>
+      <c r="E850" s="50"/>
     </row>
     <row r="851" spans="5:5">
-      <c r="E851" s="51"/>
+      <c r="E851" s="50"/>
     </row>
     <row r="852" spans="5:5">
-      <c r="E852" s="51"/>
+      <c r="E852" s="50"/>
     </row>
     <row r="853" spans="5:5">
-      <c r="E853" s="51"/>
+      <c r="E853" s="50"/>
     </row>
     <row r="854" spans="5:5">
-      <c r="E854" s="51"/>
+      <c r="E854" s="50"/>
     </row>
     <row r="855" spans="5:5">
-      <c r="E855" s="51"/>
+      <c r="E855" s="50"/>
     </row>
     <row r="856" spans="5:5">
-      <c r="E856" s="51"/>
+      <c r="E856" s="50"/>
     </row>
     <row r="857" spans="5:5">
-      <c r="E857" s="51"/>
+      <c r="E857" s="50"/>
     </row>
     <row r="858" spans="5:5">
-      <c r="E858" s="51"/>
+      <c r="E858" s="50"/>
     </row>
     <row r="859" spans="5:5">
-      <c r="E859" s="51"/>
+      <c r="E859" s="50"/>
     </row>
     <row r="860" spans="5:5">
-      <c r="E860" s="51"/>
+      <c r="E860" s="50"/>
     </row>
     <row r="861" spans="5:5">
-      <c r="E861" s="51"/>
+      <c r="E861" s="50"/>
     </row>
     <row r="862" spans="5:5">
-      <c r="E862" s="51"/>
+      <c r="E862" s="50"/>
     </row>
     <row r="863" spans="5:5">
-      <c r="E863" s="51"/>
+      <c r="E863" s="50"/>
     </row>
     <row r="864" spans="5:5">
-      <c r="E864" s="51"/>
+      <c r="E864" s="50"/>
     </row>
     <row r="865" spans="5:5">
-      <c r="E865" s="51"/>
+      <c r="E865" s="50"/>
     </row>
     <row r="866" spans="5:5">
-      <c r="E866" s="51"/>
+      <c r="E866" s="50"/>
     </row>
     <row r="867" spans="5:5">
-      <c r="E867" s="51"/>
+      <c r="E867" s="50"/>
     </row>
     <row r="868" spans="5:5">
-      <c r="E868" s="51"/>
+      <c r="E868" s="50"/>
     </row>
     <row r="869" spans="5:5">
-      <c r="E869" s="51"/>
+      <c r="E869" s="50"/>
     </row>
     <row r="870" spans="5:5">
-      <c r="E870" s="51"/>
+      <c r="E870" s="50"/>
     </row>
     <row r="871" spans="5:5">
-      <c r="E871" s="51"/>
+      <c r="E871" s="50"/>
     </row>
     <row r="872" spans="5:5">
-      <c r="E872" s="51"/>
+      <c r="E872" s="50"/>
     </row>
     <row r="873" spans="5:5">
-      <c r="E873" s="51"/>
+      <c r="E873" s="50"/>
     </row>
     <row r="874" spans="5:5">
-      <c r="E874" s="51"/>
+      <c r="E874" s="50"/>
     </row>
     <row r="875" spans="5:5">
-      <c r="E875" s="51"/>
+      <c r="E875" s="50"/>
     </row>
     <row r="876" spans="5:5">
-      <c r="E876" s="51"/>
+      <c r="E876" s="50"/>
     </row>
     <row r="877" spans="5:5">
-      <c r="E877" s="51"/>
+      <c r="E877" s="50"/>
     </row>
     <row r="878" spans="5:5">
-      <c r="E878" s="51"/>
+      <c r="E878" s="50"/>
     </row>
     <row r="879" spans="5:5">
-      <c r="E879" s="51"/>
+      <c r="E879" s="50"/>
     </row>
     <row r="880" spans="5:5">
-      <c r="E880" s="51"/>
+      <c r="E880" s="50"/>
     </row>
     <row r="881" spans="5:5">
-      <c r="E881" s="51"/>
+      <c r="E881" s="50"/>
     </row>
     <row r="882" spans="5:5">
-      <c r="E882" s="51"/>
+      <c r="E882" s="50"/>
     </row>
     <row r="883" spans="5:5">
-      <c r="E883" s="51"/>
+      <c r="E883" s="50"/>
     </row>
     <row r="884" spans="5:5">
-      <c r="E884" s="51"/>
+      <c r="E884" s="50"/>
     </row>
     <row r="885" spans="5:5">
-      <c r="E885" s="51"/>
+      <c r="E885" s="50"/>
     </row>
     <row r="886" spans="5:5">
-      <c r="E886" s="51"/>
+      <c r="E886" s="50"/>
     </row>
     <row r="887" spans="5:5">
-      <c r="E887" s="51"/>
+      <c r="E887" s="50"/>
     </row>
     <row r="888" spans="5:5">
-      <c r="E888" s="51"/>
+      <c r="E888" s="50"/>
     </row>
     <row r="889" spans="5:5">
-      <c r="E889" s="51"/>
+      <c r="E889" s="50"/>
     </row>
     <row r="890" spans="5:5">
-      <c r="E890" s="51"/>
+      <c r="E890" s="50"/>
     </row>
     <row r="891" spans="5:5">
-      <c r="E891" s="51"/>
+      <c r="E891" s="50"/>
     </row>
     <row r="892" spans="5:5">
-      <c r="E892" s="51"/>
+      <c r="E892" s="50"/>
     </row>
     <row r="893" spans="5:5">
-      <c r="E893" s="51"/>
+      <c r="E893" s="50"/>
     </row>
     <row r="894" spans="5:5">
-      <c r="E894" s="51"/>
+      <c r="E894" s="50"/>
     </row>
     <row r="895" spans="5:5">
-      <c r="E895" s="51"/>
+      <c r="E895" s="50"/>
     </row>
     <row r="896" spans="5:5">
-      <c r="E896" s="51"/>
+      <c r="E896" s="50"/>
     </row>
     <row r="897" spans="5:5">
-      <c r="E897" s="51"/>
+      <c r="E897" s="50"/>
     </row>
     <row r="898" spans="5:5">
-      <c r="E898" s="51"/>
+      <c r="E898" s="50"/>
     </row>
     <row r="899" spans="5:5">
-      <c r="E899" s="51"/>
+      <c r="E899" s="50"/>
     </row>
     <row r="900" spans="5:5">
-      <c r="E900" s="51"/>
+      <c r="E900" s="50"/>
     </row>
     <row r="901" spans="5:5">
-      <c r="E901" s="51"/>
+      <c r="E901" s="50"/>
     </row>
     <row r="902" spans="5:5">
-      <c r="E902" s="51"/>
+      <c r="E902" s="50"/>
     </row>
     <row r="903" spans="5:5">
-      <c r="E903" s="51"/>
+      <c r="E903" s="50"/>
     </row>
     <row r="904" spans="5:5">
-      <c r="E904" s="51"/>
+      <c r="E904" s="50"/>
     </row>
     <row r="905" spans="5:5">
-      <c r="E905" s="51"/>
+      <c r="E905" s="50"/>
     </row>
     <row r="906" spans="5:5">
-      <c r="E906" s="51"/>
+      <c r="E906" s="50"/>
     </row>
     <row r="907" spans="5:5">
-      <c r="E907" s="51"/>
+      <c r="E907" s="50"/>
     </row>
     <row r="908" spans="5:5">
-      <c r="E908" s="51"/>
+      <c r="E908" s="50"/>
     </row>
     <row r="909" spans="5:5">
-      <c r="E909" s="51"/>
+      <c r="E909" s="50"/>
     </row>
     <row r="910" spans="5:5">
-      <c r="E910" s="51"/>
+      <c r="E910" s="50"/>
     </row>
     <row r="911" spans="5:5">
-      <c r="E911" s="51"/>
+      <c r="E911" s="50"/>
     </row>
     <row r="912" spans="5:5">
-      <c r="E912" s="51"/>
+      <c r="E912" s="50"/>
     </row>
     <row r="913" spans="5:5">
-      <c r="E913" s="51"/>
+      <c r="E913" s="50"/>
     </row>
     <row r="914" spans="5:5">
-      <c r="E914" s="51"/>
+      <c r="E914" s="50"/>
     </row>
     <row r="915" spans="5:5">
-      <c r="E915" s="51"/>
+      <c r="E915" s="50"/>
     </row>
     <row r="916" spans="5:5">
-      <c r="E916" s="51"/>
+      <c r="E916" s="50"/>
     </row>
     <row r="917" spans="5:5">
-      <c r="E917" s="51"/>
+      <c r="E917" s="50"/>
     </row>
     <row r="918" spans="5:5">
-      <c r="E918" s="51"/>
+      <c r="E918" s="50"/>
     </row>
     <row r="919" spans="5:5">
-      <c r="E919" s="51"/>
+      <c r="E919" s="50"/>
     </row>
     <row r="920" spans="5:5">
-      <c r="E920" s="51"/>
+      <c r="E920" s="50"/>
     </row>
     <row r="921" spans="5:5">
-      <c r="E921" s="51"/>
+      <c r="E921" s="50"/>
     </row>
     <row r="922" spans="5:5">
-      <c r="E922" s="51"/>
+      <c r="E922" s="50"/>
     </row>
     <row r="923" spans="5:5">
-      <c r="E923" s="51"/>
-    </row>
-    <row r="924" spans="5:5">
-      <c r="E924" s="51"/>
+      <c r="E923" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="R5:R1048576 A1:C1 J6:K1048576 F4:I5 F7:I1048576 L4:Q5 L7:Q1048576 S4:XFD5 S7:XFD1048576 B2:C2 D4:D5 D7:D1048576 B6:XFD6 D1:XFD2" xr:uid="{3E35FD98-5103-E048-AFDC-AE1DF54F7E72}"/>
-    <dataValidation allowBlank="1" prompt="Select an OCI Region." sqref="A2 A6" xr:uid="{9BA466B3-0978-E04D-8A8A-98064B94D465}"/>
+    <dataValidation allowBlank="1" sqref="A1:C1 J5:K1048576 S3:XFD4 F6:I1048576 L6:Q1048576 L3:P4 S6:XFD1048576 B2:C2 D1:XFD2 D6:D1048576 B5:XFD5 R5:R1048576 F3:I4" xr:uid="{3E35FD98-5103-E048-AFDC-AE1DF54F7E72}"/>
+    <dataValidation allowBlank="1" prompt="Select an OCI Region." sqref="A2 A5" xr:uid="{9BA466B3-0978-E04D-8A8A-98064B94D465}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -7762,20 +7839,19 @@
   <dimension ref="A1:Z998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" customWidth="1"/>
-    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="29.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.83203125" bestFit="1" customWidth="1"/>
@@ -7793,7 +7869,7 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" ht="195" customHeight="1">
       <c r="A1" s="63" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="64"/>
@@ -7813,71 +7889,71 @@
       <c r="Q1" s="64"/>
       <c r="R1" s="64"/>
       <c r="S1" s="64"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
-    </row>
-    <row r="2" spans="1:26" s="54" customFormat="1" ht="32">
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
+    </row>
+    <row r="2" spans="1:26" s="53" customFormat="1" ht="32">
       <c r="A2" s="47" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>524</v>
+        <v>479</v>
       </c>
       <c r="D2" s="48" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="E2" s="48" t="s">
+        <v>518</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>514</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>520</v>
+      </c>
+      <c r="H2" s="48" t="s">
+        <v>507</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>508</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>496</v>
+      </c>
+      <c r="K2" s="47" t="s">
+        <v>495</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>510</v>
+      </c>
+      <c r="M2" s="47" t="s">
+        <v>509</v>
+      </c>
+      <c r="N2" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="O2" s="47" t="s">
+        <v>512</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q2" s="47" t="s">
+        <v>497</v>
+      </c>
+      <c r="R2" s="47" t="s">
+        <v>498</v>
+      </c>
+      <c r="S2" s="52" t="s">
         <v>502</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>375</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>503</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>504</v>
-      </c>
-      <c r="I2" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="J2" s="47" t="s">
-        <v>505</v>
-      </c>
-      <c r="K2" s="47" t="s">
-        <v>506</v>
-      </c>
-      <c r="L2" s="47" t="s">
-        <v>507</v>
-      </c>
-      <c r="M2" s="47" t="s">
-        <v>508</v>
-      </c>
-      <c r="N2" s="47" t="s">
-        <v>509</v>
-      </c>
-      <c r="O2" s="47" t="s">
-        <v>510</v>
-      </c>
-      <c r="P2" s="47" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q2" s="47" t="s">
-        <v>512</v>
-      </c>
-      <c r="R2" s="47" t="s">
-        <v>513</v>
-      </c>
-      <c r="S2" s="53" t="s">
-        <v>462</v>
       </c>
       <c r="T2"/>
       <c r="U2"/>
@@ -7887,4265 +7963,2564 @@
       <c r="Y2"/>
       <c r="Z2"/>
     </row>
-    <row r="3" spans="1:26" ht="32">
-      <c r="A3" s="50" t="s">
-        <v>468</v>
+    <row r="3" spans="1:26" ht="281">
+      <c r="A3" s="24" t="s">
+        <v>515</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>492</v>
-      </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="38" t="s">
-        <v>514</v>
+        <v>537</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>524</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>470</v>
+        <v>534</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>516</v>
-      </c>
-      <c r="H3" s="24">
-        <v>4</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>225</v>
+        <v>530</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>532</v>
       </c>
       <c r="J3" s="38" t="s">
         <v>517</v>
       </c>
-      <c r="K3" s="38" t="s">
-        <v>518</v>
+      <c r="K3" s="38">
+        <v>88</v>
       </c>
       <c r="L3" s="38">
-        <v>914</v>
+        <v>200</v>
       </c>
       <c r="M3" s="38">
-        <v>1390</v>
+        <v>1300</v>
       </c>
       <c r="N3" s="38">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="O3" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" s="55" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="38" t="s">
-        <v>519</v>
-      </c>
-      <c r="R3" s="55" t="s">
-        <v>520</v>
+        <v>0</v>
+      </c>
+      <c r="P3" s="54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="60" t="s">
+        <v>526</v>
+      </c>
+      <c r="R3" s="54" t="s">
+        <v>527</v>
       </c>
       <c r="S3" s="25" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="G4" s="1"/>
+        <v>523</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="281">
+      <c r="A4" s="24" t="s">
+        <v>515</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>517</v>
+      </c>
+      <c r="K4" s="38">
+        <v>88</v>
+      </c>
+      <c r="L4" s="38">
+        <v>200</v>
+      </c>
+      <c r="M4" s="38">
+        <v>1300</v>
+      </c>
+      <c r="N4" s="38">
+        <v>87</v>
+      </c>
+      <c r="O4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="60" t="s">
+        <v>526</v>
+      </c>
+      <c r="R4" s="54" t="s">
+        <v>527</v>
+      </c>
+      <c r="S4" s="25" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="5" spans="1:26">
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:26">
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:26">
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:26">
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:26">
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:26">
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:26">
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:26">
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:26">
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:26">
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:26">
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="7:7">
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="7:7">
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="7:7">
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="7:7">
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="7:7">
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="7:7">
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="7:7">
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="7:7">
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="7:7">
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="7:7">
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="7:7">
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="7:7">
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="7:7">
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="7:7">
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="7:7">
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="7:7">
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="7:7">
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="7:7">
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="7:7">
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="7:7">
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="7:7">
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="7:7">
-      <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="7:7">
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="7:7">
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="7:7">
-      <c r="G41" s="1"/>
-    </row>
-    <row r="42" spans="7:7">
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="7:7">
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="7:7">
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="7:7">
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="7:7">
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="7:7">
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="7:7">
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="7:7">
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="7:7">
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="7:7">
-      <c r="G51" s="1"/>
-    </row>
-    <row r="52" spans="7:7">
-      <c r="G52" s="1"/>
-    </row>
-    <row r="53" spans="7:7">
-      <c r="G53" s="1"/>
-    </row>
-    <row r="54" spans="7:7">
-      <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="7:7">
-      <c r="G55" s="1"/>
-    </row>
-    <row r="56" spans="7:7">
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="7:7">
-      <c r="G57" s="1"/>
-    </row>
-    <row r="58" spans="7:7">
-      <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="7:7">
-      <c r="G59" s="1"/>
-    </row>
-    <row r="60" spans="7:7">
-      <c r="G60" s="1"/>
-    </row>
-    <row r="61" spans="7:7">
-      <c r="G61" s="1"/>
-    </row>
-    <row r="62" spans="7:7">
-      <c r="G62" s="1"/>
-    </row>
-    <row r="63" spans="7:7">
-      <c r="G63" s="1"/>
-    </row>
-    <row r="64" spans="7:7">
-      <c r="G64" s="1"/>
-    </row>
-    <row r="65" spans="7:7">
-      <c r="G65" s="1"/>
-    </row>
-    <row r="66" spans="7:7">
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="7:7">
-      <c r="G67" s="1"/>
-    </row>
-    <row r="68" spans="7:7">
-      <c r="G68" s="1"/>
-    </row>
-    <row r="69" spans="7:7">
-      <c r="G69" s="1"/>
-    </row>
-    <row r="70" spans="7:7">
-      <c r="G70" s="1"/>
-    </row>
-    <row r="71" spans="7:7">
-      <c r="G71" s="1"/>
-    </row>
-    <row r="72" spans="7:7">
-      <c r="G72" s="1"/>
-    </row>
-    <row r="73" spans="7:7">
-      <c r="G73" s="1"/>
-    </row>
-    <row r="74" spans="7:7">
-      <c r="G74" s="1"/>
-    </row>
-    <row r="75" spans="7:7">
-      <c r="G75" s="1"/>
-    </row>
-    <row r="76" spans="7:7">
-      <c r="G76" s="1"/>
-    </row>
-    <row r="77" spans="7:7">
-      <c r="G77" s="1"/>
-    </row>
-    <row r="78" spans="7:7">
-      <c r="G78" s="1"/>
-    </row>
-    <row r="79" spans="7:7">
-      <c r="G79" s="1"/>
-    </row>
-    <row r="80" spans="7:7">
-      <c r="G80" s="1"/>
-    </row>
-    <row r="81" spans="7:7">
-      <c r="G81" s="1"/>
-    </row>
-    <row r="82" spans="7:7">
-      <c r="G82" s="1"/>
-    </row>
-    <row r="83" spans="7:7">
-      <c r="G83" s="1"/>
-    </row>
-    <row r="84" spans="7:7">
-      <c r="G84" s="1"/>
-    </row>
-    <row r="85" spans="7:7">
-      <c r="G85" s="1"/>
-    </row>
-    <row r="86" spans="7:7">
-      <c r="G86" s="1"/>
-    </row>
-    <row r="87" spans="7:7">
-      <c r="G87" s="1"/>
-    </row>
-    <row r="88" spans="7:7">
-      <c r="G88" s="1"/>
-    </row>
-    <row r="89" spans="7:7">
-      <c r="G89" s="1"/>
-    </row>
-    <row r="90" spans="7:7">
-      <c r="G90" s="1"/>
-    </row>
-    <row r="91" spans="7:7">
-      <c r="G91" s="1"/>
-    </row>
-    <row r="92" spans="7:7">
-      <c r="G92" s="1"/>
-    </row>
-    <row r="93" spans="7:7">
-      <c r="G93" s="1"/>
-    </row>
-    <row r="94" spans="7:7">
-      <c r="G94" s="1"/>
-    </row>
-    <row r="95" spans="7:7">
-      <c r="G95" s="1"/>
-    </row>
-    <row r="96" spans="7:7">
-      <c r="G96" s="1"/>
-    </row>
-    <row r="97" spans="7:7">
-      <c r="G97" s="1"/>
-    </row>
-    <row r="98" spans="7:7">
-      <c r="G98" s="1"/>
-    </row>
-    <row r="99" spans="7:7">
-      <c r="G99" s="1"/>
-    </row>
-    <row r="100" spans="7:7">
-      <c r="G100" s="1"/>
-    </row>
-    <row r="101" spans="7:7">
-      <c r="G101" s="1"/>
-    </row>
-    <row r="102" spans="7:7">
-      <c r="G102" s="1"/>
-    </row>
-    <row r="103" spans="7:7">
-      <c r="G103" s="1"/>
-    </row>
-    <row r="104" spans="7:7">
-      <c r="G104" s="1"/>
-    </row>
-    <row r="105" spans="7:7">
-      <c r="G105" s="1"/>
-    </row>
-    <row r="106" spans="7:7">
-      <c r="G106" s="1"/>
-    </row>
-    <row r="107" spans="7:7">
-      <c r="G107" s="1"/>
-    </row>
-    <row r="108" spans="7:7">
-      <c r="G108" s="1"/>
-    </row>
-    <row r="109" spans="7:7">
-      <c r="G109" s="1"/>
-    </row>
-    <row r="110" spans="7:7">
-      <c r="G110" s="1"/>
-    </row>
-    <row r="111" spans="7:7">
-      <c r="G111" s="1"/>
-    </row>
-    <row r="112" spans="7:7">
-      <c r="G112" s="1"/>
-    </row>
-    <row r="113" spans="7:7">
-      <c r="G113" s="1"/>
-    </row>
-    <row r="114" spans="7:7">
-      <c r="G114" s="1"/>
-    </row>
-    <row r="115" spans="7:7">
-      <c r="G115" s="1"/>
-    </row>
-    <row r="116" spans="7:7">
-      <c r="G116" s="1"/>
-    </row>
-    <row r="117" spans="7:7">
-      <c r="G117" s="1"/>
-    </row>
-    <row r="118" spans="7:7">
-      <c r="G118" s="1"/>
-    </row>
-    <row r="119" spans="7:7">
-      <c r="G119" s="1"/>
-    </row>
-    <row r="120" spans="7:7">
-      <c r="G120" s="1"/>
-    </row>
-    <row r="121" spans="7:7">
-      <c r="G121" s="1"/>
-    </row>
-    <row r="122" spans="7:7">
-      <c r="G122" s="1"/>
-    </row>
-    <row r="123" spans="7:7">
-      <c r="G123" s="1"/>
-    </row>
-    <row r="124" spans="7:7">
-      <c r="G124" s="1"/>
-    </row>
-    <row r="125" spans="7:7">
-      <c r="G125" s="1"/>
-    </row>
-    <row r="126" spans="7:7">
-      <c r="G126" s="1"/>
-    </row>
-    <row r="127" spans="7:7">
-      <c r="G127" s="1"/>
-    </row>
-    <row r="128" spans="7:7">
-      <c r="G128" s="1"/>
-    </row>
-    <row r="129" spans="7:7">
-      <c r="G129" s="1"/>
-    </row>
-    <row r="130" spans="7:7">
-      <c r="G130" s="1"/>
-    </row>
-    <row r="131" spans="7:7">
-      <c r="G131" s="1"/>
-    </row>
-    <row r="132" spans="7:7">
-      <c r="G132" s="1"/>
-    </row>
-    <row r="133" spans="7:7">
-      <c r="G133" s="1"/>
-    </row>
-    <row r="134" spans="7:7">
-      <c r="G134" s="1"/>
-    </row>
-    <row r="135" spans="7:7">
-      <c r="G135" s="1"/>
-    </row>
-    <row r="136" spans="7:7">
-      <c r="G136" s="1"/>
-    </row>
-    <row r="137" spans="7:7">
-      <c r="G137" s="1"/>
-    </row>
-    <row r="138" spans="7:7">
-      <c r="G138" s="1"/>
-    </row>
-    <row r="139" spans="7:7">
-      <c r="G139" s="1"/>
-    </row>
-    <row r="140" spans="7:7">
-      <c r="G140" s="1"/>
-    </row>
-    <row r="141" spans="7:7">
-      <c r="G141" s="1"/>
-    </row>
-    <row r="142" spans="7:7">
-      <c r="G142" s="1"/>
-    </row>
-    <row r="143" spans="7:7">
-      <c r="G143" s="1"/>
-    </row>
-    <row r="144" spans="7:7">
-      <c r="G144" s="1"/>
-    </row>
-    <row r="145" spans="7:7">
-      <c r="G145" s="1"/>
-    </row>
-    <row r="146" spans="7:7">
-      <c r="G146" s="1"/>
-    </row>
-    <row r="147" spans="7:7">
-      <c r="G147" s="1"/>
-    </row>
-    <row r="148" spans="7:7">
-      <c r="G148" s="1"/>
-    </row>
-    <row r="149" spans="7:7">
-      <c r="G149" s="1"/>
-    </row>
-    <row r="150" spans="7:7">
-      <c r="G150" s="1"/>
-    </row>
-    <row r="151" spans="7:7">
-      <c r="G151" s="1"/>
-    </row>
-    <row r="152" spans="7:7">
-      <c r="G152" s="1"/>
-    </row>
-    <row r="153" spans="7:7">
-      <c r="G153" s="1"/>
-    </row>
-    <row r="154" spans="7:7">
-      <c r="G154" s="1"/>
-    </row>
-    <row r="155" spans="7:7">
-      <c r="G155" s="1"/>
-    </row>
-    <row r="156" spans="7:7">
-      <c r="G156" s="1"/>
-    </row>
-    <row r="157" spans="7:7">
-      <c r="G157" s="1"/>
-    </row>
-    <row r="158" spans="7:7">
-      <c r="G158" s="1"/>
-    </row>
-    <row r="159" spans="7:7">
-      <c r="G159" s="1"/>
-    </row>
-    <row r="160" spans="7:7">
-      <c r="G160" s="1"/>
-    </row>
-    <row r="161" spans="7:7">
-      <c r="G161" s="1"/>
-    </row>
-    <row r="162" spans="7:7">
-      <c r="G162" s="1"/>
-    </row>
-    <row r="163" spans="7:7">
-      <c r="G163" s="1"/>
-    </row>
-    <row r="164" spans="7:7">
-      <c r="G164" s="1"/>
-    </row>
-    <row r="165" spans="7:7">
-      <c r="G165" s="1"/>
-    </row>
-    <row r="166" spans="7:7">
-      <c r="G166" s="1"/>
-    </row>
-    <row r="167" spans="7:7">
-      <c r="G167" s="1"/>
-    </row>
-    <row r="168" spans="7:7">
-      <c r="G168" s="1"/>
-    </row>
-    <row r="169" spans="7:7">
-      <c r="G169" s="1"/>
-    </row>
-    <row r="170" spans="7:7">
-      <c r="G170" s="1"/>
-    </row>
-    <row r="171" spans="7:7">
-      <c r="G171" s="1"/>
-    </row>
-    <row r="172" spans="7:7">
-      <c r="G172" s="1"/>
-    </row>
-    <row r="173" spans="7:7">
-      <c r="G173" s="1"/>
-    </row>
-    <row r="174" spans="7:7">
-      <c r="G174" s="1"/>
-    </row>
-    <row r="175" spans="7:7">
-      <c r="G175" s="1"/>
-    </row>
-    <row r="176" spans="7:7">
-      <c r="G176" s="1"/>
-    </row>
-    <row r="177" spans="7:7">
-      <c r="G177" s="1"/>
-    </row>
-    <row r="178" spans="7:7">
-      <c r="G178" s="1"/>
-    </row>
-    <row r="179" spans="7:7">
-      <c r="G179" s="1"/>
-    </row>
-    <row r="180" spans="7:7">
-      <c r="G180" s="1"/>
-    </row>
-    <row r="181" spans="7:7">
-      <c r="G181" s="1"/>
-    </row>
-    <row r="182" spans="7:7">
-      <c r="G182" s="1"/>
-    </row>
-    <row r="183" spans="7:7">
-      <c r="G183" s="1"/>
-    </row>
-    <row r="184" spans="7:7">
-      <c r="G184" s="1"/>
-    </row>
-    <row r="185" spans="7:7">
-      <c r="G185" s="1"/>
-    </row>
-    <row r="186" spans="7:7">
-      <c r="G186" s="1"/>
-    </row>
-    <row r="187" spans="7:7">
-      <c r="G187" s="1"/>
-    </row>
-    <row r="188" spans="7:7">
-      <c r="G188" s="1"/>
-    </row>
-    <row r="189" spans="7:7">
-      <c r="G189" s="1"/>
-    </row>
-    <row r="190" spans="7:7">
-      <c r="G190" s="1"/>
-    </row>
-    <row r="191" spans="7:7">
-      <c r="G191" s="1"/>
-    </row>
-    <row r="192" spans="7:7">
-      <c r="G192" s="1"/>
-    </row>
-    <row r="193" spans="7:7">
-      <c r="G193" s="1"/>
-    </row>
-    <row r="194" spans="7:7">
-      <c r="G194" s="1"/>
-    </row>
-    <row r="195" spans="7:7">
-      <c r="G195" s="1"/>
-    </row>
-    <row r="196" spans="7:7">
-      <c r="G196" s="1"/>
-    </row>
-    <row r="197" spans="7:7">
-      <c r="G197" s="1"/>
-    </row>
-    <row r="198" spans="7:7">
-      <c r="G198" s="1"/>
-    </row>
-    <row r="199" spans="7:7">
-      <c r="G199" s="1"/>
-    </row>
-    <row r="200" spans="7:7">
-      <c r="G200" s="1"/>
-    </row>
-    <row r="201" spans="7:7">
-      <c r="G201" s="1"/>
-    </row>
-    <row r="202" spans="7:7">
-      <c r="G202" s="1"/>
-    </row>
-    <row r="203" spans="7:7">
-      <c r="G203" s="1"/>
-    </row>
-    <row r="204" spans="7:7">
-      <c r="G204" s="1"/>
-    </row>
-    <row r="205" spans="7:7">
-      <c r="G205" s="1"/>
-    </row>
-    <row r="206" spans="7:7">
-      <c r="G206" s="1"/>
-    </row>
-    <row r="207" spans="7:7">
-      <c r="G207" s="1"/>
-    </row>
-    <row r="208" spans="7:7">
-      <c r="G208" s="1"/>
-    </row>
-    <row r="209" spans="7:7">
-      <c r="G209" s="1"/>
-    </row>
-    <row r="210" spans="7:7">
-      <c r="G210" s="1"/>
-    </row>
-    <row r="211" spans="7:7">
-      <c r="G211" s="1"/>
-    </row>
-    <row r="212" spans="7:7">
-      <c r="G212" s="1"/>
-    </row>
-    <row r="213" spans="7:7">
-      <c r="G213" s="1"/>
-    </row>
-    <row r="214" spans="7:7">
-      <c r="G214" s="1"/>
-    </row>
-    <row r="215" spans="7:7">
-      <c r="G215" s="1"/>
-    </row>
-    <row r="216" spans="7:7">
-      <c r="G216" s="1"/>
-    </row>
-    <row r="217" spans="7:7">
-      <c r="G217" s="1"/>
-    </row>
-    <row r="218" spans="7:7">
-      <c r="G218" s="1"/>
-    </row>
-    <row r="219" spans="7:7">
-      <c r="G219" s="1"/>
-    </row>
-    <row r="220" spans="7:7">
-      <c r="G220" s="1"/>
-    </row>
-    <row r="221" spans="7:7">
-      <c r="G221" s="1"/>
-    </row>
-    <row r="222" spans="7:7">
-      <c r="G222" s="1"/>
-    </row>
-    <row r="223" spans="7:7">
-      <c r="G223" s="1"/>
-    </row>
-    <row r="224" spans="7:7">
-      <c r="G224" s="1"/>
-    </row>
-    <row r="225" spans="7:7">
-      <c r="G225" s="1"/>
-    </row>
-    <row r="226" spans="7:7">
-      <c r="G226" s="1"/>
-    </row>
-    <row r="227" spans="7:7">
-      <c r="G227" s="1"/>
-    </row>
-    <row r="228" spans="7:7">
-      <c r="G228" s="1"/>
-    </row>
-    <row r="229" spans="7:7">
-      <c r="G229" s="1"/>
-    </row>
-    <row r="230" spans="7:7">
-      <c r="G230" s="1"/>
-    </row>
-    <row r="231" spans="7:7">
-      <c r="G231" s="1"/>
-    </row>
-    <row r="232" spans="7:7">
-      <c r="G232" s="1"/>
-    </row>
-    <row r="233" spans="7:7">
-      <c r="G233" s="1"/>
-    </row>
-    <row r="234" spans="7:7">
-      <c r="G234" s="1"/>
-    </row>
-    <row r="235" spans="7:7">
-      <c r="G235" s="1"/>
-    </row>
-    <row r="236" spans="7:7">
-      <c r="G236" s="1"/>
-    </row>
-    <row r="237" spans="7:7">
-      <c r="G237" s="1"/>
-    </row>
-    <row r="238" spans="7:7">
-      <c r="G238" s="1"/>
-    </row>
-    <row r="239" spans="7:7">
-      <c r="G239" s="1"/>
-    </row>
-    <row r="240" spans="7:7">
-      <c r="G240" s="1"/>
-    </row>
-    <row r="241" spans="7:7">
-      <c r="G241" s="1"/>
-    </row>
-    <row r="242" spans="7:7">
-      <c r="G242" s="1"/>
-    </row>
-    <row r="243" spans="7:7">
-      <c r="G243" s="1"/>
-    </row>
-    <row r="244" spans="7:7">
-      <c r="G244" s="1"/>
-    </row>
-    <row r="245" spans="7:7">
-      <c r="G245" s="1"/>
-    </row>
-    <row r="246" spans="7:7">
-      <c r="G246" s="1"/>
-    </row>
-    <row r="247" spans="7:7">
-      <c r="G247" s="1"/>
-    </row>
-    <row r="248" spans="7:7">
-      <c r="G248" s="1"/>
-    </row>
-    <row r="249" spans="7:7">
-      <c r="G249" s="1"/>
-    </row>
-    <row r="250" spans="7:7">
-      <c r="G250" s="1"/>
-    </row>
-    <row r="251" spans="7:7">
-      <c r="G251" s="1"/>
-    </row>
-    <row r="252" spans="7:7">
-      <c r="G252" s="1"/>
-    </row>
-    <row r="253" spans="7:7">
-      <c r="G253" s="1"/>
-    </row>
-    <row r="254" spans="7:7">
-      <c r="G254" s="1"/>
-    </row>
-    <row r="255" spans="7:7">
-      <c r="G255" s="1"/>
-    </row>
-    <row r="256" spans="7:7">
-      <c r="G256" s="1"/>
-    </row>
-    <row r="257" spans="7:7">
-      <c r="G257" s="1"/>
-    </row>
-    <row r="258" spans="7:7">
-      <c r="G258" s="1"/>
-    </row>
-    <row r="259" spans="7:7">
-      <c r="G259" s="1"/>
-    </row>
-    <row r="260" spans="7:7">
-      <c r="G260" s="1"/>
-    </row>
-    <row r="261" spans="7:7">
-      <c r="G261" s="1"/>
-    </row>
-    <row r="262" spans="7:7">
-      <c r="G262" s="1"/>
-    </row>
-    <row r="263" spans="7:7">
-      <c r="G263" s="1"/>
-    </row>
-    <row r="264" spans="7:7">
-      <c r="G264" s="1"/>
-    </row>
-    <row r="265" spans="7:7">
-      <c r="G265" s="1"/>
-    </row>
-    <row r="266" spans="7:7">
-      <c r="G266" s="1"/>
-    </row>
-    <row r="267" spans="7:7">
-      <c r="G267" s="1"/>
-    </row>
-    <row r="268" spans="7:7">
-      <c r="G268" s="1"/>
-    </row>
-    <row r="269" spans="7:7">
-      <c r="G269" s="1"/>
-    </row>
-    <row r="270" spans="7:7">
-      <c r="G270" s="1"/>
-    </row>
-    <row r="271" spans="7:7">
-      <c r="G271" s="1"/>
-    </row>
-    <row r="272" spans="7:7">
-      <c r="G272" s="1"/>
-    </row>
-    <row r="273" spans="7:7">
-      <c r="G273" s="1"/>
-    </row>
-    <row r="274" spans="7:7">
-      <c r="G274" s="1"/>
-    </row>
-    <row r="275" spans="7:7">
-      <c r="G275" s="1"/>
-    </row>
-    <row r="276" spans="7:7">
-      <c r="G276" s="1"/>
-    </row>
-    <row r="277" spans="7:7">
-      <c r="G277" s="1"/>
-    </row>
-    <row r="278" spans="7:7">
-      <c r="G278" s="1"/>
-    </row>
-    <row r="279" spans="7:7">
-      <c r="G279" s="1"/>
-    </row>
-    <row r="280" spans="7:7">
-      <c r="G280" s="1"/>
-    </row>
-    <row r="281" spans="7:7">
-      <c r="G281" s="1"/>
-    </row>
-    <row r="282" spans="7:7">
-      <c r="G282" s="1"/>
-    </row>
-    <row r="283" spans="7:7">
-      <c r="G283" s="1"/>
-    </row>
-    <row r="284" spans="7:7">
-      <c r="G284" s="1"/>
-    </row>
-    <row r="285" spans="7:7">
-      <c r="G285" s="1"/>
-    </row>
-    <row r="286" spans="7:7">
-      <c r="G286" s="1"/>
-    </row>
-    <row r="287" spans="7:7">
-      <c r="G287" s="1"/>
-    </row>
-    <row r="288" spans="7:7">
-      <c r="G288" s="1"/>
-    </row>
-    <row r="289" spans="7:7">
-      <c r="G289" s="1"/>
-    </row>
-    <row r="290" spans="7:7">
-      <c r="G290" s="1"/>
-    </row>
-    <row r="291" spans="7:7">
-      <c r="G291" s="1"/>
-    </row>
-    <row r="292" spans="7:7">
-      <c r="G292" s="1"/>
-    </row>
-    <row r="293" spans="7:7">
-      <c r="G293" s="1"/>
-    </row>
-    <row r="294" spans="7:7">
-      <c r="G294" s="1"/>
-    </row>
-    <row r="295" spans="7:7">
-      <c r="G295" s="1"/>
-    </row>
-    <row r="296" spans="7:7">
-      <c r="G296" s="1"/>
-    </row>
-    <row r="297" spans="7:7">
-      <c r="G297" s="1"/>
-    </row>
-    <row r="298" spans="7:7">
-      <c r="G298" s="1"/>
-    </row>
-    <row r="299" spans="7:7">
-      <c r="G299" s="1"/>
-    </row>
-    <row r="300" spans="7:7">
-      <c r="G300" s="1"/>
-    </row>
-    <row r="301" spans="7:7">
-      <c r="G301" s="1"/>
-    </row>
-    <row r="302" spans="7:7">
-      <c r="G302" s="1"/>
-    </row>
-    <row r="303" spans="7:7">
-      <c r="G303" s="1"/>
-    </row>
-    <row r="304" spans="7:7">
-      <c r="G304" s="1"/>
-    </row>
-    <row r="305" spans="7:7">
-      <c r="G305" s="1"/>
-    </row>
-    <row r="306" spans="7:7">
-      <c r="G306" s="1"/>
-    </row>
-    <row r="307" spans="7:7">
-      <c r="G307" s="1"/>
-    </row>
-    <row r="308" spans="7:7">
-      <c r="G308" s="1"/>
-    </row>
-    <row r="309" spans="7:7">
-      <c r="G309" s="1"/>
-    </row>
-    <row r="310" spans="7:7">
-      <c r="G310" s="1"/>
-    </row>
-    <row r="311" spans="7:7">
-      <c r="G311" s="1"/>
-    </row>
-    <row r="312" spans="7:7">
-      <c r="G312" s="1"/>
-    </row>
-    <row r="313" spans="7:7">
-      <c r="G313" s="1"/>
-    </row>
-    <row r="314" spans="7:7">
-      <c r="G314" s="1"/>
-    </row>
-    <row r="315" spans="7:7">
-      <c r="G315" s="1"/>
-    </row>
-    <row r="316" spans="7:7">
-      <c r="G316" s="1"/>
-    </row>
-    <row r="317" spans="7:7">
-      <c r="G317" s="1"/>
-    </row>
-    <row r="318" spans="7:7">
-      <c r="G318" s="1"/>
-    </row>
-    <row r="319" spans="7:7">
-      <c r="G319" s="1"/>
-    </row>
-    <row r="320" spans="7:7">
-      <c r="G320" s="1"/>
-    </row>
-    <row r="321" spans="7:7">
-      <c r="G321" s="1"/>
-    </row>
-    <row r="322" spans="7:7">
-      <c r="G322" s="1"/>
-    </row>
-    <row r="323" spans="7:7">
-      <c r="G323" s="1"/>
-    </row>
-    <row r="324" spans="7:7">
-      <c r="G324" s="1"/>
-    </row>
-    <row r="325" spans="7:7">
-      <c r="G325" s="1"/>
-    </row>
-    <row r="326" spans="7:7">
-      <c r="G326" s="1"/>
-    </row>
-    <row r="327" spans="7:7">
-      <c r="G327" s="1"/>
-    </row>
-    <row r="328" spans="7:7">
-      <c r="G328" s="1"/>
-    </row>
-    <row r="329" spans="7:7">
-      <c r="G329" s="1"/>
-    </row>
-    <row r="330" spans="7:7">
-      <c r="G330" s="1"/>
-    </row>
-    <row r="331" spans="7:7">
-      <c r="G331" s="1"/>
-    </row>
-    <row r="332" spans="7:7">
-      <c r="G332" s="1"/>
-    </row>
-    <row r="333" spans="7:7">
-      <c r="G333" s="1"/>
-    </row>
-    <row r="334" spans="7:7">
-      <c r="G334" s="1"/>
-    </row>
-    <row r="335" spans="7:7">
-      <c r="G335" s="1"/>
-    </row>
-    <row r="336" spans="7:7">
-      <c r="G336" s="1"/>
-    </row>
-    <row r="337" spans="7:7">
-      <c r="G337" s="1"/>
-    </row>
-    <row r="338" spans="7:7">
-      <c r="G338" s="1"/>
-    </row>
-    <row r="339" spans="7:7">
-      <c r="G339" s="1"/>
-    </row>
-    <row r="340" spans="7:7">
-      <c r="G340" s="1"/>
-    </row>
-    <row r="341" spans="7:7">
-      <c r="G341" s="1"/>
-    </row>
-    <row r="342" spans="7:7">
-      <c r="G342" s="1"/>
-    </row>
-    <row r="343" spans="7:7">
-      <c r="G343" s="1"/>
-    </row>
-    <row r="344" spans="7:7">
-      <c r="G344" s="1"/>
-    </row>
-    <row r="345" spans="7:7">
-      <c r="G345" s="1"/>
-    </row>
-    <row r="346" spans="7:7">
-      <c r="G346" s="1"/>
-    </row>
-    <row r="347" spans="7:7">
-      <c r="G347" s="1"/>
-    </row>
-    <row r="348" spans="7:7">
-      <c r="G348" s="1"/>
-    </row>
-    <row r="349" spans="7:7">
-      <c r="G349" s="1"/>
-    </row>
-    <row r="350" spans="7:7">
-      <c r="G350" s="1"/>
-    </row>
-    <row r="351" spans="7:7">
-      <c r="G351" s="1"/>
-    </row>
-    <row r="352" spans="7:7">
-      <c r="G352" s="1"/>
-    </row>
-    <row r="353" spans="7:7">
-      <c r="G353" s="1"/>
-    </row>
-    <row r="354" spans="7:7">
-      <c r="G354" s="1"/>
-    </row>
-    <row r="355" spans="7:7">
-      <c r="G355" s="1"/>
-    </row>
-    <row r="356" spans="7:7">
-      <c r="G356" s="1"/>
-    </row>
-    <row r="357" spans="7:7">
-      <c r="G357" s="1"/>
-    </row>
-    <row r="358" spans="7:7">
-      <c r="G358" s="1"/>
-    </row>
-    <row r="359" spans="7:7">
-      <c r="G359" s="1"/>
-    </row>
-    <row r="360" spans="7:7">
-      <c r="G360" s="1"/>
-    </row>
-    <row r="361" spans="7:7">
-      <c r="G361" s="1"/>
-    </row>
-    <row r="362" spans="7:7">
-      <c r="G362" s="1"/>
-    </row>
-    <row r="363" spans="7:7">
-      <c r="G363" s="1"/>
-    </row>
-    <row r="364" spans="7:7">
-      <c r="G364" s="1"/>
-    </row>
-    <row r="365" spans="7:7">
-      <c r="G365" s="1"/>
-    </row>
-    <row r="366" spans="7:7">
-      <c r="G366" s="1"/>
-    </row>
-    <row r="367" spans="7:7">
-      <c r="G367" s="1"/>
-    </row>
-    <row r="368" spans="7:7">
-      <c r="G368" s="1"/>
-    </row>
-    <row r="369" spans="7:7">
-      <c r="G369" s="1"/>
-    </row>
-    <row r="370" spans="7:7">
-      <c r="G370" s="1"/>
-    </row>
-    <row r="371" spans="7:7">
-      <c r="G371" s="1"/>
-    </row>
-    <row r="372" spans="7:7">
-      <c r="G372" s="1"/>
-    </row>
-    <row r="373" spans="7:7">
-      <c r="G373" s="1"/>
-    </row>
-    <row r="374" spans="7:7">
-      <c r="G374" s="1"/>
-    </row>
-    <row r="375" spans="7:7">
-      <c r="G375" s="1"/>
-    </row>
-    <row r="376" spans="7:7">
-      <c r="G376" s="1"/>
-    </row>
-    <row r="377" spans="7:7">
-      <c r="G377" s="1"/>
-    </row>
-    <row r="378" spans="7:7">
-      <c r="G378" s="1"/>
-    </row>
-    <row r="379" spans="7:7">
-      <c r="G379" s="1"/>
-    </row>
-    <row r="380" spans="7:7">
-      <c r="G380" s="1"/>
-    </row>
-    <row r="381" spans="7:7">
-      <c r="G381" s="1"/>
-    </row>
-    <row r="382" spans="7:7">
-      <c r="G382" s="1"/>
-    </row>
-    <row r="383" spans="7:7">
-      <c r="G383" s="1"/>
-    </row>
-    <row r="384" spans="7:7">
-      <c r="G384" s="1"/>
-    </row>
-    <row r="385" spans="2:7">
-      <c r="G385" s="1"/>
-    </row>
-    <row r="386" spans="2:7">
-      <c r="G386" s="1"/>
-    </row>
-    <row r="387" spans="2:7">
-      <c r="G387" s="1"/>
-    </row>
-    <row r="388" spans="2:7">
-      <c r="G388" s="1"/>
-    </row>
-    <row r="389" spans="2:7">
-      <c r="B389" s="2"/>
+      <c r="F5"/>
+    </row>
+    <row r="389" spans="6:7">
       <c r="F389" s="10"/>
       <c r="G389" s="10"/>
     </row>
-    <row r="390" spans="2:7">
-      <c r="B390" s="18"/>
+    <row r="390" spans="6:7">
       <c r="F390" s="17"/>
       <c r="G390" s="17"/>
     </row>
-    <row r="391" spans="2:7">
-      <c r="B391" s="18"/>
+    <row r="391" spans="6:7">
       <c r="F391" s="17"/>
       <c r="G391" s="17"/>
     </row>
-    <row r="392" spans="2:7">
-      <c r="B392" s="18"/>
+    <row r="392" spans="6:7">
       <c r="F392" s="17"/>
       <c r="G392" s="17"/>
     </row>
-    <row r="393" spans="2:7">
-      <c r="B393" s="18"/>
+    <row r="393" spans="6:7">
       <c r="F393" s="17"/>
       <c r="G393" s="17"/>
     </row>
-    <row r="394" spans="2:7">
-      <c r="B394" s="18"/>
+    <row r="394" spans="6:7">
       <c r="F394" s="17"/>
       <c r="G394" s="17"/>
     </row>
-    <row r="395" spans="2:7">
-      <c r="B395" s="18"/>
+    <row r="395" spans="6:7">
       <c r="F395" s="17"/>
       <c r="G395" s="17"/>
     </row>
-    <row r="396" spans="2:7">
-      <c r="B396" s="18"/>
+    <row r="396" spans="6:7">
       <c r="F396" s="17"/>
       <c r="G396" s="17"/>
     </row>
-    <row r="397" spans="2:7">
-      <c r="B397" s="18"/>
+    <row r="397" spans="6:7">
       <c r="F397" s="17"/>
       <c r="G397" s="17"/>
     </row>
-    <row r="398" spans="2:7">
-      <c r="B398" s="18"/>
+    <row r="398" spans="6:7">
       <c r="F398" s="17"/>
       <c r="G398" s="17"/>
     </row>
-    <row r="399" spans="2:7">
-      <c r="B399" s="18"/>
+    <row r="399" spans="6:7">
       <c r="F399" s="17"/>
       <c r="G399" s="17"/>
     </row>
-    <row r="400" spans="2:7">
-      <c r="B400" s="18"/>
+    <row r="400" spans="6:7">
       <c r="F400" s="17"/>
       <c r="G400" s="17"/>
     </row>
-    <row r="401" spans="2:7">
-      <c r="B401" s="18"/>
+    <row r="401" spans="6:7">
       <c r="F401" s="17"/>
       <c r="G401" s="17"/>
     </row>
-    <row r="402" spans="2:7">
-      <c r="B402" s="18"/>
+    <row r="402" spans="6:7">
       <c r="F402" s="17"/>
       <c r="G402" s="17"/>
     </row>
-    <row r="403" spans="2:7">
-      <c r="B403" s="18"/>
+    <row r="403" spans="6:7">
       <c r="F403" s="17"/>
       <c r="G403" s="17"/>
     </row>
-    <row r="404" spans="2:7">
-      <c r="B404" s="18"/>
+    <row r="404" spans="6:7">
       <c r="F404" s="17"/>
       <c r="G404" s="17"/>
     </row>
-    <row r="405" spans="2:7">
-      <c r="B405" s="18"/>
+    <row r="405" spans="6:7">
       <c r="F405" s="17"/>
       <c r="G405" s="17"/>
     </row>
-    <row r="406" spans="2:7">
-      <c r="B406" s="18"/>
+    <row r="406" spans="6:7">
       <c r="F406" s="17"/>
       <c r="G406" s="17"/>
     </row>
-    <row r="407" spans="2:7">
-      <c r="B407" s="18"/>
+    <row r="407" spans="6:7">
       <c r="F407" s="17"/>
       <c r="G407" s="17"/>
     </row>
-    <row r="408" spans="2:7">
-      <c r="B408" s="18"/>
+    <row r="408" spans="6:7">
       <c r="F408" s="17"/>
       <c r="G408" s="17"/>
     </row>
-    <row r="409" spans="2:7">
-      <c r="B409" s="18"/>
+    <row r="409" spans="6:7">
       <c r="F409" s="17"/>
       <c r="G409" s="17"/>
     </row>
-    <row r="410" spans="2:7">
-      <c r="B410" s="18"/>
+    <row r="410" spans="6:7">
       <c r="F410" s="17"/>
       <c r="G410" s="17"/>
     </row>
-    <row r="411" spans="2:7">
-      <c r="B411" s="18"/>
+    <row r="411" spans="6:7">
       <c r="F411" s="17"/>
       <c r="G411" s="17"/>
     </row>
-    <row r="412" spans="2:7">
-      <c r="B412" s="18"/>
+    <row r="412" spans="6:7">
       <c r="F412" s="17"/>
       <c r="G412" s="17"/>
     </row>
-    <row r="413" spans="2:7">
-      <c r="B413" s="18"/>
+    <row r="413" spans="6:7">
       <c r="F413" s="17"/>
       <c r="G413" s="17"/>
     </row>
-    <row r="414" spans="2:7">
-      <c r="B414" s="18"/>
+    <row r="414" spans="6:7">
       <c r="F414" s="17"/>
       <c r="G414" s="17"/>
     </row>
-    <row r="415" spans="2:7">
-      <c r="B415" s="18"/>
+    <row r="415" spans="6:7">
       <c r="F415" s="17"/>
       <c r="G415" s="17"/>
     </row>
-    <row r="416" spans="2:7">
-      <c r="B416" s="18"/>
+    <row r="416" spans="6:7">
       <c r="F416" s="17"/>
       <c r="G416" s="17"/>
     </row>
-    <row r="417" spans="2:7">
-      <c r="B417" s="18"/>
+    <row r="417" spans="6:7">
       <c r="F417" s="17"/>
       <c r="G417" s="17"/>
     </row>
-    <row r="418" spans="2:7">
-      <c r="B418" s="18"/>
+    <row r="418" spans="6:7">
       <c r="F418" s="17"/>
       <c r="G418" s="17"/>
     </row>
-    <row r="419" spans="2:7">
-      <c r="B419" s="18"/>
+    <row r="419" spans="6:7">
       <c r="F419" s="17"/>
       <c r="G419" s="17"/>
     </row>
-    <row r="420" spans="2:7">
-      <c r="B420" s="18"/>
+    <row r="420" spans="6:7">
       <c r="F420" s="17"/>
       <c r="G420" s="17"/>
     </row>
-    <row r="421" spans="2:7">
-      <c r="B421" s="18"/>
+    <row r="421" spans="6:7">
       <c r="F421" s="17"/>
       <c r="G421" s="17"/>
     </row>
-    <row r="422" spans="2:7">
-      <c r="B422" s="18"/>
+    <row r="422" spans="6:7">
       <c r="F422" s="17"/>
       <c r="G422" s="17"/>
     </row>
-    <row r="423" spans="2:7">
-      <c r="B423" s="18"/>
+    <row r="423" spans="6:7">
       <c r="F423" s="17"/>
       <c r="G423" s="17"/>
     </row>
-    <row r="424" spans="2:7">
-      <c r="B424" s="18"/>
+    <row r="424" spans="6:7">
       <c r="F424" s="17"/>
       <c r="G424" s="17"/>
     </row>
-    <row r="425" spans="2:7">
-      <c r="B425" s="18"/>
+    <row r="425" spans="6:7">
       <c r="F425" s="17"/>
       <c r="G425" s="17"/>
     </row>
-    <row r="426" spans="2:7">
-      <c r="B426" s="18"/>
+    <row r="426" spans="6:7">
       <c r="F426" s="17"/>
       <c r="G426" s="17"/>
     </row>
-    <row r="427" spans="2:7">
-      <c r="B427" s="18"/>
+    <row r="427" spans="6:7">
       <c r="F427" s="17"/>
       <c r="G427" s="17"/>
     </row>
-    <row r="428" spans="2:7">
-      <c r="B428" s="18"/>
+    <row r="428" spans="6:7">
       <c r="F428" s="17"/>
       <c r="G428" s="17"/>
     </row>
-    <row r="429" spans="2:7">
-      <c r="B429" s="18"/>
+    <row r="429" spans="6:7">
       <c r="F429" s="17"/>
       <c r="G429" s="17"/>
     </row>
-    <row r="430" spans="2:7">
-      <c r="B430" s="18"/>
+    <row r="430" spans="6:7">
       <c r="F430" s="17"/>
       <c r="G430" s="17"/>
     </row>
-    <row r="431" spans="2:7">
-      <c r="B431" s="18"/>
+    <row r="431" spans="6:7">
       <c r="F431" s="17"/>
       <c r="G431" s="17"/>
     </row>
-    <row r="432" spans="2:7">
-      <c r="B432" s="18"/>
+    <row r="432" spans="6:7">
       <c r="F432" s="17"/>
       <c r="G432" s="17"/>
     </row>
-    <row r="433" spans="2:7">
-      <c r="B433" s="18"/>
+    <row r="433" spans="6:7">
       <c r="F433" s="17"/>
       <c r="G433" s="17"/>
     </row>
-    <row r="434" spans="2:7">
-      <c r="B434" s="18"/>
+    <row r="434" spans="6:7">
       <c r="F434" s="17"/>
       <c r="G434" s="17"/>
     </row>
-    <row r="435" spans="2:7">
-      <c r="B435" s="18"/>
+    <row r="435" spans="6:7">
       <c r="F435" s="17"/>
       <c r="G435" s="17"/>
     </row>
-    <row r="436" spans="2:7">
-      <c r="B436" s="18"/>
+    <row r="436" spans="6:7">
       <c r="F436" s="17"/>
       <c r="G436" s="17"/>
     </row>
-    <row r="437" spans="2:7">
-      <c r="B437" s="18"/>
+    <row r="437" spans="6:7">
       <c r="F437" s="17"/>
       <c r="G437" s="17"/>
     </row>
-    <row r="438" spans="2:7">
-      <c r="B438" s="18"/>
+    <row r="438" spans="6:7">
       <c r="F438" s="17"/>
       <c r="G438" s="17"/>
     </row>
-    <row r="439" spans="2:7">
-      <c r="B439" s="18"/>
+    <row r="439" spans="6:7">
       <c r="F439" s="17"/>
       <c r="G439" s="17"/>
     </row>
-    <row r="440" spans="2:7">
-      <c r="B440" s="18"/>
+    <row r="440" spans="6:7">
       <c r="F440" s="17"/>
       <c r="G440" s="17"/>
     </row>
-    <row r="441" spans="2:7">
-      <c r="B441" s="18"/>
+    <row r="441" spans="6:7">
       <c r="F441" s="17"/>
       <c r="G441" s="17"/>
     </row>
-    <row r="442" spans="2:7">
-      <c r="B442" s="18"/>
+    <row r="442" spans="6:7">
       <c r="F442" s="17"/>
       <c r="G442" s="17"/>
     </row>
-    <row r="443" spans="2:7">
-      <c r="B443" s="18"/>
+    <row r="443" spans="6:7">
       <c r="F443" s="17"/>
       <c r="G443" s="17"/>
     </row>
-    <row r="444" spans="2:7">
-      <c r="B444" s="18"/>
+    <row r="444" spans="6:7">
       <c r="F444" s="17"/>
       <c r="G444" s="17"/>
     </row>
-    <row r="445" spans="2:7">
-      <c r="B445" s="18"/>
+    <row r="445" spans="6:7">
       <c r="F445" s="17"/>
       <c r="G445" s="17"/>
     </row>
-    <row r="446" spans="2:7">
-      <c r="B446" s="18"/>
+    <row r="446" spans="6:7">
       <c r="F446" s="17"/>
       <c r="G446" s="17"/>
     </row>
-    <row r="447" spans="2:7">
-      <c r="B447" s="18"/>
+    <row r="447" spans="6:7">
       <c r="F447" s="17"/>
       <c r="G447" s="17"/>
     </row>
-    <row r="448" spans="2:7">
-      <c r="B448" s="18"/>
+    <row r="448" spans="6:7">
       <c r="F448" s="17"/>
       <c r="G448" s="17"/>
     </row>
-    <row r="449" spans="2:7">
-      <c r="B449" s="18"/>
+    <row r="449" spans="6:7">
       <c r="F449" s="17"/>
       <c r="G449" s="17"/>
     </row>
-    <row r="450" spans="2:7">
-      <c r="B450" s="18"/>
+    <row r="450" spans="6:7">
       <c r="F450" s="17"/>
       <c r="G450" s="17"/>
     </row>
-    <row r="451" spans="2:7">
-      <c r="B451" s="18"/>
+    <row r="451" spans="6:7">
       <c r="F451" s="17"/>
       <c r="G451" s="17"/>
     </row>
-    <row r="452" spans="2:7">
-      <c r="B452" s="18"/>
+    <row r="452" spans="6:7">
       <c r="F452" s="17"/>
       <c r="G452" s="17"/>
     </row>
-    <row r="453" spans="2:7">
-      <c r="B453" s="18"/>
+    <row r="453" spans="6:7">
       <c r="F453" s="17"/>
       <c r="G453" s="17"/>
     </row>
-    <row r="454" spans="2:7">
-      <c r="B454" s="18"/>
+    <row r="454" spans="6:7">
       <c r="F454" s="17"/>
       <c r="G454" s="17"/>
     </row>
-    <row r="455" spans="2:7">
-      <c r="B455" s="18"/>
+    <row r="455" spans="6:7">
       <c r="F455" s="17"/>
       <c r="G455" s="17"/>
     </row>
-    <row r="456" spans="2:7">
-      <c r="B456" s="18"/>
+    <row r="456" spans="6:7">
       <c r="F456" s="17"/>
       <c r="G456" s="17"/>
     </row>
-    <row r="457" spans="2:7">
-      <c r="B457" s="18"/>
+    <row r="457" spans="6:7">
       <c r="F457" s="17"/>
       <c r="G457" s="17"/>
     </row>
-    <row r="458" spans="2:7">
-      <c r="B458" s="18"/>
+    <row r="458" spans="6:7">
       <c r="F458" s="17"/>
       <c r="G458" s="17"/>
     </row>
-    <row r="459" spans="2:7">
-      <c r="B459" s="18"/>
+    <row r="459" spans="6:7">
       <c r="F459" s="17"/>
       <c r="G459" s="17"/>
     </row>
-    <row r="460" spans="2:7">
-      <c r="B460" s="18"/>
+    <row r="460" spans="6:7">
       <c r="F460" s="17"/>
       <c r="G460" s="17"/>
     </row>
-    <row r="461" spans="2:7">
-      <c r="B461" s="18"/>
+    <row r="461" spans="6:7">
       <c r="F461" s="17"/>
       <c r="G461" s="17"/>
     </row>
-    <row r="462" spans="2:7">
-      <c r="B462" s="18"/>
+    <row r="462" spans="6:7">
       <c r="F462" s="17"/>
       <c r="G462" s="17"/>
     </row>
-    <row r="463" spans="2:7">
-      <c r="B463" s="18"/>
+    <row r="463" spans="6:7">
       <c r="F463" s="17"/>
       <c r="G463" s="17"/>
     </row>
-    <row r="464" spans="2:7">
-      <c r="B464" s="18"/>
+    <row r="464" spans="6:7">
       <c r="F464" s="17"/>
       <c r="G464" s="17"/>
     </row>
-    <row r="465" spans="2:7">
-      <c r="B465" s="18"/>
+    <row r="465" spans="6:7">
       <c r="F465" s="17"/>
       <c r="G465" s="17"/>
     </row>
-    <row r="466" spans="2:7">
-      <c r="B466" s="18"/>
+    <row r="466" spans="6:7">
       <c r="F466" s="17"/>
       <c r="G466" s="17"/>
     </row>
-    <row r="467" spans="2:7">
-      <c r="B467" s="18"/>
+    <row r="467" spans="6:7">
       <c r="F467" s="17"/>
       <c r="G467" s="17"/>
     </row>
-    <row r="468" spans="2:7">
-      <c r="B468" s="18"/>
+    <row r="468" spans="6:7">
       <c r="F468" s="17"/>
       <c r="G468" s="17"/>
     </row>
-    <row r="469" spans="2:7">
-      <c r="B469" s="18"/>
+    <row r="469" spans="6:7">
       <c r="F469" s="17"/>
       <c r="G469" s="17"/>
     </row>
-    <row r="470" spans="2:7">
-      <c r="B470" s="18"/>
+    <row r="470" spans="6:7">
       <c r="F470" s="17"/>
       <c r="G470" s="17"/>
     </row>
-    <row r="471" spans="2:7">
-      <c r="B471" s="18"/>
+    <row r="471" spans="6:7">
       <c r="F471" s="17"/>
       <c r="G471" s="17"/>
     </row>
-    <row r="472" spans="2:7">
-      <c r="B472" s="18"/>
+    <row r="472" spans="6:7">
       <c r="F472" s="17"/>
       <c r="G472" s="17"/>
     </row>
-    <row r="473" spans="2:7">
-      <c r="B473" s="18"/>
+    <row r="473" spans="6:7">
       <c r="F473" s="17"/>
       <c r="G473" s="17"/>
     </row>
-    <row r="474" spans="2:7">
-      <c r="B474" s="18"/>
+    <row r="474" spans="6:7">
       <c r="F474" s="17"/>
       <c r="G474" s="17"/>
     </row>
-    <row r="475" spans="2:7">
-      <c r="B475" s="18"/>
+    <row r="475" spans="6:7">
       <c r="F475" s="17"/>
       <c r="G475" s="17"/>
     </row>
-    <row r="476" spans="2:7">
-      <c r="B476" s="18"/>
+    <row r="476" spans="6:7">
       <c r="F476" s="17"/>
       <c r="G476" s="17"/>
     </row>
-    <row r="477" spans="2:7">
-      <c r="B477" s="18"/>
+    <row r="477" spans="6:7">
       <c r="F477" s="17"/>
       <c r="G477" s="17"/>
     </row>
-    <row r="478" spans="2:7">
-      <c r="B478" s="18"/>
+    <row r="478" spans="6:7">
       <c r="F478" s="17"/>
       <c r="G478" s="17"/>
     </row>
-    <row r="479" spans="2:7">
-      <c r="B479" s="18"/>
+    <row r="479" spans="6:7">
       <c r="F479" s="17"/>
       <c r="G479" s="17"/>
     </row>
-    <row r="480" spans="2:7">
-      <c r="B480" s="18"/>
+    <row r="480" spans="6:7">
       <c r="F480" s="17"/>
       <c r="G480" s="17"/>
     </row>
-    <row r="481" spans="2:7">
-      <c r="B481" s="18"/>
+    <row r="481" spans="6:7">
       <c r="F481" s="17"/>
       <c r="G481" s="17"/>
     </row>
-    <row r="482" spans="2:7">
-      <c r="B482" s="18"/>
+    <row r="482" spans="6:7">
       <c r="F482" s="17"/>
       <c r="G482" s="17"/>
     </row>
-    <row r="483" spans="2:7">
-      <c r="B483" s="18"/>
+    <row r="483" spans="6:7">
       <c r="F483" s="17"/>
       <c r="G483" s="17"/>
     </row>
-    <row r="484" spans="2:7">
-      <c r="B484" s="18"/>
+    <row r="484" spans="6:7">
       <c r="F484" s="17"/>
       <c r="G484" s="17"/>
     </row>
-    <row r="485" spans="2:7">
-      <c r="B485" s="18"/>
+    <row r="485" spans="6:7">
       <c r="F485" s="17"/>
       <c r="G485" s="17"/>
     </row>
-    <row r="486" spans="2:7">
-      <c r="B486" s="18"/>
+    <row r="486" spans="6:7">
       <c r="F486" s="17"/>
       <c r="G486" s="17"/>
     </row>
-    <row r="487" spans="2:7">
-      <c r="B487" s="18"/>
+    <row r="487" spans="6:7">
       <c r="F487" s="17"/>
       <c r="G487" s="17"/>
     </row>
-    <row r="488" spans="2:7">
-      <c r="B488" s="18"/>
+    <row r="488" spans="6:7">
       <c r="F488" s="17"/>
       <c r="G488" s="17"/>
     </row>
-    <row r="489" spans="2:7">
-      <c r="B489" s="18"/>
+    <row r="489" spans="6:7">
       <c r="F489" s="17"/>
       <c r="G489" s="17"/>
     </row>
-    <row r="490" spans="2:7">
-      <c r="B490" s="18"/>
+    <row r="490" spans="6:7">
       <c r="F490" s="17"/>
       <c r="G490" s="17"/>
     </row>
-    <row r="491" spans="2:7">
-      <c r="B491" s="18"/>
+    <row r="491" spans="6:7">
       <c r="F491" s="17"/>
       <c r="G491" s="17"/>
     </row>
-    <row r="492" spans="2:7">
-      <c r="B492" s="18"/>
+    <row r="492" spans="6:7">
       <c r="F492" s="17"/>
       <c r="G492" s="17"/>
     </row>
-    <row r="493" spans="2:7">
-      <c r="B493" s="18"/>
+    <row r="493" spans="6:7">
       <c r="F493" s="17"/>
       <c r="G493" s="17"/>
     </row>
-    <row r="494" spans="2:7">
-      <c r="B494" s="18"/>
+    <row r="494" spans="6:7">
       <c r="F494" s="17"/>
       <c r="G494" s="17"/>
     </row>
-    <row r="495" spans="2:7">
-      <c r="B495" s="18"/>
+    <row r="495" spans="6:7">
       <c r="F495" s="17"/>
       <c r="G495" s="17"/>
     </row>
-    <row r="496" spans="2:7">
-      <c r="B496" s="18"/>
+    <row r="496" spans="6:7">
       <c r="F496" s="17"/>
       <c r="G496" s="17"/>
     </row>
-    <row r="497" spans="2:7">
-      <c r="B497" s="18"/>
+    <row r="497" spans="6:7">
       <c r="F497" s="17"/>
       <c r="G497" s="17"/>
     </row>
-    <row r="498" spans="2:7">
-      <c r="B498" s="18"/>
+    <row r="498" spans="6:7">
       <c r="F498" s="17"/>
       <c r="G498" s="17"/>
     </row>
-    <row r="499" spans="2:7">
-      <c r="B499" s="18"/>
+    <row r="499" spans="6:7">
       <c r="F499" s="17"/>
       <c r="G499" s="17"/>
     </row>
-    <row r="500" spans="2:7">
-      <c r="B500" s="18"/>
+    <row r="500" spans="6:7">
       <c r="F500" s="17"/>
       <c r="G500" s="17"/>
     </row>
-    <row r="501" spans="2:7">
-      <c r="B501" s="18"/>
+    <row r="501" spans="6:7">
       <c r="F501" s="17"/>
       <c r="G501" s="17"/>
     </row>
-    <row r="502" spans="2:7">
-      <c r="B502" s="18"/>
+    <row r="502" spans="6:7">
       <c r="F502" s="17"/>
       <c r="G502" s="17"/>
     </row>
-    <row r="503" spans="2:7">
-      <c r="B503" s="18"/>
+    <row r="503" spans="6:7">
       <c r="F503" s="17"/>
       <c r="G503" s="17"/>
     </row>
-    <row r="504" spans="2:7">
-      <c r="B504" s="18"/>
+    <row r="504" spans="6:7">
       <c r="F504" s="17"/>
       <c r="G504" s="17"/>
     </row>
-    <row r="505" spans="2:7">
-      <c r="B505" s="18"/>
+    <row r="505" spans="6:7">
       <c r="F505" s="17"/>
       <c r="G505" s="17"/>
     </row>
-    <row r="506" spans="2:7">
-      <c r="B506" s="18"/>
+    <row r="506" spans="6:7">
       <c r="F506" s="17"/>
       <c r="G506" s="17"/>
     </row>
-    <row r="507" spans="2:7">
-      <c r="B507" s="18"/>
+    <row r="507" spans="6:7">
       <c r="F507" s="17"/>
       <c r="G507" s="17"/>
     </row>
-    <row r="508" spans="2:7">
-      <c r="B508" s="18"/>
+    <row r="508" spans="6:7">
       <c r="F508" s="17"/>
       <c r="G508" s="17"/>
     </row>
-    <row r="509" spans="2:7">
-      <c r="B509" s="18"/>
+    <row r="509" spans="6:7">
       <c r="F509" s="17"/>
       <c r="G509" s="17"/>
     </row>
-    <row r="510" spans="2:7">
-      <c r="B510" s="18"/>
+    <row r="510" spans="6:7">
       <c r="F510" s="17"/>
       <c r="G510" s="17"/>
     </row>
-    <row r="511" spans="2:7">
-      <c r="B511" s="18"/>
+    <row r="511" spans="6:7">
       <c r="F511" s="17"/>
       <c r="G511" s="17"/>
     </row>
-    <row r="512" spans="2:7">
-      <c r="B512" s="18"/>
+    <row r="512" spans="6:7">
       <c r="F512" s="17"/>
       <c r="G512" s="17"/>
     </row>
-    <row r="513" spans="2:7">
-      <c r="B513" s="18"/>
+    <row r="513" spans="6:7">
       <c r="F513" s="17"/>
       <c r="G513" s="17"/>
     </row>
-    <row r="514" spans="2:7">
-      <c r="B514" s="18"/>
+    <row r="514" spans="6:7">
       <c r="F514" s="17"/>
       <c r="G514" s="17"/>
     </row>
-    <row r="515" spans="2:7">
-      <c r="B515" s="18"/>
+    <row r="515" spans="6:7">
       <c r="F515" s="17"/>
       <c r="G515" s="17"/>
     </row>
-    <row r="516" spans="2:7">
-      <c r="B516" s="18"/>
+    <row r="516" spans="6:7">
       <c r="F516" s="17"/>
       <c r="G516" s="17"/>
     </row>
-    <row r="517" spans="2:7">
-      <c r="B517" s="18"/>
+    <row r="517" spans="6:7">
       <c r="F517" s="17"/>
       <c r="G517" s="17"/>
     </row>
-    <row r="518" spans="2:7">
-      <c r="B518" s="18"/>
+    <row r="518" spans="6:7">
       <c r="F518" s="17"/>
       <c r="G518" s="17"/>
     </row>
-    <row r="519" spans="2:7">
-      <c r="B519" s="18"/>
+    <row r="519" spans="6:7">
       <c r="F519" s="17"/>
       <c r="G519" s="17"/>
     </row>
-    <row r="520" spans="2:7">
-      <c r="B520" s="18"/>
+    <row r="520" spans="6:7">
       <c r="F520" s="17"/>
       <c r="G520" s="17"/>
     </row>
-    <row r="521" spans="2:7">
-      <c r="B521" s="18"/>
+    <row r="521" spans="6:7">
       <c r="F521" s="17"/>
       <c r="G521" s="17"/>
     </row>
-    <row r="522" spans="2:7">
-      <c r="B522" s="18"/>
+    <row r="522" spans="6:7">
       <c r="F522" s="17"/>
       <c r="G522" s="17"/>
     </row>
-    <row r="523" spans="2:7">
-      <c r="B523" s="18"/>
+    <row r="523" spans="6:7">
       <c r="F523" s="17"/>
       <c r="G523" s="17"/>
     </row>
-    <row r="524" spans="2:7">
-      <c r="B524" s="18"/>
+    <row r="524" spans="6:7">
       <c r="F524" s="17"/>
       <c r="G524" s="17"/>
     </row>
-    <row r="525" spans="2:7">
-      <c r="B525" s="18"/>
+    <row r="525" spans="6:7">
       <c r="F525" s="17"/>
       <c r="G525" s="17"/>
     </row>
-    <row r="526" spans="2:7">
-      <c r="B526" s="18"/>
+    <row r="526" spans="6:7">
       <c r="F526" s="17"/>
       <c r="G526" s="17"/>
     </row>
-    <row r="527" spans="2:7">
-      <c r="B527" s="18"/>
+    <row r="527" spans="6:7">
       <c r="F527" s="17"/>
       <c r="G527" s="17"/>
     </row>
-    <row r="528" spans="2:7">
-      <c r="B528" s="18"/>
+    <row r="528" spans="6:7">
       <c r="F528" s="17"/>
       <c r="G528" s="17"/>
     </row>
-    <row r="529" spans="2:7">
-      <c r="B529" s="18"/>
+    <row r="529" spans="6:7">
       <c r="F529" s="17"/>
       <c r="G529" s="17"/>
     </row>
-    <row r="530" spans="2:7">
-      <c r="B530" s="18"/>
+    <row r="530" spans="6:7">
       <c r="F530" s="17"/>
       <c r="G530" s="17"/>
     </row>
-    <row r="531" spans="2:7">
-      <c r="B531" s="18"/>
+    <row r="531" spans="6:7">
       <c r="F531" s="17"/>
       <c r="G531" s="17"/>
     </row>
-    <row r="532" spans="2:7">
-      <c r="B532" s="18"/>
+    <row r="532" spans="6:7">
       <c r="F532" s="17"/>
       <c r="G532" s="17"/>
     </row>
-    <row r="533" spans="2:7">
-      <c r="B533" s="18"/>
+    <row r="533" spans="6:7">
       <c r="F533" s="17"/>
       <c r="G533" s="17"/>
     </row>
-    <row r="534" spans="2:7">
-      <c r="B534" s="18"/>
+    <row r="534" spans="6:7">
       <c r="F534" s="17"/>
       <c r="G534" s="17"/>
     </row>
-    <row r="535" spans="2:7">
-      <c r="B535" s="18"/>
+    <row r="535" spans="6:7">
       <c r="F535" s="17"/>
       <c r="G535" s="17"/>
     </row>
-    <row r="536" spans="2:7">
-      <c r="B536" s="18"/>
+    <row r="536" spans="6:7">
       <c r="F536" s="17"/>
       <c r="G536" s="17"/>
     </row>
-    <row r="537" spans="2:7">
-      <c r="B537" s="18"/>
+    <row r="537" spans="6:7">
       <c r="F537" s="17"/>
       <c r="G537" s="17"/>
     </row>
-    <row r="538" spans="2:7">
-      <c r="B538" s="18"/>
+    <row r="538" spans="6:7">
       <c r="F538" s="17"/>
       <c r="G538" s="17"/>
     </row>
-    <row r="539" spans="2:7">
-      <c r="B539" s="18"/>
+    <row r="539" spans="6:7">
       <c r="F539" s="17"/>
       <c r="G539" s="17"/>
     </row>
-    <row r="540" spans="2:7">
-      <c r="B540" s="18"/>
+    <row r="540" spans="6:7">
       <c r="F540" s="17"/>
       <c r="G540" s="17"/>
     </row>
-    <row r="541" spans="2:7">
-      <c r="B541" s="18"/>
+    <row r="541" spans="6:7">
       <c r="F541" s="17"/>
       <c r="G541" s="17"/>
     </row>
-    <row r="542" spans="2:7">
-      <c r="B542" s="18"/>
+    <row r="542" spans="6:7">
       <c r="F542" s="17"/>
       <c r="G542" s="17"/>
     </row>
-    <row r="543" spans="2:7">
-      <c r="B543" s="18"/>
+    <row r="543" spans="6:7">
       <c r="F543" s="17"/>
       <c r="G543" s="17"/>
     </row>
-    <row r="544" spans="2:7">
-      <c r="B544" s="18"/>
+    <row r="544" spans="6:7">
       <c r="F544" s="17"/>
       <c r="G544" s="17"/>
     </row>
-    <row r="545" spans="2:7">
-      <c r="B545" s="18"/>
+    <row r="545" spans="6:7">
       <c r="F545" s="17"/>
       <c r="G545" s="17"/>
     </row>
-    <row r="546" spans="2:7">
-      <c r="B546" s="18"/>
+    <row r="546" spans="6:7">
       <c r="F546" s="17"/>
       <c r="G546" s="17"/>
     </row>
-    <row r="547" spans="2:7">
-      <c r="B547" s="18"/>
+    <row r="547" spans="6:7">
       <c r="F547" s="17"/>
       <c r="G547" s="17"/>
     </row>
-    <row r="548" spans="2:7">
-      <c r="B548" s="18"/>
+    <row r="548" spans="6:7">
       <c r="F548" s="17"/>
       <c r="G548" s="17"/>
     </row>
-    <row r="549" spans="2:7">
-      <c r="B549" s="18"/>
+    <row r="549" spans="6:7">
       <c r="F549" s="17"/>
       <c r="G549" s="17"/>
     </row>
-    <row r="550" spans="2:7">
-      <c r="B550" s="18"/>
+    <row r="550" spans="6:7">
       <c r="F550" s="17"/>
       <c r="G550" s="17"/>
     </row>
-    <row r="551" spans="2:7">
-      <c r="B551" s="18"/>
+    <row r="551" spans="6:7">
       <c r="F551" s="17"/>
       <c r="G551" s="17"/>
     </row>
-    <row r="552" spans="2:7">
-      <c r="B552" s="18"/>
+    <row r="552" spans="6:7">
       <c r="F552" s="17"/>
       <c r="G552" s="17"/>
     </row>
-    <row r="553" spans="2:7">
-      <c r="B553" s="18"/>
+    <row r="553" spans="6:7">
       <c r="F553" s="17"/>
       <c r="G553" s="17"/>
     </row>
-    <row r="554" spans="2:7">
-      <c r="B554" s="18"/>
+    <row r="554" spans="6:7">
       <c r="F554" s="17"/>
       <c r="G554" s="17"/>
     </row>
-    <row r="555" spans="2:7">
-      <c r="B555" s="18"/>
+    <row r="555" spans="6:7">
       <c r="F555" s="17"/>
       <c r="G555" s="17"/>
     </row>
-    <row r="556" spans="2:7">
-      <c r="B556" s="18"/>
+    <row r="556" spans="6:7">
       <c r="F556" s="17"/>
       <c r="G556" s="17"/>
     </row>
-    <row r="557" spans="2:7">
-      <c r="B557" s="18"/>
+    <row r="557" spans="6:7">
       <c r="F557" s="17"/>
       <c r="G557" s="17"/>
     </row>
-    <row r="558" spans="2:7">
-      <c r="B558" s="18"/>
+    <row r="558" spans="6:7">
       <c r="F558" s="17"/>
       <c r="G558" s="17"/>
     </row>
-    <row r="559" spans="2:7">
-      <c r="B559" s="18"/>
+    <row r="559" spans="6:7">
       <c r="F559" s="17"/>
       <c r="G559" s="17"/>
     </row>
-    <row r="560" spans="2:7">
-      <c r="B560" s="18"/>
+    <row r="560" spans="6:7">
       <c r="F560" s="17"/>
       <c r="G560" s="17"/>
     </row>
-    <row r="561" spans="2:7">
-      <c r="B561" s="18"/>
+    <row r="561" spans="6:7">
       <c r="F561" s="17"/>
       <c r="G561" s="17"/>
     </row>
-    <row r="562" spans="2:7">
-      <c r="B562" s="18"/>
+    <row r="562" spans="6:7">
       <c r="F562" s="17"/>
       <c r="G562" s="17"/>
     </row>
-    <row r="563" spans="2:7">
-      <c r="B563" s="18"/>
+    <row r="563" spans="6:7">
       <c r="F563" s="17"/>
       <c r="G563" s="17"/>
     </row>
-    <row r="564" spans="2:7">
-      <c r="B564" s="18"/>
+    <row r="564" spans="6:7">
       <c r="F564" s="17"/>
       <c r="G564" s="17"/>
     </row>
-    <row r="565" spans="2:7">
-      <c r="B565" s="18"/>
+    <row r="565" spans="6:7">
       <c r="F565" s="17"/>
       <c r="G565" s="17"/>
     </row>
-    <row r="566" spans="2:7">
-      <c r="B566" s="18"/>
+    <row r="566" spans="6:7">
       <c r="F566" s="17"/>
       <c r="G566" s="17"/>
     </row>
-    <row r="567" spans="2:7">
-      <c r="B567" s="18"/>
+    <row r="567" spans="6:7">
       <c r="F567" s="17"/>
       <c r="G567" s="17"/>
     </row>
-    <row r="568" spans="2:7">
-      <c r="B568" s="18"/>
+    <row r="568" spans="6:7">
       <c r="F568" s="17"/>
       <c r="G568" s="17"/>
     </row>
-    <row r="569" spans="2:7">
-      <c r="B569" s="18"/>
+    <row r="569" spans="6:7">
       <c r="F569" s="17"/>
       <c r="G569" s="17"/>
     </row>
-    <row r="570" spans="2:7">
-      <c r="B570" s="18"/>
+    <row r="570" spans="6:7">
       <c r="F570" s="17"/>
       <c r="G570" s="17"/>
     </row>
-    <row r="571" spans="2:7">
-      <c r="B571" s="18"/>
+    <row r="571" spans="6:7">
       <c r="F571" s="17"/>
       <c r="G571" s="17"/>
     </row>
-    <row r="572" spans="2:7">
-      <c r="B572" s="18"/>
+    <row r="572" spans="6:7">
       <c r="F572" s="17"/>
       <c r="G572" s="17"/>
     </row>
-    <row r="573" spans="2:7">
-      <c r="B573" s="18"/>
+    <row r="573" spans="6:7">
       <c r="F573" s="17"/>
       <c r="G573" s="17"/>
     </row>
-    <row r="574" spans="2:7">
-      <c r="B574" s="18"/>
+    <row r="574" spans="6:7">
       <c r="F574" s="17"/>
       <c r="G574" s="17"/>
     </row>
-    <row r="575" spans="2:7">
-      <c r="B575" s="18"/>
+    <row r="575" spans="6:7">
       <c r="F575" s="17"/>
       <c r="G575" s="17"/>
     </row>
-    <row r="576" spans="2:7">
-      <c r="B576" s="18"/>
+    <row r="576" spans="6:7">
       <c r="F576" s="17"/>
       <c r="G576" s="17"/>
     </row>
-    <row r="577" spans="2:7">
-      <c r="B577" s="18"/>
+    <row r="577" spans="6:7">
       <c r="F577" s="17"/>
       <c r="G577" s="17"/>
     </row>
-    <row r="578" spans="2:7">
-      <c r="B578" s="18"/>
+    <row r="578" spans="6:7">
       <c r="F578" s="17"/>
       <c r="G578" s="17"/>
     </row>
-    <row r="579" spans="2:7">
-      <c r="B579" s="18"/>
+    <row r="579" spans="6:7">
       <c r="F579" s="17"/>
       <c r="G579" s="17"/>
     </row>
-    <row r="580" spans="2:7">
-      <c r="B580" s="18"/>
+    <row r="580" spans="6:7">
       <c r="F580" s="17"/>
       <c r="G580" s="17"/>
     </row>
-    <row r="581" spans="2:7">
-      <c r="B581" s="18"/>
+    <row r="581" spans="6:7">
       <c r="F581" s="17"/>
       <c r="G581" s="17"/>
     </row>
-    <row r="582" spans="2:7">
-      <c r="B582" s="18"/>
+    <row r="582" spans="6:7">
       <c r="F582" s="17"/>
       <c r="G582" s="17"/>
     </row>
-    <row r="583" spans="2:7">
-      <c r="B583" s="18"/>
+    <row r="583" spans="6:7">
       <c r="F583" s="17"/>
       <c r="G583" s="17"/>
     </row>
-    <row r="584" spans="2:7">
-      <c r="B584" s="18"/>
+    <row r="584" spans="6:7">
       <c r="F584" s="17"/>
       <c r="G584" s="17"/>
     </row>
-    <row r="585" spans="2:7">
-      <c r="B585" s="18"/>
+    <row r="585" spans="6:7">
       <c r="F585" s="17"/>
       <c r="G585" s="17"/>
     </row>
-    <row r="586" spans="2:7">
-      <c r="B586" s="18"/>
+    <row r="586" spans="6:7">
       <c r="F586" s="17"/>
       <c r="G586" s="17"/>
     </row>
-    <row r="587" spans="2:7">
-      <c r="B587" s="18"/>
+    <row r="587" spans="6:7">
       <c r="F587" s="17"/>
       <c r="G587" s="17"/>
     </row>
-    <row r="588" spans="2:7">
-      <c r="B588" s="18"/>
+    <row r="588" spans="6:7">
       <c r="F588" s="17"/>
       <c r="G588" s="17"/>
     </row>
-    <row r="589" spans="2:7">
-      <c r="B589" s="18"/>
+    <row r="589" spans="6:7">
       <c r="F589" s="17"/>
       <c r="G589" s="17"/>
     </row>
-    <row r="590" spans="2:7">
-      <c r="B590" s="18"/>
+    <row r="590" spans="6:7">
       <c r="F590" s="17"/>
       <c r="G590" s="17"/>
     </row>
-    <row r="591" spans="2:7">
-      <c r="B591" s="18"/>
+    <row r="591" spans="6:7">
       <c r="F591" s="17"/>
       <c r="G591" s="17"/>
     </row>
-    <row r="592" spans="2:7">
-      <c r="B592" s="18"/>
+    <row r="592" spans="6:7">
       <c r="F592" s="17"/>
       <c r="G592" s="17"/>
     </row>
-    <row r="593" spans="2:7">
-      <c r="B593" s="18"/>
+    <row r="593" spans="6:7">
       <c r="F593" s="17"/>
       <c r="G593" s="17"/>
     </row>
-    <row r="594" spans="2:7">
-      <c r="B594" s="18"/>
+    <row r="594" spans="6:7">
       <c r="F594" s="17"/>
       <c r="G594" s="17"/>
     </row>
-    <row r="595" spans="2:7">
-      <c r="B595" s="18"/>
+    <row r="595" spans="6:7">
       <c r="F595" s="17"/>
       <c r="G595" s="17"/>
     </row>
-    <row r="596" spans="2:7">
-      <c r="B596" s="18"/>
+    <row r="596" spans="6:7">
       <c r="F596" s="17"/>
       <c r="G596" s="17"/>
     </row>
-    <row r="597" spans="2:7">
-      <c r="B597" s="18"/>
+    <row r="597" spans="6:7">
       <c r="F597" s="17"/>
       <c r="G597" s="17"/>
     </row>
-    <row r="598" spans="2:7">
-      <c r="B598" s="18"/>
+    <row r="598" spans="6:7">
       <c r="F598" s="17"/>
       <c r="G598" s="17"/>
     </row>
-    <row r="599" spans="2:7">
-      <c r="B599" s="18"/>
+    <row r="599" spans="6:7">
       <c r="F599" s="17"/>
       <c r="G599" s="17"/>
     </row>
-    <row r="600" spans="2:7">
-      <c r="B600" s="18"/>
+    <row r="600" spans="6:7">
       <c r="F600" s="17"/>
       <c r="G600" s="17"/>
     </row>
-    <row r="601" spans="2:7">
-      <c r="B601" s="18"/>
+    <row r="601" spans="6:7">
       <c r="F601" s="17"/>
       <c r="G601" s="17"/>
     </row>
-    <row r="602" spans="2:7">
-      <c r="B602" s="18"/>
+    <row r="602" spans="6:7">
       <c r="F602" s="17"/>
       <c r="G602" s="17"/>
     </row>
-    <row r="603" spans="2:7">
-      <c r="B603" s="18"/>
+    <row r="603" spans="6:7">
       <c r="F603" s="17"/>
       <c r="G603" s="17"/>
     </row>
-    <row r="604" spans="2:7">
-      <c r="B604" s="18"/>
+    <row r="604" spans="6:7">
       <c r="F604" s="17"/>
       <c r="G604" s="17"/>
     </row>
-    <row r="605" spans="2:7">
-      <c r="B605" s="18"/>
+    <row r="605" spans="6:7">
       <c r="F605" s="17"/>
       <c r="G605" s="17"/>
     </row>
-    <row r="606" spans="2:7">
-      <c r="B606" s="18"/>
+    <row r="606" spans="6:7">
       <c r="F606" s="17"/>
       <c r="G606" s="17"/>
     </row>
-    <row r="607" spans="2:7">
-      <c r="B607" s="18"/>
+    <row r="607" spans="6:7">
       <c r="F607" s="17"/>
       <c r="G607" s="17"/>
     </row>
-    <row r="608" spans="2:7">
-      <c r="B608" s="18"/>
+    <row r="608" spans="6:7">
       <c r="F608" s="17"/>
       <c r="G608" s="17"/>
     </row>
-    <row r="609" spans="2:7">
-      <c r="B609" s="18"/>
+    <row r="609" spans="6:7">
       <c r="F609" s="17"/>
       <c r="G609" s="17"/>
     </row>
-    <row r="610" spans="2:7">
-      <c r="B610" s="18"/>
+    <row r="610" spans="6:7">
       <c r="F610" s="17"/>
       <c r="G610" s="17"/>
     </row>
-    <row r="611" spans="2:7">
-      <c r="B611" s="18"/>
+    <row r="611" spans="6:7">
       <c r="F611" s="17"/>
       <c r="G611" s="17"/>
     </row>
-    <row r="612" spans="2:7">
-      <c r="B612" s="18"/>
+    <row r="612" spans="6:7">
       <c r="F612" s="17"/>
       <c r="G612" s="17"/>
     </row>
-    <row r="613" spans="2:7">
-      <c r="B613" s="18"/>
+    <row r="613" spans="6:7">
       <c r="F613" s="17"/>
       <c r="G613" s="17"/>
     </row>
-    <row r="614" spans="2:7">
-      <c r="B614" s="18"/>
+    <row r="614" spans="6:7">
       <c r="F614" s="17"/>
       <c r="G614" s="17"/>
     </row>
-    <row r="615" spans="2:7">
-      <c r="B615" s="18"/>
+    <row r="615" spans="6:7">
       <c r="F615" s="17"/>
       <c r="G615" s="17"/>
     </row>
-    <row r="616" spans="2:7">
-      <c r="B616" s="18"/>
+    <row r="616" spans="6:7">
       <c r="F616" s="17"/>
       <c r="G616" s="17"/>
     </row>
-    <row r="617" spans="2:7">
-      <c r="B617" s="18"/>
+    <row r="617" spans="6:7">
       <c r="F617" s="17"/>
       <c r="G617" s="17"/>
     </row>
-    <row r="618" spans="2:7">
-      <c r="B618" s="18"/>
+    <row r="618" spans="6:7">
       <c r="F618" s="17"/>
       <c r="G618" s="17"/>
     </row>
-    <row r="619" spans="2:7">
-      <c r="B619" s="18"/>
+    <row r="619" spans="6:7">
       <c r="F619" s="17"/>
       <c r="G619" s="17"/>
     </row>
-    <row r="620" spans="2:7">
-      <c r="B620" s="18"/>
+    <row r="620" spans="6:7">
       <c r="F620" s="17"/>
       <c r="G620" s="17"/>
     </row>
-    <row r="621" spans="2:7">
-      <c r="B621" s="18"/>
+    <row r="621" spans="6:7">
       <c r="F621" s="17"/>
       <c r="G621" s="17"/>
     </row>
-    <row r="622" spans="2:7">
-      <c r="B622" s="18"/>
+    <row r="622" spans="6:7">
       <c r="F622" s="17"/>
       <c r="G622" s="17"/>
     </row>
-    <row r="623" spans="2:7">
-      <c r="B623" s="18"/>
+    <row r="623" spans="6:7">
       <c r="F623" s="17"/>
       <c r="G623" s="17"/>
     </row>
-    <row r="624" spans="2:7">
-      <c r="B624" s="18"/>
+    <row r="624" spans="6:7">
       <c r="F624" s="17"/>
       <c r="G624" s="17"/>
     </row>
-    <row r="625" spans="2:7">
-      <c r="B625" s="18"/>
+    <row r="625" spans="6:7">
       <c r="F625" s="17"/>
       <c r="G625" s="17"/>
     </row>
-    <row r="626" spans="2:7">
-      <c r="B626" s="18"/>
+    <row r="626" spans="6:7">
       <c r="F626" s="17"/>
       <c r="G626" s="17"/>
     </row>
-    <row r="627" spans="2:7">
-      <c r="B627" s="18"/>
+    <row r="627" spans="6:7">
       <c r="F627" s="17"/>
       <c r="G627" s="17"/>
     </row>
-    <row r="628" spans="2:7">
-      <c r="B628" s="18"/>
+    <row r="628" spans="6:7">
       <c r="F628" s="17"/>
       <c r="G628" s="17"/>
     </row>
-    <row r="629" spans="2:7">
-      <c r="B629" s="18"/>
+    <row r="629" spans="6:7">
       <c r="F629" s="17"/>
       <c r="G629" s="17"/>
     </row>
-    <row r="630" spans="2:7">
-      <c r="B630" s="18"/>
+    <row r="630" spans="6:7">
       <c r="F630" s="17"/>
       <c r="G630" s="17"/>
     </row>
-    <row r="631" spans="2:7">
-      <c r="B631" s="18"/>
+    <row r="631" spans="6:7">
       <c r="F631" s="17"/>
       <c r="G631" s="17"/>
     </row>
-    <row r="632" spans="2:7">
-      <c r="B632" s="18"/>
+    <row r="632" spans="6:7">
       <c r="F632" s="17"/>
       <c r="G632" s="17"/>
     </row>
-    <row r="633" spans="2:7">
-      <c r="B633" s="18"/>
+    <row r="633" spans="6:7">
       <c r="F633" s="17"/>
       <c r="G633" s="17"/>
     </row>
-    <row r="634" spans="2:7">
-      <c r="B634" s="18"/>
+    <row r="634" spans="6:7">
       <c r="F634" s="17"/>
       <c r="G634" s="17"/>
     </row>
-    <row r="635" spans="2:7">
-      <c r="B635" s="18"/>
+    <row r="635" spans="6:7">
       <c r="F635" s="17"/>
       <c r="G635" s="17"/>
     </row>
-    <row r="636" spans="2:7">
-      <c r="B636" s="18"/>
+    <row r="636" spans="6:7">
       <c r="F636" s="17"/>
       <c r="G636" s="17"/>
     </row>
-    <row r="637" spans="2:7">
-      <c r="B637" s="18"/>
+    <row r="637" spans="6:7">
       <c r="F637" s="17"/>
       <c r="G637" s="17"/>
     </row>
-    <row r="638" spans="2:7">
-      <c r="B638" s="18"/>
+    <row r="638" spans="6:7">
       <c r="F638" s="17"/>
       <c r="G638" s="17"/>
     </row>
-    <row r="639" spans="2:7">
-      <c r="B639" s="18"/>
+    <row r="639" spans="6:7">
       <c r="F639" s="17"/>
       <c r="G639" s="17"/>
     </row>
-    <row r="640" spans="2:7">
-      <c r="B640" s="18"/>
+    <row r="640" spans="6:7">
       <c r="F640" s="17"/>
       <c r="G640" s="17"/>
     </row>
-    <row r="641" spans="2:7">
-      <c r="B641" s="18"/>
+    <row r="641" spans="6:7">
       <c r="F641" s="17"/>
       <c r="G641" s="17"/>
     </row>
-    <row r="642" spans="2:7">
-      <c r="B642" s="18"/>
+    <row r="642" spans="6:7">
       <c r="F642" s="17"/>
       <c r="G642" s="17"/>
     </row>
-    <row r="643" spans="2:7">
-      <c r="B643" s="18"/>
+    <row r="643" spans="6:7">
       <c r="F643" s="17"/>
       <c r="G643" s="17"/>
     </row>
-    <row r="644" spans="2:7">
-      <c r="B644" s="18"/>
+    <row r="644" spans="6:7">
       <c r="F644" s="17"/>
       <c r="G644" s="17"/>
     </row>
-    <row r="645" spans="2:7">
-      <c r="B645" s="18"/>
+    <row r="645" spans="6:7">
       <c r="F645" s="17"/>
       <c r="G645" s="17"/>
     </row>
-    <row r="646" spans="2:7">
-      <c r="B646" s="18"/>
+    <row r="646" spans="6:7">
       <c r="F646" s="17"/>
       <c r="G646" s="17"/>
     </row>
-    <row r="647" spans="2:7">
-      <c r="B647" s="18"/>
+    <row r="647" spans="6:7">
       <c r="F647" s="17"/>
       <c r="G647" s="17"/>
     </row>
-    <row r="648" spans="2:7">
-      <c r="B648" s="18"/>
+    <row r="648" spans="6:7">
       <c r="F648" s="17"/>
       <c r="G648" s="17"/>
     </row>
-    <row r="649" spans="2:7">
-      <c r="B649" s="18"/>
+    <row r="649" spans="6:7">
       <c r="F649" s="17"/>
       <c r="G649" s="17"/>
     </row>
-    <row r="650" spans="2:7">
-      <c r="B650" s="18"/>
+    <row r="650" spans="6:7">
       <c r="F650" s="17"/>
       <c r="G650" s="17"/>
     </row>
-    <row r="651" spans="2:7">
-      <c r="B651" s="18"/>
+    <row r="651" spans="6:7">
       <c r="F651" s="17"/>
       <c r="G651" s="17"/>
     </row>
-    <row r="652" spans="2:7">
-      <c r="B652" s="18"/>
+    <row r="652" spans="6:7">
       <c r="F652" s="17"/>
       <c r="G652" s="17"/>
     </row>
-    <row r="653" spans="2:7">
-      <c r="B653" s="18"/>
+    <row r="653" spans="6:7">
       <c r="F653" s="17"/>
       <c r="G653" s="17"/>
     </row>
-    <row r="654" spans="2:7">
-      <c r="B654" s="18"/>
+    <row r="654" spans="6:7">
       <c r="F654" s="17"/>
       <c r="G654" s="17"/>
     </row>
-    <row r="655" spans="2:7">
-      <c r="B655" s="18"/>
+    <row r="655" spans="6:7">
       <c r="F655" s="17"/>
       <c r="G655" s="17"/>
     </row>
-    <row r="656" spans="2:7">
-      <c r="B656" s="18"/>
+    <row r="656" spans="6:7">
       <c r="F656" s="17"/>
       <c r="G656" s="17"/>
     </row>
-    <row r="657" spans="2:7">
-      <c r="B657" s="18"/>
+    <row r="657" spans="6:7">
       <c r="F657" s="17"/>
       <c r="G657" s="17"/>
     </row>
-    <row r="658" spans="2:7">
-      <c r="B658" s="18"/>
+    <row r="658" spans="6:7">
       <c r="F658" s="17"/>
       <c r="G658" s="17"/>
     </row>
-    <row r="659" spans="2:7">
-      <c r="B659" s="18"/>
+    <row r="659" spans="6:7">
       <c r="F659" s="17"/>
       <c r="G659" s="17"/>
     </row>
-    <row r="660" spans="2:7">
-      <c r="B660" s="18"/>
+    <row r="660" spans="6:7">
       <c r="F660" s="17"/>
       <c r="G660" s="17"/>
     </row>
-    <row r="661" spans="2:7">
-      <c r="B661" s="18"/>
+    <row r="661" spans="6:7">
       <c r="F661" s="17"/>
       <c r="G661" s="17"/>
     </row>
-    <row r="662" spans="2:7">
-      <c r="B662" s="18"/>
+    <row r="662" spans="6:7">
       <c r="F662" s="17"/>
       <c r="G662" s="17"/>
     </row>
-    <row r="663" spans="2:7">
-      <c r="B663" s="18"/>
+    <row r="663" spans="6:7">
       <c r="F663" s="17"/>
       <c r="G663" s="17"/>
     </row>
-    <row r="664" spans="2:7">
-      <c r="B664" s="18"/>
+    <row r="664" spans="6:7">
       <c r="F664" s="17"/>
       <c r="G664" s="17"/>
     </row>
-    <row r="665" spans="2:7">
-      <c r="B665" s="18"/>
+    <row r="665" spans="6:7">
       <c r="F665" s="17"/>
       <c r="G665" s="17"/>
     </row>
-    <row r="666" spans="2:7">
-      <c r="B666" s="18"/>
+    <row r="666" spans="6:7">
       <c r="F666" s="17"/>
       <c r="G666" s="17"/>
     </row>
-    <row r="667" spans="2:7">
-      <c r="B667" s="18"/>
+    <row r="667" spans="6:7">
       <c r="F667" s="17"/>
       <c r="G667" s="17"/>
     </row>
-    <row r="668" spans="2:7">
-      <c r="B668" s="18"/>
+    <row r="668" spans="6:7">
       <c r="F668" s="17"/>
       <c r="G668" s="17"/>
     </row>
-    <row r="669" spans="2:7">
-      <c r="B669" s="18"/>
+    <row r="669" spans="6:7">
       <c r="F669" s="17"/>
       <c r="G669" s="17"/>
     </row>
-    <row r="670" spans="2:7">
-      <c r="B670" s="18"/>
+    <row r="670" spans="6:7">
       <c r="F670" s="17"/>
       <c r="G670" s="17"/>
     </row>
-    <row r="671" spans="2:7">
-      <c r="B671" s="18"/>
+    <row r="671" spans="6:7">
       <c r="F671" s="17"/>
       <c r="G671" s="17"/>
     </row>
-    <row r="672" spans="2:7">
-      <c r="B672" s="18"/>
+    <row r="672" spans="6:7">
       <c r="F672" s="17"/>
       <c r="G672" s="17"/>
     </row>
-    <row r="673" spans="2:7">
-      <c r="B673" s="18"/>
+    <row r="673" spans="6:7">
       <c r="F673" s="17"/>
       <c r="G673" s="17"/>
     </row>
-    <row r="674" spans="2:7">
-      <c r="B674" s="18"/>
+    <row r="674" spans="6:7">
       <c r="F674" s="17"/>
       <c r="G674" s="17"/>
     </row>
-    <row r="675" spans="2:7">
-      <c r="B675" s="18"/>
+    <row r="675" spans="6:7">
       <c r="F675" s="17"/>
       <c r="G675" s="17"/>
     </row>
-    <row r="676" spans="2:7">
-      <c r="B676" s="18"/>
+    <row r="676" spans="6:7">
       <c r="F676" s="17"/>
       <c r="G676" s="17"/>
     </row>
-    <row r="677" spans="2:7">
-      <c r="B677" s="18"/>
+    <row r="677" spans="6:7">
       <c r="F677" s="17"/>
       <c r="G677" s="17"/>
     </row>
-    <row r="678" spans="2:7">
-      <c r="B678" s="18"/>
+    <row r="678" spans="6:7">
       <c r="F678" s="17"/>
       <c r="G678" s="17"/>
     </row>
-    <row r="679" spans="2:7">
-      <c r="B679" s="18"/>
+    <row r="679" spans="6:7">
       <c r="F679" s="17"/>
       <c r="G679" s="17"/>
     </row>
-    <row r="680" spans="2:7">
-      <c r="B680" s="18"/>
+    <row r="680" spans="6:7">
       <c r="F680" s="17"/>
       <c r="G680" s="17"/>
     </row>
-    <row r="681" spans="2:7">
-      <c r="B681" s="18"/>
+    <row r="681" spans="6:7">
       <c r="F681" s="17"/>
       <c r="G681" s="17"/>
     </row>
-    <row r="682" spans="2:7">
-      <c r="B682" s="18"/>
+    <row r="682" spans="6:7">
       <c r="F682" s="17"/>
       <c r="G682" s="17"/>
     </row>
-    <row r="683" spans="2:7">
-      <c r="B683" s="18"/>
+    <row r="683" spans="6:7">
       <c r="F683" s="17"/>
       <c r="G683" s="17"/>
     </row>
-    <row r="684" spans="2:7">
-      <c r="B684" s="18"/>
+    <row r="684" spans="6:7">
       <c r="F684" s="17"/>
       <c r="G684" s="17"/>
     </row>
-    <row r="685" spans="2:7">
-      <c r="B685" s="18"/>
+    <row r="685" spans="6:7">
       <c r="F685" s="17"/>
       <c r="G685" s="17"/>
     </row>
-    <row r="686" spans="2:7">
-      <c r="B686" s="18"/>
+    <row r="686" spans="6:7">
       <c r="F686" s="17"/>
       <c r="G686" s="17"/>
     </row>
-    <row r="687" spans="2:7">
-      <c r="B687" s="18"/>
+    <row r="687" spans="6:7">
       <c r="F687" s="17"/>
       <c r="G687" s="17"/>
     </row>
-    <row r="688" spans="2:7">
-      <c r="B688" s="18"/>
+    <row r="688" spans="6:7">
       <c r="F688" s="17"/>
       <c r="G688" s="17"/>
     </row>
-    <row r="689" spans="2:7">
-      <c r="B689" s="18"/>
+    <row r="689" spans="6:7">
       <c r="F689" s="17"/>
       <c r="G689" s="17"/>
     </row>
-    <row r="690" spans="2:7">
-      <c r="B690" s="18"/>
+    <row r="690" spans="6:7">
       <c r="F690" s="17"/>
       <c r="G690" s="17"/>
     </row>
-    <row r="691" spans="2:7">
-      <c r="B691" s="18"/>
+    <row r="691" spans="6:7">
       <c r="F691" s="17"/>
       <c r="G691" s="17"/>
     </row>
-    <row r="692" spans="2:7">
-      <c r="B692" s="18"/>
+    <row r="692" spans="6:7">
       <c r="F692" s="17"/>
       <c r="G692" s="17"/>
     </row>
-    <row r="693" spans="2:7">
-      <c r="B693" s="18"/>
+    <row r="693" spans="6:7">
       <c r="F693" s="17"/>
       <c r="G693" s="17"/>
     </row>
-    <row r="694" spans="2:7">
-      <c r="B694" s="18"/>
+    <row r="694" spans="6:7">
       <c r="F694" s="17"/>
       <c r="G694" s="17"/>
     </row>
-    <row r="695" spans="2:7">
-      <c r="B695" s="18"/>
+    <row r="695" spans="6:7">
       <c r="F695" s="17"/>
       <c r="G695" s="17"/>
     </row>
-    <row r="696" spans="2:7">
-      <c r="B696" s="18"/>
+    <row r="696" spans="6:7">
       <c r="F696" s="17"/>
       <c r="G696" s="17"/>
     </row>
-    <row r="697" spans="2:7">
-      <c r="B697" s="18"/>
+    <row r="697" spans="6:7">
       <c r="F697" s="17"/>
       <c r="G697" s="17"/>
     </row>
-    <row r="698" spans="2:7">
-      <c r="B698" s="18"/>
+    <row r="698" spans="6:7">
       <c r="F698" s="17"/>
       <c r="G698" s="17"/>
     </row>
-    <row r="699" spans="2:7">
-      <c r="B699" s="18"/>
+    <row r="699" spans="6:7">
       <c r="F699" s="17"/>
       <c r="G699" s="17"/>
     </row>
-    <row r="700" spans="2:7">
-      <c r="B700" s="18"/>
+    <row r="700" spans="6:7">
       <c r="F700" s="17"/>
       <c r="G700" s="17"/>
     </row>
-    <row r="701" spans="2:7">
-      <c r="B701" s="18"/>
+    <row r="701" spans="6:7">
       <c r="F701" s="17"/>
       <c r="G701" s="17"/>
     </row>
-    <row r="702" spans="2:7">
-      <c r="B702" s="18"/>
+    <row r="702" spans="6:7">
       <c r="F702" s="17"/>
       <c r="G702" s="17"/>
     </row>
-    <row r="703" spans="2:7">
-      <c r="B703" s="18"/>
+    <row r="703" spans="6:7">
       <c r="F703" s="17"/>
       <c r="G703" s="17"/>
     </row>
-    <row r="704" spans="2:7">
-      <c r="B704" s="18"/>
+    <row r="704" spans="6:7">
       <c r="F704" s="17"/>
       <c r="G704" s="17"/>
     </row>
-    <row r="705" spans="2:7">
-      <c r="B705" s="18"/>
+    <row r="705" spans="6:7">
       <c r="F705" s="17"/>
       <c r="G705" s="17"/>
     </row>
-    <row r="706" spans="2:7">
-      <c r="B706" s="18"/>
+    <row r="706" spans="6:7">
       <c r="F706" s="17"/>
       <c r="G706" s="17"/>
     </row>
-    <row r="707" spans="2:7">
-      <c r="B707" s="18"/>
+    <row r="707" spans="6:7">
       <c r="F707" s="17"/>
       <c r="G707" s="17"/>
     </row>
-    <row r="708" spans="2:7">
-      <c r="B708" s="18"/>
+    <row r="708" spans="6:7">
       <c r="F708" s="17"/>
       <c r="G708" s="17"/>
     </row>
-    <row r="709" spans="2:7">
-      <c r="B709" s="18"/>
+    <row r="709" spans="6:7">
       <c r="F709" s="17"/>
       <c r="G709" s="17"/>
     </row>
-    <row r="710" spans="2:7">
-      <c r="B710" s="18"/>
+    <row r="710" spans="6:7">
       <c r="F710" s="17"/>
       <c r="G710" s="17"/>
     </row>
-    <row r="711" spans="2:7">
-      <c r="B711" s="18"/>
+    <row r="711" spans="6:7">
       <c r="F711" s="17"/>
       <c r="G711" s="17"/>
     </row>
-    <row r="712" spans="2:7">
-      <c r="B712" s="18"/>
+    <row r="712" spans="6:7">
       <c r="F712" s="17"/>
       <c r="G712" s="17"/>
     </row>
-    <row r="713" spans="2:7">
-      <c r="B713" s="18"/>
+    <row r="713" spans="6:7">
       <c r="F713" s="17"/>
       <c r="G713" s="17"/>
     </row>
-    <row r="714" spans="2:7">
-      <c r="B714" s="18"/>
+    <row r="714" spans="6:7">
       <c r="F714" s="17"/>
       <c r="G714" s="17"/>
     </row>
-    <row r="715" spans="2:7">
-      <c r="B715" s="18"/>
+    <row r="715" spans="6:7">
       <c r="F715" s="17"/>
       <c r="G715" s="17"/>
     </row>
-    <row r="716" spans="2:7">
-      <c r="B716" s="18"/>
+    <row r="716" spans="6:7">
       <c r="F716" s="17"/>
       <c r="G716" s="17"/>
     </row>
-    <row r="717" spans="2:7">
-      <c r="B717" s="18"/>
+    <row r="717" spans="6:7">
       <c r="F717" s="17"/>
       <c r="G717" s="17"/>
     </row>
-    <row r="718" spans="2:7">
-      <c r="B718" s="18"/>
+    <row r="718" spans="6:7">
       <c r="F718" s="17"/>
       <c r="G718" s="17"/>
     </row>
-    <row r="719" spans="2:7">
-      <c r="B719" s="18"/>
+    <row r="719" spans="6:7">
       <c r="F719" s="17"/>
       <c r="G719" s="17"/>
     </row>
-    <row r="720" spans="2:7">
-      <c r="B720" s="18"/>
+    <row r="720" spans="6:7">
       <c r="F720" s="17"/>
       <c r="G720" s="17"/>
     </row>
-    <row r="721" spans="2:7">
-      <c r="B721" s="18"/>
+    <row r="721" spans="6:7">
       <c r="F721" s="17"/>
       <c r="G721" s="17"/>
     </row>
-    <row r="722" spans="2:7">
-      <c r="B722" s="18"/>
+    <row r="722" spans="6:7">
       <c r="F722" s="17"/>
       <c r="G722" s="17"/>
     </row>
-    <row r="723" spans="2:7">
-      <c r="B723" s="18"/>
+    <row r="723" spans="6:7">
       <c r="F723" s="17"/>
       <c r="G723" s="17"/>
     </row>
-    <row r="724" spans="2:7">
-      <c r="B724" s="18"/>
+    <row r="724" spans="6:7">
       <c r="F724" s="17"/>
       <c r="G724" s="17"/>
     </row>
-    <row r="725" spans="2:7">
-      <c r="B725" s="18"/>
+    <row r="725" spans="6:7">
       <c r="F725" s="17"/>
       <c r="G725" s="17"/>
     </row>
-    <row r="726" spans="2:7">
-      <c r="B726" s="18"/>
+    <row r="726" spans="6:7">
       <c r="F726" s="17"/>
       <c r="G726" s="17"/>
     </row>
-    <row r="727" spans="2:7">
-      <c r="B727" s="18"/>
+    <row r="727" spans="6:7">
       <c r="F727" s="17"/>
       <c r="G727" s="17"/>
     </row>
-    <row r="728" spans="2:7">
-      <c r="B728" s="18"/>
+    <row r="728" spans="6:7">
       <c r="F728" s="17"/>
       <c r="G728" s="17"/>
     </row>
-    <row r="729" spans="2:7">
-      <c r="B729" s="18"/>
+    <row r="729" spans="6:7">
       <c r="F729" s="17"/>
       <c r="G729" s="17"/>
     </row>
-    <row r="730" spans="2:7">
-      <c r="B730" s="18"/>
+    <row r="730" spans="6:7">
       <c r="F730" s="17"/>
       <c r="G730" s="17"/>
     </row>
-    <row r="731" spans="2:7">
-      <c r="B731" s="18"/>
+    <row r="731" spans="6:7">
       <c r="F731" s="17"/>
       <c r="G731" s="17"/>
     </row>
-    <row r="732" spans="2:7">
-      <c r="B732" s="18"/>
+    <row r="732" spans="6:7">
       <c r="F732" s="17"/>
       <c r="G732" s="17"/>
     </row>
-    <row r="733" spans="2:7">
-      <c r="B733" s="18"/>
+    <row r="733" spans="6:7">
       <c r="F733" s="17"/>
       <c r="G733" s="17"/>
     </row>
-    <row r="734" spans="2:7">
-      <c r="B734" s="18"/>
+    <row r="734" spans="6:7">
       <c r="F734" s="17"/>
       <c r="G734" s="17"/>
     </row>
-    <row r="735" spans="2:7">
-      <c r="B735" s="18"/>
+    <row r="735" spans="6:7">
       <c r="F735" s="17"/>
       <c r="G735" s="17"/>
     </row>
-    <row r="736" spans="2:7">
-      <c r="B736" s="18"/>
+    <row r="736" spans="6:7">
       <c r="F736" s="17"/>
       <c r="G736" s="17"/>
     </row>
-    <row r="737" spans="2:7">
-      <c r="B737" s="18"/>
+    <row r="737" spans="6:7">
       <c r="F737" s="17"/>
       <c r="G737" s="17"/>
     </row>
-    <row r="738" spans="2:7">
-      <c r="B738" s="18"/>
+    <row r="738" spans="6:7">
       <c r="F738" s="17"/>
       <c r="G738" s="17"/>
     </row>
-    <row r="739" spans="2:7">
-      <c r="B739" s="18"/>
+    <row r="739" spans="6:7">
       <c r="F739" s="17"/>
       <c r="G739" s="17"/>
     </row>
-    <row r="740" spans="2:7">
-      <c r="B740" s="18"/>
+    <row r="740" spans="6:7">
       <c r="F740" s="17"/>
       <c r="G740" s="17"/>
     </row>
-    <row r="741" spans="2:7">
-      <c r="B741" s="18"/>
+    <row r="741" spans="6:7">
       <c r="F741" s="17"/>
       <c r="G741" s="17"/>
     </row>
-    <row r="742" spans="2:7">
-      <c r="B742" s="18"/>
+    <row r="742" spans="6:7">
       <c r="F742" s="17"/>
       <c r="G742" s="17"/>
     </row>
-    <row r="743" spans="2:7">
-      <c r="B743" s="18"/>
+    <row r="743" spans="6:7">
       <c r="F743" s="17"/>
       <c r="G743" s="17"/>
     </row>
-    <row r="744" spans="2:7">
-      <c r="B744" s="18"/>
+    <row r="744" spans="6:7">
       <c r="F744" s="17"/>
       <c r="G744" s="17"/>
     </row>
-    <row r="745" spans="2:7">
-      <c r="B745" s="18"/>
+    <row r="745" spans="6:7">
       <c r="F745" s="17"/>
       <c r="G745" s="17"/>
     </row>
-    <row r="746" spans="2:7">
-      <c r="B746" s="18"/>
+    <row r="746" spans="6:7">
       <c r="F746" s="17"/>
       <c r="G746" s="17"/>
     </row>
-    <row r="747" spans="2:7">
-      <c r="B747" s="18"/>
+    <row r="747" spans="6:7">
       <c r="F747" s="17"/>
       <c r="G747" s="17"/>
     </row>
-    <row r="748" spans="2:7">
-      <c r="B748" s="18"/>
+    <row r="748" spans="6:7">
       <c r="F748" s="17"/>
       <c r="G748" s="17"/>
     </row>
-    <row r="749" spans="2:7">
-      <c r="B749" s="18"/>
+    <row r="749" spans="6:7">
       <c r="F749" s="17"/>
       <c r="G749" s="17"/>
     </row>
-    <row r="750" spans="2:7">
-      <c r="B750" s="18"/>
+    <row r="750" spans="6:7">
       <c r="F750" s="17"/>
       <c r="G750" s="17"/>
     </row>
-    <row r="751" spans="2:7">
-      <c r="B751" s="18"/>
+    <row r="751" spans="6:7">
       <c r="F751" s="17"/>
       <c r="G751" s="17"/>
     </row>
-    <row r="752" spans="2:7">
-      <c r="B752" s="18"/>
+    <row r="752" spans="6:7">
       <c r="F752" s="17"/>
       <c r="G752" s="17"/>
     </row>
-    <row r="753" spans="2:7">
-      <c r="B753" s="18"/>
+    <row r="753" spans="6:7">
       <c r="F753" s="17"/>
       <c r="G753" s="17"/>
     </row>
-    <row r="754" spans="2:7">
-      <c r="B754" s="18"/>
+    <row r="754" spans="6:7">
       <c r="F754" s="17"/>
       <c r="G754" s="17"/>
     </row>
-    <row r="755" spans="2:7">
-      <c r="B755" s="18"/>
+    <row r="755" spans="6:7">
       <c r="F755" s="17"/>
       <c r="G755" s="17"/>
     </row>
-    <row r="756" spans="2:7">
-      <c r="B756" s="18"/>
+    <row r="756" spans="6:7">
       <c r="F756" s="17"/>
       <c r="G756" s="17"/>
     </row>
-    <row r="757" spans="2:7">
-      <c r="B757" s="18"/>
+    <row r="757" spans="6:7">
       <c r="F757" s="17"/>
       <c r="G757" s="17"/>
     </row>
-    <row r="758" spans="2:7">
-      <c r="B758" s="18"/>
+    <row r="758" spans="6:7">
       <c r="F758" s="17"/>
       <c r="G758" s="17"/>
     </row>
-    <row r="759" spans="2:7">
-      <c r="B759" s="18"/>
+    <row r="759" spans="6:7">
       <c r="F759" s="17"/>
       <c r="G759" s="17"/>
     </row>
-    <row r="760" spans="2:7">
-      <c r="B760" s="18"/>
+    <row r="760" spans="6:7">
       <c r="F760" s="17"/>
       <c r="G760" s="17"/>
     </row>
-    <row r="761" spans="2:7">
-      <c r="B761" s="18"/>
+    <row r="761" spans="6:7">
       <c r="F761" s="17"/>
       <c r="G761" s="17"/>
     </row>
-    <row r="762" spans="2:7">
-      <c r="B762" s="18"/>
+    <row r="762" spans="6:7">
       <c r="F762" s="17"/>
       <c r="G762" s="17"/>
     </row>
-    <row r="763" spans="2:7">
-      <c r="B763" s="18"/>
+    <row r="763" spans="6:7">
       <c r="F763" s="17"/>
       <c r="G763" s="17"/>
     </row>
-    <row r="764" spans="2:7">
-      <c r="B764" s="18"/>
+    <row r="764" spans="6:7">
       <c r="F764" s="17"/>
       <c r="G764" s="17"/>
     </row>
-    <row r="765" spans="2:7">
-      <c r="B765" s="18"/>
+    <row r="765" spans="6:7">
       <c r="F765" s="17"/>
       <c r="G765" s="17"/>
     </row>
-    <row r="766" spans="2:7">
-      <c r="B766" s="18"/>
+    <row r="766" spans="6:7">
       <c r="F766" s="17"/>
       <c r="G766" s="17"/>
     </row>
-    <row r="767" spans="2:7">
-      <c r="B767" s="18"/>
+    <row r="767" spans="6:7">
       <c r="F767" s="17"/>
       <c r="G767" s="17"/>
     </row>
-    <row r="768" spans="2:7">
-      <c r="B768" s="18"/>
+    <row r="768" spans="6:7">
       <c r="F768" s="17"/>
       <c r="G768" s="17"/>
     </row>
-    <row r="769" spans="2:7">
-      <c r="B769" s="18"/>
+    <row r="769" spans="6:7">
       <c r="F769" s="17"/>
       <c r="G769" s="17"/>
     </row>
-    <row r="770" spans="2:7">
-      <c r="B770" s="18"/>
+    <row r="770" spans="6:7">
       <c r="F770" s="17"/>
       <c r="G770" s="17"/>
     </row>
-    <row r="771" spans="2:7">
-      <c r="B771" s="18"/>
+    <row r="771" spans="6:7">
       <c r="F771" s="17"/>
       <c r="G771" s="17"/>
     </row>
-    <row r="772" spans="2:7">
-      <c r="B772" s="18"/>
+    <row r="772" spans="6:7">
       <c r="F772" s="17"/>
       <c r="G772" s="17"/>
     </row>
-    <row r="773" spans="2:7">
-      <c r="B773" s="18"/>
+    <row r="773" spans="6:7">
       <c r="F773" s="17"/>
       <c r="G773" s="17"/>
     </row>
-    <row r="774" spans="2:7">
-      <c r="B774" s="18"/>
+    <row r="774" spans="6:7">
       <c r="F774" s="17"/>
       <c r="G774" s="17"/>
     </row>
-    <row r="775" spans="2:7">
-      <c r="B775" s="18"/>
+    <row r="775" spans="6:7">
       <c r="F775" s="17"/>
       <c r="G775" s="17"/>
     </row>
-    <row r="776" spans="2:7">
-      <c r="B776" s="18"/>
+    <row r="776" spans="6:7">
       <c r="F776" s="17"/>
       <c r="G776" s="17"/>
     </row>
-    <row r="777" spans="2:7">
-      <c r="B777" s="18"/>
+    <row r="777" spans="6:7">
       <c r="F777" s="17"/>
       <c r="G777" s="17"/>
     </row>
-    <row r="778" spans="2:7">
-      <c r="B778" s="18"/>
+    <row r="778" spans="6:7">
       <c r="F778" s="17"/>
       <c r="G778" s="17"/>
     </row>
-    <row r="779" spans="2:7">
-      <c r="B779" s="18"/>
+    <row r="779" spans="6:7">
       <c r="F779" s="17"/>
       <c r="G779" s="17"/>
     </row>
-    <row r="780" spans="2:7">
-      <c r="B780" s="18"/>
+    <row r="780" spans="6:7">
       <c r="F780" s="17"/>
       <c r="G780" s="17"/>
     </row>
-    <row r="781" spans="2:7">
-      <c r="B781" s="18"/>
+    <row r="781" spans="6:7">
       <c r="F781" s="17"/>
       <c r="G781" s="17"/>
     </row>
-    <row r="782" spans="2:7">
-      <c r="B782" s="18"/>
+    <row r="782" spans="6:7">
       <c r="F782" s="17"/>
       <c r="G782" s="17"/>
     </row>
-    <row r="783" spans="2:7">
-      <c r="B783" s="18"/>
+    <row r="783" spans="6:7">
       <c r="F783" s="17"/>
       <c r="G783" s="17"/>
     </row>
-    <row r="784" spans="2:7">
-      <c r="B784" s="18"/>
+    <row r="784" spans="6:7">
       <c r="F784" s="17"/>
       <c r="G784" s="17"/>
     </row>
-    <row r="785" spans="2:7">
-      <c r="B785" s="18"/>
+    <row r="785" spans="6:7">
       <c r="F785" s="17"/>
       <c r="G785" s="17"/>
     </row>
-    <row r="786" spans="2:7">
-      <c r="B786" s="18"/>
+    <row r="786" spans="6:7">
       <c r="F786" s="17"/>
       <c r="G786" s="17"/>
     </row>
-    <row r="787" spans="2:7">
-      <c r="B787" s="18"/>
+    <row r="787" spans="6:7">
       <c r="F787" s="17"/>
       <c r="G787" s="17"/>
     </row>
-    <row r="788" spans="2:7">
-      <c r="B788" s="18"/>
+    <row r="788" spans="6:7">
       <c r="F788" s="17"/>
       <c r="G788" s="17"/>
     </row>
-    <row r="789" spans="2:7">
-      <c r="B789" s="18"/>
+    <row r="789" spans="6:7">
       <c r="F789" s="17"/>
       <c r="G789" s="17"/>
     </row>
-    <row r="790" spans="2:7">
-      <c r="B790" s="18"/>
+    <row r="790" spans="6:7">
       <c r="F790" s="17"/>
       <c r="G790" s="17"/>
     </row>
-    <row r="791" spans="2:7">
-      <c r="B791" s="18"/>
+    <row r="791" spans="6:7">
       <c r="F791" s="17"/>
       <c r="G791" s="17"/>
     </row>
-    <row r="792" spans="2:7">
-      <c r="B792" s="18"/>
+    <row r="792" spans="6:7">
       <c r="F792" s="17"/>
       <c r="G792" s="17"/>
     </row>
-    <row r="793" spans="2:7">
-      <c r="B793" s="18"/>
+    <row r="793" spans="6:7">
       <c r="F793" s="17"/>
       <c r="G793" s="17"/>
     </row>
-    <row r="794" spans="2:7">
-      <c r="B794" s="18"/>
+    <row r="794" spans="6:7">
       <c r="F794" s="17"/>
       <c r="G794" s="17"/>
     </row>
-    <row r="795" spans="2:7">
-      <c r="B795" s="18"/>
+    <row r="795" spans="6:7">
       <c r="F795" s="17"/>
       <c r="G795" s="17"/>
     </row>
-    <row r="796" spans="2:7">
-      <c r="B796" s="18"/>
+    <row r="796" spans="6:7">
       <c r="F796" s="17"/>
       <c r="G796" s="17"/>
     </row>
-    <row r="797" spans="2:7">
-      <c r="B797" s="18"/>
+    <row r="797" spans="6:7">
       <c r="F797" s="17"/>
       <c r="G797" s="17"/>
     </row>
-    <row r="798" spans="2:7">
-      <c r="B798" s="18"/>
+    <row r="798" spans="6:7">
       <c r="F798" s="17"/>
       <c r="G798" s="17"/>
     </row>
-    <row r="799" spans="2:7">
-      <c r="B799" s="18"/>
+    <row r="799" spans="6:7">
       <c r="F799" s="17"/>
       <c r="G799" s="17"/>
     </row>
-    <row r="800" spans="2:7">
-      <c r="B800" s="18"/>
+    <row r="800" spans="6:7">
       <c r="F800" s="17"/>
       <c r="G800" s="17"/>
     </row>
-    <row r="801" spans="2:7">
-      <c r="B801" s="18"/>
+    <row r="801" spans="6:7">
       <c r="F801" s="17"/>
       <c r="G801" s="17"/>
     </row>
-    <row r="802" spans="2:7">
-      <c r="B802" s="18"/>
+    <row r="802" spans="6:7">
       <c r="F802" s="17"/>
       <c r="G802" s="17"/>
     </row>
-    <row r="803" spans="2:7">
-      <c r="B803" s="18"/>
+    <row r="803" spans="6:7">
       <c r="F803" s="17"/>
       <c r="G803" s="17"/>
     </row>
-    <row r="804" spans="2:7">
-      <c r="B804" s="18"/>
+    <row r="804" spans="6:7">
       <c r="F804" s="17"/>
       <c r="G804" s="17"/>
     </row>
-    <row r="805" spans="2:7">
-      <c r="B805" s="18"/>
+    <row r="805" spans="6:7">
       <c r="F805" s="17"/>
       <c r="G805" s="17"/>
     </row>
-    <row r="806" spans="2:7">
-      <c r="B806" s="18"/>
+    <row r="806" spans="6:7">
       <c r="F806" s="17"/>
       <c r="G806" s="17"/>
     </row>
-    <row r="807" spans="2:7">
-      <c r="B807" s="18"/>
+    <row r="807" spans="6:7">
       <c r="F807" s="17"/>
       <c r="G807" s="17"/>
     </row>
-    <row r="808" spans="2:7">
-      <c r="B808" s="18"/>
+    <row r="808" spans="6:7">
       <c r="F808" s="17"/>
       <c r="G808" s="17"/>
     </row>
-    <row r="809" spans="2:7">
-      <c r="B809" s="18"/>
+    <row r="809" spans="6:7">
       <c r="F809" s="17"/>
       <c r="G809" s="17"/>
     </row>
-    <row r="810" spans="2:7">
-      <c r="B810" s="18"/>
+    <row r="810" spans="6:7">
       <c r="F810" s="17"/>
       <c r="G810" s="17"/>
     </row>
-    <row r="811" spans="2:7">
-      <c r="B811" s="18"/>
+    <row r="811" spans="6:7">
       <c r="F811" s="17"/>
       <c r="G811" s="17"/>
     </row>
-    <row r="812" spans="2:7">
-      <c r="B812" s="18"/>
+    <row r="812" spans="6:7">
       <c r="F812" s="17"/>
       <c r="G812" s="17"/>
     </row>
-    <row r="813" spans="2:7">
-      <c r="B813" s="18"/>
+    <row r="813" spans="6:7">
       <c r="F813" s="17"/>
       <c r="G813" s="17"/>
     </row>
-    <row r="814" spans="2:7">
-      <c r="B814" s="18"/>
+    <row r="814" spans="6:7">
       <c r="F814" s="17"/>
       <c r="G814" s="17"/>
     </row>
-    <row r="815" spans="2:7">
-      <c r="B815" s="18"/>
+    <row r="815" spans="6:7">
       <c r="F815" s="17"/>
       <c r="G815" s="17"/>
     </row>
-    <row r="816" spans="2:7">
-      <c r="B816" s="18"/>
+    <row r="816" spans="6:7">
       <c r="F816" s="17"/>
       <c r="G816" s="17"/>
     </row>
-    <row r="817" spans="2:7">
-      <c r="B817" s="18"/>
+    <row r="817" spans="6:7">
       <c r="F817" s="17"/>
       <c r="G817" s="17"/>
     </row>
-    <row r="818" spans="2:7">
-      <c r="B818" s="18"/>
+    <row r="818" spans="6:7">
       <c r="F818" s="17"/>
       <c r="G818" s="17"/>
     </row>
-    <row r="819" spans="2:7">
-      <c r="B819" s="18"/>
+    <row r="819" spans="6:7">
       <c r="F819" s="17"/>
       <c r="G819" s="17"/>
     </row>
-    <row r="820" spans="2:7">
-      <c r="B820" s="18"/>
+    <row r="820" spans="6:7">
       <c r="F820" s="17"/>
       <c r="G820" s="17"/>
     </row>
-    <row r="821" spans="2:7">
-      <c r="B821" s="18"/>
+    <row r="821" spans="6:7">
       <c r="F821" s="17"/>
       <c r="G821" s="17"/>
     </row>
-    <row r="822" spans="2:7">
-      <c r="B822" s="18"/>
+    <row r="822" spans="6:7">
       <c r="F822" s="17"/>
       <c r="G822" s="17"/>
     </row>
-    <row r="823" spans="2:7">
-      <c r="B823" s="18"/>
+    <row r="823" spans="6:7">
       <c r="F823" s="17"/>
       <c r="G823" s="17"/>
     </row>
-    <row r="824" spans="2:7">
-      <c r="B824" s="18"/>
+    <row r="824" spans="6:7">
       <c r="F824" s="17"/>
       <c r="G824" s="17"/>
     </row>
-    <row r="825" spans="2:7">
-      <c r="B825" s="18"/>
+    <row r="825" spans="6:7">
       <c r="F825" s="17"/>
       <c r="G825" s="17"/>
     </row>
-    <row r="826" spans="2:7">
-      <c r="B826" s="18"/>
+    <row r="826" spans="6:7">
       <c r="F826" s="17"/>
       <c r="G826" s="17"/>
     </row>
-    <row r="827" spans="2:7">
-      <c r="B827" s="18"/>
+    <row r="827" spans="6:7">
       <c r="F827" s="17"/>
       <c r="G827" s="17"/>
     </row>
-    <row r="828" spans="2:7">
-      <c r="B828" s="18"/>
+    <row r="828" spans="6:7">
       <c r="F828" s="17"/>
       <c r="G828" s="17"/>
     </row>
-    <row r="829" spans="2:7">
-      <c r="B829" s="18"/>
+    <row r="829" spans="6:7">
       <c r="F829" s="17"/>
       <c r="G829" s="17"/>
     </row>
-    <row r="830" spans="2:7">
-      <c r="B830" s="18"/>
+    <row r="830" spans="6:7">
       <c r="F830" s="17"/>
       <c r="G830" s="17"/>
     </row>
-    <row r="831" spans="2:7">
-      <c r="B831" s="18"/>
+    <row r="831" spans="6:7">
       <c r="F831" s="17"/>
       <c r="G831" s="17"/>
     </row>
-    <row r="832" spans="2:7">
-      <c r="B832" s="18"/>
+    <row r="832" spans="6:7">
       <c r="F832" s="17"/>
       <c r="G832" s="17"/>
     </row>
-    <row r="833" spans="2:7">
-      <c r="B833" s="18"/>
+    <row r="833" spans="6:7">
       <c r="F833" s="17"/>
       <c r="G833" s="17"/>
     </row>
-    <row r="834" spans="2:7">
-      <c r="B834" s="18"/>
+    <row r="834" spans="6:7">
       <c r="F834" s="17"/>
       <c r="G834" s="17"/>
     </row>
-    <row r="835" spans="2:7">
-      <c r="B835" s="18"/>
+    <row r="835" spans="6:7">
       <c r="F835" s="17"/>
       <c r="G835" s="17"/>
     </row>
-    <row r="836" spans="2:7">
-      <c r="B836" s="18"/>
+    <row r="836" spans="6:7">
       <c r="F836" s="17"/>
       <c r="G836" s="17"/>
     </row>
-    <row r="837" spans="2:7">
-      <c r="B837" s="18"/>
+    <row r="837" spans="6:7">
       <c r="F837" s="17"/>
       <c r="G837" s="17"/>
     </row>
-    <row r="838" spans="2:7">
-      <c r="B838" s="18"/>
+    <row r="838" spans="6:7">
       <c r="F838" s="17"/>
       <c r="G838" s="17"/>
     </row>
-    <row r="839" spans="2:7">
-      <c r="B839" s="18"/>
+    <row r="839" spans="6:7">
       <c r="F839" s="17"/>
       <c r="G839" s="17"/>
     </row>
-    <row r="840" spans="2:7">
-      <c r="B840" s="18"/>
+    <row r="840" spans="6:7">
       <c r="F840" s="17"/>
       <c r="G840" s="17"/>
     </row>
-    <row r="841" spans="2:7">
-      <c r="B841" s="18"/>
+    <row r="841" spans="6:7">
       <c r="F841" s="17"/>
       <c r="G841" s="17"/>
     </row>
-    <row r="842" spans="2:7">
-      <c r="B842" s="18"/>
+    <row r="842" spans="6:7">
       <c r="F842" s="17"/>
       <c r="G842" s="17"/>
     </row>
-    <row r="843" spans="2:7">
-      <c r="B843" s="18"/>
+    <row r="843" spans="6:7">
       <c r="F843" s="17"/>
       <c r="G843" s="17"/>
     </row>
-    <row r="844" spans="2:7">
-      <c r="B844" s="18"/>
+    <row r="844" spans="6:7">
       <c r="F844" s="17"/>
       <c r="G844" s="17"/>
     </row>
-    <row r="845" spans="2:7">
-      <c r="B845" s="18"/>
+    <row r="845" spans="6:7">
       <c r="F845" s="17"/>
       <c r="G845" s="17"/>
     </row>
-    <row r="846" spans="2:7">
-      <c r="B846" s="18"/>
+    <row r="846" spans="6:7">
       <c r="F846" s="17"/>
       <c r="G846" s="17"/>
     </row>
-    <row r="847" spans="2:7">
-      <c r="B847" s="18"/>
+    <row r="847" spans="6:7">
       <c r="F847" s="17"/>
       <c r="G847" s="17"/>
     </row>
-    <row r="848" spans="2:7">
-      <c r="B848" s="18"/>
+    <row r="848" spans="6:7">
       <c r="F848" s="17"/>
       <c r="G848" s="17"/>
     </row>
-    <row r="849" spans="2:7">
-      <c r="B849" s="18"/>
+    <row r="849" spans="6:7">
       <c r="F849" s="17"/>
       <c r="G849" s="17"/>
     </row>
-    <row r="850" spans="2:7">
-      <c r="B850" s="18"/>
+    <row r="850" spans="6:7">
       <c r="F850" s="17"/>
       <c r="G850" s="17"/>
     </row>
-    <row r="851" spans="2:7">
-      <c r="B851" s="18"/>
+    <row r="851" spans="6:7">
       <c r="F851" s="17"/>
       <c r="G851" s="17"/>
     </row>
-    <row r="852" spans="2:7">
-      <c r="B852" s="18"/>
+    <row r="852" spans="6:7">
       <c r="F852" s="17"/>
       <c r="G852" s="17"/>
     </row>
-    <row r="853" spans="2:7">
-      <c r="B853" s="18"/>
+    <row r="853" spans="6:7">
       <c r="F853" s="17"/>
       <c r="G853" s="17"/>
     </row>
-    <row r="854" spans="2:7">
-      <c r="B854" s="18"/>
+    <row r="854" spans="6:7">
       <c r="F854" s="17"/>
       <c r="G854" s="17"/>
     </row>
-    <row r="855" spans="2:7">
-      <c r="B855" s="18"/>
+    <row r="855" spans="6:7">
       <c r="F855" s="17"/>
       <c r="G855" s="17"/>
     </row>
-    <row r="856" spans="2:7">
-      <c r="B856" s="18"/>
+    <row r="856" spans="6:7">
       <c r="F856" s="17"/>
       <c r="G856" s="17"/>
     </row>
-    <row r="857" spans="2:7">
-      <c r="B857" s="18"/>
+    <row r="857" spans="6:7">
       <c r="F857" s="17"/>
       <c r="G857" s="17"/>
     </row>
-    <row r="858" spans="2:7">
-      <c r="B858" s="18"/>
+    <row r="858" spans="6:7">
       <c r="F858" s="17"/>
       <c r="G858" s="17"/>
     </row>
-    <row r="859" spans="2:7">
-      <c r="B859" s="18"/>
+    <row r="859" spans="6:7">
       <c r="F859" s="17"/>
       <c r="G859" s="17"/>
     </row>
-    <row r="860" spans="2:7">
-      <c r="B860" s="18"/>
+    <row r="860" spans="6:7">
       <c r="F860" s="17"/>
       <c r="G860" s="17"/>
     </row>
-    <row r="861" spans="2:7">
-      <c r="B861" s="18"/>
+    <row r="861" spans="6:7">
       <c r="F861" s="17"/>
       <c r="G861" s="17"/>
     </row>
-    <row r="862" spans="2:7">
-      <c r="B862" s="18"/>
+    <row r="862" spans="6:7">
       <c r="F862" s="17"/>
       <c r="G862" s="17"/>
     </row>
-    <row r="863" spans="2:7">
-      <c r="B863" s="18"/>
+    <row r="863" spans="6:7">
       <c r="F863" s="17"/>
       <c r="G863" s="17"/>
     </row>
-    <row r="864" spans="2:7">
-      <c r="B864" s="18"/>
+    <row r="864" spans="6:7">
       <c r="F864" s="17"/>
       <c r="G864" s="17"/>
     </row>
-    <row r="865" spans="2:7">
-      <c r="B865" s="18"/>
+    <row r="865" spans="6:7">
       <c r="F865" s="17"/>
       <c r="G865" s="17"/>
     </row>
-    <row r="866" spans="2:7">
-      <c r="B866" s="18"/>
+    <row r="866" spans="6:7">
       <c r="F866" s="17"/>
       <c r="G866" s="17"/>
     </row>
-    <row r="867" spans="2:7">
-      <c r="B867" s="18"/>
+    <row r="867" spans="6:7">
       <c r="F867" s="17"/>
       <c r="G867" s="17"/>
     </row>
-    <row r="868" spans="2:7">
-      <c r="B868" s="18"/>
+    <row r="868" spans="6:7">
       <c r="F868" s="17"/>
       <c r="G868" s="17"/>
     </row>
-    <row r="869" spans="2:7">
-      <c r="B869" s="18"/>
+    <row r="869" spans="6:7">
       <c r="F869" s="17"/>
       <c r="G869" s="17"/>
     </row>
-    <row r="870" spans="2:7">
-      <c r="B870" s="18"/>
+    <row r="870" spans="6:7">
       <c r="F870" s="17"/>
       <c r="G870" s="17"/>
     </row>
-    <row r="871" spans="2:7">
-      <c r="B871" s="18"/>
+    <row r="871" spans="6:7">
       <c r="F871" s="17"/>
       <c r="G871" s="17"/>
     </row>
-    <row r="872" spans="2:7">
-      <c r="B872" s="18"/>
+    <row r="872" spans="6:7">
       <c r="F872" s="17"/>
       <c r="G872" s="17"/>
     </row>
-    <row r="873" spans="2:7">
-      <c r="B873" s="18"/>
+    <row r="873" spans="6:7">
       <c r="F873" s="17"/>
       <c r="G873" s="17"/>
     </row>
-    <row r="874" spans="2:7">
-      <c r="B874" s="18"/>
+    <row r="874" spans="6:7">
       <c r="F874" s="17"/>
       <c r="G874" s="17"/>
     </row>
-    <row r="875" spans="2:7">
-      <c r="B875" s="18"/>
+    <row r="875" spans="6:7">
       <c r="F875" s="17"/>
       <c r="G875" s="17"/>
     </row>
-    <row r="876" spans="2:7">
-      <c r="B876" s="18"/>
+    <row r="876" spans="6:7">
       <c r="F876" s="17"/>
       <c r="G876" s="17"/>
     </row>
-    <row r="877" spans="2:7">
-      <c r="B877" s="18"/>
+    <row r="877" spans="6:7">
       <c r="F877" s="17"/>
       <c r="G877" s="17"/>
     </row>
-    <row r="878" spans="2:7">
-      <c r="B878" s="18"/>
+    <row r="878" spans="6:7">
       <c r="F878" s="17"/>
       <c r="G878" s="17"/>
     </row>
-    <row r="879" spans="2:7">
-      <c r="B879" s="18"/>
+    <row r="879" spans="6:7">
       <c r="F879" s="17"/>
       <c r="G879" s="17"/>
     </row>
-    <row r="880" spans="2:7">
-      <c r="B880" s="18"/>
+    <row r="880" spans="6:7">
       <c r="F880" s="17"/>
       <c r="G880" s="17"/>
     </row>
-    <row r="881" spans="2:7">
-      <c r="B881" s="18"/>
+    <row r="881" spans="6:7">
       <c r="F881" s="17"/>
       <c r="G881" s="17"/>
     </row>
-    <row r="882" spans="2:7">
-      <c r="B882" s="18"/>
+    <row r="882" spans="6:7">
       <c r="F882" s="17"/>
       <c r="G882" s="17"/>
     </row>
-    <row r="883" spans="2:7">
-      <c r="B883" s="18"/>
+    <row r="883" spans="6:7">
       <c r="F883" s="17"/>
       <c r="G883" s="17"/>
     </row>
-    <row r="884" spans="2:7">
-      <c r="B884" s="18"/>
+    <row r="884" spans="6:7">
       <c r="F884" s="17"/>
       <c r="G884" s="17"/>
     </row>
-    <row r="885" spans="2:7">
-      <c r="B885" s="18"/>
+    <row r="885" spans="6:7">
       <c r="F885" s="17"/>
       <c r="G885" s="17"/>
     </row>
-    <row r="886" spans="2:7">
-      <c r="B886" s="18"/>
+    <row r="886" spans="6:7">
       <c r="F886" s="17"/>
       <c r="G886" s="17"/>
     </row>
-    <row r="887" spans="2:7">
-      <c r="B887" s="18"/>
+    <row r="887" spans="6:7">
       <c r="F887" s="17"/>
       <c r="G887" s="17"/>
     </row>
-    <row r="888" spans="2:7">
-      <c r="B888" s="18"/>
+    <row r="888" spans="6:7">
       <c r="F888" s="17"/>
       <c r="G888" s="17"/>
     </row>
-    <row r="889" spans="2:7">
-      <c r="B889" s="18"/>
+    <row r="889" spans="6:7">
       <c r="F889" s="17"/>
       <c r="G889" s="17"/>
     </row>
-    <row r="890" spans="2:7">
-      <c r="B890" s="18"/>
+    <row r="890" spans="6:7">
       <c r="F890" s="17"/>
       <c r="G890" s="17"/>
     </row>
-    <row r="891" spans="2:7">
-      <c r="B891" s="18"/>
+    <row r="891" spans="6:7">
       <c r="F891" s="17"/>
       <c r="G891" s="17"/>
     </row>
-    <row r="892" spans="2:7">
-      <c r="B892" s="18"/>
+    <row r="892" spans="6:7">
       <c r="F892" s="17"/>
       <c r="G892" s="17"/>
     </row>
-    <row r="893" spans="2:7">
-      <c r="B893" s="18"/>
+    <row r="893" spans="6:7">
       <c r="F893" s="17"/>
       <c r="G893" s="17"/>
     </row>
-    <row r="894" spans="2:7">
-      <c r="B894" s="18"/>
+    <row r="894" spans="6:7">
       <c r="F894" s="17"/>
       <c r="G894" s="17"/>
     </row>
-    <row r="895" spans="2:7">
-      <c r="B895" s="18"/>
+    <row r="895" spans="6:7">
       <c r="F895" s="17"/>
       <c r="G895" s="17"/>
     </row>
-    <row r="896" spans="2:7">
-      <c r="B896" s="18"/>
+    <row r="896" spans="6:7">
       <c r="F896" s="17"/>
       <c r="G896" s="17"/>
     </row>
-    <row r="897" spans="2:7">
-      <c r="B897" s="18"/>
+    <row r="897" spans="6:7">
       <c r="F897" s="17"/>
       <c r="G897" s="17"/>
     </row>
-    <row r="898" spans="2:7">
-      <c r="B898" s="18"/>
+    <row r="898" spans="6:7">
       <c r="F898" s="17"/>
       <c r="G898" s="17"/>
     </row>
-    <row r="899" spans="2:7">
-      <c r="B899" s="18"/>
+    <row r="899" spans="6:7">
       <c r="F899" s="17"/>
       <c r="G899" s="17"/>
     </row>
-    <row r="900" spans="2:7">
-      <c r="B900" s="18"/>
+    <row r="900" spans="6:7">
       <c r="F900" s="17"/>
       <c r="G900" s="17"/>
     </row>
-    <row r="901" spans="2:7">
-      <c r="B901" s="18"/>
+    <row r="901" spans="6:7">
       <c r="F901" s="17"/>
       <c r="G901" s="17"/>
     </row>
-    <row r="902" spans="2:7">
-      <c r="B902" s="18"/>
+    <row r="902" spans="6:7">
       <c r="F902" s="17"/>
       <c r="G902" s="17"/>
     </row>
-    <row r="903" spans="2:7">
-      <c r="B903" s="18"/>
+    <row r="903" spans="6:7">
       <c r="F903" s="17"/>
       <c r="G903" s="17"/>
     </row>
-    <row r="904" spans="2:7">
-      <c r="B904" s="18"/>
+    <row r="904" spans="6:7">
       <c r="F904" s="17"/>
       <c r="G904" s="17"/>
     </row>
-    <row r="905" spans="2:7">
-      <c r="B905" s="18"/>
+    <row r="905" spans="6:7">
       <c r="F905" s="17"/>
       <c r="G905" s="17"/>
     </row>
-    <row r="906" spans="2:7">
-      <c r="B906" s="18"/>
+    <row r="906" spans="6:7">
       <c r="F906" s="17"/>
       <c r="G906" s="17"/>
     </row>
-    <row r="907" spans="2:7">
-      <c r="B907" s="18"/>
+    <row r="907" spans="6:7">
       <c r="F907" s="17"/>
       <c r="G907" s="17"/>
     </row>
-    <row r="908" spans="2:7">
-      <c r="B908" s="18"/>
+    <row r="908" spans="6:7">
       <c r="F908" s="17"/>
       <c r="G908" s="17"/>
     </row>
-    <row r="909" spans="2:7">
-      <c r="B909" s="18"/>
+    <row r="909" spans="6:7">
       <c r="F909" s="17"/>
       <c r="G909" s="17"/>
     </row>
-    <row r="910" spans="2:7">
-      <c r="B910" s="18"/>
+    <row r="910" spans="6:7">
       <c r="F910" s="17"/>
       <c r="G910" s="17"/>
     </row>
-    <row r="911" spans="2:7">
-      <c r="B911" s="18"/>
+    <row r="911" spans="6:7">
       <c r="F911" s="17"/>
       <c r="G911" s="17"/>
     </row>
-    <row r="912" spans="2:7">
-      <c r="B912" s="18"/>
+    <row r="912" spans="6:7">
       <c r="F912" s="17"/>
       <c r="G912" s="17"/>
     </row>
-    <row r="913" spans="2:7">
-      <c r="B913" s="18"/>
+    <row r="913" spans="6:7">
       <c r="F913" s="17"/>
       <c r="G913" s="17"/>
     </row>
-    <row r="914" spans="2:7">
-      <c r="B914" s="18"/>
+    <row r="914" spans="6:7">
       <c r="F914" s="17"/>
       <c r="G914" s="17"/>
     </row>
-    <row r="915" spans="2:7">
-      <c r="B915" s="18"/>
+    <row r="915" spans="6:7">
       <c r="F915" s="17"/>
       <c r="G915" s="17"/>
     </row>
-    <row r="916" spans="2:7">
-      <c r="B916" s="18"/>
+    <row r="916" spans="6:7">
       <c r="F916" s="17"/>
       <c r="G916" s="17"/>
     </row>
-    <row r="917" spans="2:7">
-      <c r="B917" s="18"/>
+    <row r="917" spans="6:7">
       <c r="F917" s="17"/>
       <c r="G917" s="17"/>
     </row>
-    <row r="918" spans="2:7">
-      <c r="B918" s="18"/>
+    <row r="918" spans="6:7">
       <c r="F918" s="17"/>
       <c r="G918" s="17"/>
     </row>
-    <row r="919" spans="2:7">
-      <c r="B919" s="18"/>
+    <row r="919" spans="6:7">
       <c r="F919" s="17"/>
       <c r="G919" s="17"/>
     </row>
-    <row r="920" spans="2:7">
-      <c r="B920" s="18"/>
+    <row r="920" spans="6:7">
       <c r="F920" s="17"/>
       <c r="G920" s="17"/>
     </row>
-    <row r="921" spans="2:7">
-      <c r="B921" s="18"/>
+    <row r="921" spans="6:7">
       <c r="F921" s="17"/>
       <c r="G921" s="17"/>
     </row>
-    <row r="922" spans="2:7">
-      <c r="B922" s="18"/>
+    <row r="922" spans="6:7">
       <c r="F922" s="17"/>
       <c r="G922" s="17"/>
     </row>
-    <row r="923" spans="2:7">
-      <c r="B923" s="18"/>
+    <row r="923" spans="6:7">
       <c r="F923" s="17"/>
       <c r="G923" s="17"/>
     </row>
-    <row r="924" spans="2:7">
-      <c r="B924" s="18"/>
+    <row r="924" spans="6:7">
       <c r="F924" s="17"/>
       <c r="G924" s="17"/>
     </row>
-    <row r="925" spans="2:7">
-      <c r="B925" s="18"/>
+    <row r="925" spans="6:7">
       <c r="F925" s="17"/>
       <c r="G925" s="17"/>
     </row>
-    <row r="926" spans="2:7">
-      <c r="B926" s="18"/>
+    <row r="926" spans="6:7">
       <c r="F926" s="17"/>
       <c r="G926" s="17"/>
     </row>
-    <row r="927" spans="2:7">
-      <c r="B927" s="18"/>
+    <row r="927" spans="6:7">
       <c r="F927" s="17"/>
       <c r="G927" s="17"/>
     </row>
-    <row r="928" spans="2:7">
-      <c r="B928" s="18"/>
+    <row r="928" spans="6:7">
       <c r="F928" s="17"/>
       <c r="G928" s="17"/>
     </row>
-    <row r="929" spans="2:7">
-      <c r="B929" s="18"/>
+    <row r="929" spans="6:7">
       <c r="F929" s="17"/>
       <c r="G929" s="17"/>
     </row>
-    <row r="930" spans="2:7">
-      <c r="B930" s="18"/>
+    <row r="930" spans="6:7">
       <c r="F930" s="17"/>
       <c r="G930" s="17"/>
     </row>
-    <row r="931" spans="2:7">
-      <c r="B931" s="18"/>
+    <row r="931" spans="6:7">
       <c r="F931" s="17"/>
       <c r="G931" s="17"/>
     </row>
-    <row r="932" spans="2:7">
-      <c r="B932" s="18"/>
+    <row r="932" spans="6:7">
       <c r="F932" s="17"/>
       <c r="G932" s="17"/>
     </row>
-    <row r="933" spans="2:7">
-      <c r="B933" s="18"/>
+    <row r="933" spans="6:7">
       <c r="F933" s="17"/>
       <c r="G933" s="17"/>
     </row>
-    <row r="934" spans="2:7">
-      <c r="B934" s="18"/>
+    <row r="934" spans="6:7">
       <c r="F934" s="17"/>
       <c r="G934" s="17"/>
     </row>
-    <row r="935" spans="2:7">
-      <c r="B935" s="18"/>
+    <row r="935" spans="6:7">
       <c r="F935" s="17"/>
       <c r="G935" s="17"/>
     </row>
-    <row r="936" spans="2:7">
-      <c r="B936" s="18"/>
+    <row r="936" spans="6:7">
       <c r="F936" s="17"/>
       <c r="G936" s="17"/>
     </row>
-    <row r="937" spans="2:7">
-      <c r="B937" s="18"/>
+    <row r="937" spans="6:7">
       <c r="F937" s="17"/>
       <c r="G937" s="17"/>
     </row>
-    <row r="938" spans="2:7">
-      <c r="B938" s="18"/>
+    <row r="938" spans="6:7">
       <c r="F938" s="17"/>
       <c r="G938" s="17"/>
     </row>
-    <row r="939" spans="2:7">
-      <c r="B939" s="18"/>
+    <row r="939" spans="6:7">
       <c r="F939" s="17"/>
       <c r="G939" s="17"/>
     </row>
-    <row r="940" spans="2:7">
-      <c r="B940" s="18"/>
+    <row r="940" spans="6:7">
       <c r="F940" s="17"/>
       <c r="G940" s="17"/>
     </row>
-    <row r="941" spans="2:7">
-      <c r="B941" s="18"/>
+    <row r="941" spans="6:7">
       <c r="F941" s="17"/>
       <c r="G941" s="17"/>
     </row>
-    <row r="942" spans="2:7">
-      <c r="B942" s="18"/>
+    <row r="942" spans="6:7">
       <c r="F942" s="17"/>
       <c r="G942" s="17"/>
     </row>
-    <row r="943" spans="2:7">
-      <c r="B943" s="18"/>
+    <row r="943" spans="6:7">
       <c r="F943" s="17"/>
       <c r="G943" s="17"/>
     </row>
-    <row r="944" spans="2:7">
-      <c r="B944" s="18"/>
+    <row r="944" spans="6:7">
       <c r="F944" s="17"/>
       <c r="G944" s="17"/>
     </row>
-    <row r="945" spans="2:7">
-      <c r="B945" s="18"/>
+    <row r="945" spans="6:7">
       <c r="F945" s="17"/>
       <c r="G945" s="17"/>
     </row>
-    <row r="946" spans="2:7">
-      <c r="B946" s="18"/>
+    <row r="946" spans="6:7">
       <c r="F946" s="17"/>
       <c r="G946" s="17"/>
     </row>
-    <row r="947" spans="2:7">
-      <c r="B947" s="18"/>
+    <row r="947" spans="6:7">
       <c r="F947" s="17"/>
       <c r="G947" s="17"/>
     </row>
-    <row r="948" spans="2:7">
-      <c r="B948" s="18"/>
+    <row r="948" spans="6:7">
       <c r="F948" s="17"/>
       <c r="G948" s="17"/>
     </row>
-    <row r="949" spans="2:7">
-      <c r="B949" s="18"/>
+    <row r="949" spans="6:7">
       <c r="F949" s="17"/>
       <c r="G949" s="17"/>
     </row>
-    <row r="950" spans="2:7">
-      <c r="B950" s="18"/>
+    <row r="950" spans="6:7">
       <c r="F950" s="17"/>
       <c r="G950" s="17"/>
     </row>
-    <row r="951" spans="2:7">
-      <c r="B951" s="18"/>
+    <row r="951" spans="6:7">
       <c r="F951" s="17"/>
       <c r="G951" s="17"/>
     </row>
-    <row r="952" spans="2:7">
-      <c r="B952" s="18"/>
+    <row r="952" spans="6:7">
       <c r="F952" s="17"/>
       <c r="G952" s="17"/>
     </row>
-    <row r="953" spans="2:7">
-      <c r="B953" s="18"/>
+    <row r="953" spans="6:7">
       <c r="F953" s="17"/>
       <c r="G953" s="17"/>
     </row>
-    <row r="954" spans="2:7">
-      <c r="B954" s="18"/>
+    <row r="954" spans="6:7">
       <c r="F954" s="17"/>
       <c r="G954" s="17"/>
     </row>
-    <row r="955" spans="2:7">
-      <c r="B955" s="18"/>
+    <row r="955" spans="6:7">
       <c r="F955" s="17"/>
       <c r="G955" s="17"/>
     </row>
-    <row r="956" spans="2:7">
-      <c r="B956" s="18"/>
+    <row r="956" spans="6:7">
       <c r="F956" s="17"/>
       <c r="G956" s="17"/>
     </row>
-    <row r="957" spans="2:7">
-      <c r="B957" s="18"/>
+    <row r="957" spans="6:7">
       <c r="F957" s="17"/>
       <c r="G957" s="17"/>
     </row>
-    <row r="958" spans="2:7">
-      <c r="B958" s="18"/>
+    <row r="958" spans="6:7">
       <c r="F958" s="17"/>
       <c r="G958" s="17"/>
     </row>
-    <row r="959" spans="2:7">
-      <c r="B959" s="18"/>
+    <row r="959" spans="6:7">
       <c r="F959" s="17"/>
       <c r="G959" s="17"/>
     </row>
-    <row r="960" spans="2:7">
-      <c r="B960" s="18"/>
+    <row r="960" spans="6:7">
       <c r="F960" s="17"/>
       <c r="G960" s="17"/>
     </row>
-    <row r="961" spans="2:7">
-      <c r="B961" s="18"/>
+    <row r="961" spans="6:7">
       <c r="F961" s="17"/>
       <c r="G961" s="17"/>
     </row>
-    <row r="962" spans="2:7">
-      <c r="B962" s="18"/>
+    <row r="962" spans="6:7">
       <c r="F962" s="17"/>
       <c r="G962" s="17"/>
     </row>
-    <row r="963" spans="2:7">
-      <c r="B963" s="18"/>
+    <row r="963" spans="6:7">
       <c r="F963" s="17"/>
       <c r="G963" s="17"/>
     </row>
-    <row r="964" spans="2:7">
-      <c r="B964" s="18"/>
+    <row r="964" spans="6:7">
       <c r="F964" s="17"/>
       <c r="G964" s="17"/>
     </row>
-    <row r="965" spans="2:7">
-      <c r="B965" s="18"/>
+    <row r="965" spans="6:7">
       <c r="F965" s="17"/>
       <c r="G965" s="17"/>
     </row>
-    <row r="966" spans="2:7">
-      <c r="B966" s="18"/>
+    <row r="966" spans="6:7">
       <c r="F966" s="17"/>
       <c r="G966" s="17"/>
     </row>
-    <row r="967" spans="2:7">
-      <c r="B967" s="18"/>
+    <row r="967" spans="6:7">
       <c r="F967" s="17"/>
       <c r="G967" s="17"/>
     </row>
-    <row r="968" spans="2:7">
-      <c r="B968" s="18"/>
+    <row r="968" spans="6:7">
       <c r="F968" s="17"/>
       <c r="G968" s="17"/>
     </row>
-    <row r="969" spans="2:7">
-      <c r="B969" s="18"/>
+    <row r="969" spans="6:7">
       <c r="F969" s="17"/>
       <c r="G969" s="17"/>
     </row>
-    <row r="970" spans="2:7">
-      <c r="B970" s="18"/>
+    <row r="970" spans="6:7">
       <c r="F970" s="17"/>
       <c r="G970" s="17"/>
     </row>
-    <row r="971" spans="2:7">
-      <c r="B971" s="18"/>
+    <row r="971" spans="6:7">
       <c r="F971" s="17"/>
       <c r="G971" s="17"/>
     </row>
-    <row r="972" spans="2:7">
-      <c r="B972" s="18"/>
+    <row r="972" spans="6:7">
       <c r="F972" s="17"/>
       <c r="G972" s="17"/>
     </row>
-    <row r="973" spans="2:7">
-      <c r="B973" s="18"/>
+    <row r="973" spans="6:7">
       <c r="F973" s="17"/>
       <c r="G973" s="17"/>
     </row>
-    <row r="974" spans="2:7">
-      <c r="B974" s="18"/>
+    <row r="974" spans="6:7">
       <c r="F974" s="17"/>
       <c r="G974" s="17"/>
     </row>
-    <row r="975" spans="2:7">
-      <c r="B975" s="18"/>
+    <row r="975" spans="6:7">
       <c r="F975" s="17"/>
       <c r="G975" s="17"/>
     </row>
-    <row r="976" spans="2:7">
-      <c r="B976" s="18"/>
+    <row r="976" spans="6:7">
       <c r="F976" s="17"/>
       <c r="G976" s="17"/>
     </row>
-    <row r="977" spans="2:7">
-      <c r="B977" s="18"/>
+    <row r="977" spans="6:7">
       <c r="F977" s="17"/>
       <c r="G977" s="17"/>
     </row>
-    <row r="978" spans="2:7">
-      <c r="B978" s="18"/>
+    <row r="978" spans="6:7">
       <c r="F978" s="17"/>
       <c r="G978" s="17"/>
     </row>
-    <row r="979" spans="2:7">
-      <c r="B979" s="18"/>
+    <row r="979" spans="6:7">
       <c r="F979" s="17"/>
       <c r="G979" s="17"/>
     </row>
-    <row r="980" spans="2:7">
-      <c r="B980" s="18"/>
+    <row r="980" spans="6:7">
       <c r="F980" s="17"/>
       <c r="G980" s="17"/>
     </row>
-    <row r="981" spans="2:7">
-      <c r="B981" s="18"/>
+    <row r="981" spans="6:7">
       <c r="F981" s="17"/>
       <c r="G981" s="17"/>
     </row>
-    <row r="982" spans="2:7">
-      <c r="B982" s="18"/>
+    <row r="982" spans="6:7">
       <c r="F982" s="17"/>
       <c r="G982" s="17"/>
     </row>
-    <row r="983" spans="2:7">
-      <c r="B983" s="18"/>
+    <row r="983" spans="6:7">
       <c r="F983" s="17"/>
       <c r="G983" s="17"/>
     </row>
-    <row r="984" spans="2:7">
-      <c r="B984" s="18"/>
+    <row r="984" spans="6:7">
       <c r="F984" s="17"/>
       <c r="G984" s="17"/>
     </row>
-    <row r="985" spans="2:7">
-      <c r="B985" s="18"/>
+    <row r="985" spans="6:7">
       <c r="F985" s="17"/>
       <c r="G985" s="17"/>
     </row>
-    <row r="986" spans="2:7">
-      <c r="B986" s="18"/>
+    <row r="986" spans="6:7">
       <c r="F986" s="17"/>
       <c r="G986" s="17"/>
     </row>
-    <row r="987" spans="2:7">
-      <c r="B987" s="18"/>
+    <row r="987" spans="6:7">
       <c r="F987" s="17"/>
       <c r="G987" s="17"/>
     </row>
-    <row r="988" spans="2:7">
-      <c r="B988" s="18"/>
+    <row r="988" spans="6:7">
       <c r="F988" s="17"/>
       <c r="G988" s="17"/>
     </row>
-    <row r="989" spans="2:7">
-      <c r="B989" s="18"/>
+    <row r="989" spans="6:7">
       <c r="F989" s="17"/>
       <c r="G989" s="17"/>
     </row>
-    <row r="990" spans="2:7">
-      <c r="B990" s="18"/>
+    <row r="990" spans="6:7">
       <c r="F990" s="17"/>
       <c r="G990" s="17"/>
     </row>
-    <row r="991" spans="2:7">
-      <c r="B991" s="18"/>
+    <row r="991" spans="6:7">
       <c r="F991" s="17"/>
       <c r="G991" s="17"/>
     </row>
-    <row r="992" spans="2:7">
-      <c r="B992" s="18"/>
+    <row r="992" spans="6:7">
       <c r="F992" s="17"/>
       <c r="G992" s="17"/>
     </row>
-    <row r="993" spans="2:7">
-      <c r="B993" s="18"/>
+    <row r="993" spans="6:7">
       <c r="F993" s="17"/>
       <c r="G993" s="17"/>
     </row>
-    <row r="994" spans="2:7">
-      <c r="B994" s="18"/>
+    <row r="994" spans="6:7">
       <c r="F994" s="17"/>
       <c r="G994" s="17"/>
     </row>
-    <row r="995" spans="2:7">
-      <c r="B995" s="18"/>
+    <row r="995" spans="6:7">
       <c r="F995" s="17"/>
       <c r="G995" s="17"/>
     </row>
-    <row r="996" spans="2:7">
-      <c r="B996" s="18"/>
+    <row r="996" spans="6:7">
       <c r="F996" s="17"/>
       <c r="G996" s="17"/>
     </row>
-    <row r="997" spans="2:7">
-      <c r="B997" s="18"/>
+    <row r="997" spans="6:7">
       <c r="F997" s="17"/>
       <c r="G997" s="17"/>
     </row>
-    <row r="998" spans="2:7">
-      <c r="B998" s="18"/>
+    <row r="998" spans="6:7">
       <c r="F998" s="17"/>
       <c r="G998" s="17"/>
     </row>
@@ -12154,10 +10529,10 @@
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation prompt="Select an OCI Region." sqref="L2:N3" xr:uid="{1E46C41F-6262-7448-8DA8-92CFFA998264}"/>
-    <dataValidation allowBlank="1" sqref="B2:D2" xr:uid="{641C78C6-B1C0-AF42-9F74-CEE2D1F3801A}"/>
-    <dataValidation showInputMessage="1" showErrorMessage="1" prompt="Select an OCI Region." sqref="L1:N1 L4:N1048576" xr:uid="{9D79D58B-5C8E-8F4C-B869-381A3AF9A9BE}"/>
-    <dataValidation allowBlank="1" prompt="Select an OCI Region." sqref="F1:G2 I1:I2 A1:A2 B1:D1 E1:E1048576 J1:K1048576 H1:H1048576 D3:D1048576 O1:P1 O3:P1048576 Q1:XFD1048576" xr:uid="{CAF04EC2-946A-3446-84D0-EA50102CA3F4}"/>
+    <dataValidation prompt="Select an OCI Region." sqref="L2:N4" xr:uid="{1E46C41F-6262-7448-8DA8-92CFFA998264}"/>
+    <dataValidation showInputMessage="1" showErrorMessage="1" prompt="Select an OCI Region." sqref="L1:N1 L5:N1048576" xr:uid="{9D79D58B-5C8E-8F4C-B869-381A3AF9A9BE}"/>
+    <dataValidation allowBlank="1" prompt="Select an OCI Region." sqref="I5:I1048576 O1:XFD1 A2 Q5:Q1048576 Q2 D5:E1048576 D2:I2 O3:P1048576 J2:K1048576 R2:XFD1048576 A1:K1" xr:uid="{CAF04EC2-946A-3446-84D0-EA50102CA3F4}"/>
+    <dataValidation allowBlank="1" sqref="B2" xr:uid="{641C78C6-B1C0-AF42-9F74-CEE2D1F3801A}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cd3_automation_toolkit/example/CD3-GCP-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-GCP-template.xlsx
@@ -1,86 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA691CF-24C4-3144-81D9-7018B5E49C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E06D3F5-078E-A747-9AD1-E6A9321BAE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19560" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
     <sheet name="ADB-Azure" sheetId="56" state="hidden" r:id="rId2"/>
-    <sheet name="EXA-Infra-GCP" sheetId="57" r:id="rId3"/>
-    <sheet name="EXA-VMClusters-GCP" sheetId="58" r:id="rId4"/>
-    <sheet name="Database_Dropdown" sheetId="40" state="hidden" r:id="rId5"/>
-    <sheet name="LB Rule Set Dropdown" sheetId="21" state="hidden" r:id="rId6"/>
-    <sheet name="drop_down_rule_set" sheetId="31" state="hidden" r:id="rId7"/>
-    <sheet name="drop_down_rule_comp" sheetId="32" state="hidden" r:id="rId8"/>
+    <sheet name="ADB-GCP" sheetId="59" r:id="rId3"/>
+    <sheet name="EXA-Infra-GCP" sheetId="57" r:id="rId4"/>
+    <sheet name="EXA-VMClusters-GCP" sheetId="58" r:id="rId5"/>
+    <sheet name="Database_Dropdown" sheetId="40" state="hidden" r:id="rId6"/>
+    <sheet name="LB Rule Set Dropdown" sheetId="21" state="hidden" r:id="rId7"/>
+    <sheet name="drop_down_rule_set" sheetId="31" state="hidden" r:id="rId8"/>
+    <sheet name="drop_down_rule_comp" sheetId="32" state="hidden" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
-    <definedName name="bm_shapes_drop" localSheetId="4">Database_Dropdown!#REF!</definedName>
-    <definedName name="bm_shapes_drop" localSheetId="7">[1]Database_Dropdown!$F$2:$F$3</definedName>
-    <definedName name="bm_shapes_drop" localSheetId="6">[2]Database_Dropdown!$F$2:$F$3</definedName>
+    <definedName name="bm_shapes_drop" localSheetId="5">Database_Dropdown!#REF!</definedName>
+    <definedName name="bm_shapes_drop" localSheetId="8">[1]Database_Dropdown!$F$2:$F$3</definedName>
+    <definedName name="bm_shapes_drop" localSheetId="7">[2]Database_Dropdown!$F$2:$F$3</definedName>
     <definedName name="bm_shapes_drop">[3]Database_Dropdown!#REF!</definedName>
-    <definedName name="char_set" localSheetId="4">Database_Dropdown!$H$2:$H$108</definedName>
-    <definedName name="char_set" localSheetId="7">[1]Database_Dropdown!$I$2:$I$108</definedName>
-    <definedName name="char_set" localSheetId="6">[2]Database_Dropdown!$I$2:$I$108</definedName>
+    <definedName name="char_set" localSheetId="5">Database_Dropdown!$H$2:$H$108</definedName>
+    <definedName name="char_set" localSheetId="8">[1]Database_Dropdown!$I$2:$I$108</definedName>
+    <definedName name="char_set" localSheetId="7">[2]Database_Dropdown!$I$2:$I$108</definedName>
     <definedName name="char_set">[3]Database_Dropdown!$H$2:$H$108</definedName>
     <definedName name="D3D1000">#REF!</definedName>
-    <definedName name="db_sersion_drop" localSheetId="4">Database_Dropdown!$C$2:$C$14</definedName>
-    <definedName name="db_sersion_drop" localSheetId="7">[1]Database_Dropdown!$C$2:$C$14</definedName>
-    <definedName name="db_sersion_drop" localSheetId="6">[2]Database_Dropdown!$C$2:$C$14</definedName>
+    <definedName name="db_sersion_drop" localSheetId="5">Database_Dropdown!$C$2:$C$14</definedName>
+    <definedName name="db_sersion_drop" localSheetId="8">[1]Database_Dropdown!$C$2:$C$14</definedName>
+    <definedName name="db_sersion_drop" localSheetId="7">[2]Database_Dropdown!$C$2:$C$14</definedName>
     <definedName name="db_sersion_drop">[3]Database_Dropdown!$C$2:$C$14</definedName>
-    <definedName name="exa_shapes_drop" localSheetId="4">Database_Dropdown!$E$2:$E$11</definedName>
-    <definedName name="exa_shapes_drop" localSheetId="7">[1]Database_Dropdown!$E$2:$E$11</definedName>
-    <definedName name="exa_shapes_drop" localSheetId="6">[2]Database_Dropdown!$E$2:$E$11</definedName>
+    <definedName name="exa_shapes_drop" localSheetId="5">Database_Dropdown!$E$2:$E$11</definedName>
+    <definedName name="exa_shapes_drop" localSheetId="8">[1]Database_Dropdown!$E$2:$E$11</definedName>
+    <definedName name="exa_shapes_drop" localSheetId="7">[2]Database_Dropdown!$E$2:$E$11</definedName>
     <definedName name="exa_shapes_drop">[3]Database_Dropdown!$E$2:$E$11</definedName>
-    <definedName name="Header_Size" localSheetId="4">'LB Rule Set Dropdown'!$F$2:$F$6</definedName>
-    <definedName name="Header_Size" localSheetId="7">'[1]Rule Set Dropdown'!$F$2:$F$6</definedName>
-    <definedName name="Header_Size" localSheetId="6">#REF!</definedName>
+    <definedName name="Header_Size" localSheetId="5">'LB Rule Set Dropdown'!$F$2:$F$6</definedName>
+    <definedName name="Header_Size" localSheetId="8">'[1]Rule Set Dropdown'!$F$2:$F$6</definedName>
+    <definedName name="Header_Size" localSheetId="7">#REF!</definedName>
     <definedName name="Header_Size">'LB Rule Set Dropdown'!$F$2:$F$6</definedName>
-    <definedName name="license_type_drop" localSheetId="4">Database_Dropdown!$F$2:$F$3</definedName>
-    <definedName name="license_type_drop" localSheetId="7">[1]Database_Dropdown!$G$2:$G$3</definedName>
-    <definedName name="license_type_drop" localSheetId="6">[2]Database_Dropdown!$G$2:$G$3</definedName>
+    <definedName name="license_type_drop" localSheetId="5">Database_Dropdown!$F$2:$F$3</definedName>
+    <definedName name="license_type_drop" localSheetId="8">[1]Database_Dropdown!$G$2:$G$3</definedName>
+    <definedName name="license_type_drop" localSheetId="7">[2]Database_Dropdown!$G$2:$G$3</definedName>
     <definedName name="license_type_drop">[3]Database_Dropdown!$F$2:$F$3</definedName>
-    <definedName name="nchar_set" localSheetId="4">Database_Dropdown!$G$2:$G$3</definedName>
-    <definedName name="nchar_set" localSheetId="7">[1]Database_Dropdown!$H$2:$H$3</definedName>
-    <definedName name="nchar_set" localSheetId="6">[2]Database_Dropdown!$H$2:$H$3</definedName>
+    <definedName name="nchar_set" localSheetId="5">Database_Dropdown!$G$2:$G$3</definedName>
+    <definedName name="nchar_set" localSheetId="8">[1]Database_Dropdown!$H$2:$H$3</definedName>
+    <definedName name="nchar_set" localSheetId="7">[2]Database_Dropdown!$H$2:$H$3</definedName>
     <definedName name="nchar_set">[3]Database_Dropdown!$G$2:$G$3</definedName>
-    <definedName name="Response_Code" localSheetId="4">'LB Rule Set Dropdown'!$E$2:$E$7</definedName>
-    <definedName name="Response_Code" localSheetId="7">'[1]Rule Set Dropdown'!$E$2:$E$7</definedName>
-    <definedName name="Response_Code" localSheetId="6">#REF!</definedName>
+    <definedName name="Response_Code" localSheetId="5">'LB Rule Set Dropdown'!$E$2:$E$7</definedName>
+    <definedName name="Response_Code" localSheetId="8">'[1]Rule Set Dropdown'!$E$2:$E$7</definedName>
+    <definedName name="Response_Code" localSheetId="7">#REF!</definedName>
     <definedName name="Response_Code">'LB Rule Set Dropdown'!$E$2:$E$7</definedName>
+    <definedName name="Shape_Option" localSheetId="5">#REF!</definedName>
+    <definedName name="Shape_Option" localSheetId="8">#REF!</definedName>
+    <definedName name="Shape_Option" localSheetId="7">#REF!</definedName>
     <definedName name="Shape_Option" localSheetId="4">#REF!</definedName>
-    <definedName name="Shape_Option" localSheetId="7">#REF!</definedName>
-    <definedName name="Shape_Option" localSheetId="6">#REF!</definedName>
-    <definedName name="Shape_Option" localSheetId="3">#REF!</definedName>
     <definedName name="Shape_Option">#REF!</definedName>
     <definedName name="Shape_Option_DB">[4]Database!$B$10:$J$10</definedName>
-    <definedName name="software_drop" localSheetId="4">Database_Dropdown!$B$2:$B$5</definedName>
-    <definedName name="software_drop" localSheetId="7">[1]Database_Dropdown!$B$2:$B$5</definedName>
-    <definedName name="software_drop" localSheetId="6">[2]Database_Dropdown!$B$2:$B$5</definedName>
+    <definedName name="software_drop" localSheetId="5">Database_Dropdown!$B$2:$B$5</definedName>
+    <definedName name="software_drop" localSheetId="8">[1]Database_Dropdown!$B$2:$B$5</definedName>
+    <definedName name="software_drop" localSheetId="7">[2]Database_Dropdown!$B$2:$B$5</definedName>
     <definedName name="software_drop">[3]Database_Dropdown!$B$2:$B$5</definedName>
-    <definedName name="VM_Shapes" localSheetId="4">Database_Dropdown!$A$2:$A$12</definedName>
+    <definedName name="VM_Shapes" localSheetId="5">Database_Dropdown!$A$2:$A$12</definedName>
     <definedName name="VM_Shapes">#REF!</definedName>
-    <definedName name="VM_shapes_drop" localSheetId="4">Database_Dropdown!$A$2:$A$7</definedName>
-    <definedName name="VM_shapes_drop" localSheetId="7">[1]Database_Dropdown!$A$2:$A$7</definedName>
-    <definedName name="VM_shapes_drop" localSheetId="6">[2]Database_Dropdown!$A$2:$A$7</definedName>
+    <definedName name="VM_shapes_drop" localSheetId="5">Database_Dropdown!$A$2:$A$7</definedName>
+    <definedName name="VM_shapes_drop" localSheetId="8">[1]Database_Dropdown!$A$2:$A$7</definedName>
+    <definedName name="VM_shapes_drop" localSheetId="7">[2]Database_Dropdown!$A$2:$A$7</definedName>
     <definedName name="VM_shapes_drop">[3]Database_Dropdown!$A$2:$A$7</definedName>
-    <definedName name="workload_drop" localSheetId="4">Database_Dropdown!$D$2:$D$3</definedName>
-    <definedName name="workload_drop" localSheetId="7">[1]Database_Dropdown!$D$2:$D$3</definedName>
-    <definedName name="workload_drop" localSheetId="6">[2]Database_Dropdown!$D$2:$D$3</definedName>
+    <definedName name="workload_drop" localSheetId="5">Database_Dropdown!$D$2:$D$3</definedName>
+    <definedName name="workload_drop" localSheetId="8">[1]Database_Dropdown!$D$2:$D$3</definedName>
+    <definedName name="workload_drop" localSheetId="7">[2]Database_Dropdown!$D$2:$D$3</definedName>
     <definedName name="workload_drop">[3]Database_Dropdown!$D$2:$D$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -99,6 +100,58 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>suruchi</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{119B0813-459A-FB42-A77A-EE9272EF8534}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leave empty for Secure Access fro Everywhere</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{9D616790-4924-E64A-8333-25E3DD3A9F2F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Leave empty for Secure Access fro Everywhere
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X2" authorId="0" shapeId="0" xr:uid="{31D6A110-E4CD-EA48-AF76-7182D9898D8D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Currently supports only one email id to be provided.
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>suruchi</author>
@@ -123,7 +176,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>suruchi</author>
@@ -206,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="563">
   <si>
     <t>Region</t>
   </si>
@@ -1640,51 +1693,6 @@
   </si>
   <si>
     <t>Customer Contacts</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CD3 Automation Toolkit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Release - v2025.2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1855,6 +1863,75 @@
     <t>Cluster Name</t>
   </si>
   <si>
+    <t>ODB Network Subnets Details</t>
+  </si>
+  <si>
+    <t>Exa-1</t>
+  </si>
+  <si>
+    <t>abc@oracle.com</t>
+  </si>
+  <si>
+    <t>environment=prod</t>
+  </si>
+  <si>
+    <t>vm-cluster-1</t>
+  </si>
+  <si>
+    <t>cluster1</t>
+  </si>
+  <si>
+    <t>ssh-rsa AAAAB3NzaC1yc2EAAAADAQABAAABAQCcQ1JVp//N4A7tsB/eLkBc/tE0WKo3cXSJVemCI/2iUb6svkXuTvMPjj1d73QfV/U21OihobXJWyVzw+1vECTlGTneYnhanX4SIeEKa7W9sreB38gKp7PXkrL6QdKxrvq1iQe6D789mcmmLW9vFFDqr8Z1E9SD4guP1mGM6UZeSl9n+WdNpse9V AL_ADT_GCP_EXA</t>
+  </si>
+  <si>
+    <t>ß</t>
+  </si>
+  <si>
+    <t>vm-cluster-2</t>
+  </si>
+  <si>
+    <t>cluster2</t>
+  </si>
+  <si>
+    <t>CREATE::dbclient-1::10.110.252.0/24::dbbkp-1::10.110.253.0/24</t>
+  </si>
+  <si>
+    <t>CREATE::dbclient-2::10.110.254.0/24::dbbkp-2::10.110.255.0/24</t>
+  </si>
+  <si>
+    <t>hostname1</t>
+  </si>
+  <si>
+    <t>hostname2</t>
+  </si>
+  <si>
+    <t>CREATE::oradb_gcp_project_id::vpc-gcp::gcp_odbnetwork::us-east4-b-r1</t>
+  </si>
+  <si>
+    <t>oradb_gcp_project_id::vpc-gcp::gcp_odbnetwork</t>
+  </si>
+  <si>
+    <t>oradb_gcp_project_2</t>
+  </si>
+  <si>
+    <t>oradb_gcp_project_1</t>
+  </si>
+  <si>
+    <t>Exa-2</t>
+  </si>
+  <si>
+    <t>oradb_gcp_project_2@Exa-2</t>
+  </si>
+  <si>
+    <t>ODB Network Subnet Details</t>
+  </si>
+  <si>
+    <t>odb_database</t>
+  </si>
+  <si>
+    <t>CREATE::dbclient-1::10.110.252.0/24</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
 Project : </t>
@@ -1879,112 +1956,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-"Defined Tags" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-                            </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.499984740745262"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>ODB Network Subnets Details</t>
-  </si>
-  <si>
-    <t>Exa-1</t>
-  </si>
-  <si>
-    <t>abc@oracle.com</t>
-  </si>
-  <si>
-    <t>environment=prod</t>
-  </si>
-  <si>
-    <t>vm-cluster-1</t>
-  </si>
-  <si>
-    <t>cluster1</t>
-  </si>
-  <si>
-    <t>ssh-rsa AAAAB3NzaC1yc2EAAAADAQABAAABAQCcQ1JVp//N4A7tsB/eLkBc/tE0WKo3cXSJVemCI/2iUb6svkXuTvMPjj1d73QfV/U21OihobXJWyVzw+1vECTlGTneYnhanX4SIeEKa7W9sreB38gKp7PXkrL6QdKxrvq1iQe6D789mcmmLW9vFFDqr8Z1E9SD4guP1mGM6UZeSl9n+WdNpse9V AL_ADT_GCP_EXA</t>
-  </si>
-  <si>
-    <t>ß</t>
-  </si>
-  <si>
-    <t>vm-cluster-2</t>
-  </si>
-  <si>
-    <t>cluster2</t>
-  </si>
-  <si>
-    <t>CREATE::dbclient-1::10.110.252.0/24::dbbkp-1::10.110.253.0/24</t>
-  </si>
-  <si>
-    <t>CREATE::dbclient-2::10.110.254.0/24::dbbkp-2::10.110.255.0/24</t>
-  </si>
-  <si>
-    <t>hostname1</t>
-  </si>
-  <si>
-    <t>hostname2</t>
-  </si>
-  <si>
-    <t>CREATE::oradb_gcp_project_id::vpc-gcp::gcp_odbnetwork::us-east4-b-r1</t>
-  </si>
-  <si>
-    <t>oradb_gcp_project_id::vpc-gcp::gcp_odbnetwork</t>
-  </si>
-  <si>
-    <t>oradb_gcp_project_2</t>
-  </si>
-  <si>
-    <t>oradb_gcp_project_1</t>
-  </si>
-  <si>
-    <t>Exa-2</t>
-  </si>
-  <si>
-    <t>oradb_gcp_project_2@Exa-2</t>
   </si>
   <si>
     <r>
@@ -2098,30 +2071,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-"Defined Tags" - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Specify the defined tag key and its value in the format - &lt;Namespace&gt;.&lt;TagKey&gt;=&lt;Value&gt;  else leave it empty.
-                             Multiple Tag Key , Values can be specified using semi colon (;) as the delimiter. 
-                            </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Example: Operations.CostCenter=01;Users.Name=user01
 </t>
     </r>
     <r>
@@ -2166,12 +2115,268 @@
       <t>Example: Asia/Calcutta | UTC | US/Pacific-New</t>
     </r>
   </si>
+  <si>
+    <t>Is Auto Scaling Enabled</t>
+  </si>
+  <si>
+    <t>Is Storage Auto Scaling Enabled</t>
+  </si>
+  <si>
+    <t>LakeHouse</t>
+  </si>
+  <si>
+    <t>Database Name</t>
+  </si>
+  <si>
+    <t>atpdb</t>
+  </si>
+  <si>
+    <t>adbdb</t>
+  </si>
+  <si>
+    <t>ATP 01</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Project : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Specify project ID
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ODB Network Detail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">s : If you want to create new network, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>use</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CREATE::&lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;::&lt;GCP_ORACLE_ZONE&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>else</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;. See sample data.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ODB Network Subnets Details </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: If you want to create new subnet, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>use</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CREATE::&lt;Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>else</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Client_Subnet_ID&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Note: To create ADB with Secure Access from Everywhere, leave Network Details columns empty.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>DB Edition</t>
+  </si>
+  <si>
+    <t>Private Endpoint IP</t>
+  </si>
+  <si>
+    <t>Private Endpoint Label</t>
+  </si>
+  <si>
+    <t>10.110.252.10</t>
+  </si>
+  <si>
+    <t>adbhost</t>
+  </si>
+  <si>
+    <t>Maintenance Schedule Type</t>
+  </si>
+  <si>
+    <t>REGULAR</t>
+  </si>
+  <si>
+    <t>EARLY</t>
+  </si>
+  <si>
+    <t>Autonomous Database ID</t>
+  </si>
+  <si>
+    <t>atp01</t>
+  </si>
+  <si>
+    <t>ATP02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CD3 Automation Toolkit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Release - v2026.2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2246,12 +2451,6 @@
     <font>
       <i/>
       <sz val="11"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Calibri (Body)"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
       <color theme="5" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2302,6 +2501,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2523,7 +2734,7 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2665,7 +2876,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2682,8 +2893,34 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2692,9 +2929,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4613,7 +4847,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="36" t="s">
-        <v>474</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -4644,34 +4878,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="79" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>475</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
+      <c r="A1" s="68" t="s">
+        <v>474</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
     </row>
     <row r="2" spans="1:19" ht="80">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>180</v>
@@ -4778,10 +5012,10 @@
         <v>0</v>
       </c>
       <c r="R3" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="S3" s="25" t="s">
         <v>476</v>
-      </c>
-      <c r="S3" s="25" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -4842,6 +5076,3102 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B20947-18B9-EF42-BC6B-2093FE6C3D90}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:Y923"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.1640625" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
+    <col min="13" max="14" width="11.33203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" customWidth="1"/>
+    <col min="18" max="19" width="11.5" customWidth="1"/>
+    <col min="20" max="20" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.1640625" customWidth="1"/>
+    <col min="22" max="22" width="11.5" customWidth="1"/>
+    <col min="23" max="23" width="9.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="102" customHeight="1">
+      <c r="A1" s="67" t="s">
+        <v>550</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+    </row>
+    <row r="2" spans="1:25" s="43" customFormat="1" ht="68" customHeight="1">
+      <c r="A2" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>559</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>513</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>538</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>552</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>553</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>546</v>
+      </c>
+      <c r="J2" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="K2" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="52" t="s">
+        <v>460</v>
+      </c>
+      <c r="M2" s="52" t="s">
+        <v>510</v>
+      </c>
+      <c r="N2" s="52" t="s">
+        <v>551</v>
+      </c>
+      <c r="O2" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="P2" s="52" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q2" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="R2" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="S2" s="61" t="s">
+        <v>463</v>
+      </c>
+      <c r="T2" s="61" t="s">
+        <v>544</v>
+      </c>
+      <c r="U2" s="61" t="s">
+        <v>543</v>
+      </c>
+      <c r="V2" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="W2" s="61" t="s">
+        <v>466</v>
+      </c>
+      <c r="X2" s="61" t="s">
+        <v>503</v>
+      </c>
+      <c r="Y2" s="52" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="64">
+      <c r="A3" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>540</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>547</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="K3" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="L3" s="24">
+        <v>2</v>
+      </c>
+      <c r="M3" s="24">
+        <v>1</v>
+      </c>
+      <c r="N3" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="O3" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q3" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="R3" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="S3" s="24">
+        <v>10</v>
+      </c>
+      <c r="T3" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="W3" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="Y3" s="24" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="48">
+      <c r="A4" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="24" t="s">
+        <v>548</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" s="24">
+        <v>2</v>
+      </c>
+      <c r="M4" s="24">
+        <v>1</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="P4" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="S4" s="24">
+        <v>10</v>
+      </c>
+      <c r="T4" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="W4" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="16">
+      <c r="A5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="63"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="18"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
+      <c r="Y5" s="18"/>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="E6" s="50"/>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="E7" s="50"/>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="E8" s="50"/>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="E9" s="50"/>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="E10" s="50"/>
+      <c r="S10" s="55" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="E11" s="50"/>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="E12" s="50"/>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="E13" s="50"/>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="E14" s="50"/>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="E15" s="50"/>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="E16" s="50"/>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="50"/>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="50"/>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" s="50"/>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20" s="50"/>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" s="50"/>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" s="50"/>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="50"/>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="50"/>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" s="50"/>
+    </row>
+    <row r="26" spans="5:5">
+      <c r="E26" s="50"/>
+    </row>
+    <row r="27" spans="5:5">
+      <c r="E27" s="50"/>
+    </row>
+    <row r="28" spans="5:5">
+      <c r="E28" s="50"/>
+    </row>
+    <row r="29" spans="5:5">
+      <c r="E29" s="50"/>
+    </row>
+    <row r="30" spans="5:5">
+      <c r="E30" s="50"/>
+    </row>
+    <row r="31" spans="5:5">
+      <c r="E31" s="50"/>
+    </row>
+    <row r="32" spans="5:5">
+      <c r="E32" s="50"/>
+    </row>
+    <row r="33" spans="5:5">
+      <c r="E33" s="50"/>
+    </row>
+    <row r="34" spans="5:5">
+      <c r="E34" s="50"/>
+    </row>
+    <row r="35" spans="5:5">
+      <c r="E35" s="50"/>
+    </row>
+    <row r="36" spans="5:5">
+      <c r="E36" s="50"/>
+    </row>
+    <row r="37" spans="5:5">
+      <c r="E37" s="50"/>
+    </row>
+    <row r="38" spans="5:5">
+      <c r="E38" s="50"/>
+    </row>
+    <row r="39" spans="5:5">
+      <c r="E39" s="50"/>
+    </row>
+    <row r="40" spans="5:5">
+      <c r="E40" s="50"/>
+    </row>
+    <row r="41" spans="5:5">
+      <c r="E41" s="50"/>
+    </row>
+    <row r="42" spans="5:5">
+      <c r="E42" s="50"/>
+    </row>
+    <row r="43" spans="5:5">
+      <c r="E43" s="50"/>
+    </row>
+    <row r="44" spans="5:5">
+      <c r="E44" s="50"/>
+    </row>
+    <row r="45" spans="5:5">
+      <c r="E45" s="50"/>
+    </row>
+    <row r="46" spans="5:5">
+      <c r="E46" s="50"/>
+    </row>
+    <row r="47" spans="5:5">
+      <c r="E47" s="50"/>
+    </row>
+    <row r="48" spans="5:5">
+      <c r="E48" s="50"/>
+    </row>
+    <row r="49" spans="5:5">
+      <c r="E49" s="50"/>
+    </row>
+    <row r="50" spans="5:5">
+      <c r="E50" s="50"/>
+    </row>
+    <row r="51" spans="5:5">
+      <c r="E51" s="50"/>
+    </row>
+    <row r="52" spans="5:5">
+      <c r="E52" s="50"/>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="50"/>
+    </row>
+    <row r="54" spans="5:5">
+      <c r="E54" s="50"/>
+    </row>
+    <row r="55" spans="5:5">
+      <c r="E55" s="50"/>
+    </row>
+    <row r="56" spans="5:5">
+      <c r="E56" s="50"/>
+    </row>
+    <row r="57" spans="5:5">
+      <c r="E57" s="50"/>
+    </row>
+    <row r="58" spans="5:5">
+      <c r="E58" s="50"/>
+    </row>
+    <row r="59" spans="5:5">
+      <c r="E59" s="50"/>
+    </row>
+    <row r="60" spans="5:5">
+      <c r="E60" s="50"/>
+    </row>
+    <row r="61" spans="5:5">
+      <c r="E61" s="50"/>
+    </row>
+    <row r="62" spans="5:5">
+      <c r="E62" s="50"/>
+    </row>
+    <row r="63" spans="5:5">
+      <c r="E63" s="50"/>
+    </row>
+    <row r="64" spans="5:5">
+      <c r="E64" s="50"/>
+    </row>
+    <row r="65" spans="5:5">
+      <c r="E65" s="50"/>
+    </row>
+    <row r="66" spans="5:5">
+      <c r="E66" s="50"/>
+    </row>
+    <row r="67" spans="5:5">
+      <c r="E67" s="50"/>
+    </row>
+    <row r="68" spans="5:5">
+      <c r="E68" s="50"/>
+    </row>
+    <row r="69" spans="5:5">
+      <c r="E69" s="50"/>
+    </row>
+    <row r="70" spans="5:5">
+      <c r="E70" s="50"/>
+    </row>
+    <row r="71" spans="5:5">
+      <c r="E71" s="50"/>
+    </row>
+    <row r="72" spans="5:5">
+      <c r="E72" s="50"/>
+    </row>
+    <row r="73" spans="5:5">
+      <c r="E73" s="50"/>
+    </row>
+    <row r="74" spans="5:5">
+      <c r="E74" s="50"/>
+    </row>
+    <row r="75" spans="5:5">
+      <c r="E75" s="50"/>
+    </row>
+    <row r="76" spans="5:5">
+      <c r="E76" s="50"/>
+    </row>
+    <row r="77" spans="5:5">
+      <c r="E77" s="50"/>
+    </row>
+    <row r="78" spans="5:5">
+      <c r="E78" s="50"/>
+    </row>
+    <row r="79" spans="5:5">
+      <c r="E79" s="50"/>
+    </row>
+    <row r="80" spans="5:5">
+      <c r="E80" s="50"/>
+    </row>
+    <row r="81" spans="5:5">
+      <c r="E81" s="50"/>
+    </row>
+    <row r="82" spans="5:5">
+      <c r="E82" s="50"/>
+    </row>
+    <row r="83" spans="5:5">
+      <c r="E83" s="50"/>
+    </row>
+    <row r="84" spans="5:5">
+      <c r="E84" s="50"/>
+    </row>
+    <row r="85" spans="5:5">
+      <c r="E85" s="50"/>
+    </row>
+    <row r="86" spans="5:5">
+      <c r="E86" s="50"/>
+    </row>
+    <row r="87" spans="5:5">
+      <c r="E87" s="50"/>
+    </row>
+    <row r="88" spans="5:5">
+      <c r="E88" s="50"/>
+    </row>
+    <row r="89" spans="5:5">
+      <c r="E89" s="50"/>
+    </row>
+    <row r="90" spans="5:5">
+      <c r="E90" s="50"/>
+    </row>
+    <row r="91" spans="5:5">
+      <c r="E91" s="50"/>
+    </row>
+    <row r="92" spans="5:5">
+      <c r="E92" s="50"/>
+    </row>
+    <row r="93" spans="5:5">
+      <c r="E93" s="50"/>
+    </row>
+    <row r="94" spans="5:5">
+      <c r="E94" s="50"/>
+    </row>
+    <row r="95" spans="5:5">
+      <c r="E95" s="50"/>
+    </row>
+    <row r="96" spans="5:5">
+      <c r="E96" s="50"/>
+    </row>
+    <row r="97" spans="5:5">
+      <c r="E97" s="50"/>
+    </row>
+    <row r="98" spans="5:5">
+      <c r="E98" s="50"/>
+    </row>
+    <row r="99" spans="5:5">
+      <c r="E99" s="50"/>
+    </row>
+    <row r="100" spans="5:5">
+      <c r="E100" s="50"/>
+    </row>
+    <row r="101" spans="5:5">
+      <c r="E101" s="50"/>
+    </row>
+    <row r="102" spans="5:5">
+      <c r="E102" s="50"/>
+    </row>
+    <row r="103" spans="5:5">
+      <c r="E103" s="50"/>
+    </row>
+    <row r="104" spans="5:5">
+      <c r="E104" s="50"/>
+    </row>
+    <row r="105" spans="5:5">
+      <c r="E105" s="50"/>
+    </row>
+    <row r="106" spans="5:5">
+      <c r="E106" s="50"/>
+    </row>
+    <row r="107" spans="5:5">
+      <c r="E107" s="50"/>
+    </row>
+    <row r="108" spans="5:5">
+      <c r="E108" s="50"/>
+    </row>
+    <row r="109" spans="5:5">
+      <c r="E109" s="50"/>
+    </row>
+    <row r="110" spans="5:5">
+      <c r="E110" s="50"/>
+    </row>
+    <row r="111" spans="5:5">
+      <c r="E111" s="50"/>
+    </row>
+    <row r="112" spans="5:5">
+      <c r="E112" s="50"/>
+    </row>
+    <row r="113" spans="5:5">
+      <c r="E113" s="50"/>
+    </row>
+    <row r="114" spans="5:5">
+      <c r="E114" s="50"/>
+    </row>
+    <row r="115" spans="5:5">
+      <c r="E115" s="50"/>
+    </row>
+    <row r="116" spans="5:5">
+      <c r="E116" s="50"/>
+    </row>
+    <row r="117" spans="5:5">
+      <c r="E117" s="50"/>
+    </row>
+    <row r="118" spans="5:5">
+      <c r="E118" s="50"/>
+    </row>
+    <row r="119" spans="5:5">
+      <c r="E119" s="50"/>
+    </row>
+    <row r="120" spans="5:5">
+      <c r="E120" s="50"/>
+    </row>
+    <row r="121" spans="5:5">
+      <c r="E121" s="50"/>
+    </row>
+    <row r="122" spans="5:5">
+      <c r="E122" s="50"/>
+    </row>
+    <row r="123" spans="5:5">
+      <c r="E123" s="50"/>
+    </row>
+    <row r="124" spans="5:5">
+      <c r="E124" s="50"/>
+    </row>
+    <row r="125" spans="5:5">
+      <c r="E125" s="50"/>
+    </row>
+    <row r="126" spans="5:5">
+      <c r="E126" s="50"/>
+    </row>
+    <row r="127" spans="5:5">
+      <c r="E127" s="50"/>
+    </row>
+    <row r="128" spans="5:5">
+      <c r="E128" s="50"/>
+    </row>
+    <row r="129" spans="5:5">
+      <c r="E129" s="50"/>
+    </row>
+    <row r="130" spans="5:5">
+      <c r="E130" s="50"/>
+    </row>
+    <row r="131" spans="5:5">
+      <c r="E131" s="50"/>
+    </row>
+    <row r="132" spans="5:5">
+      <c r="E132" s="50"/>
+    </row>
+    <row r="133" spans="5:5">
+      <c r="E133" s="50"/>
+    </row>
+    <row r="134" spans="5:5">
+      <c r="E134" s="50"/>
+    </row>
+    <row r="135" spans="5:5">
+      <c r="E135" s="50"/>
+    </row>
+    <row r="136" spans="5:5">
+      <c r="E136" s="50"/>
+    </row>
+    <row r="137" spans="5:5">
+      <c r="E137" s="50"/>
+    </row>
+    <row r="138" spans="5:5">
+      <c r="E138" s="50"/>
+    </row>
+    <row r="139" spans="5:5">
+      <c r="E139" s="50"/>
+    </row>
+    <row r="140" spans="5:5">
+      <c r="E140" s="50"/>
+    </row>
+    <row r="141" spans="5:5">
+      <c r="E141" s="50"/>
+    </row>
+    <row r="142" spans="5:5">
+      <c r="E142" s="50"/>
+    </row>
+    <row r="143" spans="5:5">
+      <c r="E143" s="50"/>
+    </row>
+    <row r="144" spans="5:5">
+      <c r="E144" s="50"/>
+    </row>
+    <row r="145" spans="5:5">
+      <c r="E145" s="50"/>
+    </row>
+    <row r="146" spans="5:5">
+      <c r="E146" s="50"/>
+    </row>
+    <row r="147" spans="5:5">
+      <c r="E147" s="50"/>
+    </row>
+    <row r="148" spans="5:5">
+      <c r="E148" s="50"/>
+    </row>
+    <row r="149" spans="5:5">
+      <c r="E149" s="50"/>
+    </row>
+    <row r="150" spans="5:5">
+      <c r="E150" s="50"/>
+    </row>
+    <row r="151" spans="5:5">
+      <c r="E151" s="50"/>
+    </row>
+    <row r="152" spans="5:5">
+      <c r="E152" s="50"/>
+    </row>
+    <row r="153" spans="5:5">
+      <c r="E153" s="50"/>
+    </row>
+    <row r="154" spans="5:5">
+      <c r="E154" s="50"/>
+    </row>
+    <row r="155" spans="5:5">
+      <c r="E155" s="50"/>
+    </row>
+    <row r="156" spans="5:5">
+      <c r="E156" s="50"/>
+    </row>
+    <row r="157" spans="5:5">
+      <c r="E157" s="50"/>
+    </row>
+    <row r="158" spans="5:5">
+      <c r="E158" s="50"/>
+    </row>
+    <row r="159" spans="5:5">
+      <c r="E159" s="50"/>
+    </row>
+    <row r="160" spans="5:5">
+      <c r="E160" s="50"/>
+    </row>
+    <row r="161" spans="5:5">
+      <c r="E161" s="50"/>
+    </row>
+    <row r="162" spans="5:5">
+      <c r="E162" s="50"/>
+    </row>
+    <row r="163" spans="5:5">
+      <c r="E163" s="50"/>
+    </row>
+    <row r="164" spans="5:5">
+      <c r="E164" s="50"/>
+    </row>
+    <row r="165" spans="5:5">
+      <c r="E165" s="50"/>
+    </row>
+    <row r="166" spans="5:5">
+      <c r="E166" s="50"/>
+    </row>
+    <row r="167" spans="5:5">
+      <c r="E167" s="50"/>
+    </row>
+    <row r="168" spans="5:5">
+      <c r="E168" s="50"/>
+    </row>
+    <row r="169" spans="5:5">
+      <c r="E169" s="50"/>
+    </row>
+    <row r="170" spans="5:5">
+      <c r="E170" s="50"/>
+    </row>
+    <row r="171" spans="5:5">
+      <c r="E171" s="50"/>
+    </row>
+    <row r="172" spans="5:5">
+      <c r="E172" s="50"/>
+    </row>
+    <row r="173" spans="5:5">
+      <c r="E173" s="50"/>
+    </row>
+    <row r="174" spans="5:5">
+      <c r="E174" s="50"/>
+    </row>
+    <row r="175" spans="5:5">
+      <c r="E175" s="50"/>
+    </row>
+    <row r="176" spans="5:5">
+      <c r="E176" s="50"/>
+    </row>
+    <row r="177" spans="5:5">
+      <c r="E177" s="50"/>
+    </row>
+    <row r="178" spans="5:5">
+      <c r="E178" s="50"/>
+    </row>
+    <row r="179" spans="5:5">
+      <c r="E179" s="50"/>
+    </row>
+    <row r="180" spans="5:5">
+      <c r="E180" s="50"/>
+    </row>
+    <row r="181" spans="5:5">
+      <c r="E181" s="50"/>
+    </row>
+    <row r="182" spans="5:5">
+      <c r="E182" s="50"/>
+    </row>
+    <row r="183" spans="5:5">
+      <c r="E183" s="50"/>
+    </row>
+    <row r="184" spans="5:5">
+      <c r="E184" s="50"/>
+    </row>
+    <row r="185" spans="5:5">
+      <c r="E185" s="50"/>
+    </row>
+    <row r="186" spans="5:5">
+      <c r="E186" s="50"/>
+    </row>
+    <row r="187" spans="5:5">
+      <c r="E187" s="50"/>
+    </row>
+    <row r="188" spans="5:5">
+      <c r="E188" s="50"/>
+    </row>
+    <row r="189" spans="5:5">
+      <c r="E189" s="50"/>
+    </row>
+    <row r="190" spans="5:5">
+      <c r="E190" s="50"/>
+    </row>
+    <row r="191" spans="5:5">
+      <c r="E191" s="50"/>
+    </row>
+    <row r="192" spans="5:5">
+      <c r="E192" s="50"/>
+    </row>
+    <row r="193" spans="5:5">
+      <c r="E193" s="50"/>
+    </row>
+    <row r="194" spans="5:5">
+      <c r="E194" s="50"/>
+    </row>
+    <row r="195" spans="5:5">
+      <c r="E195" s="50"/>
+    </row>
+    <row r="196" spans="5:5">
+      <c r="E196" s="50"/>
+    </row>
+    <row r="197" spans="5:5">
+      <c r="E197" s="50"/>
+    </row>
+    <row r="198" spans="5:5">
+      <c r="E198" s="50"/>
+    </row>
+    <row r="199" spans="5:5">
+      <c r="E199" s="50"/>
+    </row>
+    <row r="200" spans="5:5">
+      <c r="E200" s="50"/>
+    </row>
+    <row r="201" spans="5:5">
+      <c r="E201" s="50"/>
+    </row>
+    <row r="202" spans="5:5">
+      <c r="E202" s="50"/>
+    </row>
+    <row r="203" spans="5:5">
+      <c r="E203" s="50"/>
+    </row>
+    <row r="204" spans="5:5">
+      <c r="E204" s="50"/>
+    </row>
+    <row r="205" spans="5:5">
+      <c r="E205" s="50"/>
+    </row>
+    <row r="206" spans="5:5">
+      <c r="E206" s="50"/>
+    </row>
+    <row r="207" spans="5:5">
+      <c r="E207" s="50"/>
+    </row>
+    <row r="208" spans="5:5">
+      <c r="E208" s="50"/>
+    </row>
+    <row r="209" spans="5:5">
+      <c r="E209" s="50"/>
+    </row>
+    <row r="210" spans="5:5">
+      <c r="E210" s="50"/>
+    </row>
+    <row r="211" spans="5:5">
+      <c r="E211" s="50"/>
+    </row>
+    <row r="212" spans="5:5">
+      <c r="E212" s="50"/>
+    </row>
+    <row r="213" spans="5:5">
+      <c r="E213" s="50"/>
+    </row>
+    <row r="214" spans="5:5">
+      <c r="E214" s="50"/>
+    </row>
+    <row r="215" spans="5:5">
+      <c r="E215" s="50"/>
+    </row>
+    <row r="216" spans="5:5">
+      <c r="E216" s="50"/>
+    </row>
+    <row r="217" spans="5:5">
+      <c r="E217" s="50"/>
+    </row>
+    <row r="218" spans="5:5">
+      <c r="E218" s="50"/>
+    </row>
+    <row r="219" spans="5:5">
+      <c r="E219" s="50"/>
+    </row>
+    <row r="220" spans="5:5">
+      <c r="E220" s="50"/>
+    </row>
+    <row r="221" spans="5:5">
+      <c r="E221" s="50"/>
+    </row>
+    <row r="222" spans="5:5">
+      <c r="E222" s="50"/>
+    </row>
+    <row r="223" spans="5:5">
+      <c r="E223" s="50"/>
+    </row>
+    <row r="224" spans="5:5">
+      <c r="E224" s="50"/>
+    </row>
+    <row r="225" spans="5:5">
+      <c r="E225" s="50"/>
+    </row>
+    <row r="226" spans="5:5">
+      <c r="E226" s="50"/>
+    </row>
+    <row r="227" spans="5:5">
+      <c r="E227" s="50"/>
+    </row>
+    <row r="228" spans="5:5">
+      <c r="E228" s="50"/>
+    </row>
+    <row r="229" spans="5:5">
+      <c r="E229" s="50"/>
+    </row>
+    <row r="230" spans="5:5">
+      <c r="E230" s="50"/>
+    </row>
+    <row r="231" spans="5:5">
+      <c r="E231" s="50"/>
+    </row>
+    <row r="232" spans="5:5">
+      <c r="E232" s="50"/>
+    </row>
+    <row r="233" spans="5:5">
+      <c r="E233" s="50"/>
+    </row>
+    <row r="234" spans="5:5">
+      <c r="E234" s="50"/>
+    </row>
+    <row r="235" spans="5:5">
+      <c r="E235" s="50"/>
+    </row>
+    <row r="236" spans="5:5">
+      <c r="E236" s="50"/>
+    </row>
+    <row r="237" spans="5:5">
+      <c r="E237" s="50"/>
+    </row>
+    <row r="238" spans="5:5">
+      <c r="E238" s="50"/>
+    </row>
+    <row r="239" spans="5:5">
+      <c r="E239" s="50"/>
+    </row>
+    <row r="240" spans="5:5">
+      <c r="E240" s="50"/>
+    </row>
+    <row r="241" spans="5:5">
+      <c r="E241" s="50"/>
+    </row>
+    <row r="242" spans="5:5">
+      <c r="E242" s="50"/>
+    </row>
+    <row r="243" spans="5:5">
+      <c r="E243" s="50"/>
+    </row>
+    <row r="244" spans="5:5">
+      <c r="E244" s="50"/>
+    </row>
+    <row r="245" spans="5:5">
+      <c r="E245" s="50"/>
+    </row>
+    <row r="246" spans="5:5">
+      <c r="E246" s="50"/>
+    </row>
+    <row r="247" spans="5:5">
+      <c r="E247" s="50"/>
+    </row>
+    <row r="248" spans="5:5">
+      <c r="E248" s="50"/>
+    </row>
+    <row r="249" spans="5:5">
+      <c r="E249" s="50"/>
+    </row>
+    <row r="250" spans="5:5">
+      <c r="E250" s="50"/>
+    </row>
+    <row r="251" spans="5:5">
+      <c r="E251" s="50"/>
+    </row>
+    <row r="252" spans="5:5">
+      <c r="E252" s="50"/>
+    </row>
+    <row r="253" spans="5:5">
+      <c r="E253" s="50"/>
+    </row>
+    <row r="254" spans="5:5">
+      <c r="E254" s="50"/>
+    </row>
+    <row r="255" spans="5:5">
+      <c r="E255" s="50"/>
+    </row>
+    <row r="256" spans="5:5">
+      <c r="E256" s="50"/>
+    </row>
+    <row r="257" spans="5:5">
+      <c r="E257" s="50"/>
+    </row>
+    <row r="258" spans="5:5">
+      <c r="E258" s="50"/>
+    </row>
+    <row r="259" spans="5:5">
+      <c r="E259" s="50"/>
+    </row>
+    <row r="260" spans="5:5">
+      <c r="E260" s="50"/>
+    </row>
+    <row r="261" spans="5:5">
+      <c r="E261" s="50"/>
+    </row>
+    <row r="262" spans="5:5">
+      <c r="E262" s="50"/>
+    </row>
+    <row r="263" spans="5:5">
+      <c r="E263" s="50"/>
+    </row>
+    <row r="264" spans="5:5">
+      <c r="E264" s="50"/>
+    </row>
+    <row r="265" spans="5:5">
+      <c r="E265" s="50"/>
+    </row>
+    <row r="266" spans="5:5">
+      <c r="E266" s="50"/>
+    </row>
+    <row r="267" spans="5:5">
+      <c r="E267" s="50"/>
+    </row>
+    <row r="268" spans="5:5">
+      <c r="E268" s="50"/>
+    </row>
+    <row r="269" spans="5:5">
+      <c r="E269" s="50"/>
+    </row>
+    <row r="270" spans="5:5">
+      <c r="E270" s="50"/>
+    </row>
+    <row r="271" spans="5:5">
+      <c r="E271" s="50"/>
+    </row>
+    <row r="272" spans="5:5">
+      <c r="E272" s="50"/>
+    </row>
+    <row r="273" spans="5:5">
+      <c r="E273" s="50"/>
+    </row>
+    <row r="274" spans="5:5">
+      <c r="E274" s="50"/>
+    </row>
+    <row r="275" spans="5:5">
+      <c r="E275" s="50"/>
+    </row>
+    <row r="276" spans="5:5">
+      <c r="E276" s="50"/>
+    </row>
+    <row r="277" spans="5:5">
+      <c r="E277" s="50"/>
+    </row>
+    <row r="278" spans="5:5">
+      <c r="E278" s="50"/>
+    </row>
+    <row r="279" spans="5:5">
+      <c r="E279" s="50"/>
+    </row>
+    <row r="280" spans="5:5">
+      <c r="E280" s="50"/>
+    </row>
+    <row r="281" spans="5:5">
+      <c r="E281" s="50"/>
+    </row>
+    <row r="282" spans="5:5">
+      <c r="E282" s="50"/>
+    </row>
+    <row r="283" spans="5:5">
+      <c r="E283" s="50"/>
+    </row>
+    <row r="284" spans="5:5">
+      <c r="E284" s="50"/>
+    </row>
+    <row r="285" spans="5:5">
+      <c r="E285" s="50"/>
+    </row>
+    <row r="286" spans="5:5">
+      <c r="E286" s="50"/>
+    </row>
+    <row r="287" spans="5:5">
+      <c r="E287" s="50"/>
+    </row>
+    <row r="288" spans="5:5">
+      <c r="E288" s="50"/>
+    </row>
+    <row r="289" spans="5:5">
+      <c r="E289" s="50"/>
+    </row>
+    <row r="290" spans="5:5">
+      <c r="E290" s="50"/>
+    </row>
+    <row r="291" spans="5:5">
+      <c r="E291" s="50"/>
+    </row>
+    <row r="292" spans="5:5">
+      <c r="E292" s="50"/>
+    </row>
+    <row r="293" spans="5:5">
+      <c r="E293" s="50"/>
+    </row>
+    <row r="294" spans="5:5">
+      <c r="E294" s="50"/>
+    </row>
+    <row r="295" spans="5:5">
+      <c r="E295" s="50"/>
+    </row>
+    <row r="296" spans="5:5">
+      <c r="E296" s="50"/>
+    </row>
+    <row r="297" spans="5:5">
+      <c r="E297" s="50"/>
+    </row>
+    <row r="298" spans="5:5">
+      <c r="E298" s="50"/>
+    </row>
+    <row r="299" spans="5:5">
+      <c r="E299" s="50"/>
+    </row>
+    <row r="300" spans="5:5">
+      <c r="E300" s="50"/>
+    </row>
+    <row r="301" spans="5:5">
+      <c r="E301" s="50"/>
+    </row>
+    <row r="302" spans="5:5">
+      <c r="E302" s="50"/>
+    </row>
+    <row r="303" spans="5:5">
+      <c r="E303" s="50"/>
+    </row>
+    <row r="304" spans="5:5">
+      <c r="E304" s="50"/>
+    </row>
+    <row r="305" spans="5:5">
+      <c r="E305" s="50"/>
+    </row>
+    <row r="306" spans="5:5">
+      <c r="E306" s="50"/>
+    </row>
+    <row r="307" spans="5:5">
+      <c r="E307" s="50"/>
+    </row>
+    <row r="308" spans="5:5">
+      <c r="E308" s="50"/>
+    </row>
+    <row r="309" spans="5:5">
+      <c r="E309" s="50"/>
+    </row>
+    <row r="310" spans="5:5">
+      <c r="E310" s="50"/>
+    </row>
+    <row r="311" spans="5:5">
+      <c r="E311" s="50"/>
+    </row>
+    <row r="312" spans="5:5">
+      <c r="E312" s="50"/>
+    </row>
+    <row r="313" spans="5:5">
+      <c r="E313" s="50"/>
+    </row>
+    <row r="314" spans="5:5">
+      <c r="E314" s="50"/>
+    </row>
+    <row r="315" spans="5:5">
+      <c r="E315" s="50"/>
+    </row>
+    <row r="316" spans="5:5">
+      <c r="E316" s="50"/>
+    </row>
+    <row r="317" spans="5:5">
+      <c r="E317" s="50"/>
+    </row>
+    <row r="318" spans="5:5">
+      <c r="E318" s="50"/>
+    </row>
+    <row r="319" spans="5:5">
+      <c r="E319" s="50"/>
+    </row>
+    <row r="320" spans="5:5">
+      <c r="E320" s="50"/>
+    </row>
+    <row r="321" spans="5:5">
+      <c r="E321" s="50"/>
+    </row>
+    <row r="322" spans="5:5">
+      <c r="E322" s="50"/>
+    </row>
+    <row r="323" spans="5:5">
+      <c r="E323" s="50"/>
+    </row>
+    <row r="324" spans="5:5">
+      <c r="E324" s="50"/>
+    </row>
+    <row r="325" spans="5:5">
+      <c r="E325" s="50"/>
+    </row>
+    <row r="326" spans="5:5">
+      <c r="E326" s="50"/>
+    </row>
+    <row r="327" spans="5:5">
+      <c r="E327" s="50"/>
+    </row>
+    <row r="328" spans="5:5">
+      <c r="E328" s="50"/>
+    </row>
+    <row r="329" spans="5:5">
+      <c r="E329" s="50"/>
+    </row>
+    <row r="330" spans="5:5">
+      <c r="E330" s="50"/>
+    </row>
+    <row r="331" spans="5:5">
+      <c r="E331" s="50"/>
+    </row>
+    <row r="332" spans="5:5">
+      <c r="E332" s="50"/>
+    </row>
+    <row r="333" spans="5:5">
+      <c r="E333" s="50"/>
+    </row>
+    <row r="334" spans="5:5">
+      <c r="E334" s="50"/>
+    </row>
+    <row r="335" spans="5:5">
+      <c r="E335" s="50"/>
+    </row>
+    <row r="336" spans="5:5">
+      <c r="E336" s="50"/>
+    </row>
+    <row r="337" spans="5:5">
+      <c r="E337" s="50"/>
+    </row>
+    <row r="338" spans="5:5">
+      <c r="E338" s="50"/>
+    </row>
+    <row r="339" spans="5:5">
+      <c r="E339" s="50"/>
+    </row>
+    <row r="340" spans="5:5">
+      <c r="E340" s="50"/>
+    </row>
+    <row r="341" spans="5:5">
+      <c r="E341" s="50"/>
+    </row>
+    <row r="342" spans="5:5">
+      <c r="E342" s="50"/>
+    </row>
+    <row r="343" spans="5:5">
+      <c r="E343" s="50"/>
+    </row>
+    <row r="344" spans="5:5">
+      <c r="E344" s="50"/>
+    </row>
+    <row r="345" spans="5:5">
+      <c r="E345" s="50"/>
+    </row>
+    <row r="346" spans="5:5">
+      <c r="E346" s="50"/>
+    </row>
+    <row r="347" spans="5:5">
+      <c r="E347" s="50"/>
+    </row>
+    <row r="348" spans="5:5">
+      <c r="E348" s="50"/>
+    </row>
+    <row r="349" spans="5:5">
+      <c r="E349" s="50"/>
+    </row>
+    <row r="350" spans="5:5">
+      <c r="E350" s="50"/>
+    </row>
+    <row r="351" spans="5:5">
+      <c r="E351" s="50"/>
+    </row>
+    <row r="352" spans="5:5">
+      <c r="E352" s="50"/>
+    </row>
+    <row r="353" spans="5:5">
+      <c r="E353" s="50"/>
+    </row>
+    <row r="354" spans="5:5">
+      <c r="E354" s="50"/>
+    </row>
+    <row r="355" spans="5:5">
+      <c r="E355" s="50"/>
+    </row>
+    <row r="356" spans="5:5">
+      <c r="E356" s="50"/>
+    </row>
+    <row r="357" spans="5:5">
+      <c r="E357" s="50"/>
+    </row>
+    <row r="358" spans="5:5">
+      <c r="E358" s="50"/>
+    </row>
+    <row r="359" spans="5:5">
+      <c r="E359" s="50"/>
+    </row>
+    <row r="360" spans="5:5">
+      <c r="E360" s="50"/>
+    </row>
+    <row r="361" spans="5:5">
+      <c r="E361" s="50"/>
+    </row>
+    <row r="362" spans="5:5">
+      <c r="E362" s="50"/>
+    </row>
+    <row r="363" spans="5:5">
+      <c r="E363" s="50"/>
+    </row>
+    <row r="364" spans="5:5">
+      <c r="E364" s="50"/>
+    </row>
+    <row r="365" spans="5:5">
+      <c r="E365" s="50"/>
+    </row>
+    <row r="366" spans="5:5">
+      <c r="E366" s="50"/>
+    </row>
+    <row r="367" spans="5:5">
+      <c r="E367" s="50"/>
+    </row>
+    <row r="368" spans="5:5">
+      <c r="E368" s="50"/>
+    </row>
+    <row r="369" spans="5:5">
+      <c r="E369" s="50"/>
+    </row>
+    <row r="370" spans="5:5">
+      <c r="E370" s="50"/>
+    </row>
+    <row r="371" spans="5:5">
+      <c r="E371" s="50"/>
+    </row>
+    <row r="372" spans="5:5">
+      <c r="E372" s="50"/>
+    </row>
+    <row r="373" spans="5:5">
+      <c r="E373" s="50"/>
+    </row>
+    <row r="374" spans="5:5">
+      <c r="E374" s="50"/>
+    </row>
+    <row r="375" spans="5:5">
+      <c r="E375" s="50"/>
+    </row>
+    <row r="376" spans="5:5">
+      <c r="E376" s="50"/>
+    </row>
+    <row r="377" spans="5:5">
+      <c r="E377" s="50"/>
+    </row>
+    <row r="378" spans="5:5">
+      <c r="E378" s="50"/>
+    </row>
+    <row r="379" spans="5:5">
+      <c r="E379" s="50"/>
+    </row>
+    <row r="380" spans="5:5">
+      <c r="E380" s="50"/>
+    </row>
+    <row r="381" spans="5:5">
+      <c r="E381" s="50"/>
+    </row>
+    <row r="382" spans="5:5">
+      <c r="E382" s="50"/>
+    </row>
+    <row r="383" spans="5:5">
+      <c r="E383" s="50"/>
+    </row>
+    <row r="384" spans="5:5">
+      <c r="E384" s="50"/>
+    </row>
+    <row r="385" spans="5:5">
+      <c r="E385" s="50"/>
+    </row>
+    <row r="386" spans="5:5">
+      <c r="E386" s="50"/>
+    </row>
+    <row r="387" spans="5:5">
+      <c r="E387" s="50"/>
+    </row>
+    <row r="388" spans="5:5">
+      <c r="E388" s="50"/>
+    </row>
+    <row r="389" spans="5:5">
+      <c r="E389" s="50"/>
+    </row>
+    <row r="390" spans="5:5">
+      <c r="E390" s="50"/>
+    </row>
+    <row r="391" spans="5:5">
+      <c r="E391" s="50"/>
+    </row>
+    <row r="392" spans="5:5">
+      <c r="E392" s="50"/>
+    </row>
+    <row r="393" spans="5:5">
+      <c r="E393" s="50"/>
+    </row>
+    <row r="394" spans="5:5">
+      <c r="E394" s="50"/>
+    </row>
+    <row r="395" spans="5:5">
+      <c r="E395" s="50"/>
+    </row>
+    <row r="396" spans="5:5">
+      <c r="E396" s="50"/>
+    </row>
+    <row r="397" spans="5:5">
+      <c r="E397" s="50"/>
+    </row>
+    <row r="398" spans="5:5">
+      <c r="E398" s="50"/>
+    </row>
+    <row r="399" spans="5:5">
+      <c r="E399" s="50"/>
+    </row>
+    <row r="400" spans="5:5">
+      <c r="E400" s="50"/>
+    </row>
+    <row r="401" spans="5:5">
+      <c r="E401" s="50"/>
+    </row>
+    <row r="402" spans="5:5">
+      <c r="E402" s="50"/>
+    </row>
+    <row r="403" spans="5:5">
+      <c r="E403" s="50"/>
+    </row>
+    <row r="404" spans="5:5">
+      <c r="E404" s="50"/>
+    </row>
+    <row r="405" spans="5:5">
+      <c r="E405" s="50"/>
+    </row>
+    <row r="406" spans="5:5">
+      <c r="E406" s="50"/>
+    </row>
+    <row r="407" spans="5:5">
+      <c r="E407" s="50"/>
+    </row>
+    <row r="408" spans="5:5">
+      <c r="E408" s="50"/>
+    </row>
+    <row r="409" spans="5:5">
+      <c r="E409" s="50"/>
+    </row>
+    <row r="410" spans="5:5">
+      <c r="E410" s="50"/>
+    </row>
+    <row r="411" spans="5:5">
+      <c r="E411" s="50"/>
+    </row>
+    <row r="412" spans="5:5">
+      <c r="E412" s="50"/>
+    </row>
+    <row r="413" spans="5:5">
+      <c r="E413" s="50"/>
+    </row>
+    <row r="414" spans="5:5">
+      <c r="E414" s="50"/>
+    </row>
+    <row r="415" spans="5:5">
+      <c r="E415" s="50"/>
+    </row>
+    <row r="416" spans="5:5">
+      <c r="E416" s="50"/>
+    </row>
+    <row r="417" spans="5:5">
+      <c r="E417" s="50"/>
+    </row>
+    <row r="418" spans="5:5">
+      <c r="E418" s="50"/>
+    </row>
+    <row r="419" spans="5:5">
+      <c r="E419" s="50"/>
+    </row>
+    <row r="420" spans="5:5">
+      <c r="E420" s="50"/>
+    </row>
+    <row r="421" spans="5:5">
+      <c r="E421" s="50"/>
+    </row>
+    <row r="422" spans="5:5">
+      <c r="E422" s="50"/>
+    </row>
+    <row r="423" spans="5:5">
+      <c r="E423" s="50"/>
+    </row>
+    <row r="424" spans="5:5">
+      <c r="E424" s="50"/>
+    </row>
+    <row r="425" spans="5:5">
+      <c r="E425" s="50"/>
+    </row>
+    <row r="426" spans="5:5">
+      <c r="E426" s="50"/>
+    </row>
+    <row r="427" spans="5:5">
+      <c r="E427" s="50"/>
+    </row>
+    <row r="428" spans="5:5">
+      <c r="E428" s="50"/>
+    </row>
+    <row r="429" spans="5:5">
+      <c r="E429" s="50"/>
+    </row>
+    <row r="430" spans="5:5">
+      <c r="E430" s="50"/>
+    </row>
+    <row r="431" spans="5:5">
+      <c r="E431" s="50"/>
+    </row>
+    <row r="432" spans="5:5">
+      <c r="E432" s="50"/>
+    </row>
+    <row r="433" spans="5:5">
+      <c r="E433" s="50"/>
+    </row>
+    <row r="434" spans="5:5">
+      <c r="E434" s="50"/>
+    </row>
+    <row r="435" spans="5:5">
+      <c r="E435" s="50"/>
+    </row>
+    <row r="436" spans="5:5">
+      <c r="E436" s="50"/>
+    </row>
+    <row r="437" spans="5:5">
+      <c r="E437" s="50"/>
+    </row>
+    <row r="438" spans="5:5">
+      <c r="E438" s="50"/>
+    </row>
+    <row r="439" spans="5:5">
+      <c r="E439" s="50"/>
+    </row>
+    <row r="440" spans="5:5">
+      <c r="E440" s="50"/>
+    </row>
+    <row r="441" spans="5:5">
+      <c r="E441" s="50"/>
+    </row>
+    <row r="442" spans="5:5">
+      <c r="E442" s="50"/>
+    </row>
+    <row r="443" spans="5:5">
+      <c r="E443" s="50"/>
+    </row>
+    <row r="444" spans="5:5">
+      <c r="E444" s="50"/>
+    </row>
+    <row r="445" spans="5:5">
+      <c r="E445" s="50"/>
+    </row>
+    <row r="446" spans="5:5">
+      <c r="E446" s="50"/>
+    </row>
+    <row r="447" spans="5:5">
+      <c r="E447" s="50"/>
+    </row>
+    <row r="448" spans="5:5">
+      <c r="E448" s="50"/>
+    </row>
+    <row r="449" spans="5:5">
+      <c r="E449" s="50"/>
+    </row>
+    <row r="450" spans="5:5">
+      <c r="E450" s="50"/>
+    </row>
+    <row r="451" spans="5:5">
+      <c r="E451" s="50"/>
+    </row>
+    <row r="452" spans="5:5">
+      <c r="E452" s="50"/>
+    </row>
+    <row r="453" spans="5:5">
+      <c r="E453" s="50"/>
+    </row>
+    <row r="454" spans="5:5">
+      <c r="E454" s="50"/>
+    </row>
+    <row r="455" spans="5:5">
+      <c r="E455" s="50"/>
+    </row>
+    <row r="456" spans="5:5">
+      <c r="E456" s="50"/>
+    </row>
+    <row r="457" spans="5:5">
+      <c r="E457" s="50"/>
+    </row>
+    <row r="458" spans="5:5">
+      <c r="E458" s="50"/>
+    </row>
+    <row r="459" spans="5:5">
+      <c r="E459" s="50"/>
+    </row>
+    <row r="460" spans="5:5">
+      <c r="E460" s="50"/>
+    </row>
+    <row r="461" spans="5:5">
+      <c r="E461" s="50"/>
+    </row>
+    <row r="462" spans="5:5">
+      <c r="E462" s="50"/>
+    </row>
+    <row r="463" spans="5:5">
+      <c r="E463" s="50"/>
+    </row>
+    <row r="464" spans="5:5">
+      <c r="E464" s="50"/>
+    </row>
+    <row r="465" spans="5:5">
+      <c r="E465" s="50"/>
+    </row>
+    <row r="466" spans="5:5">
+      <c r="E466" s="50"/>
+    </row>
+    <row r="467" spans="5:5">
+      <c r="E467" s="50"/>
+    </row>
+    <row r="468" spans="5:5">
+      <c r="E468" s="50"/>
+    </row>
+    <row r="469" spans="5:5">
+      <c r="E469" s="50"/>
+    </row>
+    <row r="470" spans="5:5">
+      <c r="E470" s="50"/>
+    </row>
+    <row r="471" spans="5:5">
+      <c r="E471" s="50"/>
+    </row>
+    <row r="472" spans="5:5">
+      <c r="E472" s="50"/>
+    </row>
+    <row r="473" spans="5:5">
+      <c r="E473" s="50"/>
+    </row>
+    <row r="474" spans="5:5">
+      <c r="E474" s="50"/>
+    </row>
+    <row r="475" spans="5:5">
+      <c r="E475" s="50"/>
+    </row>
+    <row r="476" spans="5:5">
+      <c r="E476" s="50"/>
+    </row>
+    <row r="477" spans="5:5">
+      <c r="E477" s="50"/>
+    </row>
+    <row r="478" spans="5:5">
+      <c r="E478" s="50"/>
+    </row>
+    <row r="479" spans="5:5">
+      <c r="E479" s="50"/>
+    </row>
+    <row r="480" spans="5:5">
+      <c r="E480" s="50"/>
+    </row>
+    <row r="481" spans="5:5">
+      <c r="E481" s="50"/>
+    </row>
+    <row r="482" spans="5:5">
+      <c r="E482" s="50"/>
+    </row>
+    <row r="483" spans="5:5">
+      <c r="E483" s="50"/>
+    </row>
+    <row r="484" spans="5:5">
+      <c r="E484" s="50"/>
+    </row>
+    <row r="485" spans="5:5">
+      <c r="E485" s="50"/>
+    </row>
+    <row r="486" spans="5:5">
+      <c r="E486" s="50"/>
+    </row>
+    <row r="487" spans="5:5">
+      <c r="E487" s="50"/>
+    </row>
+    <row r="488" spans="5:5">
+      <c r="E488" s="50"/>
+    </row>
+    <row r="489" spans="5:5">
+      <c r="E489" s="50"/>
+    </row>
+    <row r="490" spans="5:5">
+      <c r="E490" s="50"/>
+    </row>
+    <row r="491" spans="5:5">
+      <c r="E491" s="50"/>
+    </row>
+    <row r="492" spans="5:5">
+      <c r="E492" s="50"/>
+    </row>
+    <row r="493" spans="5:5">
+      <c r="E493" s="50"/>
+    </row>
+    <row r="494" spans="5:5">
+      <c r="E494" s="50"/>
+    </row>
+    <row r="495" spans="5:5">
+      <c r="E495" s="50"/>
+    </row>
+    <row r="496" spans="5:5">
+      <c r="E496" s="50"/>
+    </row>
+    <row r="497" spans="5:5">
+      <c r="E497" s="50"/>
+    </row>
+    <row r="498" spans="5:5">
+      <c r="E498" s="50"/>
+    </row>
+    <row r="499" spans="5:5">
+      <c r="E499" s="50"/>
+    </row>
+    <row r="500" spans="5:5">
+      <c r="E500" s="50"/>
+    </row>
+    <row r="501" spans="5:5">
+      <c r="E501" s="50"/>
+    </row>
+    <row r="502" spans="5:5">
+      <c r="E502" s="50"/>
+    </row>
+    <row r="503" spans="5:5">
+      <c r="E503" s="50"/>
+    </row>
+    <row r="504" spans="5:5">
+      <c r="E504" s="50"/>
+    </row>
+    <row r="505" spans="5:5">
+      <c r="E505" s="50"/>
+    </row>
+    <row r="506" spans="5:5">
+      <c r="E506" s="50"/>
+    </row>
+    <row r="507" spans="5:5">
+      <c r="E507" s="50"/>
+    </row>
+    <row r="508" spans="5:5">
+      <c r="E508" s="50"/>
+    </row>
+    <row r="509" spans="5:5">
+      <c r="E509" s="50"/>
+    </row>
+    <row r="510" spans="5:5">
+      <c r="E510" s="50"/>
+    </row>
+    <row r="511" spans="5:5">
+      <c r="E511" s="50"/>
+    </row>
+    <row r="512" spans="5:5">
+      <c r="E512" s="50"/>
+    </row>
+    <row r="513" spans="5:5">
+      <c r="E513" s="50"/>
+    </row>
+    <row r="514" spans="5:5">
+      <c r="E514" s="50"/>
+    </row>
+    <row r="515" spans="5:5">
+      <c r="E515" s="50"/>
+    </row>
+    <row r="516" spans="5:5">
+      <c r="E516" s="50"/>
+    </row>
+    <row r="517" spans="5:5">
+      <c r="E517" s="50"/>
+    </row>
+    <row r="518" spans="5:5">
+      <c r="E518" s="50"/>
+    </row>
+    <row r="519" spans="5:5">
+      <c r="E519" s="50"/>
+    </row>
+    <row r="520" spans="5:5">
+      <c r="E520" s="50"/>
+    </row>
+    <row r="521" spans="5:5">
+      <c r="E521" s="50"/>
+    </row>
+    <row r="522" spans="5:5">
+      <c r="E522" s="50"/>
+    </row>
+    <row r="523" spans="5:5">
+      <c r="E523" s="50"/>
+    </row>
+    <row r="524" spans="5:5">
+      <c r="E524" s="50"/>
+    </row>
+    <row r="525" spans="5:5">
+      <c r="E525" s="50"/>
+    </row>
+    <row r="526" spans="5:5">
+      <c r="E526" s="50"/>
+    </row>
+    <row r="527" spans="5:5">
+      <c r="E527" s="50"/>
+    </row>
+    <row r="528" spans="5:5">
+      <c r="E528" s="50"/>
+    </row>
+    <row r="529" spans="5:5">
+      <c r="E529" s="50"/>
+    </row>
+    <row r="530" spans="5:5">
+      <c r="E530" s="50"/>
+    </row>
+    <row r="531" spans="5:5">
+      <c r="E531" s="50"/>
+    </row>
+    <row r="532" spans="5:5">
+      <c r="E532" s="50"/>
+    </row>
+    <row r="533" spans="5:5">
+      <c r="E533" s="50"/>
+    </row>
+    <row r="534" spans="5:5">
+      <c r="E534" s="50"/>
+    </row>
+    <row r="535" spans="5:5">
+      <c r="E535" s="50"/>
+    </row>
+    <row r="536" spans="5:5">
+      <c r="E536" s="50"/>
+    </row>
+    <row r="537" spans="5:5">
+      <c r="E537" s="50"/>
+    </row>
+    <row r="538" spans="5:5">
+      <c r="E538" s="50"/>
+    </row>
+    <row r="539" spans="5:5">
+      <c r="E539" s="50"/>
+    </row>
+    <row r="540" spans="5:5">
+      <c r="E540" s="50"/>
+    </row>
+    <row r="541" spans="5:5">
+      <c r="E541" s="50"/>
+    </row>
+    <row r="542" spans="5:5">
+      <c r="E542" s="50"/>
+    </row>
+    <row r="543" spans="5:5">
+      <c r="E543" s="50"/>
+    </row>
+    <row r="544" spans="5:5">
+      <c r="E544" s="50"/>
+    </row>
+    <row r="545" spans="5:5">
+      <c r="E545" s="50"/>
+    </row>
+    <row r="546" spans="5:5">
+      <c r="E546" s="50"/>
+    </row>
+    <row r="547" spans="5:5">
+      <c r="E547" s="50"/>
+    </row>
+    <row r="548" spans="5:5">
+      <c r="E548" s="50"/>
+    </row>
+    <row r="549" spans="5:5">
+      <c r="E549" s="50"/>
+    </row>
+    <row r="550" spans="5:5">
+      <c r="E550" s="50"/>
+    </row>
+    <row r="551" spans="5:5">
+      <c r="E551" s="50"/>
+    </row>
+    <row r="552" spans="5:5">
+      <c r="E552" s="50"/>
+    </row>
+    <row r="553" spans="5:5">
+      <c r="E553" s="50"/>
+    </row>
+    <row r="554" spans="5:5">
+      <c r="E554" s="50"/>
+    </row>
+    <row r="555" spans="5:5">
+      <c r="E555" s="50"/>
+    </row>
+    <row r="556" spans="5:5">
+      <c r="E556" s="50"/>
+    </row>
+    <row r="557" spans="5:5">
+      <c r="E557" s="50"/>
+    </row>
+    <row r="558" spans="5:5">
+      <c r="E558" s="50"/>
+    </row>
+    <row r="559" spans="5:5">
+      <c r="E559" s="50"/>
+    </row>
+    <row r="560" spans="5:5">
+      <c r="E560" s="50"/>
+    </row>
+    <row r="561" spans="5:5">
+      <c r="E561" s="50"/>
+    </row>
+    <row r="562" spans="5:5">
+      <c r="E562" s="50"/>
+    </row>
+    <row r="563" spans="5:5">
+      <c r="E563" s="50"/>
+    </row>
+    <row r="564" spans="5:5">
+      <c r="E564" s="50"/>
+    </row>
+    <row r="565" spans="5:5">
+      <c r="E565" s="50"/>
+    </row>
+    <row r="566" spans="5:5">
+      <c r="E566" s="50"/>
+    </row>
+    <row r="567" spans="5:5">
+      <c r="E567" s="50"/>
+    </row>
+    <row r="568" spans="5:5">
+      <c r="E568" s="50"/>
+    </row>
+    <row r="569" spans="5:5">
+      <c r="E569" s="50"/>
+    </row>
+    <row r="570" spans="5:5">
+      <c r="E570" s="50"/>
+    </row>
+    <row r="571" spans="5:5">
+      <c r="E571" s="50"/>
+    </row>
+    <row r="572" spans="5:5">
+      <c r="E572" s="50"/>
+    </row>
+    <row r="573" spans="5:5">
+      <c r="E573" s="50"/>
+    </row>
+    <row r="574" spans="5:5">
+      <c r="E574" s="50"/>
+    </row>
+    <row r="575" spans="5:5">
+      <c r="E575" s="50"/>
+    </row>
+    <row r="576" spans="5:5">
+      <c r="E576" s="50"/>
+    </row>
+    <row r="577" spans="5:5">
+      <c r="E577" s="50"/>
+    </row>
+    <row r="578" spans="5:5">
+      <c r="E578" s="50"/>
+    </row>
+    <row r="579" spans="5:5">
+      <c r="E579" s="50"/>
+    </row>
+    <row r="580" spans="5:5">
+      <c r="E580" s="50"/>
+    </row>
+    <row r="581" spans="5:5">
+      <c r="E581" s="50"/>
+    </row>
+    <row r="582" spans="5:5">
+      <c r="E582" s="50"/>
+    </row>
+    <row r="583" spans="5:5">
+      <c r="E583" s="50"/>
+    </row>
+    <row r="584" spans="5:5">
+      <c r="E584" s="50"/>
+    </row>
+    <row r="585" spans="5:5">
+      <c r="E585" s="50"/>
+    </row>
+    <row r="586" spans="5:5">
+      <c r="E586" s="50"/>
+    </row>
+    <row r="587" spans="5:5">
+      <c r="E587" s="50"/>
+    </row>
+    <row r="588" spans="5:5">
+      <c r="E588" s="50"/>
+    </row>
+    <row r="589" spans="5:5">
+      <c r="E589" s="50"/>
+    </row>
+    <row r="590" spans="5:5">
+      <c r="E590" s="50"/>
+    </row>
+    <row r="591" spans="5:5">
+      <c r="E591" s="50"/>
+    </row>
+    <row r="592" spans="5:5">
+      <c r="E592" s="50"/>
+    </row>
+    <row r="593" spans="5:5">
+      <c r="E593" s="50"/>
+    </row>
+    <row r="594" spans="5:5">
+      <c r="E594" s="50"/>
+    </row>
+    <row r="595" spans="5:5">
+      <c r="E595" s="50"/>
+    </row>
+    <row r="596" spans="5:5">
+      <c r="E596" s="50"/>
+    </row>
+    <row r="597" spans="5:5">
+      <c r="E597" s="50"/>
+    </row>
+    <row r="598" spans="5:5">
+      <c r="E598" s="50"/>
+    </row>
+    <row r="599" spans="5:5">
+      <c r="E599" s="50"/>
+    </row>
+    <row r="600" spans="5:5">
+      <c r="E600" s="50"/>
+    </row>
+    <row r="601" spans="5:5">
+      <c r="E601" s="50"/>
+    </row>
+    <row r="602" spans="5:5">
+      <c r="E602" s="50"/>
+    </row>
+    <row r="603" spans="5:5">
+      <c r="E603" s="50"/>
+    </row>
+    <row r="604" spans="5:5">
+      <c r="E604" s="50"/>
+    </row>
+    <row r="605" spans="5:5">
+      <c r="E605" s="50"/>
+    </row>
+    <row r="606" spans="5:5">
+      <c r="E606" s="50"/>
+    </row>
+    <row r="607" spans="5:5">
+      <c r="E607" s="50"/>
+    </row>
+    <row r="608" spans="5:5">
+      <c r="E608" s="50"/>
+    </row>
+    <row r="609" spans="5:5">
+      <c r="E609" s="50"/>
+    </row>
+    <row r="610" spans="5:5">
+      <c r="E610" s="50"/>
+    </row>
+    <row r="611" spans="5:5">
+      <c r="E611" s="50"/>
+    </row>
+    <row r="612" spans="5:5">
+      <c r="E612" s="50"/>
+    </row>
+    <row r="613" spans="5:5">
+      <c r="E613" s="50"/>
+    </row>
+    <row r="614" spans="5:5">
+      <c r="E614" s="50"/>
+    </row>
+    <row r="615" spans="5:5">
+      <c r="E615" s="50"/>
+    </row>
+    <row r="616" spans="5:5">
+      <c r="E616" s="50"/>
+    </row>
+    <row r="617" spans="5:5">
+      <c r="E617" s="50"/>
+    </row>
+    <row r="618" spans="5:5">
+      <c r="E618" s="50"/>
+    </row>
+    <row r="619" spans="5:5">
+      <c r="E619" s="50"/>
+    </row>
+    <row r="620" spans="5:5">
+      <c r="E620" s="50"/>
+    </row>
+    <row r="621" spans="5:5">
+      <c r="E621" s="50"/>
+    </row>
+    <row r="622" spans="5:5">
+      <c r="E622" s="50"/>
+    </row>
+    <row r="623" spans="5:5">
+      <c r="E623" s="50"/>
+    </row>
+    <row r="624" spans="5:5">
+      <c r="E624" s="50"/>
+    </row>
+    <row r="625" spans="5:5">
+      <c r="E625" s="50"/>
+    </row>
+    <row r="626" spans="5:5">
+      <c r="E626" s="50"/>
+    </row>
+    <row r="627" spans="5:5">
+      <c r="E627" s="50"/>
+    </row>
+    <row r="628" spans="5:5">
+      <c r="E628" s="50"/>
+    </row>
+    <row r="629" spans="5:5">
+      <c r="E629" s="50"/>
+    </row>
+    <row r="630" spans="5:5">
+      <c r="E630" s="50"/>
+    </row>
+    <row r="631" spans="5:5">
+      <c r="E631" s="50"/>
+    </row>
+    <row r="632" spans="5:5">
+      <c r="E632" s="50"/>
+    </row>
+    <row r="633" spans="5:5">
+      <c r="E633" s="50"/>
+    </row>
+    <row r="634" spans="5:5">
+      <c r="E634" s="50"/>
+    </row>
+    <row r="635" spans="5:5">
+      <c r="E635" s="50"/>
+    </row>
+    <row r="636" spans="5:5">
+      <c r="E636" s="50"/>
+    </row>
+    <row r="637" spans="5:5">
+      <c r="E637" s="50"/>
+    </row>
+    <row r="638" spans="5:5">
+      <c r="E638" s="50"/>
+    </row>
+    <row r="639" spans="5:5">
+      <c r="E639" s="50"/>
+    </row>
+    <row r="640" spans="5:5">
+      <c r="E640" s="50"/>
+    </row>
+    <row r="641" spans="5:5">
+      <c r="E641" s="50"/>
+    </row>
+    <row r="642" spans="5:5">
+      <c r="E642" s="50"/>
+    </row>
+    <row r="643" spans="5:5">
+      <c r="E643" s="50"/>
+    </row>
+    <row r="644" spans="5:5">
+      <c r="E644" s="50"/>
+    </row>
+    <row r="645" spans="5:5">
+      <c r="E645" s="50"/>
+    </row>
+    <row r="646" spans="5:5">
+      <c r="E646" s="50"/>
+    </row>
+    <row r="647" spans="5:5">
+      <c r="E647" s="50"/>
+    </row>
+    <row r="648" spans="5:5">
+      <c r="E648" s="50"/>
+    </row>
+    <row r="649" spans="5:5">
+      <c r="E649" s="50"/>
+    </row>
+    <row r="650" spans="5:5">
+      <c r="E650" s="50"/>
+    </row>
+    <row r="651" spans="5:5">
+      <c r="E651" s="50"/>
+    </row>
+    <row r="652" spans="5:5">
+      <c r="E652" s="50"/>
+    </row>
+    <row r="653" spans="5:5">
+      <c r="E653" s="50"/>
+    </row>
+    <row r="654" spans="5:5">
+      <c r="E654" s="50"/>
+    </row>
+    <row r="655" spans="5:5">
+      <c r="E655" s="50"/>
+    </row>
+    <row r="656" spans="5:5">
+      <c r="E656" s="50"/>
+    </row>
+    <row r="657" spans="5:5">
+      <c r="E657" s="50"/>
+    </row>
+    <row r="658" spans="5:5">
+      <c r="E658" s="50"/>
+    </row>
+    <row r="659" spans="5:5">
+      <c r="E659" s="50"/>
+    </row>
+    <row r="660" spans="5:5">
+      <c r="E660" s="50"/>
+    </row>
+    <row r="661" spans="5:5">
+      <c r="E661" s="50"/>
+    </row>
+    <row r="662" spans="5:5">
+      <c r="E662" s="50"/>
+    </row>
+    <row r="663" spans="5:5">
+      <c r="E663" s="50"/>
+    </row>
+    <row r="664" spans="5:5">
+      <c r="E664" s="50"/>
+    </row>
+    <row r="665" spans="5:5">
+      <c r="E665" s="50"/>
+    </row>
+    <row r="666" spans="5:5">
+      <c r="E666" s="50"/>
+    </row>
+    <row r="667" spans="5:5">
+      <c r="E667" s="50"/>
+    </row>
+    <row r="668" spans="5:5">
+      <c r="E668" s="50"/>
+    </row>
+    <row r="669" spans="5:5">
+      <c r="E669" s="50"/>
+    </row>
+    <row r="670" spans="5:5">
+      <c r="E670" s="50"/>
+    </row>
+    <row r="671" spans="5:5">
+      <c r="E671" s="50"/>
+    </row>
+    <row r="672" spans="5:5">
+      <c r="E672" s="50"/>
+    </row>
+    <row r="673" spans="5:5">
+      <c r="E673" s="50"/>
+    </row>
+    <row r="674" spans="5:5">
+      <c r="E674" s="50"/>
+    </row>
+    <row r="675" spans="5:5">
+      <c r="E675" s="50"/>
+    </row>
+    <row r="676" spans="5:5">
+      <c r="E676" s="50"/>
+    </row>
+    <row r="677" spans="5:5">
+      <c r="E677" s="50"/>
+    </row>
+    <row r="678" spans="5:5">
+      <c r="E678" s="50"/>
+    </row>
+    <row r="679" spans="5:5">
+      <c r="E679" s="50"/>
+    </row>
+    <row r="680" spans="5:5">
+      <c r="E680" s="50"/>
+    </row>
+    <row r="681" spans="5:5">
+      <c r="E681" s="50"/>
+    </row>
+    <row r="682" spans="5:5">
+      <c r="E682" s="50"/>
+    </row>
+    <row r="683" spans="5:5">
+      <c r="E683" s="50"/>
+    </row>
+    <row r="684" spans="5:5">
+      <c r="E684" s="50"/>
+    </row>
+    <row r="685" spans="5:5">
+      <c r="E685" s="50"/>
+    </row>
+    <row r="686" spans="5:5">
+      <c r="E686" s="50"/>
+    </row>
+    <row r="687" spans="5:5">
+      <c r="E687" s="50"/>
+    </row>
+    <row r="688" spans="5:5">
+      <c r="E688" s="50"/>
+    </row>
+    <row r="689" spans="5:5">
+      <c r="E689" s="50"/>
+    </row>
+    <row r="690" spans="5:5">
+      <c r="E690" s="50"/>
+    </row>
+    <row r="691" spans="5:5">
+      <c r="E691" s="50"/>
+    </row>
+    <row r="692" spans="5:5">
+      <c r="E692" s="50"/>
+    </row>
+    <row r="693" spans="5:5">
+      <c r="E693" s="50"/>
+    </row>
+    <row r="694" spans="5:5">
+      <c r="E694" s="50"/>
+    </row>
+    <row r="695" spans="5:5">
+      <c r="E695" s="50"/>
+    </row>
+    <row r="696" spans="5:5">
+      <c r="E696" s="50"/>
+    </row>
+    <row r="697" spans="5:5">
+      <c r="E697" s="50"/>
+    </row>
+    <row r="698" spans="5:5">
+      <c r="E698" s="50"/>
+    </row>
+    <row r="699" spans="5:5">
+      <c r="E699" s="50"/>
+    </row>
+    <row r="700" spans="5:5">
+      <c r="E700" s="50"/>
+    </row>
+    <row r="701" spans="5:5">
+      <c r="E701" s="50"/>
+    </row>
+    <row r="702" spans="5:5">
+      <c r="E702" s="50"/>
+    </row>
+    <row r="703" spans="5:5">
+      <c r="E703" s="50"/>
+    </row>
+    <row r="704" spans="5:5">
+      <c r="E704" s="50"/>
+    </row>
+    <row r="705" spans="5:5">
+      <c r="E705" s="50"/>
+    </row>
+    <row r="706" spans="5:5">
+      <c r="E706" s="50"/>
+    </row>
+    <row r="707" spans="5:5">
+      <c r="E707" s="50"/>
+    </row>
+    <row r="708" spans="5:5">
+      <c r="E708" s="50"/>
+    </row>
+    <row r="709" spans="5:5">
+      <c r="E709" s="50"/>
+    </row>
+    <row r="710" spans="5:5">
+      <c r="E710" s="50"/>
+    </row>
+    <row r="711" spans="5:5">
+      <c r="E711" s="50"/>
+    </row>
+    <row r="712" spans="5:5">
+      <c r="E712" s="50"/>
+    </row>
+    <row r="713" spans="5:5">
+      <c r="E713" s="50"/>
+    </row>
+    <row r="714" spans="5:5">
+      <c r="E714" s="50"/>
+    </row>
+    <row r="715" spans="5:5">
+      <c r="E715" s="50"/>
+    </row>
+    <row r="716" spans="5:5">
+      <c r="E716" s="50"/>
+    </row>
+    <row r="717" spans="5:5">
+      <c r="E717" s="50"/>
+    </row>
+    <row r="718" spans="5:5">
+      <c r="E718" s="50"/>
+    </row>
+    <row r="719" spans="5:5">
+      <c r="E719" s="50"/>
+    </row>
+    <row r="720" spans="5:5">
+      <c r="E720" s="50"/>
+    </row>
+    <row r="721" spans="5:5">
+      <c r="E721" s="50"/>
+    </row>
+    <row r="722" spans="5:5">
+      <c r="E722" s="50"/>
+    </row>
+    <row r="723" spans="5:5">
+      <c r="E723" s="50"/>
+    </row>
+    <row r="724" spans="5:5">
+      <c r="E724" s="50"/>
+    </row>
+    <row r="725" spans="5:5">
+      <c r="E725" s="50"/>
+    </row>
+    <row r="726" spans="5:5">
+      <c r="E726" s="50"/>
+    </row>
+    <row r="727" spans="5:5">
+      <c r="E727" s="50"/>
+    </row>
+    <row r="728" spans="5:5">
+      <c r="E728" s="50"/>
+    </row>
+    <row r="729" spans="5:5">
+      <c r="E729" s="50"/>
+    </row>
+    <row r="730" spans="5:5">
+      <c r="E730" s="50"/>
+    </row>
+    <row r="731" spans="5:5">
+      <c r="E731" s="50"/>
+    </row>
+    <row r="732" spans="5:5">
+      <c r="E732" s="50"/>
+    </row>
+    <row r="733" spans="5:5">
+      <c r="E733" s="50"/>
+    </row>
+    <row r="734" spans="5:5">
+      <c r="E734" s="50"/>
+    </row>
+    <row r="735" spans="5:5">
+      <c r="E735" s="50"/>
+    </row>
+    <row r="736" spans="5:5">
+      <c r="E736" s="50"/>
+    </row>
+    <row r="737" spans="5:5">
+      <c r="E737" s="50"/>
+    </row>
+    <row r="738" spans="5:5">
+      <c r="E738" s="50"/>
+    </row>
+    <row r="739" spans="5:5">
+      <c r="E739" s="50"/>
+    </row>
+    <row r="740" spans="5:5">
+      <c r="E740" s="50"/>
+    </row>
+    <row r="741" spans="5:5">
+      <c r="E741" s="50"/>
+    </row>
+    <row r="742" spans="5:5">
+      <c r="E742" s="50"/>
+    </row>
+    <row r="743" spans="5:5">
+      <c r="E743" s="50"/>
+    </row>
+    <row r="744" spans="5:5">
+      <c r="E744" s="50"/>
+    </row>
+    <row r="745" spans="5:5">
+      <c r="E745" s="50"/>
+    </row>
+    <row r="746" spans="5:5">
+      <c r="E746" s="50"/>
+    </row>
+    <row r="747" spans="5:5">
+      <c r="E747" s="50"/>
+    </row>
+    <row r="748" spans="5:5">
+      <c r="E748" s="50"/>
+    </row>
+    <row r="749" spans="5:5">
+      <c r="E749" s="50"/>
+    </row>
+    <row r="750" spans="5:5">
+      <c r="E750" s="50"/>
+    </row>
+    <row r="751" spans="5:5">
+      <c r="E751" s="50"/>
+    </row>
+    <row r="752" spans="5:5">
+      <c r="E752" s="50"/>
+    </row>
+    <row r="753" spans="5:5">
+      <c r="E753" s="50"/>
+    </row>
+    <row r="754" spans="5:5">
+      <c r="E754" s="50"/>
+    </row>
+    <row r="755" spans="5:5">
+      <c r="E755" s="50"/>
+    </row>
+    <row r="756" spans="5:5">
+      <c r="E756" s="50"/>
+    </row>
+    <row r="757" spans="5:5">
+      <c r="E757" s="50"/>
+    </row>
+    <row r="758" spans="5:5">
+      <c r="E758" s="50"/>
+    </row>
+    <row r="759" spans="5:5">
+      <c r="E759" s="50"/>
+    </row>
+    <row r="760" spans="5:5">
+      <c r="E760" s="50"/>
+    </row>
+    <row r="761" spans="5:5">
+      <c r="E761" s="50"/>
+    </row>
+    <row r="762" spans="5:5">
+      <c r="E762" s="50"/>
+    </row>
+    <row r="763" spans="5:5">
+      <c r="E763" s="50"/>
+    </row>
+    <row r="764" spans="5:5">
+      <c r="E764" s="50"/>
+    </row>
+    <row r="765" spans="5:5">
+      <c r="E765" s="50"/>
+    </row>
+    <row r="766" spans="5:5">
+      <c r="E766" s="50"/>
+    </row>
+    <row r="767" spans="5:5">
+      <c r="E767" s="50"/>
+    </row>
+    <row r="768" spans="5:5">
+      <c r="E768" s="50"/>
+    </row>
+    <row r="769" spans="5:5">
+      <c r="E769" s="50"/>
+    </row>
+    <row r="770" spans="5:5">
+      <c r="E770" s="50"/>
+    </row>
+    <row r="771" spans="5:5">
+      <c r="E771" s="50"/>
+    </row>
+    <row r="772" spans="5:5">
+      <c r="E772" s="50"/>
+    </row>
+    <row r="773" spans="5:5">
+      <c r="E773" s="50"/>
+    </row>
+    <row r="774" spans="5:5">
+      <c r="E774" s="50"/>
+    </row>
+    <row r="775" spans="5:5">
+      <c r="E775" s="50"/>
+    </row>
+    <row r="776" spans="5:5">
+      <c r="E776" s="50"/>
+    </row>
+    <row r="777" spans="5:5">
+      <c r="E777" s="50"/>
+    </row>
+    <row r="778" spans="5:5">
+      <c r="E778" s="50"/>
+    </row>
+    <row r="779" spans="5:5">
+      <c r="E779" s="50"/>
+    </row>
+    <row r="780" spans="5:5">
+      <c r="E780" s="50"/>
+    </row>
+    <row r="781" spans="5:5">
+      <c r="E781" s="50"/>
+    </row>
+    <row r="782" spans="5:5">
+      <c r="E782" s="50"/>
+    </row>
+    <row r="783" spans="5:5">
+      <c r="E783" s="50"/>
+    </row>
+    <row r="784" spans="5:5">
+      <c r="E784" s="50"/>
+    </row>
+    <row r="785" spans="5:5">
+      <c r="E785" s="50"/>
+    </row>
+    <row r="786" spans="5:5">
+      <c r="E786" s="50"/>
+    </row>
+    <row r="787" spans="5:5">
+      <c r="E787" s="50"/>
+    </row>
+    <row r="788" spans="5:5">
+      <c r="E788" s="50"/>
+    </row>
+    <row r="789" spans="5:5">
+      <c r="E789" s="50"/>
+    </row>
+    <row r="790" spans="5:5">
+      <c r="E790" s="50"/>
+    </row>
+    <row r="791" spans="5:5">
+      <c r="E791" s="50"/>
+    </row>
+    <row r="792" spans="5:5">
+      <c r="E792" s="50"/>
+    </row>
+    <row r="793" spans="5:5">
+      <c r="E793" s="50"/>
+    </row>
+    <row r="794" spans="5:5">
+      <c r="E794" s="50"/>
+    </row>
+    <row r="795" spans="5:5">
+      <c r="E795" s="50"/>
+    </row>
+    <row r="796" spans="5:5">
+      <c r="E796" s="50"/>
+    </row>
+    <row r="797" spans="5:5">
+      <c r="E797" s="50"/>
+    </row>
+    <row r="798" spans="5:5">
+      <c r="E798" s="50"/>
+    </row>
+    <row r="799" spans="5:5">
+      <c r="E799" s="50"/>
+    </row>
+    <row r="800" spans="5:5">
+      <c r="E800" s="50"/>
+    </row>
+    <row r="801" spans="5:5">
+      <c r="E801" s="50"/>
+    </row>
+    <row r="802" spans="5:5">
+      <c r="E802" s="50"/>
+    </row>
+    <row r="803" spans="5:5">
+      <c r="E803" s="50"/>
+    </row>
+    <row r="804" spans="5:5">
+      <c r="E804" s="50"/>
+    </row>
+    <row r="805" spans="5:5">
+      <c r="E805" s="50"/>
+    </row>
+    <row r="806" spans="5:5">
+      <c r="E806" s="50"/>
+    </row>
+    <row r="807" spans="5:5">
+      <c r="E807" s="50"/>
+    </row>
+    <row r="808" spans="5:5">
+      <c r="E808" s="50"/>
+    </row>
+    <row r="809" spans="5:5">
+      <c r="E809" s="50"/>
+    </row>
+    <row r="810" spans="5:5">
+      <c r="E810" s="50"/>
+    </row>
+    <row r="811" spans="5:5">
+      <c r="E811" s="50"/>
+    </row>
+    <row r="812" spans="5:5">
+      <c r="E812" s="50"/>
+    </row>
+    <row r="813" spans="5:5">
+      <c r="E813" s="50"/>
+    </row>
+    <row r="814" spans="5:5">
+      <c r="E814" s="50"/>
+    </row>
+    <row r="815" spans="5:5">
+      <c r="E815" s="50"/>
+    </row>
+    <row r="816" spans="5:5">
+      <c r="E816" s="50"/>
+    </row>
+    <row r="817" spans="5:5">
+      <c r="E817" s="50"/>
+    </row>
+    <row r="818" spans="5:5">
+      <c r="E818" s="50"/>
+    </row>
+    <row r="819" spans="5:5">
+      <c r="E819" s="50"/>
+    </row>
+    <row r="820" spans="5:5">
+      <c r="E820" s="50"/>
+    </row>
+    <row r="821" spans="5:5">
+      <c r="E821" s="50"/>
+    </row>
+    <row r="822" spans="5:5">
+      <c r="E822" s="50"/>
+    </row>
+    <row r="823" spans="5:5">
+      <c r="E823" s="50"/>
+    </row>
+    <row r="824" spans="5:5">
+      <c r="E824" s="50"/>
+    </row>
+    <row r="825" spans="5:5">
+      <c r="E825" s="50"/>
+    </row>
+    <row r="826" spans="5:5">
+      <c r="E826" s="50"/>
+    </row>
+    <row r="827" spans="5:5">
+      <c r="E827" s="50"/>
+    </row>
+    <row r="828" spans="5:5">
+      <c r="E828" s="50"/>
+    </row>
+    <row r="829" spans="5:5">
+      <c r="E829" s="50"/>
+    </row>
+    <row r="830" spans="5:5">
+      <c r="E830" s="50"/>
+    </row>
+    <row r="831" spans="5:5">
+      <c r="E831" s="50"/>
+    </row>
+    <row r="832" spans="5:5">
+      <c r="E832" s="50"/>
+    </row>
+    <row r="833" spans="5:5">
+      <c r="E833" s="50"/>
+    </row>
+    <row r="834" spans="5:5">
+      <c r="E834" s="50"/>
+    </row>
+    <row r="835" spans="5:5">
+      <c r="E835" s="50"/>
+    </row>
+    <row r="836" spans="5:5">
+      <c r="E836" s="50"/>
+    </row>
+    <row r="837" spans="5:5">
+      <c r="E837" s="50"/>
+    </row>
+    <row r="838" spans="5:5">
+      <c r="E838" s="50"/>
+    </row>
+    <row r="839" spans="5:5">
+      <c r="E839" s="50"/>
+    </row>
+    <row r="840" spans="5:5">
+      <c r="E840" s="50"/>
+    </row>
+    <row r="841" spans="5:5">
+      <c r="E841" s="50"/>
+    </row>
+    <row r="842" spans="5:5">
+      <c r="E842" s="50"/>
+    </row>
+    <row r="843" spans="5:5">
+      <c r="E843" s="50"/>
+    </row>
+    <row r="844" spans="5:5">
+      <c r="E844" s="50"/>
+    </row>
+    <row r="845" spans="5:5">
+      <c r="E845" s="50"/>
+    </row>
+    <row r="846" spans="5:5">
+      <c r="E846" s="50"/>
+    </row>
+    <row r="847" spans="5:5">
+      <c r="E847" s="50"/>
+    </row>
+    <row r="848" spans="5:5">
+      <c r="E848" s="50"/>
+    </row>
+    <row r="849" spans="5:5">
+      <c r="E849" s="50"/>
+    </row>
+    <row r="850" spans="5:5">
+      <c r="E850" s="50"/>
+    </row>
+    <row r="851" spans="5:5">
+      <c r="E851" s="50"/>
+    </row>
+    <row r="852" spans="5:5">
+      <c r="E852" s="50"/>
+    </row>
+    <row r="853" spans="5:5">
+      <c r="E853" s="50"/>
+    </row>
+    <row r="854" spans="5:5">
+      <c r="E854" s="50"/>
+    </row>
+    <row r="855" spans="5:5">
+      <c r="E855" s="50"/>
+    </row>
+    <row r="856" spans="5:5">
+      <c r="E856" s="50"/>
+    </row>
+    <row r="857" spans="5:5">
+      <c r="E857" s="50"/>
+    </row>
+    <row r="858" spans="5:5">
+      <c r="E858" s="50"/>
+    </row>
+    <row r="859" spans="5:5">
+      <c r="E859" s="50"/>
+    </row>
+    <row r="860" spans="5:5">
+      <c r="E860" s="50"/>
+    </row>
+    <row r="861" spans="5:5">
+      <c r="E861" s="50"/>
+    </row>
+    <row r="862" spans="5:5">
+      <c r="E862" s="50"/>
+    </row>
+    <row r="863" spans="5:5">
+      <c r="E863" s="50"/>
+    </row>
+    <row r="864" spans="5:5">
+      <c r="E864" s="50"/>
+    </row>
+    <row r="865" spans="5:5">
+      <c r="E865" s="50"/>
+    </row>
+    <row r="866" spans="5:5">
+      <c r="E866" s="50"/>
+    </row>
+    <row r="867" spans="5:5">
+      <c r="E867" s="50"/>
+    </row>
+    <row r="868" spans="5:5">
+      <c r="E868" s="50"/>
+    </row>
+    <row r="869" spans="5:5">
+      <c r="E869" s="50"/>
+    </row>
+    <row r="870" spans="5:5">
+      <c r="E870" s="50"/>
+    </row>
+    <row r="871" spans="5:5">
+      <c r="E871" s="50"/>
+    </row>
+    <row r="872" spans="5:5">
+      <c r="E872" s="50"/>
+    </row>
+    <row r="873" spans="5:5">
+      <c r="E873" s="50"/>
+    </row>
+    <row r="874" spans="5:5">
+      <c r="E874" s="50"/>
+    </row>
+    <row r="875" spans="5:5">
+      <c r="E875" s="50"/>
+    </row>
+    <row r="876" spans="5:5">
+      <c r="E876" s="50"/>
+    </row>
+    <row r="877" spans="5:5">
+      <c r="E877" s="50"/>
+    </row>
+    <row r="878" spans="5:5">
+      <c r="E878" s="50"/>
+    </row>
+    <row r="879" spans="5:5">
+      <c r="E879" s="50"/>
+    </row>
+    <row r="880" spans="5:5">
+      <c r="E880" s="50"/>
+    </row>
+    <row r="881" spans="5:5">
+      <c r="E881" s="50"/>
+    </row>
+    <row r="882" spans="5:5">
+      <c r="E882" s="50"/>
+    </row>
+    <row r="883" spans="5:5">
+      <c r="E883" s="50"/>
+    </row>
+    <row r="884" spans="5:5">
+      <c r="E884" s="50"/>
+    </row>
+    <row r="885" spans="5:5">
+      <c r="E885" s="50"/>
+    </row>
+    <row r="886" spans="5:5">
+      <c r="E886" s="50"/>
+    </row>
+    <row r="887" spans="5:5">
+      <c r="E887" s="50"/>
+    </row>
+    <row r="888" spans="5:5">
+      <c r="E888" s="50"/>
+    </row>
+    <row r="889" spans="5:5">
+      <c r="E889" s="50"/>
+    </row>
+    <row r="890" spans="5:5">
+      <c r="E890" s="50"/>
+    </row>
+    <row r="891" spans="5:5">
+      <c r="E891" s="50"/>
+    </row>
+    <row r="892" spans="5:5">
+      <c r="E892" s="50"/>
+    </row>
+    <row r="893" spans="5:5">
+      <c r="E893" s="50"/>
+    </row>
+    <row r="894" spans="5:5">
+      <c r="E894" s="50"/>
+    </row>
+    <row r="895" spans="5:5">
+      <c r="E895" s="50"/>
+    </row>
+    <row r="896" spans="5:5">
+      <c r="E896" s="50"/>
+    </row>
+    <row r="897" spans="5:5">
+      <c r="E897" s="50"/>
+    </row>
+    <row r="898" spans="5:5">
+      <c r="E898" s="50"/>
+    </row>
+    <row r="899" spans="5:5">
+      <c r="E899" s="50"/>
+    </row>
+    <row r="900" spans="5:5">
+      <c r="E900" s="50"/>
+    </row>
+    <row r="901" spans="5:5">
+      <c r="E901" s="50"/>
+    </row>
+    <row r="902" spans="5:5">
+      <c r="E902" s="50"/>
+    </row>
+    <row r="903" spans="5:5">
+      <c r="E903" s="50"/>
+    </row>
+    <row r="904" spans="5:5">
+      <c r="E904" s="50"/>
+    </row>
+    <row r="905" spans="5:5">
+      <c r="E905" s="50"/>
+    </row>
+    <row r="906" spans="5:5">
+      <c r="E906" s="50"/>
+    </row>
+    <row r="907" spans="5:5">
+      <c r="E907" s="50"/>
+    </row>
+    <row r="908" spans="5:5">
+      <c r="E908" s="50"/>
+    </row>
+    <row r="909" spans="5:5">
+      <c r="E909" s="50"/>
+    </row>
+    <row r="910" spans="5:5">
+      <c r="E910" s="50"/>
+    </row>
+    <row r="911" spans="5:5">
+      <c r="E911" s="50"/>
+    </row>
+    <row r="912" spans="5:5">
+      <c r="E912" s="50"/>
+    </row>
+    <row r="913" spans="5:5">
+      <c r="E913" s="50"/>
+    </row>
+    <row r="914" spans="5:5">
+      <c r="E914" s="50"/>
+    </row>
+    <row r="915" spans="5:5">
+      <c r="E915" s="50"/>
+    </row>
+    <row r="916" spans="5:5">
+      <c r="E916" s="50"/>
+    </row>
+    <row r="917" spans="5:5">
+      <c r="E917" s="50"/>
+    </row>
+    <row r="918" spans="5:5">
+      <c r="E918" s="50"/>
+    </row>
+    <row r="919" spans="5:5">
+      <c r="E919" s="50"/>
+    </row>
+    <row r="920" spans="5:5">
+      <c r="E920" s="50"/>
+    </row>
+    <row r="921" spans="5:5">
+      <c r="E921" s="50"/>
+    </row>
+    <row r="922" spans="5:5">
+      <c r="E922" s="50"/>
+    </row>
+    <row r="923" spans="5:5">
+      <c r="E923" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:Y1"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation allowBlank="1" prompt="Select an OCI Region." sqref="A2 A5" xr:uid="{995BB45D-EDE0-9C44-8B84-4B4A4C38C563}"/>
+    <dataValidation allowBlank="1" sqref="C3:D4 Q14:S15 X2:XFD4 C6:D1048576 Q16:U1048576 Q6:T13 W5:XFD1048576 V6:V13 A1 Z1:XFD1 Q5:U5 U5:U13 Q2:U2 W2 L5:M1048576 B2:H2 I2:M4 B5:M5 F6:K1048576" xr:uid="{33A0BCB3-4009-9940-BFA1-E2CB2D361EE1}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="P1:P1048576" xr:uid="{A5FDBD08-A99F-B740-88A1-851AD4AB8DB0}">
+      <formula1>"BRING_YOUR_OWN_LICENSE,LICENSE_INCLUDED"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="O1:O1048576" xr:uid="{9E1C7F79-F5D9-964F-BDC3-EB4313650312}">
+      <formula1>"LakeHouse,ATP,JSON,APEX"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="N1:N1048576" xr:uid="{EE023586-C61D-3344-A926-3B6FA7E51E26}">
+      <formula1>"STANDARD_EDITION,ENTERPRISE_EDITION"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="V1:V1048576" xr:uid="{C22A7240-264B-E047-BCCC-3956BA7D9F84}">
+      <formula1>"EARLY,REGULAR"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;K000000 Confidential - Oracle Restricted&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Confidential - Oracle Restricted</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323F920-E339-A34A-868B-703334E9F0D5}">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -4865,99 +8195,99 @@
     <col min="18" max="18" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="119.25" customHeight="1">
-      <c r="A1" s="62" t="s">
-        <v>519</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
+    <row r="1" spans="1:18" ht="56" customHeight="1">
+      <c r="A1" s="69" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
     </row>
     <row r="2" spans="1:18" ht="48">
       <c r="A2" s="47" t="s">
+        <v>498</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>499</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="C2" s="47" t="s">
         <v>500</v>
       </c>
-      <c r="C2" s="47" t="s">
-        <v>501</v>
-      </c>
       <c r="D2" s="48" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="47" t="s">
+        <v>479</v>
+      </c>
+      <c r="G2" s="47" t="s">
         <v>480</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="H2" s="47" t="s">
         <v>481</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="I2" s="47" t="s">
         <v>482</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="J2" s="47" t="s">
         <v>483</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="K2" s="47" t="s">
         <v>484</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="L2" s="47" t="s">
         <v>485</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="M2" s="47" t="s">
         <v>486</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="N2" s="47" t="s">
         <v>487</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="O2" s="47" t="s">
         <v>488</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="P2" s="47" t="s">
         <v>489</v>
       </c>
-      <c r="P2" s="47" t="s">
-        <v>490</v>
-      </c>
       <c r="Q2" s="47" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="R2" s="49" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>515</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>516</v>
-      </c>
       <c r="C3" s="24" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F3" s="24">
         <v>2</v>
@@ -4966,16 +8296,16 @@
         <v>3</v>
       </c>
       <c r="H3" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="I3" s="24" t="s">
         <v>492</v>
       </c>
-      <c r="I3" s="24" t="s">
-        <v>493</v>
-      </c>
       <c r="J3" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
@@ -4983,27 +8313,27 @@
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
       <c r="Q3" s="24" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="R3" s="24" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>515</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>516</v>
-      </c>
       <c r="C4" s="24" t="s">
+        <v>534</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>536</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>538</v>
-      </c>
       <c r="E4" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F4" s="24">
         <v>2</v>
@@ -5012,16 +8342,16 @@
         <v>3</v>
       </c>
       <c r="H4" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="I4" s="24" t="s">
         <v>492</v>
       </c>
-      <c r="I4" s="24" t="s">
-        <v>493</v>
-      </c>
       <c r="J4" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
@@ -5029,10 +8359,10 @@
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
       <c r="Q4" s="24" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="16">
@@ -5072,7 +8402,7 @@
     <row r="10" spans="1:18">
       <c r="E10" s="50"/>
       <c r="P10" s="55" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -7831,7 +11161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E7A92D-7601-0A43-A0AF-C01C8D26C66F}">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
@@ -7867,28 +11197,28 @@
     <col min="28" max="28" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" ht="195" customHeight="1">
-      <c r="A1" s="63" t="s">
-        <v>540</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
+    <row r="1" spans="1:26" s="1" customFormat="1" ht="132" customHeight="1">
+      <c r="A1" s="70" t="s">
+        <v>542</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
       <c r="T1" s="51"/>
       <c r="U1" s="51"/>
       <c r="V1" s="51"/>
@@ -7899,61 +11229,61 @@
     </row>
     <row r="2" spans="1:26" s="53" customFormat="1" ht="32">
       <c r="A2" s="47" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>493</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>517</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>513</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>518</v>
+      </c>
+      <c r="H2" s="48" t="s">
+        <v>506</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>507</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>495</v>
+      </c>
+      <c r="K2" s="47" t="s">
+        <v>494</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>509</v>
+      </c>
+      <c r="M2" s="47" t="s">
+        <v>508</v>
+      </c>
+      <c r="N2" s="47" t="s">
+        <v>510</v>
+      </c>
+      <c r="O2" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>512</v>
+      </c>
+      <c r="Q2" s="47" t="s">
+        <v>496</v>
+      </c>
+      <c r="R2" s="47" t="s">
+        <v>497</v>
+      </c>
+      <c r="S2" s="52" t="s">
         <v>501</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>479</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>494</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>518</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>514</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>520</v>
-      </c>
-      <c r="H2" s="48" t="s">
-        <v>507</v>
-      </c>
-      <c r="I2" s="47" t="s">
-        <v>508</v>
-      </c>
-      <c r="J2" s="47" t="s">
-        <v>496</v>
-      </c>
-      <c r="K2" s="47" t="s">
-        <v>495</v>
-      </c>
-      <c r="L2" s="47" t="s">
-        <v>510</v>
-      </c>
-      <c r="M2" s="47" t="s">
-        <v>509</v>
-      </c>
-      <c r="N2" s="47" t="s">
-        <v>511</v>
-      </c>
-      <c r="O2" s="47" t="s">
-        <v>512</v>
-      </c>
-      <c r="P2" s="47" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q2" s="47" t="s">
-        <v>497</v>
-      </c>
-      <c r="R2" s="47" t="s">
-        <v>498</v>
-      </c>
-      <c r="S2" s="52" t="s">
-        <v>502</v>
       </c>
       <c r="T2"/>
       <c r="U2"/>
@@ -7965,34 +11295,34 @@
     </row>
     <row r="3" spans="1:26" ht="281">
       <c r="A3" s="24" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H3" s="25" t="s">
         <v>97</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J3" s="38" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K3" s="38">
         <v>88</v>
@@ -8013,45 +11343,45 @@
         <v>0</v>
       </c>
       <c r="Q3" s="60" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="R3" s="54" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="S3" s="25" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="281">
       <c r="A4" s="24" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B4" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>537</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>539</v>
-      </c>
       <c r="D4" s="24" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E4" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="G4" s="25" t="s">
         <v>529</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>535</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>531</v>
       </c>
       <c r="H4" s="25" t="s">
         <v>97</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K4" s="38">
         <v>88</v>
@@ -8072,13 +11402,13 @@
         <v>0</v>
       </c>
       <c r="Q4" s="60" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="R4" s="54" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="S4" s="25" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:26">
@@ -10544,7 +13874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F48E23C-F15A-8649-ADB9-6B0FFE9380CD}">
   <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -11574,7 +14904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="28.75" customHeight="1"/>
@@ -11898,7 +15228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:AV202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="28.5" defaultRowHeight="15"/>
@@ -18320,7 +21650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>

--- a/cd3_automation_toolkit/example/CD3-GCP-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-GCP-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10726"/>
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ulaganathan/Documents/CD3_Developer/release-v2026.2.0/outputs/workbook-audit-v2026.2.0-20260731/candidate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E06D3F5-078E-A747-9AD1-E6A9321BAE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B71B99-D2B3-1447-B575-FF8ACD449395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19560" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1960,162 +1960,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Project</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : Specify project ID</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Exadata Infra Display Name : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If Exa Infra is in different project than VM cluster then specify as &lt;exa_infra_project&gt;@&lt;exa_infra_display_name&gt;. See sample data in row 4.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-ODB Network Details :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> If you want to create new network, use CREATE::&lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;::&lt;GCP_ORACLE_ZONE&gt; else &lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;. See sample data.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-ODB Network Subnets Details : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If you want to create new subnets, use CREATE::&lt;Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt;::&lt;Backup_Subnet_ID&gt;::&lt;Backup_Subnet_CIDR&gt; else Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt;::&lt;Backup_Subnet_ID&gt;::&lt;Backup_Subnet_CIDR&gt; See sample data.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Time Zone"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Specify the time zone to use for the DB system.The value should be the same as displayed in OCI Console and is Case Sensitive.
-                           </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Example: Asia/Calcutta | UTC | US/Pacific-New</t>
-    </r>
-  </si>
-  <si>
     <t>Is Auto Scaling Enabled</t>
   </si>
   <si>
@@ -2137,163 +1981,6 @@
     <t>ATP 01</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-Project : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Specify project ID
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ODB Network Detail</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">s : If you want to create new network, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>use</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> CREATE::&lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;::&lt;GCP_ORACLE_ZONE&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>else</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;. See sample data.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">ODB Network Subnets Details </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: If you want to create new subnet, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>use</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> CREATE::&lt;Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>else</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Client_Subnet_ID&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Note: To create ADB with Secure Access from Everywhere, leave Network Details columns empty.
-</t>
-    </r>
-  </si>
-  <si>
     <t>DB Edition</t>
   </si>
   <si>
@@ -2327,56 +2014,30 @@
     <t>ATP02</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CD3 Automation Toolkit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Release - v2026.2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+    <t>CD3 Automation Toolkit Release - v2026.2.0
+Added create and offline tfvars support for ADB and Exadata at GCP, plus ADB export. Exadata export is not included.</t>
+  </si>
+  <si>
+    <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Project - Specify the GCP project ID.
+ODB Network Details - New network: CREATE::&lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;::&lt;GCP_ORACLE_ZONE&gt;; existing network: &lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;. Append ::&lt;GCP_ORACLE_ZONE&gt; to the existing-network format when required.
+ODB Network Subnet Details - New subnet: CREATE::&lt;Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt;; existing subnet: &lt;Client_Subnet_ID&gt;.
+To create ADB with secure access from everywhere, leave both network-details columns blank.</t>
+  </si>
+  <si>
+    <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Project - Specify the GCP project ID.
+Exadata Infra Display Name - If Exadata Infrastructure is in a different project, use &lt;exa_infra_project&gt;@&lt;exa_infra_display_name&gt;.
+ODB Network Details - New network: CREATE::&lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;::&lt;GCP_ORACLE_ZONE&gt;; existing network: &lt;ODB-Network-Project&gt;::&lt;Associated-VPC-Network-Name&gt;::&lt;ODB-Network-ID&gt;.
+ODB Network Subnets Details - New subnets: CREATE::&lt;Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt;::&lt;Backup_Subnet_ID&gt;::&lt;Backup_Subnet_CIDR&gt;; existing subnets: &lt;Client_Subnet_ID&gt;::&lt;Client_Subnet_CIDR&gt;::&lt;Backup_Subnet_ID&gt;::&lt;Backup_Subnet_CIDR&gt;.
+"Time Zone" - Use the exact case-sensitive value displayed in OCI Console. Examples: Asia/Calcutta | UTC | US/Pacific-New</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2444,34 +2105,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="5" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2876,7 +2509,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2893,7 +2526,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2919,10 +2552,10 @@
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4847,7 +4480,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="36" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -4878,27 +4511,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="79" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>474</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
     </row>
     <row r="2" spans="1:19" ht="80">
       <c r="A2" s="7" t="s">
@@ -5106,34 +4739,34 @@
     <col min="25" max="25" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="102" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>550</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
+    <row r="1" spans="1:25" ht="125" customHeight="1">
+      <c r="A1" s="68" t="s">
+        <v>561</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
     </row>
     <row r="2" spans="1:25" s="43" customFormat="1" ht="68" customHeight="1">
       <c r="A2" s="61" t="s">
@@ -5146,7 +4779,7 @@
         <v>180</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E2" s="52" t="s">
         <v>513</v>
@@ -5155,13 +4788,13 @@
         <v>538</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I2" s="52" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J2" s="52" t="s">
         <v>110</v>
@@ -5176,7 +4809,7 @@
         <v>510</v>
       </c>
       <c r="N2" s="52" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="O2" s="52" t="s">
         <v>181</v>
@@ -5194,13 +4827,13 @@
         <v>463</v>
       </c>
       <c r="T2" s="61" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="U2" s="61" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="V2" s="61" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="W2" s="61" t="s">
         <v>466</v>
@@ -5220,10 +4853,10 @@
         <v>539</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>532</v>
@@ -5232,13 +4865,13 @@
         <v>540</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J3" s="24" t="s">
         <v>471</v>
@@ -5277,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="24" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="W3" s="24" t="b">
         <v>0</v>
@@ -5297,7 +4930,7 @@
         <v>539</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D4" s="24"/>
       <c r="E4" s="25"/>
@@ -5305,7 +4938,7 @@
       <c r="G4" s="25"/>
       <c r="H4" s="25"/>
       <c r="I4" s="24" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J4" s="24" t="s">
         <v>471</v>
@@ -5323,7 +4956,7 @@
         <v>104</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="P4" s="25" t="s">
         <v>225</v>
@@ -5344,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="V4" s="24" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="W4" s="24" t="b">
         <v>1</v>
@@ -8199,23 +7832,23 @@
       <c r="A1" s="69" t="s">
         <v>541</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
     </row>
     <row r="2" spans="1:18" ht="48">
       <c r="A2" s="47" t="s">
@@ -11197,28 +10830,28 @@
     <col min="28" max="28" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" ht="132" customHeight="1">
+    <row r="1" spans="1:26" s="1" customFormat="1" ht="165" customHeight="1">
       <c r="A1" s="70" t="s">
-        <v>542</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
+        <v>562</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
       <c r="T1" s="51"/>
       <c r="U1" s="51"/>
       <c r="V1" s="51"/>
